--- a/Planilla labores 26-27.xlsx
+++ b/Planilla labores 26-27.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30203"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30215"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="1137" documentId="11_9BB9DD218D925F84F52BED1A4A92F57EE502BB5A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{185E70F7-2EDD-41CA-877B-348D7CC8746E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0260B383-6954-4CCB-B8DD-3E85EC1BE408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Invierno" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="166">
   <si>
     <t>Análisis suelo</t>
   </si>
@@ -488,6 +488,12 @@
     <t>Puesto</t>
   </si>
   <si>
+    <t xml:space="preserve">Cultivo Invierno </t>
+  </si>
+  <si>
+    <t>Cult Verano</t>
+  </si>
+  <si>
     <t>dic</t>
   </si>
   <si>
@@ -527,13 +533,7 @@
     <t>Sta Rafaela</t>
   </si>
   <si>
-    <t>Blanqueada</t>
-  </si>
-  <si>
     <t>Campana</t>
-  </si>
-  <si>
-    <t>Pereira</t>
   </si>
 </sst>
 </file>
@@ -618,7 +618,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="22">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -745,6 +745,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="8">
     <border>
@@ -825,7 +831,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -956,18 +962,6 @@
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -980,6 +974,72 @@
     <xf numFmtId="14" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1010,69 +1070,6 @@
     <xf numFmtId="0" fontId="5" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1085,8 +1082,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1468,157 +1465,157 @@
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
       <c r="D1" s="4"/>
-      <c r="F1" s="52" t="s">
+      <c r="F1" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="53" t="s">
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
+      <c r="L1" s="70"/>
+      <c r="M1" s="70"/>
+      <c r="N1" s="70"/>
+      <c r="O1" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="54"/>
-      <c r="Q1" s="54"/>
-      <c r="R1" s="54"/>
-      <c r="S1" s="54"/>
-      <c r="T1" s="54"/>
-      <c r="U1" s="54"/>
-      <c r="V1" s="54"/>
-      <c r="W1" s="55" t="s">
+      <c r="P1" s="72"/>
+      <c r="Q1" s="72"/>
+      <c r="R1" s="72"/>
+      <c r="S1" s="72"/>
+      <c r="T1" s="72"/>
+      <c r="U1" s="72"/>
+      <c r="V1" s="72"/>
+      <c r="W1" s="73" t="s">
         <v>2</v>
       </c>
-      <c r="X1" s="55"/>
-      <c r="Y1" s="55"/>
-      <c r="Z1" s="55"/>
-      <c r="AA1" s="55"/>
-      <c r="AB1" s="55"/>
-      <c r="AC1" s="55"/>
-      <c r="AD1" s="55"/>
-      <c r="AE1" s="55"/>
-      <c r="AF1" s="55"/>
-      <c r="AG1" s="61" t="s">
+      <c r="X1" s="73"/>
+      <c r="Y1" s="73"/>
+      <c r="Z1" s="73"/>
+      <c r="AA1" s="73"/>
+      <c r="AB1" s="73"/>
+      <c r="AC1" s="73"/>
+      <c r="AD1" s="73"/>
+      <c r="AE1" s="73"/>
+      <c r="AF1" s="73"/>
+      <c r="AG1" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="AH1" s="61"/>
-      <c r="AI1" s="61"/>
-      <c r="AJ1" s="61"/>
-      <c r="AK1" s="56" t="s">
+      <c r="AH1" s="79"/>
+      <c r="AI1" s="79"/>
+      <c r="AJ1" s="79"/>
+      <c r="AK1" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="AL1" s="56"/>
-      <c r="AM1" s="56"/>
-      <c r="AN1" s="56"/>
-      <c r="AO1" s="56"/>
-      <c r="AP1" s="57"/>
-      <c r="AQ1" s="58" t="s">
+      <c r="AL1" s="74"/>
+      <c r="AM1" s="74"/>
+      <c r="AN1" s="74"/>
+      <c r="AO1" s="74"/>
+      <c r="AP1" s="75"/>
+      <c r="AQ1" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="AR1" s="59"/>
-      <c r="AS1" s="59"/>
-      <c r="AT1" s="59"/>
-      <c r="AU1" s="59"/>
-      <c r="AV1" s="59"/>
-      <c r="AW1" s="60"/>
-      <c r="AX1" s="62" t="s">
+      <c r="AR1" s="77"/>
+      <c r="AS1" s="77"/>
+      <c r="AT1" s="77"/>
+      <c r="AU1" s="77"/>
+      <c r="AV1" s="77"/>
+      <c r="AW1" s="78"/>
+      <c r="AX1" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="AY1" s="63"/>
-      <c r="AZ1" s="63"/>
-      <c r="BA1" s="63"/>
-      <c r="BB1" s="63"/>
-      <c r="BC1" s="64"/>
-      <c r="BD1" s="71" t="s">
+      <c r="AY1" s="60"/>
+      <c r="AZ1" s="60"/>
+      <c r="BA1" s="60"/>
+      <c r="BB1" s="60"/>
+      <c r="BC1" s="61"/>
+      <c r="BD1" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="BE1" s="72"/>
-      <c r="BF1" s="73"/>
-      <c r="BG1" s="65" t="s">
+      <c r="BE1" s="68"/>
+      <c r="BF1" s="69"/>
+      <c r="BG1" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="BH1" s="66"/>
-      <c r="BI1" s="67" t="s">
+      <c r="BH1" s="63"/>
+      <c r="BI1" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="BJ1" s="67"/>
-      <c r="BK1" s="67"/>
-      <c r="BL1" s="67"/>
-      <c r="BM1" s="67"/>
-      <c r="BN1" s="68" t="s">
+      <c r="BJ1" s="64"/>
+      <c r="BK1" s="64"/>
+      <c r="BL1" s="64"/>
+      <c r="BM1" s="64"/>
+      <c r="BN1" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="BO1" s="69"/>
-      <c r="BP1" s="69"/>
-      <c r="BQ1" s="69"/>
-      <c r="BR1" s="69"/>
-      <c r="BS1" s="70"/>
-      <c r="BT1" s="69" t="s">
+      <c r="BO1" s="52"/>
+      <c r="BP1" s="52"/>
+      <c r="BQ1" s="52"/>
+      <c r="BR1" s="52"/>
+      <c r="BS1" s="66"/>
+      <c r="BT1" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="BU1" s="69"/>
-      <c r="BV1" s="69"/>
-      <c r="BW1" s="69"/>
-      <c r="BX1" s="69"/>
-      <c r="BY1" s="69"/>
-      <c r="BZ1" s="69" t="s">
+      <c r="BU1" s="52"/>
+      <c r="BV1" s="52"/>
+      <c r="BW1" s="52"/>
+      <c r="BX1" s="52"/>
+      <c r="BY1" s="52"/>
+      <c r="BZ1" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="CA1" s="69"/>
-      <c r="CB1" s="69"/>
-      <c r="CC1" s="69"/>
-      <c r="CD1" s="69"/>
-      <c r="CE1" s="69"/>
+      <c r="CA1" s="52"/>
+      <c r="CB1" s="52"/>
+      <c r="CC1" s="52"/>
+      <c r="CD1" s="52"/>
+      <c r="CE1" s="52"/>
       <c r="CF1" s="23"/>
-      <c r="CG1" s="77" t="s">
+      <c r="CG1" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="CH1" s="77"/>
-      <c r="CI1" s="77"/>
-      <c r="CJ1" s="78" t="s">
+      <c r="CH1" s="53"/>
+      <c r="CI1" s="53"/>
+      <c r="CJ1" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="CK1" s="78"/>
-      <c r="CL1" s="78"/>
-      <c r="CM1" s="78"/>
-      <c r="CN1" s="78"/>
-      <c r="CO1" s="79" t="s">
+      <c r="CK1" s="54"/>
+      <c r="CL1" s="54"/>
+      <c r="CM1" s="54"/>
+      <c r="CN1" s="54"/>
+      <c r="CO1" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="CP1" s="79"/>
-      <c r="CQ1" s="79"/>
-      <c r="CR1" s="79"/>
-      <c r="CS1" s="79"/>
-      <c r="CT1" s="79"/>
-      <c r="CU1" s="79"/>
-      <c r="CV1" s="79"/>
-      <c r="CW1" s="79"/>
-      <c r="CX1" s="79"/>
-      <c r="CY1" s="80"/>
-      <c r="CZ1" s="81" t="s">
+      <c r="CP1" s="55"/>
+      <c r="CQ1" s="55"/>
+      <c r="CR1" s="55"/>
+      <c r="CS1" s="55"/>
+      <c r="CT1" s="55"/>
+      <c r="CU1" s="55"/>
+      <c r="CV1" s="55"/>
+      <c r="CW1" s="55"/>
+      <c r="CX1" s="55"/>
+      <c r="CY1" s="56"/>
+      <c r="CZ1" s="57" t="s">
         <v>16</v>
       </c>
-      <c r="DA1" s="75"/>
-      <c r="DB1" s="82"/>
-      <c r="DC1" s="74" t="s">
+      <c r="DA1" s="50"/>
+      <c r="DB1" s="58"/>
+      <c r="DC1" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="DD1" s="75"/>
-      <c r="DE1" s="75"/>
-      <c r="DF1" s="75" t="s">
+      <c r="DD1" s="50"/>
+      <c r="DE1" s="50"/>
+      <c r="DF1" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="DG1" s="75"/>
-      <c r="DH1" s="75"/>
-      <c r="DI1" s="76" t="s">
+      <c r="DG1" s="50"/>
+      <c r="DH1" s="50"/>
+      <c r="DI1" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="DJ1" s="76"/>
-      <c r="DK1" s="76"/>
-      <c r="DL1" s="76"/>
+      <c r="DJ1" s="51"/>
+      <c r="DK1" s="51"/>
+      <c r="DL1" s="51"/>
     </row>
     <row r="2" spans="1:116" ht="21">
       <c r="A2" s="5" t="s">
@@ -1786,13 +1783,13 @@
       <c r="BC2" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="BD2" s="48" t="s">
+      <c r="BD2" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="BE2" s="48" t="s">
+      <c r="BE2" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="BF2" s="48" t="s">
+      <c r="BF2" s="44" t="s">
         <v>41</v>
       </c>
       <c r="BG2" s="27" t="s">
@@ -1986,31 +1983,31 @@
       <c r="E3" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="F3" s="49">
+      <c r="F3" s="45">
         <v>46157</v>
       </c>
-      <c r="G3" s="50" t="s">
+      <c r="G3" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="H3" s="50">
+      <c r="H3" s="46">
         <v>5</v>
       </c>
-      <c r="I3" s="50">
+      <c r="I3" s="46">
         <v>8</v>
       </c>
-      <c r="J3" s="50">
+      <c r="J3" s="46">
         <v>0.37</v>
       </c>
-      <c r="K3" s="50">
+      <c r="K3" s="46">
         <v>19</v>
       </c>
-      <c r="L3" s="50">
+      <c r="L3" s="46">
         <v>0.26</v>
       </c>
-      <c r="M3" s="50">
+      <c r="M3" s="46">
         <v>5.6</v>
       </c>
-      <c r="N3" s="50">
+      <c r="N3" s="46">
         <v>3.5</v>
       </c>
       <c r="O3" s="17">
@@ -2042,7 +2039,7 @@
       <c r="AB3" s="34"/>
       <c r="AC3" s="34"/>
       <c r="AD3" s="34"/>
-      <c r="AE3" s="51">
+      <c r="AE3" s="47">
         <v>46158</v>
       </c>
       <c r="AF3" s="34" t="s">
@@ -2550,7 +2547,7 @@
       </c>
       <c r="AC14" s="34"/>
       <c r="AD14" s="34"/>
-      <c r="AE14" s="51">
+      <c r="AE14" s="47">
         <v>46174</v>
       </c>
       <c r="AF14" s="34" t="s">
@@ -2658,7 +2655,7 @@
       </c>
       <c r="AC15" s="34"/>
       <c r="AD15" s="34"/>
-      <c r="AE15" s="51">
+      <c r="AE15" s="47">
         <v>46174</v>
       </c>
       <c r="AF15" s="34" t="s">
@@ -2766,7 +2763,7 @@
       </c>
       <c r="AC16" s="34"/>
       <c r="AD16" s="34"/>
-      <c r="AE16" s="51">
+      <c r="AE16" s="47">
         <v>46174</v>
       </c>
       <c r="AF16" s="34" t="s">
@@ -2874,7 +2871,7 @@
       </c>
       <c r="AC17" s="34"/>
       <c r="AD17" s="34"/>
-      <c r="AE17" s="51">
+      <c r="AE17" s="47">
         <v>46174</v>
       </c>
       <c r="AF17" s="34" t="s">
@@ -2982,7 +2979,7 @@
       </c>
       <c r="AC18" s="34"/>
       <c r="AD18" s="34"/>
-      <c r="AE18" s="51">
+      <c r="AE18" s="47">
         <v>46174</v>
       </c>
       <c r="AF18" s="34" t="s">
@@ -2998,10 +2995,10 @@
       <c r="AJ18" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="AK18" s="87" t="s">
+      <c r="AK18" s="48" t="s">
         <v>104</v>
       </c>
-      <c r="AL18" s="87" t="s">
+      <c r="AL18" s="48" t="s">
         <v>105</v>
       </c>
       <c r="AM18" s="34">
@@ -3100,7 +3097,7 @@
       </c>
       <c r="AC19" s="34"/>
       <c r="AD19" s="34"/>
-      <c r="AE19" s="51">
+      <c r="AE19" s="47">
         <v>46174</v>
       </c>
       <c r="AF19" s="34" t="s">
@@ -3116,10 +3113,10 @@
       <c r="AJ19" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="AK19" s="87" t="s">
+      <c r="AK19" s="48" t="s">
         <v>106</v>
       </c>
-      <c r="AL19" s="87" t="s">
+      <c r="AL19" s="48" t="s">
         <v>107</v>
       </c>
       <c r="AM19" s="34">
@@ -3164,31 +3161,31 @@
       <c r="E20" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="F20" s="49">
+      <c r="F20" s="45">
         <v>46157</v>
       </c>
-      <c r="G20" s="50" t="s">
+      <c r="G20" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="H20" s="50">
+      <c r="H20" s="46">
         <v>5</v>
       </c>
-      <c r="I20" s="50">
+      <c r="I20" s="46">
         <v>19</v>
       </c>
-      <c r="J20" s="50">
+      <c r="J20" s="46">
         <v>0.21</v>
       </c>
-      <c r="K20" s="50">
+      <c r="K20" s="46">
         <v>10</v>
       </c>
-      <c r="L20" s="50">
+      <c r="L20" s="46">
         <v>0.33</v>
       </c>
-      <c r="M20" s="50">
+      <c r="M20" s="46">
         <v>5.6</v>
       </c>
-      <c r="N20" s="50">
+      <c r="N20" s="46">
         <v>2.6</v>
       </c>
       <c r="O20" s="34">
@@ -3227,7 +3224,7 @@
       <c r="AB20" s="34"/>
       <c r="AC20" s="34"/>
       <c r="AD20" s="34"/>
-      <c r="AE20" s="51">
+      <c r="AE20" s="47">
         <v>46159</v>
       </c>
       <c r="AF20" s="34" t="s">
@@ -3285,31 +3282,31 @@
       <c r="E21" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="F21" s="49">
+      <c r="F21" s="45">
         <v>46157</v>
       </c>
-      <c r="G21" s="50" t="s">
+      <c r="G21" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="H21" s="50">
+      <c r="H21" s="46">
         <v>4</v>
       </c>
-      <c r="I21" s="50">
+      <c r="I21" s="46">
         <v>14</v>
       </c>
-      <c r="J21" s="50">
+      <c r="J21" s="46">
         <v>0.24</v>
       </c>
-      <c r="K21" s="50">
+      <c r="K21" s="46">
         <v>11</v>
       </c>
-      <c r="L21" s="50">
+      <c r="L21" s="46">
         <v>0.48</v>
       </c>
-      <c r="M21" s="50">
+      <c r="M21" s="46">
         <v>5.3</v>
       </c>
-      <c r="N21" s="50">
+      <c r="N21" s="46">
         <v>2.2999999999999998</v>
       </c>
       <c r="O21" s="34">
@@ -3348,7 +3345,7 @@
       <c r="AB21" s="34"/>
       <c r="AC21" s="34"/>
       <c r="AD21" s="34"/>
-      <c r="AE21" s="51">
+      <c r="AE21" s="47">
         <v>46159</v>
       </c>
       <c r="AF21" s="34" t="s">
@@ -3406,31 +3403,31 @@
       <c r="E22" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="F22" s="49">
+      <c r="F22" s="45">
         <v>46157</v>
       </c>
-      <c r="G22" s="50" t="s">
+      <c r="G22" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="H22" s="50">
+      <c r="H22" s="46">
         <v>4</v>
       </c>
-      <c r="I22" s="50">
+      <c r="I22" s="46">
         <v>15</v>
       </c>
-      <c r="J22" s="50">
+      <c r="J22" s="46">
         <v>0.23</v>
       </c>
-      <c r="K22" s="50">
+      <c r="K22" s="46">
         <v>12</v>
       </c>
-      <c r="L22" s="50">
+      <c r="L22" s="46">
         <v>0.66</v>
       </c>
-      <c r="M22" s="50">
+      <c r="M22" s="46">
         <v>5.3</v>
       </c>
-      <c r="N22" s="50">
+      <c r="N22" s="46">
         <v>2.5</v>
       </c>
       <c r="O22" s="34">
@@ -3469,7 +3466,7 @@
       <c r="AB22" s="34"/>
       <c r="AC22" s="34"/>
       <c r="AD22" s="34"/>
-      <c r="AE22" s="51">
+      <c r="AE22" s="47">
         <v>46159</v>
       </c>
       <c r="AF22" s="34" t="s">
@@ -3527,31 +3524,31 @@
       <c r="E23" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="F23" s="49">
+      <c r="F23" s="45">
         <v>46157</v>
       </c>
-      <c r="G23" s="50" t="s">
+      <c r="G23" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="H23" s="50">
+      <c r="H23" s="46">
         <v>4</v>
       </c>
-      <c r="I23" s="50">
+      <c r="I23" s="46">
         <v>11</v>
       </c>
-      <c r="J23" s="50">
+      <c r="J23" s="46">
         <v>0.23</v>
       </c>
-      <c r="K23" s="50">
+      <c r="K23" s="46">
         <v>9</v>
       </c>
-      <c r="L23" s="50">
+      <c r="L23" s="46">
         <v>0.35</v>
       </c>
-      <c r="M23" s="50">
+      <c r="M23" s="46">
         <v>5.3</v>
       </c>
-      <c r="N23" s="50">
+      <c r="N23" s="46">
         <v>2.4</v>
       </c>
       <c r="O23" s="34">
@@ -3590,7 +3587,7 @@
       <c r="AB23" s="34"/>
       <c r="AC23" s="34"/>
       <c r="AD23" s="34"/>
-      <c r="AE23" s="51">
+      <c r="AE23" s="47">
         <v>46159</v>
       </c>
       <c r="AF23" s="34" t="s">
@@ -3729,31 +3726,31 @@
       <c r="E26" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="F26" s="49">
+      <c r="F26" s="45">
         <v>46157</v>
       </c>
-      <c r="G26" s="50" t="s">
+      <c r="G26" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="H26" s="50">
+      <c r="H26" s="46">
         <v>5</v>
       </c>
-      <c r="I26" s="50">
+      <c r="I26" s="46">
         <v>4</v>
       </c>
-      <c r="J26" s="50">
+      <c r="J26" s="46">
         <v>0.28999999999999998</v>
       </c>
-      <c r="K26" s="50">
+      <c r="K26" s="46">
         <v>10</v>
       </c>
-      <c r="L26" s="50">
+      <c r="L26" s="46">
         <v>0.67</v>
       </c>
-      <c r="M26" s="50">
+      <c r="M26" s="46">
         <v>5.4</v>
       </c>
-      <c r="N26" s="50">
+      <c r="N26" s="46">
         <v>3.7</v>
       </c>
       <c r="O26" s="34">
@@ -3792,7 +3789,7 @@
       <c r="AB26" s="34"/>
       <c r="AC26" s="34"/>
       <c r="AD26" s="34"/>
-      <c r="AE26" s="51">
+      <c r="AE26" s="47">
         <v>46159</v>
       </c>
       <c r="AF26" s="34" t="s">
@@ -3928,7 +3925,7 @@
       <c r="AB28" s="34"/>
       <c r="AC28" s="34"/>
       <c r="AD28" s="34"/>
-      <c r="AE28" s="51">
+      <c r="AE28" s="47">
         <v>46057</v>
       </c>
       <c r="AF28" s="34" t="s">
@@ -4131,7 +4128,7 @@
       <c r="AB31" s="34"/>
       <c r="AC31" s="34"/>
       <c r="AD31" s="34"/>
-      <c r="AE31" s="51" t="s">
+      <c r="AE31" s="47" t="s">
         <v>123</v>
       </c>
       <c r="AF31" s="34" t="s">
@@ -4257,7 +4254,7 @@
       <c r="AB32" s="34"/>
       <c r="AC32" s="34"/>
       <c r="AD32" s="34"/>
-      <c r="AE32" s="51" t="s">
+      <c r="AE32" s="47" t="s">
         <v>123</v>
       </c>
       <c r="AF32" s="34" t="s">
@@ -4383,7 +4380,7 @@
       <c r="AB33" s="34"/>
       <c r="AC33" s="34"/>
       <c r="AD33" s="34"/>
-      <c r="AE33" s="51" t="s">
+      <c r="AE33" s="47" t="s">
         <v>123</v>
       </c>
       <c r="AF33" s="34" t="s">
@@ -4672,7 +4669,7 @@
       <c r="AB38" s="34"/>
       <c r="AC38" s="34"/>
       <c r="AD38" s="34"/>
-      <c r="AE38" s="51" t="s">
+      <c r="AE38" s="47" t="s">
         <v>123</v>
       </c>
       <c r="AF38" s="34" t="s">
@@ -5008,7 +5005,7 @@
       </c>
       <c r="AC44" s="34"/>
       <c r="AD44" s="34"/>
-      <c r="AE44" s="51">
+      <c r="AE44" s="47">
         <v>46167</v>
       </c>
       <c r="AF44" s="34" t="s">
@@ -5138,7 +5135,7 @@
       </c>
       <c r="AC46" s="34"/>
       <c r="AD46" s="34"/>
-      <c r="AE46" s="51">
+      <c r="AE46" s="47">
         <v>46167</v>
       </c>
       <c r="AF46" s="34" t="s">
@@ -5228,7 +5225,7 @@
       </c>
       <c r="AC47" s="34"/>
       <c r="AD47" s="34"/>
-      <c r="AE47" s="51">
+      <c r="AE47" s="47">
         <v>46167</v>
       </c>
       <c r="AF47" s="34" t="s">
@@ -5318,7 +5315,7 @@
       </c>
       <c r="AC48" s="34"/>
       <c r="AD48" s="34"/>
-      <c r="AE48" s="51">
+      <c r="AE48" s="47">
         <v>46167</v>
       </c>
       <c r="AF48" s="34" t="s">
@@ -5408,7 +5405,7 @@
       </c>
       <c r="AC49" s="34"/>
       <c r="AD49" s="34"/>
-      <c r="AE49" s="51">
+      <c r="AE49" s="47">
         <v>46167</v>
       </c>
       <c r="AF49" s="34" t="s">
@@ -5498,7 +5495,7 @@
       </c>
       <c r="AC50" s="34"/>
       <c r="AD50" s="34"/>
-      <c r="AE50" s="51">
+      <c r="AE50" s="47">
         <v>46167</v>
       </c>
       <c r="AF50" s="34" t="s">
@@ -5812,6 +5809,18 @@
   </sheetData>
   <autoFilter ref="A2:AF53" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="20">
+    <mergeCell ref="F1:N1"/>
+    <mergeCell ref="O1:V1"/>
+    <mergeCell ref="W1:AF1"/>
+    <mergeCell ref="AK1:AP1"/>
+    <mergeCell ref="AQ1:AW1"/>
+    <mergeCell ref="AG1:AJ1"/>
+    <mergeCell ref="AX1:BC1"/>
+    <mergeCell ref="BG1:BH1"/>
+    <mergeCell ref="BI1:BM1"/>
+    <mergeCell ref="BN1:BS1"/>
+    <mergeCell ref="BT1:BY1"/>
+    <mergeCell ref="BD1:BF1"/>
     <mergeCell ref="DC1:DE1"/>
     <mergeCell ref="DF1:DH1"/>
     <mergeCell ref="DI1:DL1"/>
@@ -5820,18 +5829,6 @@
     <mergeCell ref="CJ1:CN1"/>
     <mergeCell ref="CO1:CY1"/>
     <mergeCell ref="CZ1:DB1"/>
-    <mergeCell ref="AX1:BC1"/>
-    <mergeCell ref="BG1:BH1"/>
-    <mergeCell ref="BI1:BM1"/>
-    <mergeCell ref="BN1:BS1"/>
-    <mergeCell ref="BT1:BY1"/>
-    <mergeCell ref="BD1:BF1"/>
-    <mergeCell ref="F1:N1"/>
-    <mergeCell ref="O1:V1"/>
-    <mergeCell ref="W1:AF1"/>
-    <mergeCell ref="AK1:AP1"/>
-    <mergeCell ref="AQ1:AW1"/>
-    <mergeCell ref="AG1:AJ1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5839,16 +5836,915 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB45D919-FE15-4609-BAFC-CE592C260F0A}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="21">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="17"/>
+    </row>
+    <row r="2" spans="1:5" ht="20.25">
+      <c r="A2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="21">
+      <c r="A3" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" s="6">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6">
+        <v>203.49</v>
+      </c>
+      <c r="D3" s="84" t="s">
+        <v>85</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="21">
+      <c r="A4" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B4" s="6">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6">
+        <v>215</v>
+      </c>
+      <c r="D4" s="84" t="s">
+        <v>94</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="21">
+      <c r="A5" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" s="6">
+        <v>3</v>
+      </c>
+      <c r="C5" s="6">
+        <v>46.12</v>
+      </c>
+      <c r="D5" s="84" t="s">
+        <v>94</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="21">
+      <c r="A6" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" s="6">
+        <v>7</v>
+      </c>
+      <c r="C6" s="6">
+        <v>24.03</v>
+      </c>
+      <c r="D6" s="84" t="s">
+        <v>94</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="21">
+      <c r="A7" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B7" s="6">
+        <v>8</v>
+      </c>
+      <c r="C7" s="6">
+        <v>22.55</v>
+      </c>
+      <c r="D7" s="84" t="s">
+        <v>94</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="21">
+      <c r="A8" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B8" s="6">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>62.73</v>
+      </c>
+      <c r="D8" s="84" t="s">
+        <v>94</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="21">
+      <c r="A9" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="6">
+        <v>10</v>
+      </c>
+      <c r="C9" s="6">
+        <v>29.7</v>
+      </c>
+      <c r="D9" s="84" t="s">
+        <v>94</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="21">
+      <c r="A10" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" s="6">
+        <v>11</v>
+      </c>
+      <c r="C10" s="6">
+        <v>270.44</v>
+      </c>
+      <c r="D10" s="84" t="s">
+        <v>94</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="21">
+      <c r="A11" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B11" s="6">
+        <v>12</v>
+      </c>
+      <c r="C11" s="6">
+        <v>64.25</v>
+      </c>
+      <c r="D11" s="84" t="s">
+        <v>94</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="21">
+      <c r="A12" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B12" s="6">
+        <v>13</v>
+      </c>
+      <c r="C12" s="6">
+        <v>29.89</v>
+      </c>
+      <c r="D12" s="84" t="s">
+        <v>94</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="21">
+      <c r="A13" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" s="6">
+        <v>6</v>
+      </c>
+      <c r="C13" s="6">
+        <v>52.63</v>
+      </c>
+      <c r="D13" s="84" t="s">
+        <v>94</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="21">
+      <c r="A14" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B14" s="6">
+        <v>7</v>
+      </c>
+      <c r="C14" s="6">
+        <v>60.61</v>
+      </c>
+      <c r="D14" s="84" t="s">
+        <v>100</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="21">
+      <c r="A15" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B15" s="6">
+        <v>11</v>
+      </c>
+      <c r="C15" s="6">
+        <v>56.69</v>
+      </c>
+      <c r="D15" s="84" t="s">
+        <v>100</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="21">
+      <c r="A16" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B16" s="6">
+        <v>12</v>
+      </c>
+      <c r="C16" s="6">
+        <v>49.78</v>
+      </c>
+      <c r="D16" s="84" t="s">
+        <v>100</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="21">
+      <c r="A17" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B17" s="6">
+        <v>13</v>
+      </c>
+      <c r="C17" s="6">
+        <v>26.67</v>
+      </c>
+      <c r="D17" s="84" t="s">
+        <v>100</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="21">
+      <c r="A18" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B18" s="6">
+        <v>14</v>
+      </c>
+      <c r="C18" s="6">
+        <v>33.96</v>
+      </c>
+      <c r="D18" s="84" t="s">
+        <v>100</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="21">
+      <c r="A19" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B19" s="6">
+        <v>16</v>
+      </c>
+      <c r="C19" s="6">
+        <v>91.46</v>
+      </c>
+      <c r="D19" s="84" t="s">
+        <v>100</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="21">
+      <c r="A20" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B20" s="6">
+        <v>1</v>
+      </c>
+      <c r="C20" s="6">
+        <v>58.59</v>
+      </c>
+      <c r="D20" s="84" t="s">
+        <v>85</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="21">
+      <c r="A21" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B21" s="6">
+        <v>2</v>
+      </c>
+      <c r="C21" s="6">
+        <v>40.99</v>
+      </c>
+      <c r="D21" s="84" t="s">
+        <v>85</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="21">
+      <c r="A22" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B22" s="6">
+        <v>3</v>
+      </c>
+      <c r="C22" s="6">
+        <v>63.11</v>
+      </c>
+      <c r="D22" s="84" t="s">
+        <v>85</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="21">
+      <c r="A23" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B23" s="6">
+        <v>4</v>
+      </c>
+      <c r="C23" s="6">
+        <v>71.48</v>
+      </c>
+      <c r="D23" s="84" t="s">
+        <v>85</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="21">
+      <c r="A24" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B24" s="6">
+        <v>5</v>
+      </c>
+      <c r="C24" s="6">
+        <v>67.739999999999995</v>
+      </c>
+      <c r="D24" s="84" t="s">
+        <v>94</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="21">
+      <c r="A25" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B25" s="6">
+        <v>6</v>
+      </c>
+      <c r="C25" s="6">
+        <v>24.52</v>
+      </c>
+      <c r="D25" s="84" t="s">
+        <v>94</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="21">
+      <c r="A26" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B26" s="6">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>31</v>
+      </c>
+      <c r="D26" s="84" t="s">
+        <v>85</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="21">
+      <c r="A27" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B27" s="6">
+        <v>12</v>
+      </c>
+      <c r="C27" s="6">
+        <v>67</v>
+      </c>
+      <c r="D27" s="84" t="s">
+        <v>94</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="21">
+      <c r="A28" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B28" s="6">
+        <v>1</v>
+      </c>
+      <c r="C28" s="6">
+        <v>138.88</v>
+      </c>
+      <c r="D28" s="84" t="s">
+        <v>85</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="21">
+      <c r="A29" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B29" s="6">
+        <v>2</v>
+      </c>
+      <c r="C29" s="6">
+        <v>141.69999999999999</v>
+      </c>
+      <c r="D29" s="84" t="s">
+        <v>94</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="21">
+      <c r="A30" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B30" s="6">
+        <v>1</v>
+      </c>
+      <c r="C30" s="6">
+        <v>101.74</v>
+      </c>
+      <c r="D30" s="84" t="s">
+        <v>94</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="21">
+      <c r="A31" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B31" s="6">
+        <v>2</v>
+      </c>
+      <c r="C31" s="6">
+        <v>34.99</v>
+      </c>
+      <c r="D31" s="84" t="s">
+        <v>85</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="21">
+      <c r="A32" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B32" s="6">
+        <v>3</v>
+      </c>
+      <c r="C32" s="6">
+        <v>301.24</v>
+      </c>
+      <c r="D32" s="84" t="s">
+        <v>85</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="21">
+      <c r="A33" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B33" s="6">
+        <v>4</v>
+      </c>
+      <c r="C33" s="6">
+        <v>180.2</v>
+      </c>
+      <c r="D33" s="84" t="s">
+        <v>85</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="21">
+      <c r="A34" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B34" s="6">
+        <v>5</v>
+      </c>
+      <c r="C34" s="6">
+        <v>59.08</v>
+      </c>
+      <c r="D34" s="84" t="s">
+        <v>94</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="21">
+      <c r="A35" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B35" s="6">
+        <v>7</v>
+      </c>
+      <c r="C35" s="6">
+        <v>46.79</v>
+      </c>
+      <c r="D35" s="84" t="s">
+        <v>94</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="21">
+      <c r="A36" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B36" s="6">
+        <v>8</v>
+      </c>
+      <c r="C36" s="6">
+        <v>59.05</v>
+      </c>
+      <c r="D36" s="84" t="s">
+        <v>94</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="21">
+      <c r="A37" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B37" s="6">
+        <v>9</v>
+      </c>
+      <c r="C37" s="6">
+        <v>103.45</v>
+      </c>
+      <c r="D37" s="84" t="s">
+        <v>94</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="21">
+      <c r="A38" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B38" s="6">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>101.88</v>
+      </c>
+      <c r="D38" s="84" t="s">
+        <v>85</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="21">
+      <c r="A39" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B39" s="6">
+        <v>11</v>
+      </c>
+      <c r="C39" s="6">
+        <v>53.38</v>
+      </c>
+      <c r="D39" s="84" t="s">
+        <v>94</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="21">
+      <c r="A40" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B40" s="6">
+        <v>12</v>
+      </c>
+      <c r="C40" s="6">
+        <v>102.7</v>
+      </c>
+      <c r="D40" s="84" t="s">
+        <v>94</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="21">
+      <c r="A41" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B41" s="6">
+        <v>13</v>
+      </c>
+      <c r="C41" s="6">
+        <v>87.11</v>
+      </c>
+      <c r="D41" s="84" t="s">
+        <v>94</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="21">
+      <c r="A42" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B42" s="6">
+        <v>14</v>
+      </c>
+      <c r="C42" s="6">
+        <v>59.42</v>
+      </c>
+      <c r="D42" s="84" t="s">
+        <v>94</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="21">
+      <c r="A43" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B43" s="6">
+        <v>15</v>
+      </c>
+      <c r="C43" s="6">
+        <v>35.96</v>
+      </c>
+      <c r="D43" s="84" t="s">
+        <v>94</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="21">
+      <c r="A44" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C44" s="6">
+        <v>386.2</v>
+      </c>
+      <c r="D44" s="84" t="s">
+        <v>136</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="21">
+      <c r="A45" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="C45" s="6">
+        <v>120</v>
+      </c>
+      <c r="D45" s="84" t="s">
+        <v>94</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="21">
+      <c r="A46" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C46" s="9">
+        <v>163</v>
+      </c>
+      <c r="D46" s="84" t="s">
+        <v>136</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="21">
+      <c r="A47" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="C47" s="6">
+        <v>189.75</v>
+      </c>
+      <c r="D47" s="84" t="s">
+        <v>136</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="21">
+      <c r="A48" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C48" s="6">
+        <v>169.61</v>
+      </c>
+      <c r="D48" s="84" t="s">
+        <v>136</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="21">
+      <c r="A49" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="C49" s="6">
+        <v>118.35</v>
+      </c>
+      <c r="D49" s="84" t="s">
+        <v>136</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="21">
+      <c r="A50" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C50" s="6">
+        <v>243.29</v>
+      </c>
+      <c r="D50" s="84" t="s">
+        <v>136</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="21">
+      <c r="A51" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C51" s="6">
+        <v>201.78</v>
+      </c>
+      <c r="D51" s="84" t="s">
+        <v>94</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="21">
+      <c r="A52" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C52" s="6">
+        <v>150.52000000000001</v>
+      </c>
+      <c r="D52" s="84" t="s">
+        <v>94</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="21">
+      <c r="A53" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C53" s="6">
+        <v>225.15</v>
+      </c>
+      <c r="D53" s="84" t="s">
+        <v>94</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9596069D-6E41-4381-B3ED-F63518FBA9EA}">
-  <dimension ref="A1:AX9"/>
+  <dimension ref="A1:AX7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.28515625" customWidth="1"/>
@@ -5860,218 +6756,218 @@
       <c r="B1" s="37">
         <v>2022</v>
       </c>
-      <c r="C1" s="83">
+      <c r="C1" s="80">
         <v>2023</v>
       </c>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="84"/>
-      <c r="G1" s="84"/>
-      <c r="H1" s="84"/>
-      <c r="I1" s="84"/>
-      <c r="J1" s="84"/>
-      <c r="K1" s="84"/>
-      <c r="L1" s="84"/>
-      <c r="M1" s="84"/>
-      <c r="N1" s="84"/>
-      <c r="O1" s="83">
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
+      <c r="M1" s="81"/>
+      <c r="N1" s="81"/>
+      <c r="O1" s="80">
         <v>2024</v>
       </c>
-      <c r="P1" s="84"/>
-      <c r="Q1" s="84"/>
-      <c r="R1" s="84"/>
-      <c r="S1" s="84"/>
-      <c r="T1" s="84"/>
-      <c r="U1" s="84"/>
-      <c r="V1" s="84"/>
-      <c r="W1" s="84"/>
-      <c r="X1" s="84"/>
-      <c r="Y1" s="84"/>
-      <c r="Z1" s="85"/>
-      <c r="AA1" s="84">
+      <c r="P1" s="81"/>
+      <c r="Q1" s="81"/>
+      <c r="R1" s="81"/>
+      <c r="S1" s="81"/>
+      <c r="T1" s="81"/>
+      <c r="U1" s="81"/>
+      <c r="V1" s="81"/>
+      <c r="W1" s="81"/>
+      <c r="X1" s="81"/>
+      <c r="Y1" s="81"/>
+      <c r="Z1" s="82"/>
+      <c r="AA1" s="81">
         <v>2025</v>
       </c>
-      <c r="AB1" s="84"/>
-      <c r="AC1" s="84"/>
-      <c r="AD1" s="84"/>
-      <c r="AE1" s="84"/>
-      <c r="AF1" s="84"/>
-      <c r="AG1" s="84"/>
-      <c r="AH1" s="84"/>
-      <c r="AI1" s="84"/>
-      <c r="AJ1" s="84"/>
-      <c r="AK1" s="84"/>
-      <c r="AL1" s="84"/>
-      <c r="AM1" s="86">
+      <c r="AB1" s="81"/>
+      <c r="AC1" s="81"/>
+      <c r="AD1" s="81"/>
+      <c r="AE1" s="81"/>
+      <c r="AF1" s="81"/>
+      <c r="AG1" s="81"/>
+      <c r="AH1" s="81"/>
+      <c r="AI1" s="81"/>
+      <c r="AJ1" s="81"/>
+      <c r="AK1" s="81"/>
+      <c r="AL1" s="81"/>
+      <c r="AM1" s="83">
         <v>2026</v>
       </c>
-      <c r="AN1" s="86"/>
-      <c r="AO1" s="86"/>
-      <c r="AP1" s="86"/>
-      <c r="AQ1" s="86"/>
-      <c r="AR1" s="86"/>
-      <c r="AS1" s="86"/>
-      <c r="AT1" s="86"/>
-      <c r="AU1" s="86"/>
-      <c r="AV1" s="86"/>
-      <c r="AW1" s="86"/>
-      <c r="AX1" s="86"/>
+      <c r="AN1" s="83"/>
+      <c r="AO1" s="83"/>
+      <c r="AP1" s="83"/>
+      <c r="AQ1" s="83"/>
+      <c r="AR1" s="83"/>
+      <c r="AS1" s="83"/>
+      <c r="AT1" s="83"/>
+      <c r="AU1" s="83"/>
+      <c r="AV1" s="83"/>
+      <c r="AW1" s="83"/>
+      <c r="AX1" s="83"/>
     </row>
     <row r="2" spans="1:50">
       <c r="A2" s="37" t="s">
         <v>20</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C2" s="38" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D2" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="E2" s="37" t="s">
+        <v>155</v>
+      </c>
+      <c r="F2" s="37" t="s">
+        <v>156</v>
+      </c>
+      <c r="G2" s="37" t="s">
+        <v>157</v>
+      </c>
+      <c r="H2" s="37" t="s">
+        <v>158</v>
+      </c>
+      <c r="I2" s="37" t="s">
+        <v>159</v>
+      </c>
+      <c r="J2" s="37" t="s">
+        <v>160</v>
+      </c>
+      <c r="K2" s="37" t="s">
+        <v>161</v>
+      </c>
+      <c r="L2" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="M2" s="37" t="s">
+        <v>163</v>
+      </c>
+      <c r="N2" s="37" t="s">
         <v>152</v>
       </c>
-      <c r="E2" s="37" t="s">
+      <c r="O2" s="38" t="s">
         <v>153</v>
       </c>
-      <c r="F2" s="37" t="s">
+      <c r="P2" s="37" t="s">
         <v>154</v>
       </c>
-      <c r="G2" s="37" t="s">
+      <c r="Q2" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H2" s="37" t="s">
+      <c r="R2" s="37" t="s">
         <v>156</v>
       </c>
-      <c r="I2" s="37" t="s">
+      <c r="S2" s="37" t="s">
         <v>157</v>
       </c>
-      <c r="J2" s="37" t="s">
+      <c r="T2" s="37" t="s">
         <v>158</v>
       </c>
-      <c r="K2" s="37" t="s">
+      <c r="U2" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="L2" s="37" t="s">
+      <c r="V2" s="37" t="s">
         <v>160</v>
       </c>
-      <c r="M2" s="37" t="s">
+      <c r="W2" s="37" t="s">
         <v>161</v>
       </c>
-      <c r="N2" s="37" t="s">
-        <v>150</v>
-      </c>
-      <c r="O2" s="38" t="s">
-        <v>151</v>
-      </c>
-      <c r="P2" s="37" t="s">
+      <c r="X2" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="Y2" s="37" t="s">
+        <v>163</v>
+      </c>
+      <c r="Z2" s="39" t="s">
         <v>152</v>
       </c>
-      <c r="Q2" s="37" t="s">
+      <c r="AA2" s="37" t="s">
         <v>153</v>
       </c>
-      <c r="R2" s="37" t="s">
+      <c r="AB2" s="37" t="s">
         <v>154</v>
       </c>
-      <c r="S2" s="37" t="s">
+      <c r="AC2" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="T2" s="37" t="s">
+      <c r="AD2" s="37" t="s">
         <v>156</v>
       </c>
-      <c r="U2" s="37" t="s">
+      <c r="AE2" s="37" t="s">
         <v>157</v>
       </c>
-      <c r="V2" s="37" t="s">
+      <c r="AF2" s="37" t="s">
         <v>158</v>
       </c>
-      <c r="W2" s="37" t="s">
+      <c r="AG2" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="X2" s="37" t="s">
+      <c r="AH2" s="37" t="s">
         <v>160</v>
       </c>
-      <c r="Y2" s="37" t="s">
+      <c r="AI2" s="37" t="s">
         <v>161</v>
       </c>
-      <c r="Z2" s="39" t="s">
-        <v>150</v>
-      </c>
-      <c r="AA2" s="37" t="s">
-        <v>151</v>
-      </c>
-      <c r="AB2" s="37" t="s">
+      <c r="AJ2" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="AK2" s="37" t="s">
+        <v>163</v>
+      </c>
+      <c r="AL2" s="37" t="s">
         <v>152</v>
       </c>
-      <c r="AC2" s="37" t="s">
+      <c r="AM2" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="AD2" s="37" t="s">
+      <c r="AN2" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="AE2" s="37" t="s">
+      <c r="AO2" s="17" t="s">
         <v>155</v>
       </c>
-      <c r="AF2" s="37" t="s">
+      <c r="AP2" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="AG2" s="37" t="s">
+      <c r="AQ2" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="AH2" s="37" t="s">
+      <c r="AR2" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="AI2" s="37" t="s">
+      <c r="AS2" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="AJ2" s="37" t="s">
+      <c r="AT2" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="AK2" s="37" t="s">
+      <c r="AU2" s="17" t="s">
         <v>161</v>
       </c>
-      <c r="AL2" s="37" t="s">
-        <v>150</v>
-      </c>
-      <c r="AM2" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="AN2" s="17" t="s">
+      <c r="AV2" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="AW2" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="AX2" s="17" t="s">
         <v>152</v>
-      </c>
-      <c r="AO2" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="AP2" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="AQ2" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="AR2" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="AS2" s="17" t="s">
-        <v>157</v>
-      </c>
-      <c r="AT2" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="AU2" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="AV2" s="17" t="s">
-        <v>160</v>
-      </c>
-      <c r="AW2" s="17" t="s">
-        <v>161</v>
-      </c>
-      <c r="AX2" s="17" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:50">
       <c r="A3" s="37" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B3" s="37">
         <v>45</v>
@@ -6206,7 +7102,10 @@
       <c r="AQ3" s="17">
         <v>92</v>
       </c>
-      <c r="AR3" s="17"/>
+      <c r="AR3" s="17">
+        <f>137-AQ3</f>
+        <v>45</v>
+      </c>
       <c r="AS3" s="17"/>
       <c r="AT3" s="17"/>
       <c r="AU3" s="17"/>
@@ -6215,433 +7114,442 @@
       <c r="AX3" s="17"/>
     </row>
     <row r="4" spans="1:50">
-      <c r="A4" s="37" t="s">
-        <v>163</v>
-      </c>
-      <c r="B4" s="37">
-        <v>45</v>
-      </c>
-      <c r="C4" s="38">
-        <v>35</v>
-      </c>
-      <c r="D4" s="37">
-        <v>50</v>
-      </c>
-      <c r="E4" s="37">
-        <v>50</v>
-      </c>
-      <c r="F4" s="37">
+      <c r="A4" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="B4" s="40">
+        <v>47</v>
+      </c>
+      <c r="C4" s="41">
         <v>30</v>
       </c>
-      <c r="G4" s="37">
-        <v>131</v>
-      </c>
-      <c r="H4" s="37">
-        <v>35</v>
-      </c>
-      <c r="I4" s="37">
-        <v>113</v>
-      </c>
-      <c r="J4" s="37">
-        <v>45</v>
-      </c>
-      <c r="K4" s="37">
-        <v>90</v>
-      </c>
-      <c r="L4" s="37">
-        <v>105</v>
-      </c>
-      <c r="M4" s="37">
-        <v>100</v>
-      </c>
-      <c r="N4" s="37">
-        <v>310</v>
-      </c>
-      <c r="O4" s="38">
-        <v>110</v>
-      </c>
-      <c r="P4" s="37">
-        <v>163</v>
-      </c>
-      <c r="Q4" s="37">
-        <v>380</v>
-      </c>
-      <c r="R4" s="37">
-        <v>288</v>
-      </c>
-      <c r="S4" s="37">
-        <v>165</v>
-      </c>
-      <c r="T4" s="37">
+      <c r="D4" s="40">
+        <v>25</v>
+      </c>
+      <c r="E4" s="40">
+        <v>95</v>
+      </c>
+      <c r="F4" s="40">
+        <v>66</v>
+      </c>
+      <c r="G4" s="40">
+        <v>118</v>
+      </c>
+      <c r="H4" s="40">
         <v>15</v>
       </c>
-      <c r="U4" s="37">
-        <v>15</v>
-      </c>
-      <c r="V4" s="37">
-        <v>80</v>
-      </c>
-      <c r="W4" s="37">
-        <v>36</v>
-      </c>
-      <c r="X4" s="37">
+      <c r="I4" s="40">
+        <v>135</v>
+      </c>
+      <c r="J4" s="40">
+        <v>30</v>
+      </c>
+      <c r="K4" s="40">
+        <v>126</v>
+      </c>
+      <c r="L4" s="40">
+        <v>85</v>
+      </c>
+      <c r="M4" s="40">
+        <v>205</v>
+      </c>
+      <c r="N4" s="40">
+        <v>412</v>
+      </c>
+      <c r="O4" s="41">
+        <v>140</v>
+      </c>
+      <c r="P4" s="40">
+        <v>70</v>
+      </c>
+      <c r="Q4" s="40">
+        <v>337</v>
+      </c>
+      <c r="R4" s="40">
+        <v>347</v>
+      </c>
+      <c r="S4" s="40">
+        <v>313</v>
+      </c>
+      <c r="T4" s="40">
+        <v>20</v>
+      </c>
+      <c r="U4" s="40">
+        <v>10</v>
+      </c>
+      <c r="V4" s="40">
         <v>95</v>
       </c>
-      <c r="Y4" s="37">
-        <v>137</v>
-      </c>
-      <c r="Z4" s="39">
-        <v>98</v>
-      </c>
-      <c r="AA4" s="37">
-        <v>95</v>
-      </c>
-      <c r="AB4" s="37">
-        <v>175</v>
-      </c>
-      <c r="AC4" s="37">
-        <v>110</v>
-      </c>
-      <c r="AD4" s="37">
-        <v>61</v>
-      </c>
-      <c r="AE4" s="37">
-        <v>149</v>
-      </c>
-      <c r="AF4" s="37">
-        <f>45+52</f>
-        <v>97</v>
-      </c>
-      <c r="AG4" s="37">
-        <v>80</v>
-      </c>
-      <c r="AH4" s="37">
-        <f>15+60</f>
-        <v>75</v>
-      </c>
-      <c r="AI4" s="37">
-        <f>65+10+13+10</f>
-        <v>98</v>
-      </c>
-      <c r="AJ4" s="37">
-        <f>45+3</f>
-        <v>48</v>
-      </c>
-      <c r="AK4" s="37">
-        <f>3+30+50+18</f>
-        <v>101</v>
-      </c>
-      <c r="AL4" s="37">
-        <f>12+10</f>
-        <v>22</v>
-      </c>
-      <c r="AM4" s="17">
-        <v>25</v>
-      </c>
-      <c r="AN4" s="17">
-        <v>70</v>
-      </c>
-      <c r="AO4" s="17">
-        <f>1+45+20</f>
-        <v>66</v>
-      </c>
-      <c r="AP4" s="17">
-        <v>165</v>
-      </c>
-      <c r="AQ4" s="17">
-        <v>92</v>
-      </c>
-      <c r="AR4" s="17"/>
-      <c r="AS4" s="17"/>
-      <c r="AT4" s="17"/>
-      <c r="AU4" s="17"/>
-      <c r="AV4" s="17"/>
-      <c r="AW4" s="17"/>
-      <c r="AX4" s="17"/>
-    </row>
-    <row r="5" spans="1:50">
-      <c r="A5" s="40" t="s">
-        <v>83</v>
-      </c>
-      <c r="B5" s="40">
-        <v>47</v>
-      </c>
-      <c r="C5" s="41">
-        <v>30</v>
-      </c>
-      <c r="D5" s="40">
-        <v>25</v>
-      </c>
-      <c r="E5" s="40">
-        <v>95</v>
-      </c>
-      <c r="F5" s="40">
-        <v>66</v>
-      </c>
-      <c r="G5" s="40">
-        <v>118</v>
-      </c>
-      <c r="H5" s="40">
-        <v>15</v>
-      </c>
-      <c r="I5" s="40">
-        <v>135</v>
-      </c>
-      <c r="J5" s="40">
-        <v>30</v>
-      </c>
-      <c r="K5" s="40">
-        <v>126</v>
-      </c>
-      <c r="L5" s="40">
-        <v>85</v>
-      </c>
-      <c r="M5" s="40">
-        <v>205</v>
-      </c>
-      <c r="N5" s="40">
-        <v>412</v>
-      </c>
-      <c r="O5" s="41">
-        <v>140</v>
-      </c>
-      <c r="P5" s="40">
-        <v>70</v>
-      </c>
-      <c r="Q5" s="40">
-        <v>337</v>
-      </c>
-      <c r="R5" s="40">
-        <v>347</v>
-      </c>
-      <c r="S5" s="40">
-        <v>313</v>
-      </c>
-      <c r="T5" s="40">
-        <v>20</v>
-      </c>
-      <c r="U5" s="40">
-        <v>10</v>
-      </c>
-      <c r="V5" s="40">
-        <v>95</v>
-      </c>
-      <c r="W5" s="40">
+      <c r="W4" s="40">
         <v>109</v>
       </c>
-      <c r="X5" s="40">
+      <c r="X4" s="40">
         <v>211</v>
       </c>
-      <c r="Y5" s="40">
+      <c r="Y4" s="40">
         <v>183</v>
       </c>
-      <c r="Z5" s="42">
+      <c r="Z4" s="42">
         <v>54</v>
       </c>
-      <c r="AA5" s="40">
+      <c r="AA4" s="40">
         <v>72</v>
       </c>
-      <c r="AB5" s="40">
+      <c r="AB4" s="40">
         <v>193</v>
       </c>
-      <c r="AC5" s="40">
+      <c r="AC4" s="40">
         <v>170</v>
       </c>
-      <c r="AD5" s="40">
+      <c r="AD4" s="40">
         <v>86</v>
       </c>
-      <c r="AE5" s="40">
+      <c r="AE4" s="40">
         <v>152</v>
       </c>
-      <c r="AF5" s="40">
+      <c r="AF4" s="40">
         <f>70+55</f>
         <v>125</v>
       </c>
-      <c r="AG5" s="40">
+      <c r="AG4" s="40">
         <v>115</v>
       </c>
-      <c r="AH5" s="40">
+      <c r="AH4" s="40">
         <f>35+90</f>
         <v>125</v>
       </c>
-      <c r="AI5" s="40">
+      <c r="AI4" s="40">
         <f>65+6+20+10</f>
         <v>101</v>
       </c>
-      <c r="AJ5" s="40">
+      <c r="AJ4" s="40">
         <f>45+2+110</f>
         <v>157</v>
       </c>
-      <c r="AK5" s="40">
+      <c r="AK4" s="40">
         <f>3+52+50+20</f>
         <v>125</v>
       </c>
-      <c r="AL5" s="40">
+      <c r="AL4" s="40">
         <f>160+11+31</f>
         <v>202</v>
       </c>
-      <c r="AM5" s="43">
+      <c r="AM4" s="43">
         <v>60</v>
       </c>
-      <c r="AN5" s="43">
+      <c r="AN4" s="43">
         <v>120</v>
       </c>
-      <c r="AO5" s="43">
+      <c r="AO4" s="43">
         <f>1+63+60</f>
         <v>124</v>
       </c>
-      <c r="AP5" s="43">
+      <c r="AP4" s="43">
         <v>214</v>
       </c>
-      <c r="AQ5" s="43">
+      <c r="AQ4" s="43">
         <v>69</v>
       </c>
-      <c r="AR5" s="43"/>
-      <c r="AS5" s="43"/>
-      <c r="AT5" s="43"/>
-      <c r="AU5" s="43"/>
-      <c r="AV5" s="43"/>
-      <c r="AW5" s="43"/>
-      <c r="AX5" s="43"/>
+      <c r="AR4" s="43">
+        <f>125-AQ4</f>
+        <v>56</v>
+      </c>
+      <c r="AS4" s="43"/>
+      <c r="AT4" s="43"/>
+      <c r="AU4" s="43"/>
+      <c r="AV4" s="43"/>
+      <c r="AW4" s="43"/>
+      <c r="AX4" s="43"/>
+    </row>
+    <row r="5" spans="1:50">
+      <c r="A5" s="37" t="s">
+        <v>165</v>
+      </c>
+      <c r="B5" s="37">
+        <v>35</v>
+      </c>
+      <c r="C5" s="38">
+        <v>20</v>
+      </c>
+      <c r="D5" s="37">
+        <v>17</v>
+      </c>
+      <c r="E5" s="37">
+        <v>55</v>
+      </c>
+      <c r="F5" s="37">
+        <v>40</v>
+      </c>
+      <c r="G5" s="37">
+        <v>71</v>
+      </c>
+      <c r="H5" s="37">
+        <v>45</v>
+      </c>
+      <c r="I5" s="37">
+        <v>91</v>
+      </c>
+      <c r="J5" s="37">
+        <v>30</v>
+      </c>
+      <c r="K5" s="37">
+        <v>160</v>
+      </c>
+      <c r="L5" s="37">
+        <v>80</v>
+      </c>
+      <c r="M5" s="37">
+        <v>158</v>
+      </c>
+      <c r="N5" s="37">
+        <v>280</v>
+      </c>
+      <c r="O5" s="38">
+        <v>80</v>
+      </c>
+      <c r="P5" s="37">
+        <v>173</v>
+      </c>
+      <c r="Q5" s="37">
+        <v>275</v>
+      </c>
+      <c r="R5" s="37">
+        <v>381</v>
+      </c>
+      <c r="S5" s="37">
+        <v>239</v>
+      </c>
+      <c r="T5" s="37">
+        <v>95</v>
+      </c>
+      <c r="U5" s="37">
+        <v>12</v>
+      </c>
+      <c r="V5" s="37">
+        <v>78</v>
+      </c>
+      <c r="W5" s="37">
+        <v>103</v>
+      </c>
+      <c r="X5" s="37">
+        <v>109</v>
+      </c>
+      <c r="Y5" s="37">
+        <v>154</v>
+      </c>
+      <c r="Z5" s="39">
+        <v>110</v>
+      </c>
+      <c r="AA5" s="37">
+        <v>65</v>
+      </c>
+      <c r="AB5" s="37">
+        <v>169</v>
+      </c>
+      <c r="AC5" s="37">
+        <v>133</v>
+      </c>
+      <c r="AD5" s="37">
+        <v>73</v>
+      </c>
+      <c r="AE5" s="37">
+        <v>150</v>
+      </c>
+      <c r="AF5" s="37">
+        <f>45+35</f>
+        <v>80</v>
+      </c>
+      <c r="AG5" s="37">
+        <v>110</v>
+      </c>
+      <c r="AH5" s="37">
+        <f>3+57</f>
+        <v>60</v>
+      </c>
+      <c r="AI5" s="37">
+        <f>45+10+11+10</f>
+        <v>76</v>
+      </c>
+      <c r="AJ5" s="37">
+        <f>48+2+150</f>
+        <v>200</v>
+      </c>
+      <c r="AK5" s="37">
+        <f>3+25+23+35</f>
+        <v>86</v>
+      </c>
+      <c r="AL5" s="37">
+        <f>40+22</f>
+        <v>62</v>
+      </c>
+      <c r="AM5" s="17">
+        <v>25</v>
+      </c>
+      <c r="AN5" s="17">
+        <v>70</v>
+      </c>
+      <c r="AO5" s="17">
+        <f>1+45+55</f>
+        <v>101</v>
+      </c>
+      <c r="AP5" s="17">
+        <v>160</v>
+      </c>
+      <c r="AQ5" s="17">
+        <v>268</v>
+      </c>
+      <c r="AR5" s="17">
+        <f>309-AQ5</f>
+        <v>41</v>
+      </c>
+      <c r="AS5" s="17"/>
+      <c r="AT5" s="17"/>
+      <c r="AU5" s="17"/>
+      <c r="AV5" s="17"/>
+      <c r="AW5" s="17"/>
+      <c r="AX5" s="17"/>
     </row>
     <row r="6" spans="1:50">
       <c r="A6" s="37" t="s">
-        <v>164</v>
+        <v>99</v>
       </c>
       <c r="B6" s="37">
+        <v>47</v>
+      </c>
+      <c r="C6" s="38">
+        <v>30</v>
+      </c>
+      <c r="D6" s="37">
+        <v>25</v>
+      </c>
+      <c r="E6" s="37">
+        <v>95</v>
+      </c>
+      <c r="F6" s="37">
+        <v>78</v>
+      </c>
+      <c r="G6" s="37">
+        <v>102</v>
+      </c>
+      <c r="H6" s="37">
+        <v>11</v>
+      </c>
+      <c r="I6" s="37">
+        <v>130</v>
+      </c>
+      <c r="J6" s="37">
         <v>35</v>
       </c>
-      <c r="C6" s="38">
-        <v>20</v>
-      </c>
-      <c r="D6" s="37">
-        <v>17</v>
-      </c>
-      <c r="E6" s="37">
-        <v>55</v>
-      </c>
-      <c r="F6" s="37">
-        <v>40</v>
-      </c>
-      <c r="G6" s="37">
-        <v>71</v>
-      </c>
-      <c r="H6" s="37">
-        <v>45</v>
-      </c>
-      <c r="I6" s="37">
-        <v>91</v>
-      </c>
-      <c r="J6" s="37">
-        <v>30</v>
-      </c>
       <c r="K6" s="37">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="L6" s="37">
         <v>80</v>
       </c>
       <c r="M6" s="37">
+        <v>200</v>
+      </c>
+      <c r="N6" s="37">
+        <v>352</v>
+      </c>
+      <c r="O6" s="38">
+        <v>107</v>
+      </c>
+      <c r="P6" s="37">
+        <v>90</v>
+      </c>
+      <c r="Q6" s="37">
+        <v>250</v>
+      </c>
+      <c r="R6" s="37">
+        <v>330</v>
+      </c>
+      <c r="S6" s="37">
+        <v>310</v>
+      </c>
+      <c r="T6" s="37">
+        <v>20</v>
+      </c>
+      <c r="U6" s="37">
+        <v>10</v>
+      </c>
+      <c r="V6" s="37">
+        <v>100</v>
+      </c>
+      <c r="W6" s="37">
+        <v>118</v>
+      </c>
+      <c r="X6" s="37">
+        <v>202</v>
+      </c>
+      <c r="Y6" s="37">
+        <v>169</v>
+      </c>
+      <c r="Z6" s="39">
+        <v>42</v>
+      </c>
+      <c r="AA6" s="37">
+        <v>20</v>
+      </c>
+      <c r="AB6" s="37">
+        <v>174</v>
+      </c>
+      <c r="AC6" s="37">
         <v>158</v>
       </c>
-      <c r="N6" s="37">
-        <v>280</v>
-      </c>
-      <c r="O6" s="38">
-        <v>80</v>
-      </c>
-      <c r="P6" s="37">
-        <v>173</v>
-      </c>
-      <c r="Q6" s="37">
-        <v>275</v>
-      </c>
-      <c r="R6" s="37">
-        <v>381</v>
-      </c>
-      <c r="S6" s="37">
-        <v>239</v>
-      </c>
-      <c r="T6" s="37">
-        <v>95</v>
-      </c>
-      <c r="U6" s="37">
-        <v>12</v>
-      </c>
-      <c r="V6" s="37">
-        <v>78</v>
-      </c>
-      <c r="W6" s="37">
-        <v>103</v>
-      </c>
-      <c r="X6" s="37">
+      <c r="AD6" s="37">
+        <v>100</v>
+      </c>
+      <c r="AE6" s="37">
         <v>109</v>
       </c>
-      <c r="Y6" s="37">
-        <v>154</v>
-      </c>
-      <c r="Z6" s="39">
-        <v>110</v>
-      </c>
-      <c r="AA6" s="37">
-        <v>65</v>
-      </c>
-      <c r="AB6" s="37">
-        <v>169</v>
-      </c>
-      <c r="AC6" s="37">
-        <v>133</v>
-      </c>
-      <c r="AD6" s="37">
-        <v>73</v>
-      </c>
-      <c r="AE6" s="37">
-        <v>150</v>
-      </c>
       <c r="AF6" s="37">
-        <f>45+35</f>
-        <v>80</v>
+        <f>87+75</f>
+        <v>162</v>
       </c>
       <c r="AG6" s="37">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="AH6" s="37">
-        <f>3+57</f>
-        <v>60</v>
+        <f>30+78</f>
+        <v>108</v>
       </c>
       <c r="AI6" s="37">
-        <f>45+10+11+10</f>
-        <v>76</v>
+        <f>63+6+22+18</f>
+        <v>109</v>
       </c>
       <c r="AJ6" s="37">
-        <f>48+2+150</f>
-        <v>200</v>
+        <f>40+11+178</f>
+        <v>229</v>
       </c>
       <c r="AK6" s="37">
-        <f>3+25+23+35</f>
-        <v>86</v>
+        <f>3+68+51+18</f>
+        <v>140</v>
       </c>
       <c r="AL6" s="37">
-        <f>40+22</f>
+        <f>160+11+30</f>
+        <v>201</v>
+      </c>
+      <c r="AM6" s="17">
+        <v>51</v>
+      </c>
+      <c r="AN6" s="17">
+        <v>145</v>
+      </c>
+      <c r="AO6" s="17">
+        <f>1+62+60</f>
+        <v>123</v>
+      </c>
+      <c r="AP6" s="17">
+        <v>226</v>
+      </c>
+      <c r="AQ6" s="17">
         <v>62</v>
       </c>
-      <c r="AM6" s="17">
-        <v>25</v>
-      </c>
-      <c r="AN6" s="17">
-        <v>70</v>
-      </c>
-      <c r="AO6" s="17">
-        <f>1+45+55</f>
-        <v>101</v>
-      </c>
-      <c r="AP6" s="17">
-        <v>160</v>
-      </c>
-      <c r="AQ6" s="17">
-        <v>268</v>
-      </c>
-      <c r="AR6" s="17"/>
+      <c r="AR6" s="17">
+        <f>120-AQ6</f>
+        <v>58</v>
+      </c>
       <c r="AS6" s="17"/>
       <c r="AT6" s="17"/>
       <c r="AU6" s="17"/>
@@ -6651,438 +7559,150 @@
     </row>
     <row r="7" spans="1:50">
       <c r="A7" s="37" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="B7" s="37">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C7" s="38">
+        <v>20</v>
+      </c>
+      <c r="D7" s="37">
+        <v>17</v>
+      </c>
+      <c r="E7" s="37">
+        <v>55</v>
+      </c>
+      <c r="F7" s="37">
+        <v>60</v>
+      </c>
+      <c r="G7" s="37">
+        <v>87</v>
+      </c>
+      <c r="H7" s="37">
+        <v>10</v>
+      </c>
+      <c r="I7" s="37">
+        <v>110</v>
+      </c>
+      <c r="J7" s="37">
         <v>30</v>
       </c>
-      <c r="D7" s="37">
-        <v>25</v>
-      </c>
-      <c r="E7" s="37">
-        <v>95</v>
-      </c>
-      <c r="F7" s="37">
-        <v>78</v>
-      </c>
-      <c r="G7" s="37">
-        <v>102</v>
-      </c>
-      <c r="H7" s="37">
-        <v>11</v>
-      </c>
-      <c r="I7" s="37">
-        <v>130</v>
-      </c>
-      <c r="J7" s="37">
-        <v>35</v>
-      </c>
       <c r="K7" s="37">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="L7" s="37">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="M7" s="37">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="N7" s="37">
-        <v>352</v>
+        <v>255</v>
       </c>
       <c r="O7" s="38">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="P7" s="37">
-        <v>90</v>
+        <v>117</v>
       </c>
       <c r="Q7" s="37">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="R7" s="37">
-        <v>330</v>
+        <v>280</v>
       </c>
       <c r="S7" s="37">
-        <v>310</v>
+        <v>155</v>
       </c>
       <c r="T7" s="37">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U7" s="37">
         <v>10</v>
       </c>
       <c r="V7" s="37">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="W7" s="37">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="X7" s="37">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="Y7" s="37">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Z7" s="39">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AA7" s="37">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="AB7" s="37">
-        <v>174</v>
+        <v>132</v>
       </c>
       <c r="AC7" s="37">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="AD7" s="37">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AE7" s="37">
-        <v>109</v>
+        <v>192</v>
       </c>
       <c r="AF7" s="37">
-        <f>87+75</f>
-        <v>162</v>
+        <f>45+35</f>
+        <v>80</v>
       </c>
       <c r="AG7" s="37">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="AH7" s="37">
-        <f>30+78</f>
-        <v>108</v>
+        <f>1+68</f>
+        <v>69</v>
       </c>
       <c r="AI7" s="37">
-        <f>63+6+22+18</f>
-        <v>109</v>
+        <f>40+10+10+10</f>
+        <v>70</v>
       </c>
       <c r="AJ7" s="37">
-        <f>40+11+178</f>
-        <v>229</v>
+        <f>40+2+117</f>
+        <v>159</v>
       </c>
       <c r="AK7" s="37">
-        <f>3+68+51+18</f>
-        <v>140</v>
+        <f>3+35+30+15</f>
+        <v>83</v>
       </c>
       <c r="AL7" s="37">
-        <f>160+11+30</f>
-        <v>201</v>
+        <f>63+30</f>
+        <v>93</v>
       </c>
       <c r="AM7" s="17">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="AN7" s="17">
-        <v>145</v>
+        <v>70</v>
       </c>
       <c r="AO7" s="17">
-        <f>1+62+60</f>
-        <v>123</v>
+        <f>2+45+90</f>
+        <v>137</v>
       </c>
       <c r="AP7" s="17">
-        <v>226</v>
+        <v>115</v>
       </c>
       <c r="AQ7" s="17">
-        <v>62</v>
-      </c>
-      <c r="AR7" s="17"/>
+        <v>300</v>
+      </c>
+      <c r="AR7" s="17">
+        <v>46</v>
+      </c>
       <c r="AS7" s="17"/>
       <c r="AT7" s="17"/>
       <c r="AU7" s="17"/>
       <c r="AV7" s="17"/>
       <c r="AW7" s="17"/>
       <c r="AX7" s="17"/>
-    </row>
-    <row r="8" spans="1:50">
-      <c r="A8" s="44" t="s">
-        <v>165</v>
-      </c>
-      <c r="B8" s="44">
-        <v>47</v>
-      </c>
-      <c r="C8" s="45">
-        <v>30</v>
-      </c>
-      <c r="D8" s="44">
-        <v>25</v>
-      </c>
-      <c r="E8" s="44">
-        <v>95</v>
-      </c>
-      <c r="F8" s="44">
-        <v>70</v>
-      </c>
-      <c r="G8" s="44">
-        <v>100</v>
-      </c>
-      <c r="H8" s="44">
-        <v>11</v>
-      </c>
-      <c r="I8" s="44">
-        <v>140</v>
-      </c>
-      <c r="J8" s="44">
-        <v>35</v>
-      </c>
-      <c r="K8" s="44">
-        <v>166</v>
-      </c>
-      <c r="L8" s="44">
-        <v>40</v>
-      </c>
-      <c r="M8" s="44">
-        <v>205</v>
-      </c>
-      <c r="N8" s="44">
-        <v>350</v>
-      </c>
-      <c r="O8" s="45">
-        <v>150</v>
-      </c>
-      <c r="P8" s="44">
-        <v>90</v>
-      </c>
-      <c r="Q8" s="44">
-        <v>250</v>
-      </c>
-      <c r="R8" s="44">
-        <v>340</v>
-      </c>
-      <c r="S8" s="44">
-        <v>300</v>
-      </c>
-      <c r="T8" s="44">
-        <v>20</v>
-      </c>
-      <c r="U8" s="44">
-        <v>10</v>
-      </c>
-      <c r="V8" s="44">
-        <v>95</v>
-      </c>
-      <c r="W8" s="44">
-        <v>111</v>
-      </c>
-      <c r="X8" s="44">
-        <v>196</v>
-      </c>
-      <c r="Y8" s="44">
-        <v>180</v>
-      </c>
-      <c r="Z8" s="46">
-        <v>48</v>
-      </c>
-      <c r="AA8" s="44">
-        <v>30</v>
-      </c>
-      <c r="AB8" s="44">
-        <v>182</v>
-      </c>
-      <c r="AC8" s="44">
-        <v>165</v>
-      </c>
-      <c r="AD8" s="44">
-        <v>90</v>
-      </c>
-      <c r="AE8" s="44">
-        <v>129</v>
-      </c>
-      <c r="AF8" s="44">
-        <f>75+80</f>
-        <v>155</v>
-      </c>
-      <c r="AG8" s="44">
-        <v>105</v>
-      </c>
-      <c r="AH8" s="44">
-        <f>30+80</f>
-        <v>110</v>
-      </c>
-      <c r="AI8" s="44">
-        <f>65+6+22+15</f>
-        <v>108</v>
-      </c>
-      <c r="AJ8" s="44">
-        <f>40+3+130</f>
-        <v>173</v>
-      </c>
-      <c r="AK8" s="44">
-        <f>3+50+69+20</f>
-        <v>142</v>
-      </c>
-      <c r="AL8" s="44">
-        <f>160+11+30</f>
-        <v>201</v>
-      </c>
-      <c r="AM8" s="47">
-        <v>50</v>
-      </c>
-      <c r="AN8" s="47">
-        <v>70</v>
-      </c>
-      <c r="AO8" s="47">
-        <f>1+62+60</f>
-        <v>123</v>
-      </c>
-      <c r="AP8" s="47">
-        <v>220</v>
-      </c>
-      <c r="AQ8" s="47">
-        <v>65</v>
-      </c>
-      <c r="AR8" s="47"/>
-      <c r="AS8" s="47"/>
-      <c r="AT8" s="47"/>
-      <c r="AU8" s="47"/>
-      <c r="AV8" s="47"/>
-      <c r="AW8" s="47"/>
-      <c r="AX8" s="47"/>
-    </row>
-    <row r="9" spans="1:50">
-      <c r="A9" s="37" t="s">
-        <v>113</v>
-      </c>
-      <c r="B9" s="37">
-        <v>35</v>
-      </c>
-      <c r="C9" s="38">
-        <v>20</v>
-      </c>
-      <c r="D9" s="37">
-        <v>17</v>
-      </c>
-      <c r="E9" s="37">
-        <v>55</v>
-      </c>
-      <c r="F9" s="37">
-        <v>60</v>
-      </c>
-      <c r="G9" s="37">
-        <v>87</v>
-      </c>
-      <c r="H9" s="37">
-        <v>10</v>
-      </c>
-      <c r="I9" s="37">
-        <v>110</v>
-      </c>
-      <c r="J9" s="37">
-        <v>30</v>
-      </c>
-      <c r="K9" s="37">
-        <v>140</v>
-      </c>
-      <c r="L9" s="37">
-        <v>70</v>
-      </c>
-      <c r="M9" s="37">
-        <v>150</v>
-      </c>
-      <c r="N9" s="37">
-        <v>255</v>
-      </c>
-      <c r="O9" s="38">
-        <v>110</v>
-      </c>
-      <c r="P9" s="37">
-        <v>117</v>
-      </c>
-      <c r="Q9" s="37">
-        <v>300</v>
-      </c>
-      <c r="R9" s="37">
-        <v>280</v>
-      </c>
-      <c r="S9" s="37">
-        <v>155</v>
-      </c>
-      <c r="T9" s="37">
-        <v>21</v>
-      </c>
-      <c r="U9" s="37">
-        <v>10</v>
-      </c>
-      <c r="V9" s="37">
-        <v>73</v>
-      </c>
-      <c r="W9" s="37">
-        <v>120</v>
-      </c>
-      <c r="X9" s="37">
-        <v>193</v>
-      </c>
-      <c r="Y9" s="37">
-        <v>168</v>
-      </c>
-      <c r="Z9" s="39">
-        <v>95</v>
-      </c>
-      <c r="AA9" s="37">
-        <v>50</v>
-      </c>
-      <c r="AB9" s="37">
-        <v>132</v>
-      </c>
-      <c r="AC9" s="37">
-        <v>140</v>
-      </c>
-      <c r="AD9" s="37">
-        <v>77</v>
-      </c>
-      <c r="AE9" s="37">
-        <v>192</v>
-      </c>
-      <c r="AF9" s="37">
-        <f>45+35</f>
-        <v>80</v>
-      </c>
-      <c r="AG9" s="37">
-        <v>102</v>
-      </c>
-      <c r="AH9" s="37">
-        <f>1+68</f>
-        <v>69</v>
-      </c>
-      <c r="AI9" s="37">
-        <f>40+10+10+10</f>
-        <v>70</v>
-      </c>
-      <c r="AJ9" s="37">
-        <f>40+2+117</f>
-        <v>159</v>
-      </c>
-      <c r="AK9" s="37">
-        <f>3+35+30+15</f>
-        <v>83</v>
-      </c>
-      <c r="AL9" s="37">
-        <f>63+30</f>
-        <v>93</v>
-      </c>
-      <c r="AM9" s="17">
-        <v>33</v>
-      </c>
-      <c r="AN9" s="17">
-        <v>70</v>
-      </c>
-      <c r="AO9" s="17">
-        <f>2+45+90</f>
-        <v>137</v>
-      </c>
-      <c r="AP9" s="17">
-        <v>115</v>
-      </c>
-      <c r="AQ9" s="17">
-        <v>300</v>
-      </c>
-      <c r="AR9" s="17"/>
-      <c r="AS9" s="17"/>
-      <c r="AT9" s="17"/>
-      <c r="AU9" s="17"/>
-      <c r="AV9" s="17"/>
-      <c r="AW9" s="17"/>
-      <c r="AX9" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -7096,6 +7716,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="28867580-4592-47a8-a490-5f1990c83971" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6f4b1271-3e48-4fa4-9395-5da21e2ace23">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100711D466C73CDF643807BA842554885B1" ma:contentTypeVersion="16" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="8e1c5aa86496f51e6901b2b089969625">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6f4b1271-3e48-4fa4-9395-5da21e2ace23" xmlns:ns3="28867580-4592-47a8-a490-5f1990c83971" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8574df20a81ac730ef1e2c2435c9ef30" ns2:_="" ns3:_="">
     <xsd:import namespace="6f4b1271-3e48-4fa4-9395-5da21e2ace23"/>
@@ -7336,28 +7976,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="28867580-4592-47a8-a490-5f1990c83971" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6f4b1271-3e48-4fa4-9395-5da21e2ace23">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE668D04-A599-40BD-83B4-4E55F7C43B16}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ABBBF542-46E2-4D90-B593-1F03D9E2A95E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7365,5 +7985,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ABBBF542-46E2-4D90-B593-1F03D9E2A95E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE668D04-A599-40BD-83B4-4E55F7C43B16}"/>
 </file>
--- a/Planilla labores 26-27.xlsx
+++ b/Planilla labores 26-27.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30215"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0260B383-6954-4CCB-B8DD-3E85EC1BE408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8E5EEE44-6D32-495A-8A88-9D6C5818353F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Invierno" sheetId="1" r:id="rId1"/>
@@ -13,7 +13,7 @@
     <sheet name="Lluvias" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Invierno!$A$2:$AF$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Invierno!$A$2:$AI$53</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="169">
   <si>
     <t>Análisis suelo</t>
   </si>
@@ -149,16 +149,25 @@
     <t>Foszinc</t>
   </si>
   <si>
+    <t>CaSO4</t>
+  </si>
+  <si>
     <t>Origen P</t>
   </si>
   <si>
     <t>Origen K</t>
   </si>
   <si>
+    <t>Origen S</t>
+  </si>
+  <si>
     <t>Fecha (P)</t>
   </si>
   <si>
     <t>Fecha (k)</t>
+  </si>
+  <si>
+    <t>Fecha (S)</t>
   </si>
   <si>
     <t>Contratista</t>
@@ -1399,7 +1408,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DL104"/>
+  <dimension ref="A1:DO104"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.28515625" style="17" bestFit="1" customWidth="1"/>
@@ -1412,55 +1421,58 @@
     <col min="8" max="14" width="9.140625" style="17" hidden="1" customWidth="1"/>
     <col min="15" max="16" width="9.140625" style="17" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="11.7109375" style="17" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="15.5703125" style="17" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.85546875" style="17" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16.42578125" style="17" bestFit="1" customWidth="1"/>
-    <col min="22" max="30" width="9.140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.42578125" style="17" bestFit="1" customWidth="1"/>
-    <col min="32" max="35" width="9.140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="10.85546875" style="17" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.85546875" style="17" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="20.5703125" style="17" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="20.5703125" style="17" customWidth="1"/>
-    <col min="40" max="40" width="16" style="17" customWidth="1"/>
-    <col min="41" max="41" width="16" style="17" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="18" style="17" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="13.42578125" style="17" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="20.5703125" style="17" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="20.5703125" style="17" customWidth="1"/>
-    <col min="46" max="46" width="24.140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="9.140625" style="17"/>
-    <col min="48" max="48" width="16" style="17" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="18" style="17" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="13.42578125" style="17" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="20.5703125" style="17" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="24.140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="9.140625" style="17"/>
-    <col min="54" max="54" width="16" style="17" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="18" style="17" bestFit="1" customWidth="1"/>
-    <col min="56" max="58" width="18" style="17" customWidth="1"/>
-    <col min="59" max="59" width="9.140625" style="17"/>
-    <col min="60" max="60" width="11" style="17" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="12" style="17" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="12.28515625" style="17" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="10.42578125" style="17" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="9.7109375" style="17" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="16" style="17" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="9.140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="67" max="68" width="9.140625" style="17"/>
+    <col min="18" max="18" width="11.7109375" style="17" customWidth="1"/>
+    <col min="19" max="20" width="15.5703125" style="17" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.5703125" style="17" customWidth="1"/>
+    <col min="22" max="22" width="16.85546875" style="17" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16.42578125" style="17" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="16.42578125" style="17" customWidth="1"/>
+    <col min="25" max="33" width="9.140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="11.42578125" style="17" bestFit="1" customWidth="1"/>
+    <col min="35" max="38" width="9.140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="10.85546875" style="17" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="17" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="20.5703125" style="17" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="20.5703125" style="17" customWidth="1"/>
+    <col min="43" max="43" width="16" style="17" customWidth="1"/>
+    <col min="44" max="44" width="16" style="17" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="18" style="17" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="13.42578125" style="17" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="20.5703125" style="17" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="20.5703125" style="17" customWidth="1"/>
+    <col min="49" max="49" width="24.140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="9.140625" style="17"/>
+    <col min="51" max="51" width="16" style="17" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="18" style="17" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="13.42578125" style="17" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="20.5703125" style="17" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="24.140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="9.140625" style="17"/>
+    <col min="57" max="57" width="16" style="17" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="18" style="17" bestFit="1" customWidth="1"/>
+    <col min="59" max="61" width="18" style="17" customWidth="1"/>
+    <col min="62" max="62" width="9.140625" style="17"/>
+    <col min="63" max="63" width="11" style="17" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="12" style="17" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="12.28515625" style="17" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="10.42578125" style="17" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="9.7109375" style="17" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="16" style="17" bestFit="1" customWidth="1"/>
     <col min="69" max="69" width="9.140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="9.140625" style="17"/>
-    <col min="71" max="71" width="9.140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="9.140625" style="17"/>
-    <col min="73" max="77" width="9.140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="9.140625" style="17"/>
-    <col min="79" max="83" width="9.140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="84" max="84" width="9.140625" style="17"/>
-    <col min="85" max="116" width="9.140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="117" max="16384" width="9.140625" style="17"/>
+    <col min="70" max="71" width="9.140625" style="17"/>
+    <col min="72" max="72" width="9.140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="9.140625" style="17"/>
+    <col min="74" max="74" width="9.140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="9.140625" style="17"/>
+    <col min="76" max="80" width="9.140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="9.140625" style="17"/>
+    <col min="82" max="86" width="9.140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="87" max="87" width="9.140625" style="17"/>
+    <col min="88" max="119" width="9.140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="120" max="16384" width="9.140625" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:116" ht="21">
+    <row r="1" spans="1:119" ht="21">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
@@ -1486,138 +1498,141 @@
       <c r="T1" s="72"/>
       <c r="U1" s="72"/>
       <c r="V1" s="72"/>
-      <c r="W1" s="73" t="s">
+      <c r="W1" s="72"/>
+      <c r="X1" s="72"/>
+      <c r="Y1" s="72"/>
+      <c r="Z1" s="73" t="s">
         <v>2</v>
       </c>
-      <c r="X1" s="73"/>
-      <c r="Y1" s="73"/>
-      <c r="Z1" s="73"/>
       <c r="AA1" s="73"/>
       <c r="AB1" s="73"/>
       <c r="AC1" s="73"/>
       <c r="AD1" s="73"/>
       <c r="AE1" s="73"/>
       <c r="AF1" s="73"/>
-      <c r="AG1" s="79" t="s">
+      <c r="AG1" s="73"/>
+      <c r="AH1" s="73"/>
+      <c r="AI1" s="73"/>
+      <c r="AJ1" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="AH1" s="79"/>
-      <c r="AI1" s="79"/>
-      <c r="AJ1" s="79"/>
-      <c r="AK1" s="74" t="s">
+      <c r="AK1" s="79"/>
+      <c r="AL1" s="79"/>
+      <c r="AM1" s="79"/>
+      <c r="AN1" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="AL1" s="74"/>
-      <c r="AM1" s="74"/>
-      <c r="AN1" s="74"/>
       <c r="AO1" s="74"/>
-      <c r="AP1" s="75"/>
-      <c r="AQ1" s="76" t="s">
+      <c r="AP1" s="74"/>
+      <c r="AQ1" s="74"/>
+      <c r="AR1" s="74"/>
+      <c r="AS1" s="75"/>
+      <c r="AT1" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="AR1" s="77"/>
-      <c r="AS1" s="77"/>
-      <c r="AT1" s="77"/>
       <c r="AU1" s="77"/>
       <c r="AV1" s="77"/>
-      <c r="AW1" s="78"/>
-      <c r="AX1" s="59" t="s">
+      <c r="AW1" s="77"/>
+      <c r="AX1" s="77"/>
+      <c r="AY1" s="77"/>
+      <c r="AZ1" s="78"/>
+      <c r="BA1" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="AY1" s="60"/>
-      <c r="AZ1" s="60"/>
-      <c r="BA1" s="60"/>
       <c r="BB1" s="60"/>
-      <c r="BC1" s="61"/>
-      <c r="BD1" s="67" t="s">
+      <c r="BC1" s="60"/>
+      <c r="BD1" s="60"/>
+      <c r="BE1" s="60"/>
+      <c r="BF1" s="61"/>
+      <c r="BG1" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="BE1" s="68"/>
-      <c r="BF1" s="69"/>
-      <c r="BG1" s="62" t="s">
+      <c r="BH1" s="68"/>
+      <c r="BI1" s="69"/>
+      <c r="BJ1" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="BH1" s="63"/>
-      <c r="BI1" s="64" t="s">
+      <c r="BK1" s="63"/>
+      <c r="BL1" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="BJ1" s="64"/>
-      <c r="BK1" s="64"/>
-      <c r="BL1" s="64"/>
       <c r="BM1" s="64"/>
-      <c r="BN1" s="65" t="s">
+      <c r="BN1" s="64"/>
+      <c r="BO1" s="64"/>
+      <c r="BP1" s="64"/>
+      <c r="BQ1" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="BO1" s="52"/>
-      <c r="BP1" s="52"/>
-      <c r="BQ1" s="52"/>
       <c r="BR1" s="52"/>
-      <c r="BS1" s="66"/>
-      <c r="BT1" s="52" t="s">
+      <c r="BS1" s="52"/>
+      <c r="BT1" s="52"/>
+      <c r="BU1" s="52"/>
+      <c r="BV1" s="66"/>
+      <c r="BW1" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="BU1" s="52"/>
-      <c r="BV1" s="52"/>
-      <c r="BW1" s="52"/>
       <c r="BX1" s="52"/>
       <c r="BY1" s="52"/>
-      <c r="BZ1" s="52" t="s">
-        <v>12</v>
-      </c>
+      <c r="BZ1" s="52"/>
       <c r="CA1" s="52"/>
       <c r="CB1" s="52"/>
-      <c r="CC1" s="52"/>
+      <c r="CC1" s="52" t="s">
+        <v>12</v>
+      </c>
       <c r="CD1" s="52"/>
       <c r="CE1" s="52"/>
-      <c r="CF1" s="23"/>
-      <c r="CG1" s="53" t="s">
+      <c r="CF1" s="52"/>
+      <c r="CG1" s="52"/>
+      <c r="CH1" s="52"/>
+      <c r="CI1" s="23"/>
+      <c r="CJ1" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="CH1" s="53"/>
-      <c r="CI1" s="53"/>
-      <c r="CJ1" s="54" t="s">
+      <c r="CK1" s="53"/>
+      <c r="CL1" s="53"/>
+      <c r="CM1" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="CK1" s="54"/>
-      <c r="CL1" s="54"/>
-      <c r="CM1" s="54"/>
       <c r="CN1" s="54"/>
-      <c r="CO1" s="55" t="s">
+      <c r="CO1" s="54"/>
+      <c r="CP1" s="54"/>
+      <c r="CQ1" s="54"/>
+      <c r="CR1" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="CP1" s="55"/>
-      <c r="CQ1" s="55"/>
-      <c r="CR1" s="55"/>
       <c r="CS1" s="55"/>
       <c r="CT1" s="55"/>
       <c r="CU1" s="55"/>
       <c r="CV1" s="55"/>
       <c r="CW1" s="55"/>
       <c r="CX1" s="55"/>
-      <c r="CY1" s="56"/>
-      <c r="CZ1" s="57" t="s">
+      <c r="CY1" s="55"/>
+      <c r="CZ1" s="55"/>
+      <c r="DA1" s="55"/>
+      <c r="DB1" s="56"/>
+      <c r="DC1" s="57" t="s">
         <v>16</v>
       </c>
-      <c r="DA1" s="50"/>
-      <c r="DB1" s="58"/>
-      <c r="DC1" s="49" t="s">
+      <c r="DD1" s="50"/>
+      <c r="DE1" s="58"/>
+      <c r="DF1" s="49" t="s">
         <v>17</v>
-      </c>
-      <c r="DD1" s="50"/>
-      <c r="DE1" s="50"/>
-      <c r="DF1" s="50" t="s">
-        <v>18</v>
       </c>
       <c r="DG1" s="50"/>
       <c r="DH1" s="50"/>
-      <c r="DI1" s="51" t="s">
+      <c r="DI1" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="DJ1" s="50"/>
+      <c r="DK1" s="50"/>
+      <c r="DL1" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="DJ1" s="51"/>
-      <c r="DK1" s="51"/>
-      <c r="DL1" s="51"/>
-    </row>
-    <row r="2" spans="1:116" ht="21">
+      <c r="DM1" s="51"/>
+      <c r="DN1" s="51"/>
+      <c r="DO1" s="51"/>
+    </row>
+    <row r="2" spans="1:119" ht="21">
       <c r="A2" s="5" t="s">
         <v>20</v>
       </c>
@@ -1681,16 +1696,16 @@
       <c r="U2" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="V2" s="14" t="s">
+      <c r="V2" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="W2" s="15" t="s">
+      <c r="W2" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="X2" s="15" t="s">
+      <c r="X2" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="Y2" s="15" t="s">
+      <c r="Y2" s="14" t="s">
         <v>44</v>
       </c>
       <c r="Z2" s="15" t="s">
@@ -1709,205 +1724,205 @@
         <v>49</v>
       </c>
       <c r="AE2" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF2" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="AG2" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH2" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="AF2" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG2" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="AH2" s="36" t="s">
-        <v>49</v>
-      </c>
-      <c r="AI2" s="36" t="s">
+      <c r="AI2" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="AJ2" s="36" t="s">
+        <v>45</v>
+      </c>
+      <c r="AK2" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="AL2" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="AJ2" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="AK2" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="AL2" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="AM2" s="16" t="s">
-        <v>52</v>
+      <c r="AM2" s="36" t="s">
+        <v>44</v>
       </c>
       <c r="AN2" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="AO2" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="AP2" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="AQ2" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="AO2" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="AP2" s="16" t="s">
+      <c r="AR2" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="AS2" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="AT2" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="AQ2" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="AR2" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="AS2" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="AT2" s="20" t="s">
+      <c r="AU2" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="AU2" s="20" t="s">
+      <c r="AV2" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="AV2" s="20" t="s">
-        <v>41</v>
-      </c>
       <c r="AW2" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX2" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="AY2" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="AZ2" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="BA2" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="AX2" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="AY2" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="AZ2" s="21" t="s">
+      <c r="BB2" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="BA2" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="BB2" s="21" t="s">
-        <v>41</v>
-      </c>
       <c r="BC2" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="BD2" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="BD2" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="BE2" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="BF2" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="BE2" s="44" t="s">
+      <c r="BG2" s="44" t="s">
+        <v>59</v>
+      </c>
+      <c r="BH2" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="BF2" s="44" t="s">
-        <v>41</v>
-      </c>
-      <c r="BG2" s="27" t="s">
-        <v>57</v>
-      </c>
-      <c r="BH2" s="27" t="s">
-        <v>58</v>
-      </c>
-      <c r="BI2" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="BJ2" s="22" t="s">
+      <c r="BI2" s="44" t="s">
+        <v>44</v>
+      </c>
+      <c r="BJ2" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="BK2" s="22" t="s">
+      <c r="BK2" s="27" t="s">
         <v>61</v>
       </c>
       <c r="BL2" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="BM2" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="BN2" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="BO2" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="BM2" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="BN2" s="28" t="s">
-        <v>62</v>
-      </c>
-      <c r="BO2" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="BP2" s="29" t="s">
-        <v>52</v>
-      </c>
-      <c r="BQ2" s="29" t="s">
-        <v>61</v>
+      <c r="BP2" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="BQ2" s="28" t="s">
+        <v>65</v>
       </c>
       <c r="BR2" s="29" t="s">
         <v>25</v>
       </c>
       <c r="BS2" s="29" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="BT2" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="BU2" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="BU2" s="29" t="s">
-        <v>63</v>
-      </c>
       <c r="BV2" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="BW2" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="BX2" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="BY2" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="BZ2" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="BW2" s="29" t="s">
-        <v>61</v>
-      </c>
-      <c r="BX2" s="29" t="s">
+      <c r="CA2" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="BY2" s="29" t="s">
-        <v>41</v>
-      </c>
-      <c r="BZ2" s="29" t="s">
+      <c r="CB2" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="CC2" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="CA2" s="29" t="s">
-        <v>65</v>
-      </c>
-      <c r="CB2" s="29" t="s">
-        <v>66</v>
-      </c>
-      <c r="CC2" s="29" t="s">
-        <v>61</v>
-      </c>
       <c r="CD2" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="CE2" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="CF2" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="CG2" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="CE2" s="29" t="s">
-        <v>41</v>
-      </c>
-      <c r="CF2" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="CG2" s="31" t="s">
+      <c r="CH2" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="CI2" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="CJ2" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="CH2" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="CI2" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="CJ2" s="32" t="s">
+      <c r="CK2" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="CL2" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="CM2" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="CK2" s="32" t="s">
-        <v>68</v>
-      </c>
-      <c r="CL2" s="32" t="s">
-        <v>55</v>
-      </c>
-      <c r="CM2" s="32" t="s">
-        <v>69</v>
-      </c>
       <c r="CN2" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="CO2" s="33" t="s">
+        <v>71</v>
+      </c>
+      <c r="CO2" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="CP2" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="CQ2" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="CR2" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="CP2" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="CQ2" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="CR2" s="33" t="s">
-        <v>71</v>
-      </c>
       <c r="CS2" s="33" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="CT2" s="33" t="s">
         <v>73</v>
@@ -1925,51 +1940,60 @@
         <v>77</v>
       </c>
       <c r="CY2" s="33" t="s">
-        <v>41</v>
-      </c>
-      <c r="CZ2" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="DA2" s="24" t="s">
-        <v>68</v>
-      </c>
-      <c r="DB2" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="DC2" s="25" t="s">
-        <v>78</v>
+      <c r="CZ2" s="33" t="s">
+        <v>79</v>
+      </c>
+      <c r="DA2" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="DB2" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="DC2" s="24" t="s">
+        <v>81</v>
       </c>
       <c r="DD2" s="24" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="DE2" s="24" t="s">
         <v>25</v>
       </c>
       <c r="DF2" s="25" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="DG2" s="24" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="DH2" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="DI2" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="DJ2" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="DK2" s="26" t="s">
+      <c r="DI2" s="25" t="s">
         <v>81</v>
+      </c>
+      <c r="DJ2" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="DK2" s="24" t="s">
+        <v>25</v>
       </c>
       <c r="DL2" s="26" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="3" spans="1:116" ht="21">
+      <c r="DM2" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="DN2" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="DO2" s="26" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:119" ht="21">
       <c r="A3" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B3" s="6">
         <v>1</v>
@@ -1978,16 +2002,16 @@
         <v>203.49</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F3" s="45">
         <v>46157</v>
       </c>
       <c r="G3" s="46" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H3" s="46">
         <v>5</v>
@@ -2016,70 +2040,70 @@
       <c r="P3" s="17">
         <v>100</v>
       </c>
-      <c r="R3" s="17" t="s">
-        <v>87</v>
-      </c>
       <c r="S3" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="V3" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="W3" s="34">
+        <v>90</v>
+      </c>
+      <c r="T3" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="Y3" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z3" s="34">
         <v>3</v>
       </c>
-      <c r="X3" s="34">
+      <c r="AA3" s="34">
         <v>1</v>
       </c>
-      <c r="Y3" s="34">
+      <c r="AB3" s="34">
         <v>0.45</v>
       </c>
-      <c r="Z3" s="34"/>
-      <c r="AA3" s="34"/>
-      <c r="AB3" s="34"/>
       <c r="AC3" s="34"/>
       <c r="AD3" s="34"/>
-      <c r="AE3" s="47">
+      <c r="AE3" s="34"/>
+      <c r="AF3" s="34"/>
+      <c r="AG3" s="34"/>
+      <c r="AH3" s="47">
         <v>46158</v>
       </c>
-      <c r="AF3" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="AK3" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="AL3" s="34" t="s">
+      <c r="AI3" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="AN3" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="AO3" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="AP3" s="34">
+        <v>3.6</v>
+      </c>
+      <c r="AQ3" s="35">
+        <v>46167</v>
+      </c>
+      <c r="AR3" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="AS3" s="34" t="s">
+        <v>95</v>
+      </c>
+      <c r="BL3" s="17">
+        <v>98</v>
+      </c>
+      <c r="BN3" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="AM3" s="34">
-        <v>3.6</v>
-      </c>
-      <c r="AN3" s="35">
-        <v>46167</v>
-      </c>
-      <c r="AO3" s="34" t="s">
+      <c r="BP3" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="AP3" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="BI3" s="17">
+      <c r="CI3" s="17">
+        <f>+CE3+BY3+BS3+BL3</f>
         <v>98</v>
       </c>
-      <c r="BK3" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="BM3" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="CF3" s="17">
-        <f>+CB3+BV3+BP3+BI3</f>
-        <v>98</v>
-      </c>
-    </row>
-    <row r="4" spans="1:116" ht="21">
+    </row>
+    <row r="4" spans="1:119" ht="21">
       <c r="A4" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B4" s="6">
         <v>2</v>
@@ -2088,38 +2112,38 @@
         <v>215</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="AE4" s="18"/>
-      <c r="AK4" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="AL4" s="34" t="s">
-        <v>96</v>
-      </c>
-      <c r="AM4" s="34">
+        <v>97</v>
+      </c>
+      <c r="AH4" s="18"/>
+      <c r="AN4" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="AO4" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP4" s="34">
         <v>40</v>
       </c>
-      <c r="AN4" s="35">
+      <c r="AQ4" s="35">
         <v>46137</v>
       </c>
-      <c r="AO4" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="AP4" s="34" t="s">
-        <v>98</v>
-      </c>
-      <c r="CF4" s="17">
-        <f t="shared" ref="CF4:CF53" si="0">+CB4+BV4+BP4+BI4</f>
+      <c r="AR4" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="AS4" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="CI4" s="17">
+        <f t="shared" ref="CI4:CI53" si="0">+CE4+BY4+BS4+BL4</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:116" ht="21">
+    <row r="5" spans="1:119" ht="21">
       <c r="A5" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B5" s="6">
         <v>3</v>
@@ -2128,38 +2152,38 @@
         <v>46.12</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="AE5" s="18"/>
-      <c r="AK5" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="AL5" s="34" t="s">
-        <v>96</v>
-      </c>
-      <c r="AM5" s="34">
+        <v>97</v>
+      </c>
+      <c r="AH5" s="18"/>
+      <c r="AN5" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="AO5" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP5" s="34">
         <v>40</v>
       </c>
-      <c r="AN5" s="35">
+      <c r="AQ5" s="35">
         <v>46137</v>
       </c>
-      <c r="AO5" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="AP5" s="34" t="s">
-        <v>98</v>
-      </c>
-      <c r="CF5" s="17">
+      <c r="AR5" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="AS5" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="CI5" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:116" ht="21">
+    <row r="6" spans="1:119" ht="21">
       <c r="A6" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B6" s="6">
         <v>7</v>
@@ -2168,38 +2192,38 @@
         <v>24.03</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="AE6" s="18"/>
-      <c r="AK6" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="AL6" s="34" t="s">
-        <v>96</v>
-      </c>
-      <c r="AM6" s="34">
+        <v>97</v>
+      </c>
+      <c r="AH6" s="18"/>
+      <c r="AN6" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="AO6" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP6" s="34">
         <v>40</v>
       </c>
-      <c r="AN6" s="35">
+      <c r="AQ6" s="35">
         <v>46137</v>
       </c>
-      <c r="AO6" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="AP6" s="34" t="s">
-        <v>98</v>
-      </c>
-      <c r="CF6" s="17">
+      <c r="AR6" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="AS6" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="CI6" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:116" ht="21">
+    <row r="7" spans="1:119" ht="21">
       <c r="A7" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B7" s="6">
         <v>8</v>
@@ -2208,38 +2232,38 @@
         <v>22.55</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="AE7" s="18"/>
-      <c r="AK7" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="AL7" s="34" t="s">
-        <v>96</v>
-      </c>
-      <c r="AM7" s="34">
+        <v>97</v>
+      </c>
+      <c r="AH7" s="18"/>
+      <c r="AN7" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="AO7" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP7" s="34">
         <v>40</v>
       </c>
-      <c r="AN7" s="35">
+      <c r="AQ7" s="35">
         <v>46137</v>
       </c>
-      <c r="AO7" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="AP7" s="34" t="s">
-        <v>98</v>
-      </c>
-      <c r="CF7" s="17">
+      <c r="AR7" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="AS7" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="CI7" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:116" ht="21">
+    <row r="8" spans="1:119" ht="21">
       <c r="A8" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B8" s="6">
         <v>9</v>
@@ -2248,38 +2272,38 @@
         <v>62.73</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="AE8" s="18"/>
-      <c r="AK8" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="AL8" s="34" t="s">
-        <v>96</v>
-      </c>
-      <c r="AM8" s="34">
+        <v>97</v>
+      </c>
+      <c r="AH8" s="18"/>
+      <c r="AN8" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="AO8" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP8" s="34">
         <v>40</v>
       </c>
-      <c r="AN8" s="35">
+      <c r="AQ8" s="35">
         <v>46137</v>
       </c>
-      <c r="AO8" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="AP8" s="34" t="s">
-        <v>98</v>
-      </c>
-      <c r="CF8" s="17">
+      <c r="AR8" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="AS8" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="CI8" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:116" ht="21">
+    <row r="9" spans="1:119" ht="21">
       <c r="A9" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B9" s="6">
         <v>10</v>
@@ -2288,38 +2312,38 @@
         <v>29.7</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="AE9" s="18"/>
-      <c r="AK9" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="AL9" s="34" t="s">
-        <v>96</v>
-      </c>
-      <c r="AM9" s="34">
+        <v>97</v>
+      </c>
+      <c r="AH9" s="18"/>
+      <c r="AN9" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="AO9" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP9" s="34">
         <v>40</v>
       </c>
-      <c r="AN9" s="35">
+      <c r="AQ9" s="35">
         <v>46137</v>
       </c>
-      <c r="AO9" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="AP9" s="34" t="s">
-        <v>98</v>
-      </c>
-      <c r="CF9" s="17">
+      <c r="AR9" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="AS9" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="CI9" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:116" ht="21">
+    <row r="10" spans="1:119" ht="21">
       <c r="A10" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B10" s="6">
         <v>11</v>
@@ -2328,38 +2352,38 @@
         <v>270.44</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="AE10" s="18"/>
-      <c r="AK10" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="AL10" s="34" t="s">
-        <v>96</v>
-      </c>
-      <c r="AM10" s="34">
+        <v>97</v>
+      </c>
+      <c r="AH10" s="18"/>
+      <c r="AN10" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="AO10" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP10" s="34">
         <v>40</v>
       </c>
-      <c r="AN10" s="35">
+      <c r="AQ10" s="35">
         <v>46137</v>
       </c>
-      <c r="AO10" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="AP10" s="34" t="s">
-        <v>98</v>
-      </c>
-      <c r="CF10" s="17">
+      <c r="AR10" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="AS10" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="CI10" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:116" ht="21">
+    <row r="11" spans="1:119" ht="21">
       <c r="A11" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B11" s="6">
         <v>12</v>
@@ -2368,38 +2392,38 @@
         <v>64.25</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="AE11" s="18"/>
-      <c r="AK11" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="AL11" s="34" t="s">
-        <v>96</v>
-      </c>
-      <c r="AM11" s="34">
+        <v>97</v>
+      </c>
+      <c r="AH11" s="18"/>
+      <c r="AN11" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="AO11" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP11" s="34">
         <v>40</v>
       </c>
-      <c r="AN11" s="35">
+      <c r="AQ11" s="35">
         <v>46137</v>
       </c>
-      <c r="AO11" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="AP11" s="34" t="s">
-        <v>98</v>
-      </c>
-      <c r="CF11" s="17">
+      <c r="AR11" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="AS11" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="CI11" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:116" ht="21">
+    <row r="12" spans="1:119" ht="21">
       <c r="A12" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B12" s="6">
         <v>13</v>
@@ -2408,38 +2432,38 @@
         <v>29.89</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="AE12" s="18"/>
-      <c r="AK12" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="AL12" s="34" t="s">
-        <v>96</v>
-      </c>
-      <c r="AM12" s="34">
+        <v>97</v>
+      </c>
+      <c r="AH12" s="18"/>
+      <c r="AN12" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="AO12" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP12" s="34">
         <v>40</v>
       </c>
-      <c r="AN12" s="35">
+      <c r="AQ12" s="35">
         <v>46137</v>
       </c>
-      <c r="AO12" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="AP12" s="34" t="s">
-        <v>98</v>
-      </c>
-      <c r="CF12" s="17">
+      <c r="AR12" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="AS12" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="CI12" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:116" ht="21">
+    <row r="13" spans="1:119" ht="21">
       <c r="A13" s="6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B13" s="6">
         <v>6</v>
@@ -2448,38 +2472,38 @@
         <v>52.63</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="AE13" s="18"/>
-      <c r="AK13" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="AL13" s="34" t="s">
-        <v>96</v>
-      </c>
-      <c r="AM13" s="34">
+        <v>97</v>
+      </c>
+      <c r="AH13" s="18"/>
+      <c r="AN13" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="AO13" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP13" s="34">
         <v>40</v>
       </c>
-      <c r="AN13" s="35">
+      <c r="AQ13" s="35">
         <v>46139</v>
       </c>
-      <c r="AO13" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="AP13" s="34" t="s">
-        <v>98</v>
-      </c>
-      <c r="CF13" s="17">
+      <c r="AR13" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="AS13" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="CI13" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:116" ht="21">
+    <row r="14" spans="1:119" ht="21">
       <c r="A14" s="6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B14" s="6">
         <v>7</v>
@@ -2488,16 +2512,16 @@
         <v>60.61</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F14" s="19">
         <v>46175</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H14" s="17">
         <v>9</v>
@@ -2526,68 +2550,68 @@
       <c r="P14" s="17">
         <v>100</v>
       </c>
-      <c r="R14" s="17" t="s">
-        <v>87</v>
-      </c>
       <c r="S14" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="V14" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="W14" s="34">
+        <v>90</v>
+      </c>
+      <c r="T14" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="Y14" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z14" s="34">
         <v>3</v>
       </c>
-      <c r="X14" s="34"/>
-      <c r="Y14" s="34"/>
-      <c r="Z14" s="34"/>
       <c r="AA14" s="34"/>
-      <c r="AB14" s="34">
-        <v>0.35</v>
-      </c>
+      <c r="AB14" s="34"/>
       <c r="AC14" s="34"/>
       <c r="AD14" s="34"/>
-      <c r="AE14" s="47">
+      <c r="AE14" s="34">
+        <v>0.35</v>
+      </c>
+      <c r="AF14" s="34"/>
+      <c r="AG14" s="34"/>
+      <c r="AH14" s="47">
         <v>46174</v>
       </c>
-      <c r="AF14" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="AK14" s="34" t="s">
-        <v>101</v>
-      </c>
-      <c r="AL14" s="34" t="s">
+      <c r="AI14" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="AN14" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="AO14" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="AP14" s="34">
+        <v>135</v>
+      </c>
+      <c r="AQ14" s="35">
+        <v>46176</v>
+      </c>
+      <c r="AR14" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="AS14" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="BL14" s="17">
+        <v>94</v>
+      </c>
+      <c r="BN14" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="AM14" s="34">
-        <v>135</v>
-      </c>
-      <c r="AN14" s="35">
-        <v>46176</v>
-      </c>
-      <c r="AO14" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="AP14" s="34" t="s">
-        <v>102</v>
-      </c>
-      <c r="BI14" s="17">
-        <v>94</v>
-      </c>
-      <c r="BK14" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="BM14" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="CF14" s="17">
+      <c r="BP14" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="CI14" s="17">
         <f t="shared" si="0"/>
         <v>94</v>
       </c>
     </row>
-    <row r="15" spans="1:116" ht="21">
+    <row r="15" spans="1:119" ht="21">
       <c r="A15" s="6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B15" s="6">
         <v>11</v>
@@ -2596,16 +2620,16 @@
         <v>56.69</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F15" s="19">
         <v>46175</v>
       </c>
       <c r="G15" s="17" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H15" s="17">
         <v>6</v>
@@ -2634,68 +2658,68 @@
       <c r="P15" s="17">
         <v>100</v>
       </c>
-      <c r="R15" s="17" t="s">
-        <v>87</v>
-      </c>
       <c r="S15" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="V15" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="W15" s="34">
+        <v>90</v>
+      </c>
+      <c r="T15" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="Y15" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z15" s="34">
         <v>3</v>
       </c>
-      <c r="X15" s="34"/>
-      <c r="Y15" s="34"/>
-      <c r="Z15" s="34"/>
       <c r="AA15" s="34"/>
-      <c r="AB15" s="34">
-        <v>0.35</v>
-      </c>
+      <c r="AB15" s="34"/>
       <c r="AC15" s="34"/>
       <c r="AD15" s="34"/>
-      <c r="AE15" s="47">
+      <c r="AE15" s="34">
+        <v>0.35</v>
+      </c>
+      <c r="AF15" s="34"/>
+      <c r="AG15" s="34"/>
+      <c r="AH15" s="47">
         <v>46174</v>
       </c>
-      <c r="AF15" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="AK15" s="34" t="s">
-        <v>101</v>
-      </c>
-      <c r="AL15" s="34" t="s">
+      <c r="AI15" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="AN15" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="AO15" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="AP15" s="34">
+        <v>135</v>
+      </c>
+      <c r="AQ15" s="35">
+        <v>46172</v>
+      </c>
+      <c r="AR15" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="AS15" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="BL15" s="17">
+        <v>94</v>
+      </c>
+      <c r="BN15" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="AM15" s="34">
-        <v>135</v>
-      </c>
-      <c r="AN15" s="35">
-        <v>46172</v>
-      </c>
-      <c r="AO15" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="AP15" s="34" t="s">
-        <v>102</v>
-      </c>
-      <c r="BI15" s="17">
-        <v>94</v>
-      </c>
-      <c r="BK15" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="BM15" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="CF15" s="17">
+      <c r="BP15" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="CI15" s="17">
         <f t="shared" si="0"/>
         <v>94</v>
       </c>
     </row>
-    <row r="16" spans="1:116" ht="21">
+    <row r="16" spans="1:119" ht="21">
       <c r="A16" s="6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B16" s="6">
         <v>12</v>
@@ -2704,16 +2728,16 @@
         <v>49.78</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F16" s="19">
         <v>46175</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H16" s="17">
         <v>6</v>
@@ -2742,68 +2766,68 @@
       <c r="P16" s="17">
         <v>100</v>
       </c>
-      <c r="R16" s="17" t="s">
-        <v>87</v>
-      </c>
       <c r="S16" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="V16" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="W16" s="34">
+        <v>90</v>
+      </c>
+      <c r="T16" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="Y16" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z16" s="34">
         <v>3</v>
       </c>
-      <c r="X16" s="34"/>
-      <c r="Y16" s="34"/>
-      <c r="Z16" s="34"/>
       <c r="AA16" s="34"/>
-      <c r="AB16" s="34">
-        <v>0.35</v>
-      </c>
+      <c r="AB16" s="34"/>
       <c r="AC16" s="34"/>
       <c r="AD16" s="34"/>
-      <c r="AE16" s="47">
+      <c r="AE16" s="34">
+        <v>0.35</v>
+      </c>
+      <c r="AF16" s="34"/>
+      <c r="AG16" s="34"/>
+      <c r="AH16" s="47">
         <v>46174</v>
       </c>
-      <c r="AF16" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="AK16" s="34" t="s">
-        <v>101</v>
-      </c>
-      <c r="AL16" s="34" t="s">
+      <c r="AI16" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="AN16" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="AO16" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="AP16" s="34">
+        <v>135</v>
+      </c>
+      <c r="AQ16" s="35">
+        <v>46173</v>
+      </c>
+      <c r="AR16" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="AS16" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="BL16" s="17">
+        <v>94</v>
+      </c>
+      <c r="BN16" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="AM16" s="34">
-        <v>135</v>
-      </c>
-      <c r="AN16" s="35">
-        <v>46173</v>
-      </c>
-      <c r="AO16" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="AP16" s="34" t="s">
-        <v>102</v>
-      </c>
-      <c r="BI16" s="17">
-        <v>94</v>
-      </c>
-      <c r="BK16" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="BM16" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="CF16" s="17">
+      <c r="BP16" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="CI16" s="17">
         <f t="shared" si="0"/>
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:84" ht="21">
+    <row r="17" spans="1:87" ht="21">
       <c r="A17" s="6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B17" s="6">
         <v>13</v>
@@ -2812,16 +2836,16 @@
         <v>26.67</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F17" s="19">
         <v>46175</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H17" s="17">
         <v>6</v>
@@ -2850,68 +2874,68 @@
       <c r="P17" s="17">
         <v>100</v>
       </c>
-      <c r="R17" s="17" t="s">
-        <v>87</v>
-      </c>
       <c r="S17" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="V17" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="W17" s="34">
+        <v>90</v>
+      </c>
+      <c r="T17" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="Y17" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z17" s="34">
         <v>3</v>
       </c>
-      <c r="X17" s="34"/>
-      <c r="Y17" s="34"/>
-      <c r="Z17" s="34"/>
       <c r="AA17" s="34"/>
-      <c r="AB17" s="34">
-        <v>0.35</v>
-      </c>
+      <c r="AB17" s="34"/>
       <c r="AC17" s="34"/>
       <c r="AD17" s="34"/>
-      <c r="AE17" s="47">
+      <c r="AE17" s="34">
+        <v>0.35</v>
+      </c>
+      <c r="AF17" s="34"/>
+      <c r="AG17" s="34"/>
+      <c r="AH17" s="47">
         <v>46174</v>
       </c>
-      <c r="AF17" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="AK17" s="34" t="s">
-        <v>101</v>
-      </c>
-      <c r="AL17" s="34" t="s">
+      <c r="AI17" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="AN17" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="AO17" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="AP17" s="34">
+        <v>135</v>
+      </c>
+      <c r="AQ17" s="35">
+        <v>46174</v>
+      </c>
+      <c r="AR17" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="AS17" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="BL17" s="17">
+        <v>94</v>
+      </c>
+      <c r="BN17" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="AM17" s="34">
-        <v>135</v>
-      </c>
-      <c r="AN17" s="35">
-        <v>46174</v>
-      </c>
-      <c r="AO17" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="AP17" s="34" t="s">
-        <v>102</v>
-      </c>
-      <c r="BI17" s="17">
-        <v>94</v>
-      </c>
-      <c r="BK17" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="BM17" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="CF17" s="17">
+      <c r="BP17" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="CI17" s="17">
         <f t="shared" si="0"/>
         <v>94</v>
       </c>
     </row>
-    <row r="18" spans="1:84" ht="21">
+    <row r="18" spans="1:87" ht="21">
       <c r="A18" s="6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B18" s="6">
         <v>14</v>
@@ -2920,16 +2944,16 @@
         <v>33.96</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F18" s="19">
         <v>46175</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H18" s="17">
         <v>7</v>
@@ -2958,78 +2982,78 @@
       <c r="P18" s="17">
         <v>100</v>
       </c>
-      <c r="R18" s="17" t="s">
-        <v>87</v>
-      </c>
       <c r="S18" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="V18" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="W18" s="34">
+        <v>90</v>
+      </c>
+      <c r="T18" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="Y18" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z18" s="34">
         <v>3</v>
       </c>
-      <c r="X18" s="34"/>
-      <c r="Y18" s="34"/>
-      <c r="Z18" s="34"/>
       <c r="AA18" s="34"/>
-      <c r="AB18" s="34">
-        <v>0.35</v>
-      </c>
+      <c r="AB18" s="34"/>
       <c r="AC18" s="34"/>
       <c r="AD18" s="34"/>
-      <c r="AE18" s="47">
+      <c r="AE18" s="34">
+        <v>0.35</v>
+      </c>
+      <c r="AF18" s="34"/>
+      <c r="AG18" s="34"/>
+      <c r="AH18" s="47">
         <v>46174</v>
       </c>
-      <c r="AF18" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="AG18" s="34"/>
-      <c r="AH18" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="AI18" s="35">
+      <c r="AI18" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="AJ18" s="34"/>
+      <c r="AK18" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="AL18" s="35">
         <v>46164</v>
       </c>
-      <c r="AJ18" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="AK18" s="48" t="s">
-        <v>104</v>
-      </c>
-      <c r="AL18" s="48" t="s">
+      <c r="AM18" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="AN18" s="48" t="s">
+        <v>107</v>
+      </c>
+      <c r="AO18" s="48" t="s">
+        <v>108</v>
+      </c>
+      <c r="AP18" s="34">
+        <v>135</v>
+      </c>
+      <c r="AQ18" s="35">
+        <v>46175</v>
+      </c>
+      <c r="AR18" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="AS18" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="AM18" s="34">
-        <v>135</v>
-      </c>
-      <c r="AN18" s="35">
-        <v>46175</v>
-      </c>
-      <c r="AO18" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="AP18" s="34" t="s">
-        <v>102</v>
-      </c>
-      <c r="BI18" s="17">
+      <c r="BL18" s="17">
         <v>94</v>
       </c>
-      <c r="BK18" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="BM18" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="CF18" s="17">
+      <c r="BN18" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="BP18" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="CI18" s="17">
         <f t="shared" si="0"/>
         <v>94</v>
       </c>
     </row>
-    <row r="19" spans="1:84" ht="21">
+    <row r="19" spans="1:87" ht="21">
       <c r="A19" s="6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B19" s="6">
         <v>16</v>
@@ -3038,16 +3062,16 @@
         <v>91.46</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F19" s="19">
         <v>46175</v>
       </c>
       <c r="G19" s="17" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H19" s="17">
         <v>7</v>
@@ -3076,78 +3100,78 @@
       <c r="P19" s="17">
         <v>100</v>
       </c>
-      <c r="R19" s="17" t="s">
-        <v>87</v>
-      </c>
       <c r="S19" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="V19" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="W19" s="34">
+        <v>90</v>
+      </c>
+      <c r="T19" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="Y19" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z19" s="34">
         <v>3</v>
       </c>
-      <c r="X19" s="34"/>
-      <c r="Y19" s="34"/>
-      <c r="Z19" s="34"/>
       <c r="AA19" s="34"/>
-      <c r="AB19" s="34">
-        <v>0.35</v>
-      </c>
+      <c r="AB19" s="34"/>
       <c r="AC19" s="34"/>
       <c r="AD19" s="34"/>
-      <c r="AE19" s="47">
+      <c r="AE19" s="34">
+        <v>0.35</v>
+      </c>
+      <c r="AF19" s="34"/>
+      <c r="AG19" s="34"/>
+      <c r="AH19" s="47">
         <v>46174</v>
       </c>
-      <c r="AF19" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="AG19" s="34"/>
-      <c r="AH19" s="34">
+      <c r="AI19" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="AJ19" s="34"/>
+      <c r="AK19" s="34">
         <v>2.5</v>
       </c>
-      <c r="AI19" s="35">
+      <c r="AL19" s="35">
         <v>46164</v>
       </c>
-      <c r="AJ19" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="AK19" s="48" t="s">
-        <v>106</v>
-      </c>
-      <c r="AL19" s="48" t="s">
-        <v>107</v>
-      </c>
-      <c r="AM19" s="34">
+      <c r="AM19" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="AN19" s="48" t="s">
+        <v>109</v>
+      </c>
+      <c r="AO19" s="48" t="s">
+        <v>110</v>
+      </c>
+      <c r="AP19" s="34">
         <v>135</v>
       </c>
-      <c r="AN19" s="35">
+      <c r="AQ19" s="35">
         <v>46176</v>
       </c>
-      <c r="AO19" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="AP19" s="34" t="s">
-        <v>102</v>
-      </c>
-      <c r="BI19" s="17">
+      <c r="AR19" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="AS19" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="BL19" s="17">
         <v>94</v>
       </c>
-      <c r="BK19" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="BM19" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="CF19" s="17">
+      <c r="BN19" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="BP19" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="CI19" s="17">
         <f t="shared" si="0"/>
         <v>94</v>
       </c>
     </row>
-    <row r="20" spans="1:84" ht="21">
+    <row r="20" spans="1:87" ht="21">
       <c r="A20" s="6" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B20" s="6">
         <v>1</v>
@@ -3156,16 +3180,16 @@
         <v>58.59</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F20" s="45">
         <v>46157</v>
       </c>
       <c r="G20" s="46" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H20" s="46">
         <v>5</v>
@@ -3195,80 +3219,83 @@
         <v>150</v>
       </c>
       <c r="Q20" s="34"/>
-      <c r="R20" s="34" t="s">
-        <v>87</v>
-      </c>
+      <c r="R20" s="34"/>
       <c r="S20" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="T20" s="35">
+        <v>90</v>
+      </c>
+      <c r="T20" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="U20" s="34"/>
+      <c r="V20" s="35">
         <v>46172</v>
       </c>
-      <c r="U20" s="35">
+      <c r="W20" s="35">
         <v>46172</v>
       </c>
-      <c r="V20" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="W20" s="34">
+      <c r="X20" s="35"/>
+      <c r="Y20" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z20" s="34">
         <v>3</v>
       </c>
-      <c r="X20" s="34">
+      <c r="AA20" s="34">
         <v>1</v>
       </c>
-      <c r="Y20" s="34">
+      <c r="AB20" s="34">
         <v>0.45</v>
       </c>
-      <c r="Z20" s="34"/>
-      <c r="AA20" s="34"/>
-      <c r="AB20" s="34"/>
       <c r="AC20" s="34"/>
       <c r="AD20" s="34"/>
-      <c r="AE20" s="47">
+      <c r="AE20" s="34"/>
+      <c r="AF20" s="34"/>
+      <c r="AG20" s="34"/>
+      <c r="AH20" s="47">
         <v>46159</v>
       </c>
-      <c r="AF20" s="34" t="s">
+      <c r="AI20" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN20" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="AO20" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="AP20" s="34">
+        <v>3.8</v>
+      </c>
+      <c r="AQ20" s="35">
+        <v>46160</v>
+      </c>
+      <c r="AR20" s="34" t="s">
+        <v>112</v>
+      </c>
+      <c r="AS20" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="BL20" s="34">
+        <v>110</v>
+      </c>
+      <c r="BM20" s="34"/>
+      <c r="BN20" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="BO20" s="35">
+        <v>46172</v>
+      </c>
+      <c r="BP20" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="AK20" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="AL20" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="AM20" s="34">
-        <v>3.8</v>
-      </c>
-      <c r="AN20" s="35">
-        <v>46160</v>
-      </c>
-      <c r="AO20" s="34" t="s">
-        <v>109</v>
-      </c>
-      <c r="AP20" s="34" t="s">
-        <v>110</v>
-      </c>
-      <c r="BI20" s="34">
-        <v>110</v>
-      </c>
-      <c r="BJ20" s="34"/>
-      <c r="BK20" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="BL20" s="35">
-        <v>46172</v>
-      </c>
-      <c r="BM20" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="CF20" s="17">
+      <c r="CI20" s="17">
         <f t="shared" si="0"/>
         <v>110</v>
       </c>
     </row>
-    <row r="21" spans="1:84" ht="21">
+    <row r="21" spans="1:87" ht="21">
       <c r="A21" s="6" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B21" s="6">
         <v>2</v>
@@ -3277,16 +3304,16 @@
         <v>40.99</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F21" s="45">
         <v>46157</v>
       </c>
       <c r="G21" s="46" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H21" s="46">
         <v>4</v>
@@ -3316,80 +3343,83 @@
         <v>150</v>
       </c>
       <c r="Q21" s="34"/>
-      <c r="R21" s="34" t="s">
-        <v>87</v>
-      </c>
+      <c r="R21" s="34"/>
       <c r="S21" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="T21" s="35">
+        <v>90</v>
+      </c>
+      <c r="T21" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="U21" s="34"/>
+      <c r="V21" s="35">
         <v>46172</v>
       </c>
-      <c r="U21" s="35">
+      <c r="W21" s="35">
         <v>46172</v>
       </c>
-      <c r="V21" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="W21" s="34">
+      <c r="X21" s="35"/>
+      <c r="Y21" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z21" s="34">
         <v>3</v>
       </c>
-      <c r="X21" s="34">
+      <c r="AA21" s="34">
         <v>1</v>
       </c>
-      <c r="Y21" s="34">
+      <c r="AB21" s="34">
         <v>0.45</v>
       </c>
-      <c r="Z21" s="34"/>
-      <c r="AA21" s="34"/>
-      <c r="AB21" s="34"/>
       <c r="AC21" s="34"/>
       <c r="AD21" s="34"/>
-      <c r="AE21" s="47">
+      <c r="AE21" s="34"/>
+      <c r="AF21" s="34"/>
+      <c r="AG21" s="34"/>
+      <c r="AH21" s="47">
         <v>46159</v>
       </c>
-      <c r="AF21" s="34" t="s">
+      <c r="AI21" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN21" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="AO21" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="AP21" s="34">
+        <v>3.8</v>
+      </c>
+      <c r="AQ21" s="35">
+        <v>46162</v>
+      </c>
+      <c r="AR21" s="34" t="s">
+        <v>112</v>
+      </c>
+      <c r="AS21" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="BL21" s="34">
+        <v>110</v>
+      </c>
+      <c r="BM21" s="34"/>
+      <c r="BN21" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="BO21" s="35">
+        <v>46172</v>
+      </c>
+      <c r="BP21" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="AK21" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="AL21" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="AM21" s="34">
-        <v>3.8</v>
-      </c>
-      <c r="AN21" s="35">
-        <v>46162</v>
-      </c>
-      <c r="AO21" s="34" t="s">
-        <v>109</v>
-      </c>
-      <c r="AP21" s="34" t="s">
-        <v>110</v>
-      </c>
-      <c r="BI21" s="34">
-        <v>110</v>
-      </c>
-      <c r="BJ21" s="34"/>
-      <c r="BK21" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="BL21" s="35">
-        <v>46172</v>
-      </c>
-      <c r="BM21" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="CF21" s="17">
+      <c r="CI21" s="17">
         <f t="shared" si="0"/>
         <v>110</v>
       </c>
     </row>
-    <row r="22" spans="1:84" ht="21">
+    <row r="22" spans="1:87" ht="21">
       <c r="A22" s="6" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B22" s="6">
         <v>3</v>
@@ -3398,16 +3428,16 @@
         <v>63.11</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F22" s="45">
         <v>46157</v>
       </c>
       <c r="G22" s="46" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H22" s="46">
         <v>4</v>
@@ -3437,80 +3467,83 @@
         <v>150</v>
       </c>
       <c r="Q22" s="34"/>
-      <c r="R22" s="34" t="s">
-        <v>87</v>
-      </c>
+      <c r="R22" s="34"/>
       <c r="S22" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="T22" s="35">
+        <v>90</v>
+      </c>
+      <c r="T22" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="U22" s="34"/>
+      <c r="V22" s="35">
         <v>46172</v>
       </c>
-      <c r="U22" s="35">
+      <c r="W22" s="35">
         <v>46172</v>
       </c>
-      <c r="V22" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="W22" s="34">
+      <c r="X22" s="35"/>
+      <c r="Y22" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z22" s="34">
         <v>3</v>
       </c>
-      <c r="X22" s="34">
+      <c r="AA22" s="34">
         <v>1</v>
       </c>
-      <c r="Y22" s="34">
+      <c r="AB22" s="34">
         <v>0.45</v>
       </c>
-      <c r="Z22" s="34"/>
-      <c r="AA22" s="34"/>
-      <c r="AB22" s="34"/>
       <c r="AC22" s="34"/>
       <c r="AD22" s="34"/>
-      <c r="AE22" s="47">
+      <c r="AE22" s="34"/>
+      <c r="AF22" s="34"/>
+      <c r="AG22" s="34"/>
+      <c r="AH22" s="47">
         <v>46159</v>
       </c>
-      <c r="AF22" s="34" t="s">
+      <c r="AI22" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN22" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="AO22" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="AP22" s="34">
+        <v>4</v>
+      </c>
+      <c r="AQ22" s="35">
+        <v>46160</v>
+      </c>
+      <c r="AR22" s="34" t="s">
+        <v>112</v>
+      </c>
+      <c r="AS22" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="BL22" s="34">
+        <v>110</v>
+      </c>
+      <c r="BM22" s="34"/>
+      <c r="BN22" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="BO22" s="35">
+        <v>46172</v>
+      </c>
+      <c r="BP22" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="AK22" s="34" t="s">
-        <v>111</v>
-      </c>
-      <c r="AL22" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="AM22" s="34">
-        <v>4</v>
-      </c>
-      <c r="AN22" s="35">
-        <v>46160</v>
-      </c>
-      <c r="AO22" s="34" t="s">
-        <v>109</v>
-      </c>
-      <c r="AP22" s="34" t="s">
-        <v>110</v>
-      </c>
-      <c r="BI22" s="34">
-        <v>110</v>
-      </c>
-      <c r="BJ22" s="34"/>
-      <c r="BK22" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="BL22" s="35">
-        <v>46172</v>
-      </c>
-      <c r="BM22" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="CF22" s="17">
+      <c r="CI22" s="17">
         <f t="shared" si="0"/>
         <v>110</v>
       </c>
     </row>
-    <row r="23" spans="1:84" ht="21">
+    <row r="23" spans="1:87" ht="21">
       <c r="A23" s="6" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B23" s="6">
         <v>4</v>
@@ -3519,16 +3552,16 @@
         <v>71.48</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F23" s="45">
         <v>46157</v>
       </c>
       <c r="G23" s="46" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H23" s="46">
         <v>4</v>
@@ -3558,81 +3591,84 @@
         <v>150</v>
       </c>
       <c r="Q23" s="34"/>
-      <c r="R23" s="34" t="s">
-        <v>87</v>
-      </c>
+      <c r="R23" s="34"/>
       <c r="S23" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="T23" s="35">
+        <v>90</v>
+      </c>
+      <c r="T23" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="U23" s="34"/>
+      <c r="V23" s="35">
         <v>46172</v>
       </c>
-      <c r="U23" s="35">
+      <c r="W23" s="35">
         <v>46172</v>
       </c>
-      <c r="V23" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="W23" s="34">
+      <c r="X23" s="35"/>
+      <c r="Y23" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z23" s="34">
         <v>3</v>
       </c>
-      <c r="X23" s="34">
+      <c r="AA23" s="34">
         <v>1</v>
       </c>
-      <c r="Y23" s="34">
+      <c r="AB23" s="34">
         <v>0.45</v>
       </c>
-      <c r="Z23" s="34"/>
-      <c r="AA23" s="34"/>
-      <c r="AB23" s="34"/>
       <c r="AC23" s="34"/>
       <c r="AD23" s="34"/>
-      <c r="AE23" s="47">
+      <c r="AE23" s="34"/>
+      <c r="AF23" s="34"/>
+      <c r="AG23" s="34"/>
+      <c r="AH23" s="47">
         <v>46159</v>
       </c>
-      <c r="AF23" s="34" t="s">
+      <c r="AI23" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="AL23" s="19"/>
+      <c r="AN23" s="34" t="s">
+        <v>115</v>
+      </c>
+      <c r="AO23" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="AP23" s="34">
+        <v>4</v>
+      </c>
+      <c r="AQ23" s="35">
+        <v>46158</v>
+      </c>
+      <c r="AR23" s="34" t="s">
+        <v>112</v>
+      </c>
+      <c r="AS23" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="BL23" s="34">
+        <v>110</v>
+      </c>
+      <c r="BM23" s="34"/>
+      <c r="BN23" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="BO23" s="35">
+        <v>46172</v>
+      </c>
+      <c r="BP23" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="AI23" s="19"/>
-      <c r="AK23" s="34" t="s">
-        <v>112</v>
-      </c>
-      <c r="AL23" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="AM23" s="34">
-        <v>4</v>
-      </c>
-      <c r="AN23" s="35">
-        <v>46158</v>
-      </c>
-      <c r="AO23" s="34" t="s">
-        <v>109</v>
-      </c>
-      <c r="AP23" s="34" t="s">
-        <v>110</v>
-      </c>
-      <c r="BI23" s="34">
-        <v>110</v>
-      </c>
-      <c r="BJ23" s="34"/>
-      <c r="BK23" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="BL23" s="35">
-        <v>46172</v>
-      </c>
-      <c r="BM23" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="CF23" s="17">
+      <c r="CI23" s="17">
         <f t="shared" si="0"/>
         <v>110</v>
       </c>
     </row>
-    <row r="24" spans="1:84" ht="21">
+    <row r="24" spans="1:87" ht="21">
       <c r="A24" s="6" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B24" s="6">
         <v>5</v>
@@ -3641,38 +3677,38 @@
         <v>67.739999999999995</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="AE24" s="18"/>
-      <c r="AK24" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="AL24" s="34" t="s">
-        <v>96</v>
-      </c>
-      <c r="AM24" s="34">
+        <v>97</v>
+      </c>
+      <c r="AH24" s="18"/>
+      <c r="AN24" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="AO24" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP24" s="34">
         <v>80</v>
       </c>
-      <c r="AN24" s="35">
+      <c r="AQ24" s="35">
         <v>46135</v>
       </c>
-      <c r="AO24" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="AP24" s="34" t="s">
-        <v>98</v>
-      </c>
-      <c r="CF24" s="17">
+      <c r="AR24" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="AS24" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="CI24" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:84" ht="21">
+    <row r="25" spans="1:87" ht="21">
       <c r="A25" s="6" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B25" s="6">
         <v>6</v>
@@ -3681,38 +3717,38 @@
         <v>24.52</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="AE25" s="18"/>
-      <c r="AK25" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="AL25" s="34" t="s">
-        <v>96</v>
-      </c>
-      <c r="AM25" s="34">
+        <v>97</v>
+      </c>
+      <c r="AH25" s="18"/>
+      <c r="AN25" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="AO25" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP25" s="34">
         <v>80</v>
       </c>
-      <c r="AN25" s="35">
+      <c r="AQ25" s="35">
         <v>46135</v>
       </c>
-      <c r="AO25" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="AP25" s="34" t="s">
-        <v>98</v>
-      </c>
-      <c r="CF25" s="17">
+      <c r="AR25" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="AS25" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="CI25" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:84" ht="21">
+    <row r="26" spans="1:87" ht="21">
       <c r="A26" s="6" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B26" s="6">
         <v>11</v>
@@ -3721,16 +3757,16 @@
         <v>31</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F26" s="45">
         <v>46157</v>
       </c>
       <c r="G26" s="46" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H26" s="46">
         <v>5</v>
@@ -3760,80 +3796,83 @@
         <v>150</v>
       </c>
       <c r="Q26" s="34"/>
-      <c r="R26" s="34" t="s">
-        <v>87</v>
-      </c>
+      <c r="R26" s="34"/>
       <c r="S26" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="T26" s="35">
+        <v>90</v>
+      </c>
+      <c r="T26" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="U26" s="34"/>
+      <c r="V26" s="35">
         <v>46172</v>
       </c>
-      <c r="U26" s="35">
+      <c r="W26" s="35">
         <v>46172</v>
       </c>
-      <c r="V26" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="W26" s="34">
+      <c r="X26" s="35"/>
+      <c r="Y26" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z26" s="34">
         <v>3</v>
       </c>
-      <c r="X26" s="34">
+      <c r="AA26" s="34">
         <v>1</v>
       </c>
-      <c r="Y26" s="34">
+      <c r="AB26" s="34">
         <v>0.45</v>
       </c>
-      <c r="Z26" s="34"/>
-      <c r="AA26" s="34"/>
-      <c r="AB26" s="34"/>
       <c r="AC26" s="34"/>
       <c r="AD26" s="34"/>
-      <c r="AE26" s="47">
+      <c r="AE26" s="34"/>
+      <c r="AF26" s="34"/>
+      <c r="AG26" s="34"/>
+      <c r="AH26" s="47">
         <v>46159</v>
       </c>
-      <c r="AF26" s="34" t="s">
+      <c r="AI26" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN26" s="34" t="s">
+        <v>115</v>
+      </c>
+      <c r="AO26" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="AP26" s="34">
+        <v>4</v>
+      </c>
+      <c r="AQ26" s="35">
+        <v>46159</v>
+      </c>
+      <c r="AR26" s="34" t="s">
+        <v>112</v>
+      </c>
+      <c r="AS26" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="BL26" s="34">
+        <v>110</v>
+      </c>
+      <c r="BM26" s="34"/>
+      <c r="BN26" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="BO26" s="35">
+        <v>46172</v>
+      </c>
+      <c r="BP26" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="AK26" s="34" t="s">
-        <v>112</v>
-      </c>
-      <c r="AL26" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="AM26" s="34">
-        <v>4</v>
-      </c>
-      <c r="AN26" s="35">
-        <v>46159</v>
-      </c>
-      <c r="AO26" s="34" t="s">
-        <v>109</v>
-      </c>
-      <c r="AP26" s="34" t="s">
-        <v>110</v>
-      </c>
-      <c r="BI26" s="34">
-        <v>110</v>
-      </c>
-      <c r="BJ26" s="34"/>
-      <c r="BK26" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="BL26" s="35">
-        <v>46172</v>
-      </c>
-      <c r="BM26" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="CF26" s="17">
+      <c r="CI26" s="17">
         <f t="shared" si="0"/>
         <v>110</v>
       </c>
     </row>
-    <row r="27" spans="1:84" ht="21">
+    <row r="27" spans="1:87" ht="21">
       <c r="A27" s="6" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B27" s="6">
         <v>12</v>
@@ -3842,38 +3881,38 @@
         <v>67</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="AE27" s="18"/>
-      <c r="AK27" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="AL27" s="34" t="s">
-        <v>96</v>
-      </c>
-      <c r="AM27" s="34">
+        <v>97</v>
+      </c>
+      <c r="AH27" s="18"/>
+      <c r="AN27" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="AO27" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP27" s="34">
         <v>80</v>
       </c>
-      <c r="AN27" s="35">
+      <c r="AQ27" s="35">
         <v>46135</v>
       </c>
-      <c r="AO27" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="AP27" s="34" t="s">
-        <v>98</v>
-      </c>
-      <c r="CF27" s="17">
+      <c r="AR27" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="AS27" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="CI27" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:84" ht="21">
+    <row r="28" spans="1:87" ht="21">
       <c r="A28" s="6" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B28" s="6">
         <v>1</v>
@@ -3882,13 +3921,13 @@
         <v>138.88</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G28" s="17" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="P28" s="17">
         <v>145.9</v>
@@ -3896,110 +3935,119 @@
       <c r="Q28" s="17">
         <v>107.2</v>
       </c>
-      <c r="R28" s="17" t="s">
-        <v>116</v>
+      <c r="R28" s="17">
+        <v>100</v>
       </c>
       <c r="S28" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="T28" s="19">
+        <v>119</v>
+      </c>
+      <c r="T28" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="U28" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="V28" s="19">
         <v>46175</v>
       </c>
-      <c r="U28" s="19">
+      <c r="W28" s="19">
         <v>46175</v>
       </c>
-      <c r="V28" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="W28" s="34">
+      <c r="X28" s="19">
+        <v>46175</v>
+      </c>
+      <c r="Y28" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z28" s="34">
         <v>3</v>
       </c>
-      <c r="X28" s="34">
+      <c r="AA28" s="34">
         <v>1</v>
       </c>
-      <c r="Y28" s="34">
+      <c r="AB28" s="34">
         <v>0.45</v>
       </c>
-      <c r="Z28" s="34"/>
-      <c r="AA28" s="34"/>
-      <c r="AB28" s="34"/>
       <c r="AC28" s="34"/>
       <c r="AD28" s="34"/>
-      <c r="AE28" s="47">
+      <c r="AE28" s="34"/>
+      <c r="AF28" s="34"/>
+      <c r="AG28" s="34"/>
+      <c r="AH28" s="47">
         <v>46057</v>
       </c>
-      <c r="AF28" s="34" t="s">
+      <c r="AI28" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="AJ28" s="34">
+        <v>3</v>
+      </c>
+      <c r="AK28" s="34"/>
+      <c r="AL28" s="35">
+        <v>46164</v>
+      </c>
+      <c r="AM28" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN28" s="34" t="s">
+        <v>115</v>
+      </c>
+      <c r="AO28" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="AP28" s="34">
+        <v>3.5</v>
+      </c>
+      <c r="AQ28" s="35">
+        <v>46143</v>
+      </c>
+      <c r="AR28" s="34" t="s">
+        <v>112</v>
+      </c>
+      <c r="AS28" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="AT28" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="AU28" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="AV28" s="34">
+        <v>3.6</v>
+      </c>
+      <c r="AW28" s="35">
+        <v>46162</v>
+      </c>
+      <c r="AX28" s="34">
+        <v>138.88</v>
+      </c>
+      <c r="AY28" s="34" t="s">
+        <v>112</v>
+      </c>
+      <c r="AZ28" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="BL28" s="17">
+        <v>100</v>
+      </c>
+      <c r="BN28" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="BO28" s="19">
+        <v>46175</v>
+      </c>
+      <c r="BP28" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="AG28" s="34">
-        <v>3</v>
-      </c>
-      <c r="AH28" s="34"/>
-      <c r="AI28" s="35">
-        <v>46164</v>
-      </c>
-      <c r="AJ28" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="AK28" s="34" t="s">
-        <v>112</v>
-      </c>
-      <c r="AL28" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="AM28" s="34">
-        <v>3.5</v>
-      </c>
-      <c r="AN28" s="35">
-        <v>46143</v>
-      </c>
-      <c r="AO28" s="34" t="s">
-        <v>109</v>
-      </c>
-      <c r="AP28" s="34" t="s">
-        <v>110</v>
-      </c>
-      <c r="AQ28" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="AR28" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="AS28" s="34">
-        <v>3.6</v>
-      </c>
-      <c r="AT28" s="35">
-        <v>46162</v>
-      </c>
-      <c r="AU28" s="34">
-        <v>138.88</v>
-      </c>
-      <c r="AV28" s="34" t="s">
-        <v>109</v>
-      </c>
-      <c r="AW28" s="34" t="s">
-        <v>110</v>
-      </c>
-      <c r="BI28" s="17">
-        <v>100</v>
-      </c>
-      <c r="BK28" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="BL28" s="19">
-        <v>46175</v>
-      </c>
-      <c r="BM28" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="CF28" s="17">
+      <c r="CI28" s="17">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="1:84" ht="21">
+    <row r="29" spans="1:87" ht="21">
       <c r="A29" s="6" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B29" s="6">
         <v>2</v>
@@ -4008,38 +4056,38 @@
         <v>141.69999999999999</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="AE29" s="18"/>
-      <c r="AK29" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="AL29" s="34" t="s">
-        <v>96</v>
-      </c>
-      <c r="AM29" s="34">
+        <v>97</v>
+      </c>
+      <c r="AH29" s="18"/>
+      <c r="AN29" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="AO29" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP29" s="34">
         <v>80</v>
       </c>
-      <c r="AN29" s="35">
+      <c r="AQ29" s="35">
         <v>46134</v>
       </c>
-      <c r="AO29" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="AP29" s="34" t="s">
-        <v>98</v>
-      </c>
-      <c r="CF29" s="17">
+      <c r="AR29" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="AS29" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="CI29" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:84" ht="21">
+    <row r="30" spans="1:87" ht="21">
       <c r="A30" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B30" s="6">
         <v>1</v>
@@ -4048,38 +4096,38 @@
         <v>101.74</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="AE30" s="18"/>
-      <c r="AK30" s="34" t="s">
-        <v>119</v>
-      </c>
-      <c r="AL30" s="34" t="s">
-        <v>120</v>
-      </c>
-      <c r="AM30" s="34">
+        <v>97</v>
+      </c>
+      <c r="AH30" s="18"/>
+      <c r="AN30" s="34" t="s">
+        <v>122</v>
+      </c>
+      <c r="AO30" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="AP30" s="34">
         <v>10</v>
       </c>
-      <c r="AN30" s="35">
+      <c r="AQ30" s="35">
         <v>46170</v>
       </c>
-      <c r="AO30" s="34" t="s">
-        <v>121</v>
-      </c>
-      <c r="AP30" s="34" t="s">
-        <v>122</v>
-      </c>
-      <c r="CF30" s="17">
+      <c r="AR30" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="AS30" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="CI30" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:84" ht="21">
+    <row r="31" spans="1:87" ht="21">
       <c r="A31" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B31" s="6">
         <v>2</v>
@@ -4088,13 +4136,13 @@
         <v>34.99</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G31" s="17" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="P31" s="34">
         <v>120</v>
@@ -4102,110 +4150,112 @@
       <c r="Q31" s="17">
         <v>50</v>
       </c>
-      <c r="R31" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="S31" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="U31" s="35">
+      <c r="S31" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="T31" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="U31" s="34"/>
+      <c r="W31" s="35">
         <v>46170</v>
       </c>
-      <c r="V31" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="W31" s="34">
+      <c r="X31" s="35"/>
+      <c r="Y31" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z31" s="34">
         <v>3</v>
       </c>
-      <c r="X31" s="34">
+      <c r="AA31" s="34">
         <v>1</v>
       </c>
-      <c r="Y31" s="34">
+      <c r="AB31" s="34">
         <v>0.45</v>
       </c>
-      <c r="Z31" s="34"/>
-      <c r="AA31" s="34"/>
-      <c r="AB31" s="34"/>
       <c r="AC31" s="34"/>
       <c r="AD31" s="34"/>
-      <c r="AE31" s="47" t="s">
-        <v>123</v>
-      </c>
-      <c r="AF31" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="AG31" s="34">
+      <c r="AE31" s="34"/>
+      <c r="AF31" s="34"/>
+      <c r="AG31" s="34"/>
+      <c r="AH31" s="47" t="s">
+        <v>126</v>
+      </c>
+      <c r="AI31" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="AJ31" s="34">
         <v>3.5</v>
       </c>
-      <c r="AH31" s="34">
+      <c r="AK31" s="34">
         <v>2.5</v>
       </c>
-      <c r="AI31" s="35">
+      <c r="AL31" s="35">
         <v>46136</v>
       </c>
-      <c r="AJ31" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="AK31" s="34" t="s">
-        <v>124</v>
-      </c>
-      <c r="AL31" s="34" t="s">
+      <c r="AM31" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN31" s="34" t="s">
+        <v>127</v>
+      </c>
+      <c r="AO31" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="AP31" s="34">
+        <v>3.5</v>
+      </c>
+      <c r="AQ31" s="35">
+        <v>46139</v>
+      </c>
+      <c r="AR31" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="AS31" s="34" t="s">
+        <v>95</v>
+      </c>
+      <c r="AT31" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="AU31" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="AV31" s="34">
+        <v>3.6</v>
+      </c>
+      <c r="AW31" s="35">
+        <v>46171</v>
+      </c>
+      <c r="AX31" s="34">
+        <v>34.99</v>
+      </c>
+      <c r="AY31" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="AZ31" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="BL31" s="34">
+        <v>95</v>
+      </c>
+      <c r="BM31" s="34"/>
+      <c r="BN31" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="AM31" s="34">
-        <v>3.5</v>
-      </c>
-      <c r="AN31" s="35">
-        <v>46139</v>
-      </c>
-      <c r="AO31" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="AP31" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="AQ31" s="34" t="s">
-        <v>125</v>
-      </c>
-      <c r="AR31" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="AS31" s="34">
-        <v>3.6</v>
-      </c>
-      <c r="AT31" s="35">
-        <v>46171</v>
-      </c>
-      <c r="AU31" s="34">
-        <v>34.99</v>
-      </c>
-      <c r="AV31" s="34" t="s">
-        <v>126</v>
-      </c>
-      <c r="AW31" s="34" t="s">
-        <v>110</v>
-      </c>
-      <c r="BI31" s="34">
-        <v>95</v>
-      </c>
-      <c r="BJ31" s="34"/>
-      <c r="BK31" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="BL31" s="35">
+      <c r="BO31" s="35">
         <v>46143</v>
       </c>
-      <c r="BM31" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="CF31" s="17">
+      <c r="BP31" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="CI31" s="17">
         <f t="shared" si="0"/>
         <v>95</v>
       </c>
     </row>
-    <row r="32" spans="1:84" ht="21">
+    <row r="32" spans="1:87" ht="21">
       <c r="A32" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B32" s="6">
         <v>3</v>
@@ -4214,13 +4264,13 @@
         <v>301.24</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="P32" s="34">
         <v>113.3</v>
@@ -4228,110 +4278,112 @@
       <c r="Q32" s="17">
         <v>72.3</v>
       </c>
-      <c r="R32" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="S32" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="U32" s="35">
+      <c r="S32" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="T32" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="U32" s="34"/>
+      <c r="W32" s="35">
         <v>46170</v>
       </c>
-      <c r="V32" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="W32" s="34">
+      <c r="X32" s="35"/>
+      <c r="Y32" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z32" s="34">
         <v>3</v>
       </c>
-      <c r="X32" s="34">
+      <c r="AA32" s="34">
         <v>1</v>
       </c>
-      <c r="Y32" s="34">
+      <c r="AB32" s="34">
         <v>0.45</v>
       </c>
-      <c r="Z32" s="34"/>
-      <c r="AA32" s="34"/>
-      <c r="AB32" s="34"/>
       <c r="AC32" s="34"/>
       <c r="AD32" s="34"/>
-      <c r="AE32" s="47" t="s">
-        <v>123</v>
-      </c>
-      <c r="AF32" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="AG32" s="34">
+      <c r="AE32" s="34"/>
+      <c r="AF32" s="34"/>
+      <c r="AG32" s="34"/>
+      <c r="AH32" s="47" t="s">
+        <v>126</v>
+      </c>
+      <c r="AI32" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="AJ32" s="34">
         <v>3.5</v>
       </c>
-      <c r="AH32" s="34">
+      <c r="AK32" s="34">
         <v>2.5</v>
       </c>
-      <c r="AI32" s="35">
+      <c r="AL32" s="35">
         <v>46136</v>
       </c>
-      <c r="AJ32" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="AK32" s="34" t="s">
-        <v>124</v>
-      </c>
-      <c r="AL32" s="34" t="s">
+      <c r="AM32" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN32" s="34" t="s">
+        <v>127</v>
+      </c>
+      <c r="AO32" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="AP32" s="34">
+        <v>3.5</v>
+      </c>
+      <c r="AQ32" s="35">
+        <v>46132</v>
+      </c>
+      <c r="AR32" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="AS32" s="34" t="s">
+        <v>95</v>
+      </c>
+      <c r="AT32" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="AU32" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="AV32" s="34">
+        <v>3.6</v>
+      </c>
+      <c r="AW32" s="35">
+        <v>46172</v>
+      </c>
+      <c r="AX32" s="34">
+        <v>210</v>
+      </c>
+      <c r="AY32" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="AZ32" s="34" t="s">
+        <v>132</v>
+      </c>
+      <c r="BL32" s="34">
+        <v>95</v>
+      </c>
+      <c r="BM32" s="34"/>
+      <c r="BN32" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="AM32" s="34">
-        <v>3.5</v>
-      </c>
-      <c r="AN32" s="35">
-        <v>46132</v>
-      </c>
-      <c r="AO32" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="AP32" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="AQ32" s="34" t="s">
-        <v>127</v>
-      </c>
-      <c r="AR32" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="AS32" s="34">
-        <v>3.6</v>
-      </c>
-      <c r="AT32" s="35">
-        <v>46172</v>
-      </c>
-      <c r="AU32" s="34">
-        <v>210</v>
-      </c>
-      <c r="AV32" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="AW32" s="34" t="s">
-        <v>129</v>
-      </c>
-      <c r="BI32" s="34">
-        <v>95</v>
-      </c>
-      <c r="BJ32" s="34"/>
-      <c r="BK32" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="BL32" s="35">
+      <c r="BO32" s="35">
         <v>46143</v>
       </c>
-      <c r="BM32" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="CF32" s="17">
+      <c r="BP32" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="CI32" s="17">
         <f t="shared" si="0"/>
         <v>95</v>
       </c>
     </row>
-    <row r="33" spans="1:84" ht="21">
+    <row r="33" spans="1:87" ht="21">
       <c r="A33" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B33" s="6">
         <v>4</v>
@@ -4340,13 +4392,13 @@
         <v>180.2</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G33" s="17" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="P33" s="34">
         <v>120.7</v>
@@ -4354,110 +4406,112 @@
       <c r="Q33" s="17">
         <v>92.5</v>
       </c>
-      <c r="R33" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="S33" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="U33" s="35">
+      <c r="S33" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="T33" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="U33" s="34"/>
+      <c r="W33" s="35">
         <v>46170</v>
       </c>
-      <c r="V33" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="W33" s="34">
+      <c r="X33" s="35"/>
+      <c r="Y33" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z33" s="34">
         <v>3</v>
       </c>
-      <c r="X33" s="34">
+      <c r="AA33" s="34">
         <v>1</v>
       </c>
-      <c r="Y33" s="34">
+      <c r="AB33" s="34">
         <v>0.45</v>
       </c>
-      <c r="Z33" s="34"/>
-      <c r="AA33" s="34"/>
-      <c r="AB33" s="34"/>
       <c r="AC33" s="34"/>
       <c r="AD33" s="34"/>
-      <c r="AE33" s="47" t="s">
-        <v>123</v>
-      </c>
-      <c r="AF33" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="AG33" s="34">
+      <c r="AE33" s="34"/>
+      <c r="AF33" s="34"/>
+      <c r="AG33" s="34"/>
+      <c r="AH33" s="47" t="s">
+        <v>126</v>
+      </c>
+      <c r="AI33" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="AJ33" s="34">
         <v>3.5</v>
       </c>
-      <c r="AH33" s="34">
+      <c r="AK33" s="34">
         <v>2.5</v>
       </c>
-      <c r="AI33" s="35">
+      <c r="AL33" s="35">
         <v>46136</v>
       </c>
-      <c r="AJ33" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="AK33" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="AL33" s="34" t="s">
+      <c r="AM33" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN33" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="AO33" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="AP33" s="34">
+        <v>3.5</v>
+      </c>
+      <c r="AQ33" s="35">
+        <v>46141</v>
+      </c>
+      <c r="AR33" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="AS33" s="34" t="s">
+        <v>95</v>
+      </c>
+      <c r="AT33" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="AU33" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="AV33" s="34">
+        <v>3.6</v>
+      </c>
+      <c r="AW33" s="35">
+        <v>46172</v>
+      </c>
+      <c r="AX33" s="34">
+        <v>131.5</v>
+      </c>
+      <c r="AY33" s="34" t="s">
+        <v>135</v>
+      </c>
+      <c r="AZ33" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="BL33" s="34">
+        <v>95</v>
+      </c>
+      <c r="BM33" s="34"/>
+      <c r="BN33" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="AM33" s="34">
-        <v>3.5</v>
-      </c>
-      <c r="AN33" s="35">
-        <v>46141</v>
-      </c>
-      <c r="AO33" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="AP33" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="AQ33" s="34" t="s">
-        <v>131</v>
-      </c>
-      <c r="AR33" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="AS33" s="34">
-        <v>3.6</v>
-      </c>
-      <c r="AT33" s="35">
-        <v>46172</v>
-      </c>
-      <c r="AU33" s="34">
-        <v>131.5</v>
-      </c>
-      <c r="AV33" s="34" t="s">
-        <v>132</v>
-      </c>
-      <c r="AW33" s="34" t="s">
-        <v>110</v>
-      </c>
-      <c r="BI33" s="34">
-        <v>95</v>
-      </c>
-      <c r="BJ33" s="34"/>
-      <c r="BK33" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="BL33" s="35">
+      <c r="BO33" s="35">
         <v>46143</v>
       </c>
-      <c r="BM33" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="CF33" s="17">
+      <c r="BP33" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="CI33" s="17">
         <f t="shared" si="0"/>
         <v>95</v>
       </c>
     </row>
-    <row r="34" spans="1:84" ht="21">
+    <row r="34" spans="1:87" ht="21">
       <c r="A34" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B34" s="6">
         <v>5</v>
@@ -4466,38 +4520,38 @@
         <v>59.08</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="AE34" s="18"/>
-      <c r="AK34" s="34" t="s">
-        <v>119</v>
-      </c>
-      <c r="AL34" s="34" t="s">
-        <v>120</v>
-      </c>
-      <c r="AM34" s="34">
+        <v>97</v>
+      </c>
+      <c r="AH34" s="18"/>
+      <c r="AN34" s="34" t="s">
+        <v>122</v>
+      </c>
+      <c r="AO34" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="AP34" s="34">
         <v>10</v>
       </c>
-      <c r="AN34" s="35">
+      <c r="AQ34" s="35">
         <v>46170</v>
       </c>
-      <c r="AO34" s="34" t="s">
-        <v>121</v>
-      </c>
-      <c r="AP34" s="34" t="s">
-        <v>122</v>
-      </c>
-      <c r="CF34" s="17">
+      <c r="AR34" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="AS34" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="CI34" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:84" ht="21">
+    <row r="35" spans="1:87" ht="21">
       <c r="A35" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B35" s="6">
         <v>7</v>
@@ -4506,38 +4560,38 @@
         <v>46.79</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="AE35" s="18"/>
-      <c r="AK35" s="34" t="s">
-        <v>119</v>
-      </c>
-      <c r="AL35" s="34" t="s">
-        <v>120</v>
-      </c>
-      <c r="AM35" s="34">
+        <v>97</v>
+      </c>
+      <c r="AH35" s="18"/>
+      <c r="AN35" s="34" t="s">
+        <v>122</v>
+      </c>
+      <c r="AO35" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="AP35" s="34">
         <v>10</v>
       </c>
-      <c r="AN35" s="35">
+      <c r="AQ35" s="35">
         <v>46134</v>
       </c>
-      <c r="AO35" s="34" t="s">
-        <v>121</v>
-      </c>
-      <c r="AP35" s="34" t="s">
-        <v>133</v>
-      </c>
-      <c r="CF35" s="17">
+      <c r="AR35" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="AS35" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="CI35" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:84" ht="21">
+    <row r="36" spans="1:87" ht="21">
       <c r="A36" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B36" s="6">
         <v>8</v>
@@ -4546,38 +4600,38 @@
         <v>59.05</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="AE36" s="18"/>
-      <c r="AK36" s="34" t="s">
-        <v>119</v>
-      </c>
-      <c r="AL36" s="34" t="s">
-        <v>120</v>
-      </c>
-      <c r="AM36" s="34">
+        <v>97</v>
+      </c>
+      <c r="AH36" s="18"/>
+      <c r="AN36" s="34" t="s">
+        <v>122</v>
+      </c>
+      <c r="AO36" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="AP36" s="34">
         <v>10</v>
       </c>
-      <c r="AN36" s="35">
+      <c r="AQ36" s="35">
         <v>46134</v>
       </c>
-      <c r="AO36" s="34" t="s">
-        <v>121</v>
-      </c>
-      <c r="AP36" s="34" t="s">
-        <v>133</v>
-      </c>
-      <c r="CF36" s="17">
+      <c r="AR36" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="AS36" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="CI36" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:84" ht="21">
+    <row r="37" spans="1:87" ht="21">
       <c r="A37" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B37" s="6">
         <v>9</v>
@@ -4586,38 +4640,38 @@
         <v>103.45</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="AE37" s="18"/>
-      <c r="AK37" s="34" t="s">
-        <v>119</v>
-      </c>
-      <c r="AL37" s="34" t="s">
-        <v>120</v>
-      </c>
-      <c r="AM37" s="34">
+        <v>97</v>
+      </c>
+      <c r="AH37" s="18"/>
+      <c r="AN37" s="34" t="s">
+        <v>122</v>
+      </c>
+      <c r="AO37" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="AP37" s="34">
         <v>10</v>
       </c>
-      <c r="AN37" s="35">
+      <c r="AQ37" s="35">
         <v>46132</v>
       </c>
-      <c r="AO37" s="34" t="s">
-        <v>121</v>
-      </c>
-      <c r="AP37" s="34" t="s">
-        <v>133</v>
-      </c>
-      <c r="CF37" s="17">
+      <c r="AR37" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="AS37" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="CI37" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:84" ht="21">
+    <row r="38" spans="1:87" ht="21">
       <c r="A38" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B38" s="6">
         <v>10</v>
@@ -4626,13 +4680,13 @@
         <v>101.88</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G38" s="17" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="P38" s="34">
         <v>97.9</v>
@@ -4640,122 +4694,124 @@
       <c r="Q38" s="17">
         <v>83.7</v>
       </c>
-      <c r="R38" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="S38" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="T38" s="19">
+      <c r="S38" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="T38" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="U38" s="34"/>
+      <c r="V38" s="19">
         <v>46176</v>
       </c>
-      <c r="U38" s="35">
+      <c r="W38" s="35">
         <v>46170</v>
       </c>
-      <c r="V38" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="W38" s="34">
+      <c r="X38" s="35"/>
+      <c r="Y38" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z38" s="34">
         <v>3</v>
       </c>
-      <c r="X38" s="34">
+      <c r="AA38" s="34">
         <v>1</v>
       </c>
-      <c r="Y38" s="34">
+      <c r="AB38" s="34">
         <v>0.45</v>
       </c>
-      <c r="Z38" s="34"/>
-      <c r="AA38" s="34"/>
-      <c r="AB38" s="34"/>
       <c r="AC38" s="34"/>
       <c r="AD38" s="34"/>
-      <c r="AE38" s="47" t="s">
-        <v>123</v>
-      </c>
-      <c r="AF38" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="AG38" s="34">
+      <c r="AE38" s="34"/>
+      <c r="AF38" s="34"/>
+      <c r="AG38" s="34"/>
+      <c r="AH38" s="47" t="s">
+        <v>126</v>
+      </c>
+      <c r="AI38" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="AJ38" s="34">
         <v>3.5</v>
       </c>
-      <c r="AH38" s="34">
+      <c r="AK38" s="34">
         <v>2.5</v>
       </c>
-      <c r="AI38" s="35">
+      <c r="AL38" s="35">
         <v>46136</v>
       </c>
-      <c r="AJ38" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="AK38" s="34" t="s">
+      <c r="AM38" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN38" s="34" t="s">
+        <v>127</v>
+      </c>
+      <c r="AO38" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="AP38" s="34">
+        <v>3.5</v>
+      </c>
+      <c r="AQ38" s="35">
+        <v>46139</v>
+      </c>
+      <c r="AR38" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="AS38" s="34" t="s">
+        <v>95</v>
+      </c>
+      <c r="AT38" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="AU38" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="AV38" s="34">
+        <v>3.6</v>
+      </c>
+      <c r="AW38" s="35">
+        <v>46171</v>
+      </c>
+      <c r="AX38" s="34">
+        <v>101.88</v>
+      </c>
+      <c r="AY38" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="AZ38" s="34" t="s">
+        <v>95</v>
+      </c>
+      <c r="BG38" s="34">
+        <v>2</v>
+      </c>
+      <c r="BH38" s="35">
+        <v>46174</v>
+      </c>
+      <c r="BI38" s="34" t="s">
         <v>124</v>
       </c>
-      <c r="AL38" s="34" t="s">
+      <c r="BL38" s="34">
+        <v>95</v>
+      </c>
+      <c r="BM38" s="34"/>
+      <c r="BN38" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="AM38" s="34">
-        <v>3.5</v>
-      </c>
-      <c r="AN38" s="35">
-        <v>46139</v>
-      </c>
-      <c r="AO38" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="AP38" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="AQ38" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="AR38" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="AS38" s="34">
-        <v>3.6</v>
-      </c>
-      <c r="AT38" s="35">
-        <v>46171</v>
-      </c>
-      <c r="AU38" s="34">
-        <v>101.88</v>
-      </c>
-      <c r="AV38" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="AW38" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="BD38" s="34">
-        <v>2</v>
-      </c>
-      <c r="BE38" s="35">
-        <v>46174</v>
-      </c>
-      <c r="BF38" s="34" t="s">
-        <v>121</v>
-      </c>
-      <c r="BI38" s="34">
-        <v>95</v>
-      </c>
-      <c r="BJ38" s="34"/>
-      <c r="BK38" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="BL38" s="35">
+      <c r="BO38" s="35">
         <v>46143</v>
       </c>
-      <c r="BM38" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="CF38" s="17">
+      <c r="BP38" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="CI38" s="17">
         <f t="shared" si="0"/>
         <v>95</v>
       </c>
     </row>
-    <row r="39" spans="1:84" ht="21">
+    <row r="39" spans="1:87" ht="21">
       <c r="A39" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B39" s="6">
         <v>11</v>
@@ -4764,38 +4820,38 @@
         <v>53.38</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="AE39" s="18"/>
-      <c r="AK39" s="34" t="s">
-        <v>119</v>
-      </c>
-      <c r="AL39" s="34" t="s">
-        <v>120</v>
-      </c>
-      <c r="AM39" s="34">
+        <v>97</v>
+      </c>
+      <c r="AH39" s="18"/>
+      <c r="AN39" s="34" t="s">
+        <v>122</v>
+      </c>
+      <c r="AO39" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="AP39" s="34">
         <v>10</v>
       </c>
-      <c r="AN39" s="35">
+      <c r="AQ39" s="35">
         <v>46170</v>
       </c>
-      <c r="AO39" s="34" t="s">
-        <v>121</v>
-      </c>
-      <c r="AP39" s="34" t="s">
-        <v>122</v>
-      </c>
-      <c r="CF39" s="17">
+      <c r="AR39" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="AS39" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="CI39" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:84" ht="21">
+    <row r="40" spans="1:87" ht="21">
       <c r="A40" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B40" s="6">
         <v>12</v>
@@ -4804,38 +4860,38 @@
         <v>102.7</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="AE40" s="18"/>
-      <c r="AK40" s="34" t="s">
-        <v>119</v>
-      </c>
-      <c r="AL40" s="34" t="s">
-        <v>120</v>
-      </c>
-      <c r="AM40" s="34">
+        <v>97</v>
+      </c>
+      <c r="AH40" s="18"/>
+      <c r="AN40" s="34" t="s">
+        <v>122</v>
+      </c>
+      <c r="AO40" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="AP40" s="34">
         <v>10</v>
       </c>
-      <c r="AN40" s="35">
+      <c r="AQ40" s="35">
         <v>46126</v>
       </c>
-      <c r="AO40" s="34" t="s">
-        <v>121</v>
-      </c>
-      <c r="AP40" s="34" t="s">
-        <v>133</v>
-      </c>
-      <c r="CF40" s="17">
+      <c r="AR40" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="AS40" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="CI40" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:84" ht="21">
+    <row r="41" spans="1:87" ht="21">
       <c r="A41" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B41" s="6">
         <v>13</v>
@@ -4844,38 +4900,38 @@
         <v>87.11</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="AE41" s="18"/>
-      <c r="AK41" s="34" t="s">
-        <v>119</v>
-      </c>
-      <c r="AL41" s="34" t="s">
-        <v>120</v>
-      </c>
-      <c r="AM41" s="34">
+        <v>97</v>
+      </c>
+      <c r="AH41" s="18"/>
+      <c r="AN41" s="34" t="s">
+        <v>122</v>
+      </c>
+      <c r="AO41" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="AP41" s="34">
         <v>10</v>
       </c>
-      <c r="AN41" s="35">
+      <c r="AQ41" s="35">
         <v>46135</v>
       </c>
-      <c r="AO41" s="34" t="s">
-        <v>121</v>
-      </c>
-      <c r="AP41" s="34" t="s">
-        <v>133</v>
-      </c>
-      <c r="CF41" s="17">
+      <c r="AR41" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="AS41" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="CI41" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:84" ht="21">
+    <row r="42" spans="1:87" ht="21">
       <c r="A42" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B42" s="6">
         <v>14</v>
@@ -4884,38 +4940,38 @@
         <v>59.42</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="AE42" s="18"/>
-      <c r="AK42" s="34" t="s">
-        <v>119</v>
-      </c>
-      <c r="AL42" s="34" t="s">
-        <v>120</v>
-      </c>
-      <c r="AM42" s="34">
+        <v>97</v>
+      </c>
+      <c r="AH42" s="18"/>
+      <c r="AN42" s="34" t="s">
+        <v>122</v>
+      </c>
+      <c r="AO42" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="AP42" s="34">
         <v>10</v>
       </c>
-      <c r="AN42" s="35">
+      <c r="AQ42" s="35">
         <v>46135</v>
       </c>
-      <c r="AO42" s="34" t="s">
-        <v>121</v>
-      </c>
-      <c r="AP42" s="34" t="s">
-        <v>133</v>
-      </c>
-      <c r="CF42" s="17">
+      <c r="AR42" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="AS42" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="CI42" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:84" ht="21">
+    <row r="43" spans="1:87" ht="21">
       <c r="A43" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B43" s="6">
         <v>15</v>
@@ -4924,53 +4980,53 @@
         <v>35.96</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="AE43" s="18"/>
-      <c r="AK43" s="34" t="s">
-        <v>119</v>
-      </c>
-      <c r="AL43" s="34" t="s">
-        <v>120</v>
-      </c>
-      <c r="AM43" s="34">
+        <v>97</v>
+      </c>
+      <c r="AH43" s="18"/>
+      <c r="AN43" s="34" t="s">
+        <v>122</v>
+      </c>
+      <c r="AO43" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="AP43" s="34">
         <v>10</v>
       </c>
-      <c r="AN43" s="35">
+      <c r="AQ43" s="35">
         <v>46136</v>
       </c>
-      <c r="AO43" s="34" t="s">
-        <v>121</v>
-      </c>
-      <c r="AP43" s="34" t="s">
-        <v>133</v>
-      </c>
-      <c r="CF43" s="17">
+      <c r="AR43" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="AS43" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="CI43" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:84" ht="21">
+    <row r="44" spans="1:87" ht="21">
       <c r="A44" s="6" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C44" s="6">
         <v>386.2</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G44" s="17" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="P44" s="34">
         <v>61.5</v>
@@ -4978,129 +5034,131 @@
       <c r="Q44" s="17">
         <v>107.3</v>
       </c>
-      <c r="R44" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="S44" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="T44" s="19">
+      <c r="S44" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="T44" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="U44" s="34"/>
+      <c r="V44" s="19">
         <v>46176</v>
       </c>
-      <c r="U44" s="35">
+      <c r="W44" s="35">
         <v>46172</v>
       </c>
-      <c r="V44" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="W44" s="34">
+      <c r="X44" s="35"/>
+      <c r="Y44" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z44" s="34">
         <v>3</v>
       </c>
-      <c r="X44" s="34"/>
-      <c r="Y44" s="34"/>
-      <c r="Z44" s="34"/>
       <c r="AA44" s="34"/>
-      <c r="AB44" s="34">
-        <v>0.35</v>
-      </c>
+      <c r="AB44" s="34"/>
       <c r="AC44" s="34"/>
       <c r="AD44" s="34"/>
-      <c r="AE44" s="47">
+      <c r="AE44" s="34">
+        <v>0.35</v>
+      </c>
+      <c r="AF44" s="34"/>
+      <c r="AG44" s="34"/>
+      <c r="AH44" s="47">
         <v>46167</v>
       </c>
-      <c r="AF44" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="AK44" s="34" t="s">
-        <v>137</v>
-      </c>
-      <c r="AL44" s="34" t="s">
-        <v>120</v>
-      </c>
-      <c r="AM44" s="34">
+      <c r="AI44" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN44" s="34" t="s">
+        <v>140</v>
+      </c>
+      <c r="AO44" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="AP44" s="34">
         <v>146.93</v>
       </c>
-      <c r="AN44" s="35">
+      <c r="AQ44" s="35">
         <v>46165</v>
       </c>
-      <c r="AO44" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="AP44" s="34" t="s">
-        <v>102</v>
-      </c>
-      <c r="BI44" s="17">
+      <c r="AR44" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="AS44" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="BL44" s="17">
         <v>93</v>
       </c>
-      <c r="BK44" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="BM44" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="CF44" s="17">
+      <c r="BN44" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="BP44" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="CI44" s="17">
         <f t="shared" si="0"/>
         <v>93</v>
       </c>
     </row>
-    <row r="45" spans="1:84" ht="21">
+    <row r="45" spans="1:87" ht="21">
       <c r="A45" s="6" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C45" s="6">
         <v>120</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="AE45" s="18"/>
-      <c r="AK45" s="34" t="s">
-        <v>119</v>
-      </c>
-      <c r="AL45" s="34" t="s">
-        <v>120</v>
-      </c>
-      <c r="AM45" s="34">
+        <v>97</v>
+      </c>
+      <c r="AH45" s="18"/>
+      <c r="AN45" s="34" t="s">
+        <v>122</v>
+      </c>
+      <c r="AO45" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="AP45" s="34">
         <v>10</v>
       </c>
-      <c r="AN45" s="35">
+      <c r="AQ45" s="35">
         <v>46175</v>
       </c>
-      <c r="AO45" s="34" t="s">
-        <v>121</v>
-      </c>
-      <c r="AP45" s="34" t="s">
-        <v>133</v>
-      </c>
-      <c r="CF45" s="17">
+      <c r="AR45" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="AS45" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="CI45" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:84" ht="21">
+    <row r="46" spans="1:87" ht="21">
       <c r="A46" s="6" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C46" s="9">
         <v>163</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G46" s="17" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="P46" s="34">
         <v>93.9</v>
@@ -5108,89 +5166,91 @@
       <c r="Q46" s="17">
         <v>108.1</v>
       </c>
-      <c r="R46" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="S46" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="T46" s="19">
+      <c r="S46" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="T46" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="U46" s="34"/>
+      <c r="V46" s="19">
         <v>46176</v>
       </c>
-      <c r="U46" s="35">
+      <c r="W46" s="35">
         <v>46172</v>
       </c>
-      <c r="V46" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="W46" s="34">
+      <c r="X46" s="35"/>
+      <c r="Y46" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z46" s="34">
         <v>3</v>
       </c>
-      <c r="X46" s="34"/>
-      <c r="Y46" s="34"/>
-      <c r="Z46" s="34"/>
       <c r="AA46" s="34"/>
-      <c r="AB46" s="34">
-        <v>0.35</v>
-      </c>
+      <c r="AB46" s="34"/>
       <c r="AC46" s="34"/>
       <c r="AD46" s="34"/>
-      <c r="AE46" s="47">
+      <c r="AE46" s="34">
+        <v>0.35</v>
+      </c>
+      <c r="AF46" s="34"/>
+      <c r="AG46" s="34"/>
+      <c r="AH46" s="47">
         <v>46167</v>
       </c>
-      <c r="AF46" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="AK46" s="34" t="s">
-        <v>137</v>
-      </c>
-      <c r="AL46" s="34" t="s">
+      <c r="AI46" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN46" s="34" t="s">
         <v>140</v>
       </c>
-      <c r="AM46" s="34">
+      <c r="AO46" s="34" t="s">
+        <v>143</v>
+      </c>
+      <c r="AP46" s="34">
         <v>146.93</v>
       </c>
-      <c r="AN46" s="35">
+      <c r="AQ46" s="35">
         <v>46169</v>
       </c>
-      <c r="AO46" s="34" t="s">
-        <v>141</v>
-      </c>
-      <c r="AP46" s="34" t="s">
-        <v>102</v>
-      </c>
-      <c r="BI46" s="17">
+      <c r="AR46" s="34" t="s">
+        <v>144</v>
+      </c>
+      <c r="AS46" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="BL46" s="17">
         <v>93</v>
       </c>
-      <c r="BK46" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="BM46" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="CF46" s="17">
+      <c r="BN46" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="BP46" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="CI46" s="17">
         <f t="shared" si="0"/>
         <v>93</v>
       </c>
     </row>
-    <row r="47" spans="1:84" ht="21">
+    <row r="47" spans="1:87" ht="21">
       <c r="A47" s="6" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C47" s="6">
         <v>189.75</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G47" s="17" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="P47" s="34">
         <v>78.8</v>
@@ -5198,89 +5258,91 @@
       <c r="Q47" s="17">
         <v>110.8</v>
       </c>
-      <c r="R47" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="S47" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="T47" s="19">
+      <c r="S47" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="T47" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="U47" s="34"/>
+      <c r="V47" s="19">
         <v>46175</v>
       </c>
-      <c r="U47" s="35">
+      <c r="W47" s="35">
         <v>46172</v>
       </c>
-      <c r="V47" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="W47" s="34">
+      <c r="X47" s="35"/>
+      <c r="Y47" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z47" s="34">
         <v>3</v>
       </c>
-      <c r="X47" s="34"/>
-      <c r="Y47" s="34"/>
-      <c r="Z47" s="34"/>
       <c r="AA47" s="34"/>
-      <c r="AB47" s="34">
-        <v>0.35</v>
-      </c>
+      <c r="AB47" s="34"/>
       <c r="AC47" s="34"/>
       <c r="AD47" s="34"/>
-      <c r="AE47" s="47">
+      <c r="AE47" s="34">
+        <v>0.35</v>
+      </c>
+      <c r="AF47" s="34"/>
+      <c r="AG47" s="34"/>
+      <c r="AH47" s="47">
         <v>46167</v>
       </c>
-      <c r="AF47" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="AK47" s="34" t="s">
-        <v>137</v>
-      </c>
-      <c r="AL47" s="34" t="s">
-        <v>120</v>
-      </c>
-      <c r="AM47" s="34">
+      <c r="AI47" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN47" s="34" t="s">
+        <v>140</v>
+      </c>
+      <c r="AO47" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="AP47" s="34">
         <v>146.93</v>
       </c>
-      <c r="AN47" s="35">
+      <c r="AQ47" s="35">
         <v>46162</v>
       </c>
-      <c r="AO47" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="AP47" s="34" t="s">
-        <v>102</v>
-      </c>
-      <c r="BI47" s="17">
+      <c r="AR47" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="AS47" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="BL47" s="17">
         <v>93</v>
       </c>
-      <c r="BK47" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="BM47" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="CF47" s="17">
+      <c r="BN47" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="BP47" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="CI47" s="17">
         <f t="shared" si="0"/>
         <v>93</v>
       </c>
     </row>
-    <row r="48" spans="1:84" ht="21">
+    <row r="48" spans="1:87" ht="21">
       <c r="A48" s="6" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C48" s="6">
         <v>169.61</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G48" s="17" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="P48" s="34">
         <v>91</v>
@@ -5288,89 +5350,91 @@
       <c r="Q48" s="17">
         <v>142.69999999999999</v>
       </c>
-      <c r="R48" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="S48" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="T48" s="19">
+      <c r="S48" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="T48" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="U48" s="34"/>
+      <c r="V48" s="19">
         <v>46176</v>
       </c>
-      <c r="U48" s="35">
+      <c r="W48" s="35">
         <v>46172</v>
       </c>
-      <c r="V48" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="W48" s="34">
+      <c r="X48" s="35"/>
+      <c r="Y48" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z48" s="34">
         <v>3</v>
       </c>
-      <c r="X48" s="34"/>
-      <c r="Y48" s="34"/>
-      <c r="Z48" s="34"/>
       <c r="AA48" s="34"/>
-      <c r="AB48" s="34">
-        <v>0.35</v>
-      </c>
+      <c r="AB48" s="34"/>
       <c r="AC48" s="34"/>
       <c r="AD48" s="34"/>
-      <c r="AE48" s="47">
+      <c r="AE48" s="34">
+        <v>0.35</v>
+      </c>
+      <c r="AF48" s="34"/>
+      <c r="AG48" s="34"/>
+      <c r="AH48" s="47">
         <v>46167</v>
       </c>
-      <c r="AF48" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="AK48" s="34" t="s">
-        <v>137</v>
-      </c>
-      <c r="AL48" s="34" t="s">
+      <c r="AI48" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN48" s="34" t="s">
         <v>140</v>
       </c>
-      <c r="AM48" s="34">
+      <c r="AO48" s="34" t="s">
+        <v>143</v>
+      </c>
+      <c r="AP48" s="34">
         <v>146.93</v>
       </c>
-      <c r="AN48" s="35">
+      <c r="AQ48" s="35">
         <v>46172</v>
       </c>
-      <c r="AO48" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="AP48" s="34" t="s">
-        <v>102</v>
-      </c>
-      <c r="BI48" s="17">
+      <c r="AR48" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="AS48" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="BL48" s="17">
         <v>93</v>
       </c>
-      <c r="BK48" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="BM48" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="CF48" s="17">
+      <c r="BN48" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="BP48" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="CI48" s="17">
         <f t="shared" si="0"/>
         <v>93</v>
       </c>
     </row>
-    <row r="49" spans="1:84" ht="21">
+    <row r="49" spans="1:87" ht="21">
       <c r="A49" s="6" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C49" s="6">
         <v>118.35</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G49" s="17" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="P49" s="34">
         <v>84.8</v>
@@ -5378,89 +5442,91 @@
       <c r="Q49" s="17">
         <v>105.9</v>
       </c>
-      <c r="R49" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="S49" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="T49" s="19">
+      <c r="S49" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="T49" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="U49" s="34"/>
+      <c r="V49" s="19">
         <v>46175</v>
       </c>
-      <c r="U49" s="35">
+      <c r="W49" s="35">
         <v>46172</v>
       </c>
-      <c r="V49" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="W49" s="34">
+      <c r="X49" s="35"/>
+      <c r="Y49" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z49" s="34">
         <v>3</v>
       </c>
-      <c r="X49" s="34"/>
-      <c r="Y49" s="34"/>
-      <c r="Z49" s="34"/>
       <c r="AA49" s="34"/>
-      <c r="AB49" s="34">
-        <v>0.35</v>
-      </c>
+      <c r="AB49" s="34"/>
       <c r="AC49" s="34"/>
       <c r="AD49" s="34"/>
-      <c r="AE49" s="47">
+      <c r="AE49" s="34">
+        <v>0.35</v>
+      </c>
+      <c r="AF49" s="34"/>
+      <c r="AG49" s="34"/>
+      <c r="AH49" s="47">
         <v>46167</v>
       </c>
-      <c r="AF49" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="AK49" s="34" t="s">
-        <v>145</v>
-      </c>
-      <c r="AL49" s="34" t="s">
-        <v>120</v>
-      </c>
-      <c r="AM49" s="34">
+      <c r="AI49" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN49" s="34" t="s">
+        <v>148</v>
+      </c>
+      <c r="AO49" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="AP49" s="34">
         <v>120.28</v>
       </c>
-      <c r="AN49" s="35">
+      <c r="AQ49" s="35">
         <v>46166</v>
       </c>
-      <c r="AO49" s="34" t="s">
-        <v>141</v>
-      </c>
-      <c r="AP49" s="34" t="s">
-        <v>102</v>
-      </c>
-      <c r="BI49" s="17">
+      <c r="AR49" s="34" t="s">
+        <v>144</v>
+      </c>
+      <c r="AS49" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="BL49" s="17">
         <v>93</v>
       </c>
-      <c r="BK49" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="BM49" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="CF49" s="17">
+      <c r="BN49" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="BP49" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="CI49" s="17">
         <f t="shared" si="0"/>
         <v>93</v>
       </c>
     </row>
-    <row r="50" spans="1:84" ht="21">
+    <row r="50" spans="1:87" ht="21">
       <c r="A50" s="6" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C50" s="6">
         <v>243.29</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G50" s="17" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="P50" s="34">
         <v>105.1</v>
@@ -5468,367 +5534,369 @@
       <c r="Q50" s="17">
         <v>88.1</v>
       </c>
-      <c r="R50" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="S50" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="T50" s="19">
+      <c r="S50" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="T50" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="U50" s="34"/>
+      <c r="V50" s="19">
         <v>46174</v>
       </c>
-      <c r="U50" s="35">
+      <c r="W50" s="35">
         <v>46172</v>
       </c>
-      <c r="V50" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="W50" s="34">
+      <c r="X50" s="35"/>
+      <c r="Y50" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z50" s="34">
         <v>3</v>
       </c>
-      <c r="X50" s="34"/>
-      <c r="Y50" s="34"/>
-      <c r="Z50" s="34"/>
       <c r="AA50" s="34"/>
-      <c r="AB50" s="34">
-        <v>0.35</v>
-      </c>
+      <c r="AB50" s="34"/>
       <c r="AC50" s="34"/>
       <c r="AD50" s="34"/>
-      <c r="AE50" s="47">
+      <c r="AE50" s="34">
+        <v>0.35</v>
+      </c>
+      <c r="AF50" s="34"/>
+      <c r="AG50" s="34"/>
+      <c r="AH50" s="47">
         <v>46167</v>
       </c>
-      <c r="AF50" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="AK50" s="34" t="s">
-        <v>145</v>
-      </c>
-      <c r="AL50" s="34" t="s">
-        <v>120</v>
-      </c>
-      <c r="AM50" s="34">
+      <c r="AI50" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN50" s="34" t="s">
+        <v>148</v>
+      </c>
+      <c r="AO50" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="AP50" s="34">
         <v>120.28</v>
       </c>
-      <c r="AN50" s="35">
+      <c r="AQ50" s="35">
         <v>46163</v>
       </c>
-      <c r="AO50" s="34" t="s">
-        <v>141</v>
-      </c>
-      <c r="AP50" s="34" t="s">
-        <v>102</v>
-      </c>
-      <c r="BI50" s="17">
+      <c r="AR50" s="34" t="s">
+        <v>144</v>
+      </c>
+      <c r="AS50" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="BL50" s="17">
         <v>93</v>
       </c>
-      <c r="BK50" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="BM50" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="CF50" s="17">
+      <c r="BN50" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="BP50" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="CI50" s="17">
         <f t="shared" si="0"/>
         <v>93</v>
       </c>
     </row>
-    <row r="51" spans="1:84" ht="21">
+    <row r="51" spans="1:87" ht="21">
       <c r="A51" s="6" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C51" s="6">
         <v>201.78</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="AE51" s="18"/>
-      <c r="AK51" s="34" t="s">
-        <v>119</v>
-      </c>
-      <c r="AL51" s="34" t="s">
-        <v>120</v>
-      </c>
-      <c r="AM51" s="34">
+        <v>97</v>
+      </c>
+      <c r="AH51" s="18"/>
+      <c r="AN51" s="34" t="s">
+        <v>122</v>
+      </c>
+      <c r="AO51" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="AP51" s="34">
         <v>10</v>
       </c>
-      <c r="AN51" s="35">
+      <c r="AQ51" s="35">
         <v>46143</v>
       </c>
-      <c r="AO51" s="34" t="s">
-        <v>121</v>
-      </c>
-      <c r="AP51" s="34" t="s">
-        <v>133</v>
-      </c>
-      <c r="CF51" s="17">
+      <c r="AR51" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="AS51" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="CI51" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:84" ht="21">
+    <row r="52" spans="1:87" ht="21">
       <c r="A52" s="6" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C52" s="6">
         <v>150.52000000000001</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="AE52" s="18"/>
-      <c r="AK52" s="34" t="s">
-        <v>119</v>
-      </c>
-      <c r="AL52" s="34" t="s">
-        <v>120</v>
-      </c>
-      <c r="AM52" s="34">
+        <v>97</v>
+      </c>
+      <c r="AH52" s="18"/>
+      <c r="AN52" s="34" t="s">
+        <v>122</v>
+      </c>
+      <c r="AO52" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="AP52" s="34">
         <v>10</v>
       </c>
-      <c r="AN52" s="35">
+      <c r="AQ52" s="35">
         <v>46143</v>
       </c>
-      <c r="AO52" s="34" t="s">
-        <v>121</v>
-      </c>
-      <c r="AP52" s="34" t="s">
-        <v>133</v>
-      </c>
-      <c r="CF52" s="17">
+      <c r="AR52" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="AS52" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="CI52" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:84" ht="21">
+    <row r="53" spans="1:87" ht="21">
       <c r="A53" s="6" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C53" s="6">
         <v>225.15</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="AE53" s="18"/>
-      <c r="AK53" s="34" t="s">
-        <v>119</v>
-      </c>
-      <c r="AL53" s="34" t="s">
-        <v>120</v>
-      </c>
-      <c r="AM53" s="34">
+        <v>97</v>
+      </c>
+      <c r="AH53" s="18"/>
+      <c r="AN53" s="34" t="s">
+        <v>122</v>
+      </c>
+      <c r="AO53" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="AP53" s="34">
         <v>10</v>
       </c>
-      <c r="AN53" s="35">
+      <c r="AQ53" s="35">
         <v>46143</v>
       </c>
-      <c r="AO53" s="34" t="s">
-        <v>121</v>
-      </c>
-      <c r="AP53" s="34" t="s">
-        <v>133</v>
-      </c>
-      <c r="CF53" s="17">
+      <c r="AR53" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="AS53" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="CI53" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:84">
-      <c r="AE54" s="18"/>
-    </row>
-    <row r="55" spans="1:84">
-      <c r="AE55" s="18"/>
-    </row>
-    <row r="56" spans="1:84">
-      <c r="AE56" s="18"/>
-    </row>
-    <row r="57" spans="1:84">
-      <c r="AE57" s="18"/>
-    </row>
-    <row r="58" spans="1:84">
-      <c r="AE58" s="18"/>
-    </row>
-    <row r="59" spans="1:84">
-      <c r="AE59" s="18"/>
-    </row>
-    <row r="60" spans="1:84">
-      <c r="AE60" s="18"/>
-    </row>
-    <row r="61" spans="1:84">
-      <c r="AE61" s="18"/>
-    </row>
-    <row r="62" spans="1:84">
-      <c r="AE62" s="18"/>
-    </row>
-    <row r="63" spans="1:84">
-      <c r="AE63" s="18"/>
-    </row>
-    <row r="64" spans="1:84">
-      <c r="AE64" s="18"/>
-    </row>
-    <row r="65" spans="31:31">
-      <c r="AE65" s="18"/>
-    </row>
-    <row r="66" spans="31:31">
-      <c r="AE66" s="18"/>
-    </row>
-    <row r="67" spans="31:31">
-      <c r="AE67" s="18"/>
-    </row>
-    <row r="68" spans="31:31">
-      <c r="AE68" s="18"/>
-    </row>
-    <row r="69" spans="31:31">
-      <c r="AE69" s="18"/>
-    </row>
-    <row r="70" spans="31:31">
-      <c r="AE70" s="18"/>
-    </row>
-    <row r="71" spans="31:31">
-      <c r="AE71" s="18"/>
-    </row>
-    <row r="72" spans="31:31">
-      <c r="AE72" s="18"/>
-    </row>
-    <row r="73" spans="31:31">
-      <c r="AE73" s="18"/>
-    </row>
-    <row r="74" spans="31:31">
-      <c r="AE74" s="18"/>
-    </row>
-    <row r="75" spans="31:31">
-      <c r="AE75" s="18"/>
-    </row>
-    <row r="76" spans="31:31">
-      <c r="AE76" s="18"/>
-    </row>
-    <row r="77" spans="31:31">
-      <c r="AE77" s="18"/>
-    </row>
-    <row r="78" spans="31:31">
-      <c r="AE78" s="18"/>
-    </row>
-    <row r="79" spans="31:31">
-      <c r="AE79" s="18"/>
-    </row>
-    <row r="80" spans="31:31">
-      <c r="AE80" s="18"/>
-    </row>
-    <row r="81" spans="31:31">
-      <c r="AE81" s="18"/>
-    </row>
-    <row r="82" spans="31:31">
-      <c r="AE82" s="18"/>
-    </row>
-    <row r="83" spans="31:31">
-      <c r="AE83" s="18"/>
-    </row>
-    <row r="84" spans="31:31">
-      <c r="AE84" s="18"/>
-    </row>
-    <row r="85" spans="31:31">
-      <c r="AE85" s="18"/>
-    </row>
-    <row r="86" spans="31:31">
-      <c r="AE86" s="18"/>
-    </row>
-    <row r="87" spans="31:31">
-      <c r="AE87" s="18"/>
-    </row>
-    <row r="88" spans="31:31">
-      <c r="AE88" s="18"/>
-    </row>
-    <row r="89" spans="31:31">
-      <c r="AE89" s="18"/>
-    </row>
-    <row r="90" spans="31:31">
-      <c r="AE90" s="18"/>
-    </row>
-    <row r="91" spans="31:31">
-      <c r="AE91" s="18"/>
-    </row>
-    <row r="92" spans="31:31">
-      <c r="AE92" s="18"/>
-    </row>
-    <row r="93" spans="31:31">
-      <c r="AE93" s="18"/>
-    </row>
-    <row r="94" spans="31:31">
-      <c r="AE94" s="18"/>
-    </row>
-    <row r="95" spans="31:31">
-      <c r="AE95" s="18"/>
-    </row>
-    <row r="96" spans="31:31">
-      <c r="AE96" s="18"/>
-    </row>
-    <row r="97" spans="31:31">
-      <c r="AE97" s="18"/>
-    </row>
-    <row r="98" spans="31:31">
-      <c r="AE98" s="18"/>
-    </row>
-    <row r="99" spans="31:31">
-      <c r="AE99" s="18"/>
-    </row>
-    <row r="100" spans="31:31">
-      <c r="AE100" s="18"/>
-    </row>
-    <row r="101" spans="31:31">
-      <c r="AE101" s="18"/>
-    </row>
-    <row r="102" spans="31:31">
-      <c r="AE102" s="18"/>
-    </row>
-    <row r="103" spans="31:31">
-      <c r="AE103" s="18"/>
-    </row>
-    <row r="104" spans="31:31">
-      <c r="AE104" s="18"/>
+    <row r="54" spans="1:87">
+      <c r="AH54" s="18"/>
+    </row>
+    <row r="55" spans="1:87">
+      <c r="AH55" s="18"/>
+    </row>
+    <row r="56" spans="1:87">
+      <c r="AH56" s="18"/>
+    </row>
+    <row r="57" spans="1:87">
+      <c r="AH57" s="18"/>
+    </row>
+    <row r="58" spans="1:87">
+      <c r="AH58" s="18"/>
+    </row>
+    <row r="59" spans="1:87">
+      <c r="AH59" s="18"/>
+    </row>
+    <row r="60" spans="1:87">
+      <c r="AH60" s="18"/>
+    </row>
+    <row r="61" spans="1:87">
+      <c r="AH61" s="18"/>
+    </row>
+    <row r="62" spans="1:87">
+      <c r="AH62" s="18"/>
+    </row>
+    <row r="63" spans="1:87">
+      <c r="AH63" s="18"/>
+    </row>
+    <row r="64" spans="1:87">
+      <c r="AH64" s="18"/>
+    </row>
+    <row r="65" spans="34:34">
+      <c r="AH65" s="18"/>
+    </row>
+    <row r="66" spans="34:34">
+      <c r="AH66" s="18"/>
+    </row>
+    <row r="67" spans="34:34">
+      <c r="AH67" s="18"/>
+    </row>
+    <row r="68" spans="34:34">
+      <c r="AH68" s="18"/>
+    </row>
+    <row r="69" spans="34:34">
+      <c r="AH69" s="18"/>
+    </row>
+    <row r="70" spans="34:34">
+      <c r="AH70" s="18"/>
+    </row>
+    <row r="71" spans="34:34">
+      <c r="AH71" s="18"/>
+    </row>
+    <row r="72" spans="34:34">
+      <c r="AH72" s="18"/>
+    </row>
+    <row r="73" spans="34:34">
+      <c r="AH73" s="18"/>
+    </row>
+    <row r="74" spans="34:34">
+      <c r="AH74" s="18"/>
+    </row>
+    <row r="75" spans="34:34">
+      <c r="AH75" s="18"/>
+    </row>
+    <row r="76" spans="34:34">
+      <c r="AH76" s="18"/>
+    </row>
+    <row r="77" spans="34:34">
+      <c r="AH77" s="18"/>
+    </row>
+    <row r="78" spans="34:34">
+      <c r="AH78" s="18"/>
+    </row>
+    <row r="79" spans="34:34">
+      <c r="AH79" s="18"/>
+    </row>
+    <row r="80" spans="34:34">
+      <c r="AH80" s="18"/>
+    </row>
+    <row r="81" spans="34:34">
+      <c r="AH81" s="18"/>
+    </row>
+    <row r="82" spans="34:34">
+      <c r="AH82" s="18"/>
+    </row>
+    <row r="83" spans="34:34">
+      <c r="AH83" s="18"/>
+    </row>
+    <row r="84" spans="34:34">
+      <c r="AH84" s="18"/>
+    </row>
+    <row r="85" spans="34:34">
+      <c r="AH85" s="18"/>
+    </row>
+    <row r="86" spans="34:34">
+      <c r="AH86" s="18"/>
+    </row>
+    <row r="87" spans="34:34">
+      <c r="AH87" s="18"/>
+    </row>
+    <row r="88" spans="34:34">
+      <c r="AH88" s="18"/>
+    </row>
+    <row r="89" spans="34:34">
+      <c r="AH89" s="18"/>
+    </row>
+    <row r="90" spans="34:34">
+      <c r="AH90" s="18"/>
+    </row>
+    <row r="91" spans="34:34">
+      <c r="AH91" s="18"/>
+    </row>
+    <row r="92" spans="34:34">
+      <c r="AH92" s="18"/>
+    </row>
+    <row r="93" spans="34:34">
+      <c r="AH93" s="18"/>
+    </row>
+    <row r="94" spans="34:34">
+      <c r="AH94" s="18"/>
+    </row>
+    <row r="95" spans="34:34">
+      <c r="AH95" s="18"/>
+    </row>
+    <row r="96" spans="34:34">
+      <c r="AH96" s="18"/>
+    </row>
+    <row r="97" spans="34:34">
+      <c r="AH97" s="18"/>
+    </row>
+    <row r="98" spans="34:34">
+      <c r="AH98" s="18"/>
+    </row>
+    <row r="99" spans="34:34">
+      <c r="AH99" s="18"/>
+    </row>
+    <row r="100" spans="34:34">
+      <c r="AH100" s="18"/>
+    </row>
+    <row r="101" spans="34:34">
+      <c r="AH101" s="18"/>
+    </row>
+    <row r="102" spans="34:34">
+      <c r="AH102" s="18"/>
+    </row>
+    <row r="103" spans="34:34">
+      <c r="AH103" s="18"/>
+    </row>
+    <row r="104" spans="34:34">
+      <c r="AH104" s="18"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AF53" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:AI53" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="20">
     <mergeCell ref="F1:N1"/>
-    <mergeCell ref="O1:V1"/>
-    <mergeCell ref="W1:AF1"/>
-    <mergeCell ref="AK1:AP1"/>
-    <mergeCell ref="AQ1:AW1"/>
-    <mergeCell ref="AG1:AJ1"/>
-    <mergeCell ref="AX1:BC1"/>
-    <mergeCell ref="BG1:BH1"/>
-    <mergeCell ref="BI1:BM1"/>
-    <mergeCell ref="BN1:BS1"/>
-    <mergeCell ref="BT1:BY1"/>
-    <mergeCell ref="BD1:BF1"/>
+    <mergeCell ref="O1:Y1"/>
+    <mergeCell ref="Z1:AI1"/>
+    <mergeCell ref="AN1:AS1"/>
+    <mergeCell ref="AT1:AZ1"/>
+    <mergeCell ref="AJ1:AM1"/>
+    <mergeCell ref="BA1:BF1"/>
+    <mergeCell ref="BJ1:BK1"/>
+    <mergeCell ref="BL1:BP1"/>
+    <mergeCell ref="BQ1:BV1"/>
+    <mergeCell ref="BW1:CB1"/>
+    <mergeCell ref="BG1:BI1"/>
+    <mergeCell ref="DF1:DH1"/>
+    <mergeCell ref="DI1:DK1"/>
+    <mergeCell ref="DL1:DO1"/>
+    <mergeCell ref="CC1:CH1"/>
+    <mergeCell ref="CJ1:CL1"/>
+    <mergeCell ref="CM1:CQ1"/>
+    <mergeCell ref="CR1:DB1"/>
     <mergeCell ref="DC1:DE1"/>
-    <mergeCell ref="DF1:DH1"/>
-    <mergeCell ref="DI1:DL1"/>
-    <mergeCell ref="BZ1:CE1"/>
-    <mergeCell ref="CG1:CI1"/>
-    <mergeCell ref="CJ1:CN1"/>
-    <mergeCell ref="CO1:CY1"/>
-    <mergeCell ref="CZ1:DB1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5864,15 +5932,15 @@
         <v>22</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="21">
       <c r="A3" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B3" s="6">
         <v>1</v>
@@ -5881,15 +5949,15 @@
         <v>203.49</v>
       </c>
       <c r="D3" s="84" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="21">
       <c r="A4" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B4" s="6">
         <v>2</v>
@@ -5898,15 +5966,15 @@
         <v>215</v>
       </c>
       <c r="D4" s="84" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="21">
       <c r="A5" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B5" s="6">
         <v>3</v>
@@ -5915,15 +5983,15 @@
         <v>46.12</v>
       </c>
       <c r="D5" s="84" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="21">
       <c r="A6" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B6" s="6">
         <v>7</v>
@@ -5932,15 +6000,15 @@
         <v>24.03</v>
       </c>
       <c r="D6" s="84" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="21">
       <c r="A7" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B7" s="6">
         <v>8</v>
@@ -5949,15 +6017,15 @@
         <v>22.55</v>
       </c>
       <c r="D7" s="84" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="21">
       <c r="A8" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B8" s="6">
         <v>9</v>
@@ -5966,15 +6034,15 @@
         <v>62.73</v>
       </c>
       <c r="D8" s="84" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="21">
       <c r="A9" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B9" s="6">
         <v>10</v>
@@ -5983,15 +6051,15 @@
         <v>29.7</v>
       </c>
       <c r="D9" s="84" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="21">
       <c r="A10" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B10" s="6">
         <v>11</v>
@@ -6000,15 +6068,15 @@
         <v>270.44</v>
       </c>
       <c r="D10" s="84" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="21">
       <c r="A11" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B11" s="6">
         <v>12</v>
@@ -6017,15 +6085,15 @@
         <v>64.25</v>
       </c>
       <c r="D11" s="84" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="21">
       <c r="A12" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B12" s="6">
         <v>13</v>
@@ -6034,15 +6102,15 @@
         <v>29.89</v>
       </c>
       <c r="D12" s="84" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="21">
       <c r="A13" s="6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B13" s="6">
         <v>6</v>
@@ -6051,15 +6119,15 @@
         <v>52.63</v>
       </c>
       <c r="D13" s="84" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="21">
       <c r="A14" s="6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B14" s="6">
         <v>7</v>
@@ -6068,15 +6136,15 @@
         <v>60.61</v>
       </c>
       <c r="D14" s="84" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="21">
       <c r="A15" s="6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B15" s="6">
         <v>11</v>
@@ -6085,15 +6153,15 @@
         <v>56.69</v>
       </c>
       <c r="D15" s="84" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="21">
       <c r="A16" s="6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B16" s="6">
         <v>12</v>
@@ -6102,15 +6170,15 @@
         <v>49.78</v>
       </c>
       <c r="D16" s="84" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="21">
       <c r="A17" s="6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B17" s="6">
         <v>13</v>
@@ -6119,15 +6187,15 @@
         <v>26.67</v>
       </c>
       <c r="D17" s="84" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="21">
       <c r="A18" s="6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B18" s="6">
         <v>14</v>
@@ -6136,15 +6204,15 @@
         <v>33.96</v>
       </c>
       <c r="D18" s="84" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="21">
       <c r="A19" s="6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B19" s="6">
         <v>16</v>
@@ -6153,15 +6221,15 @@
         <v>91.46</v>
       </c>
       <c r="D19" s="84" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="21">
       <c r="A20" s="6" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B20" s="6">
         <v>1</v>
@@ -6170,15 +6238,15 @@
         <v>58.59</v>
       </c>
       <c r="D20" s="84" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="21">
       <c r="A21" s="6" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B21" s="6">
         <v>2</v>
@@ -6187,15 +6255,15 @@
         <v>40.99</v>
       </c>
       <c r="D21" s="84" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="21">
       <c r="A22" s="6" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B22" s="6">
         <v>3</v>
@@ -6204,15 +6272,15 @@
         <v>63.11</v>
       </c>
       <c r="D22" s="84" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="21">
       <c r="A23" s="6" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B23" s="6">
         <v>4</v>
@@ -6221,15 +6289,15 @@
         <v>71.48</v>
       </c>
       <c r="D23" s="84" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="21">
       <c r="A24" s="6" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B24" s="6">
         <v>5</v>
@@ -6238,15 +6306,15 @@
         <v>67.739999999999995</v>
       </c>
       <c r="D24" s="84" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="21">
       <c r="A25" s="6" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B25" s="6">
         <v>6</v>
@@ -6255,15 +6323,15 @@
         <v>24.52</v>
       </c>
       <c r="D25" s="84" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="21">
       <c r="A26" s="6" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B26" s="6">
         <v>11</v>
@@ -6272,15 +6340,15 @@
         <v>31</v>
       </c>
       <c r="D26" s="84" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="21">
       <c r="A27" s="6" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B27" s="6">
         <v>12</v>
@@ -6289,15 +6357,15 @@
         <v>67</v>
       </c>
       <c r="D27" s="84" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="21">
       <c r="A28" s="6" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B28" s="6">
         <v>1</v>
@@ -6306,15 +6374,15 @@
         <v>138.88</v>
       </c>
       <c r="D28" s="84" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="21">
       <c r="A29" s="6" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B29" s="6">
         <v>2</v>
@@ -6323,15 +6391,15 @@
         <v>141.69999999999999</v>
       </c>
       <c r="D29" s="84" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="21">
       <c r="A30" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B30" s="6">
         <v>1</v>
@@ -6340,15 +6408,15 @@
         <v>101.74</v>
       </c>
       <c r="D30" s="84" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="21">
       <c r="A31" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B31" s="6">
         <v>2</v>
@@ -6357,15 +6425,15 @@
         <v>34.99</v>
       </c>
       <c r="D31" s="84" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="21">
       <c r="A32" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B32" s="6">
         <v>3</v>
@@ -6374,15 +6442,15 @@
         <v>301.24</v>
       </c>
       <c r="D32" s="84" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="21">
       <c r="A33" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B33" s="6">
         <v>4</v>
@@ -6391,15 +6459,15 @@
         <v>180.2</v>
       </c>
       <c r="D33" s="84" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="21">
       <c r="A34" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B34" s="6">
         <v>5</v>
@@ -6408,15 +6476,15 @@
         <v>59.08</v>
       </c>
       <c r="D34" s="84" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="21">
       <c r="A35" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B35" s="6">
         <v>7</v>
@@ -6425,15 +6493,15 @@
         <v>46.79</v>
       </c>
       <c r="D35" s="84" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="21">
       <c r="A36" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B36" s="6">
         <v>8</v>
@@ -6442,15 +6510,15 @@
         <v>59.05</v>
       </c>
       <c r="D36" s="84" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="21">
       <c r="A37" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B37" s="6">
         <v>9</v>
@@ -6459,15 +6527,15 @@
         <v>103.45</v>
       </c>
       <c r="D37" s="84" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="21">
       <c r="A38" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B38" s="6">
         <v>10</v>
@@ -6476,15 +6544,15 @@
         <v>101.88</v>
       </c>
       <c r="D38" s="84" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="21">
       <c r="A39" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B39" s="6">
         <v>11</v>
@@ -6493,15 +6561,15 @@
         <v>53.38</v>
       </c>
       <c r="D39" s="84" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="21">
       <c r="A40" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B40" s="6">
         <v>12</v>
@@ -6510,15 +6578,15 @@
         <v>102.7</v>
       </c>
       <c r="D40" s="84" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="21">
       <c r="A41" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B41" s="6">
         <v>13</v>
@@ -6527,15 +6595,15 @@
         <v>87.11</v>
       </c>
       <c r="D41" s="84" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="21">
       <c r="A42" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B42" s="6">
         <v>14</v>
@@ -6544,15 +6612,15 @@
         <v>59.42</v>
       </c>
       <c r="D42" s="84" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="21">
       <c r="A43" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B43" s="6">
         <v>15</v>
@@ -6561,180 +6629,180 @@
         <v>35.96</v>
       </c>
       <c r="D43" s="84" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="21">
       <c r="A44" s="6" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C44" s="6">
         <v>386.2</v>
       </c>
       <c r="D44" s="84" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="21">
       <c r="A45" s="6" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C45" s="6">
         <v>120</v>
       </c>
       <c r="D45" s="84" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="21">
       <c r="A46" s="6" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C46" s="9">
         <v>163</v>
       </c>
       <c r="D46" s="84" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="21">
       <c r="A47" s="6" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C47" s="6">
         <v>189.75</v>
       </c>
       <c r="D47" s="84" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="21">
       <c r="A48" s="6" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C48" s="6">
         <v>169.61</v>
       </c>
       <c r="D48" s="84" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="21">
       <c r="A49" s="6" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C49" s="6">
         <v>118.35</v>
       </c>
       <c r="D49" s="84" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="21">
       <c r="A50" s="6" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C50" s="6">
         <v>243.29</v>
       </c>
       <c r="D50" s="84" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="21">
       <c r="A51" s="6" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C51" s="6">
         <v>201.78</v>
       </c>
       <c r="D51" s="84" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="21">
       <c r="A52" s="6" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C52" s="6">
         <v>150.52000000000001</v>
       </c>
       <c r="D52" s="84" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="21">
       <c r="A53" s="6" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C53" s="6">
         <v>225.15</v>
       </c>
       <c r="D53" s="84" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -6818,156 +6886,156 @@
         <v>20</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C2" s="38" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D2" s="37" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E2" s="37" t="s">
+        <v>158</v>
+      </c>
+      <c r="F2" s="37" t="s">
+        <v>159</v>
+      </c>
+      <c r="G2" s="37" t="s">
+        <v>160</v>
+      </c>
+      <c r="H2" s="37" t="s">
+        <v>161</v>
+      </c>
+      <c r="I2" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="J2" s="37" t="s">
+        <v>163</v>
+      </c>
+      <c r="K2" s="37" t="s">
+        <v>164</v>
+      </c>
+      <c r="L2" s="37" t="s">
+        <v>165</v>
+      </c>
+      <c r="M2" s="37" t="s">
+        <v>166</v>
+      </c>
+      <c r="N2" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="F2" s="37" t="s">
+      <c r="O2" s="38" t="s">
         <v>156</v>
       </c>
-      <c r="G2" s="37" t="s">
+      <c r="P2" s="37" t="s">
         <v>157</v>
       </c>
-      <c r="H2" s="37" t="s">
+      <c r="Q2" s="37" t="s">
         <v>158</v>
       </c>
-      <c r="I2" s="37" t="s">
+      <c r="R2" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="J2" s="37" t="s">
+      <c r="S2" s="37" t="s">
         <v>160</v>
       </c>
-      <c r="K2" s="37" t="s">
+      <c r="T2" s="37" t="s">
         <v>161</v>
       </c>
-      <c r="L2" s="37" t="s">
+      <c r="U2" s="37" t="s">
         <v>162</v>
       </c>
-      <c r="M2" s="37" t="s">
+      <c r="V2" s="37" t="s">
         <v>163</v>
       </c>
-      <c r="N2" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="O2" s="38" t="s">
-        <v>153</v>
-      </c>
-      <c r="P2" s="37" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q2" s="37" t="s">
+      <c r="W2" s="37" t="s">
+        <v>164</v>
+      </c>
+      <c r="X2" s="37" t="s">
+        <v>165</v>
+      </c>
+      <c r="Y2" s="37" t="s">
+        <v>166</v>
+      </c>
+      <c r="Z2" s="39" t="s">
         <v>155</v>
       </c>
-      <c r="R2" s="37" t="s">
+      <c r="AA2" s="37" t="s">
         <v>156</v>
       </c>
-      <c r="S2" s="37" t="s">
+      <c r="AB2" s="37" t="s">
         <v>157</v>
       </c>
-      <c r="T2" s="37" t="s">
+      <c r="AC2" s="37" t="s">
         <v>158</v>
       </c>
-      <c r="U2" s="37" t="s">
+      <c r="AD2" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="V2" s="37" t="s">
+      <c r="AE2" s="37" t="s">
         <v>160</v>
       </c>
-      <c r="W2" s="37" t="s">
+      <c r="AF2" s="37" t="s">
         <v>161</v>
       </c>
-      <c r="X2" s="37" t="s">
+      <c r="AG2" s="37" t="s">
         <v>162</v>
       </c>
-      <c r="Y2" s="37" t="s">
+      <c r="AH2" s="37" t="s">
         <v>163</v>
       </c>
-      <c r="Z2" s="39" t="s">
-        <v>152</v>
-      </c>
-      <c r="AA2" s="37" t="s">
-        <v>153</v>
-      </c>
-      <c r="AB2" s="37" t="s">
-        <v>154</v>
-      </c>
-      <c r="AC2" s="37" t="s">
+      <c r="AI2" s="37" t="s">
+        <v>164</v>
+      </c>
+      <c r="AJ2" s="37" t="s">
+        <v>165</v>
+      </c>
+      <c r="AK2" s="37" t="s">
+        <v>166</v>
+      </c>
+      <c r="AL2" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="AD2" s="37" t="s">
+      <c r="AM2" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="AE2" s="37" t="s">
+      <c r="AN2" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="AF2" s="37" t="s">
+      <c r="AO2" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="AG2" s="37" t="s">
+      <c r="AP2" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="AH2" s="37" t="s">
+      <c r="AQ2" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="AI2" s="37" t="s">
+      <c r="AR2" s="17" t="s">
         <v>161</v>
       </c>
-      <c r="AJ2" s="37" t="s">
+      <c r="AS2" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="AK2" s="37" t="s">
+      <c r="AT2" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="AL2" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="AM2" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="AN2" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="AO2" s="17" t="s">
+      <c r="AU2" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="AV2" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="AW2" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="AX2" s="17" t="s">
         <v>155</v>
-      </c>
-      <c r="AP2" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="AQ2" s="17" t="s">
-        <v>157</v>
-      </c>
-      <c r="AR2" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="AS2" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="AT2" s="17" t="s">
-        <v>160</v>
-      </c>
-      <c r="AU2" s="17" t="s">
-        <v>161</v>
-      </c>
-      <c r="AV2" s="17" t="s">
-        <v>162</v>
-      </c>
-      <c r="AW2" s="17" t="s">
-        <v>163</v>
-      </c>
-      <c r="AX2" s="17" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:50">
       <c r="A3" s="37" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B3" s="37">
         <v>45</v>
@@ -7115,7 +7183,7 @@
     </row>
     <row r="4" spans="1:50">
       <c r="A4" s="40" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B4" s="40">
         <v>47</v>
@@ -7263,7 +7331,7 @@
     </row>
     <row r="5" spans="1:50">
       <c r="A5" s="37" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B5" s="37">
         <v>35</v>
@@ -7411,7 +7479,7 @@
     </row>
     <row r="6" spans="1:50">
       <c r="A6" s="37" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B6" s="37">
         <v>47</v>
@@ -7559,7 +7627,7 @@
     </row>
     <row r="7" spans="1:50">
       <c r="A7" s="37" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B7" s="37">
         <v>35</v>

--- a/Planilla labores 26-27.xlsx
+++ b/Planilla labores 26-27.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30215"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8E5EEE44-6D32-495A-8A88-9D6C5818353F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{13244E1D-A13F-4866-9C60-FE1961213832}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13,6 +13,7 @@
     <sheet name="Lluvias" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Verano!$A$2:$E$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Invierno!$A$2:$AI$53</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="180">
   <si>
     <t>Análisis suelo</t>
   </si>
@@ -257,15 +258,15 @@
     <t>Zona</t>
   </si>
   <si>
+    <t>Korvetto</t>
+  </si>
+  <si>
     <t>Lontrel</t>
   </si>
   <si>
     <t>Tordon</t>
   </si>
   <si>
-    <t>Arsenal</t>
-  </si>
-  <si>
     <t>Axial</t>
   </si>
   <si>
@@ -278,7 +279,7 @@
     <t>Vitagrow</t>
   </si>
   <si>
-    <t>Tronador</t>
+    <t>Tronador (1pack/25ha)</t>
   </si>
   <si>
     <t>Producto</t>
@@ -311,6 +312,12 @@
     <t>Cargill</t>
   </si>
   <si>
+    <t>Cofco</t>
+  </si>
+  <si>
+    <t>Programado</t>
+  </si>
+  <si>
     <t>Belassi</t>
   </si>
   <si>
@@ -326,6 +333,9 @@
     <t>Plantadora</t>
   </si>
   <si>
+    <t>todo menos fondo y frente de 24ha</t>
+  </si>
+  <si>
     <t>Sj2</t>
   </si>
   <si>
@@ -356,6 +366,9 @@
     <t>Araña</t>
   </si>
   <si>
+    <t>todo</t>
+  </si>
+  <si>
     <t>2,5 (10ha)</t>
   </si>
   <si>
@@ -371,6 +384,9 @@
     <t>Galpon Hub y Bichadero</t>
   </si>
   <si>
+    <t>todo menos melgas contra 15</t>
+  </si>
+  <si>
     <t>La Campana</t>
   </si>
   <si>
@@ -395,7 +411,7 @@
     <t>EasyAgro</t>
   </si>
   <si>
-    <t>Cofco</t>
+    <t>de la entrada hasta la mitad</t>
   </si>
   <si>
     <t>La Blanqueada</t>
@@ -461,6 +477,9 @@
     <t>Osiris</t>
   </si>
   <si>
+    <t>todo menos contra juanes</t>
+  </si>
+  <si>
     <t>Chaniar norte</t>
   </si>
   <si>
@@ -473,19 +492,34 @@
     <t>Frilor</t>
   </si>
   <si>
+    <t>todo menos melgas del manguera</t>
+  </si>
+  <si>
     <t>Los Juanes</t>
   </si>
   <si>
+    <t>todo menos fondo</t>
+  </si>
+  <si>
     <t>Manguera E</t>
   </si>
   <si>
+    <t>todo menos lenguas contra vecino</t>
+  </si>
+  <si>
     <t>Manguera w</t>
   </si>
   <si>
     <t>Olimpia</t>
   </si>
   <si>
+    <t>todo menos ctra puesto</t>
+  </si>
+  <si>
     <t>Nianiez</t>
+  </si>
+  <si>
+    <t>todo menos entrada a la izquierda</t>
   </si>
   <si>
     <t>Trillo</t>
@@ -549,9 +583,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@"/>
     <numFmt numFmtId="165" formatCode="#,##0.00_ ;\-#,##0.00\ "/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -840,7 +875,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -986,6 +1021,18 @@
     <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1090,9 +1137,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1408,7 +1452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DO104"/>
+  <dimension ref="A1:DP104"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.28515625" style="17" bestFit="1" customWidth="1"/>
@@ -1416,223 +1460,221 @@
     <col min="3" max="3" width="10.85546875" style="17" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.140625" style="17" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="18.28515625" style="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" style="17" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="16.5703125" style="17" hidden="1" customWidth="1"/>
-    <col min="8" max="14" width="9.140625" style="17" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.7109375" style="17" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.7109375" style="17" customWidth="1"/>
-    <col min="19" max="20" width="15.5703125" style="17" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.5703125" style="17" customWidth="1"/>
-    <col min="22" max="22" width="16.85546875" style="17" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="16.42578125" style="17" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="16.42578125" style="17" customWidth="1"/>
-    <col min="25" max="33" width="9.140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="11.42578125" style="17" bestFit="1" customWidth="1"/>
-    <col min="35" max="38" width="9.140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="10.85546875" style="17" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="17" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="20.5703125" style="17" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="20.5703125" style="17" customWidth="1"/>
-    <col min="43" max="43" width="16" style="17" customWidth="1"/>
-    <col min="44" max="44" width="16" style="17" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="18" style="17" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="13.42578125" style="17" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="20.5703125" style="17" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="20.5703125" style="17" customWidth="1"/>
-    <col min="49" max="49" width="24.140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="9.140625" style="17"/>
-    <col min="51" max="51" width="16" style="17" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="18" style="17" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="13.42578125" style="17" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="20.5703125" style="17" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="24.140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="9.140625" style="17"/>
-    <col min="57" max="57" width="16" style="17" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="18" style="17" bestFit="1" customWidth="1"/>
-    <col min="59" max="61" width="18" style="17" customWidth="1"/>
-    <col min="62" max="62" width="9.140625" style="17"/>
-    <col min="63" max="63" width="11" style="17" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="12" style="17" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="12.28515625" style="17" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="10.42578125" style="17" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="9.7109375" style="17" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="16" style="17" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="9.140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="70" max="71" width="9.140625" style="17"/>
-    <col min="72" max="72" width="9.140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="9.140625" style="17"/>
-    <col min="74" max="74" width="9.140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="9.140625" style="17"/>
-    <col min="76" max="80" width="9.140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="81" max="81" width="9.140625" style="17"/>
-    <col min="82" max="86" width="9.140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="87" max="87" width="9.140625" style="17"/>
-    <col min="88" max="119" width="9.140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="120" max="16384" width="9.140625" style="17"/>
+    <col min="6" max="6" width="9.7109375" style="17" customWidth="1"/>
+    <col min="7" max="7" width="16.5703125" style="17" customWidth="1"/>
+    <col min="8" max="16" width="9.140625" style="17" customWidth="1"/>
+    <col min="17" max="18" width="11.7109375" style="17" customWidth="1"/>
+    <col min="19" max="21" width="15.5703125" style="17" customWidth="1"/>
+    <col min="22" max="22" width="16.85546875" style="17" customWidth="1"/>
+    <col min="23" max="24" width="16.42578125" style="17" customWidth="1"/>
+    <col min="25" max="33" width="9.140625" style="17" customWidth="1"/>
+    <col min="34" max="34" width="11.42578125" style="17" customWidth="1"/>
+    <col min="35" max="38" width="9.140625" style="17" customWidth="1"/>
+    <col min="39" max="39" width="10.85546875" style="17" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="17" customWidth="1"/>
+    <col min="41" max="42" width="20.5703125" style="17" customWidth="1"/>
+    <col min="43" max="44" width="16" style="17" customWidth="1"/>
+    <col min="45" max="45" width="18" style="17" customWidth="1"/>
+    <col min="46" max="46" width="13.42578125" style="17" customWidth="1"/>
+    <col min="47" max="48" width="20.5703125" style="17" customWidth="1"/>
+    <col min="49" max="49" width="24.140625" style="17" customWidth="1"/>
+    <col min="50" max="50" width="9.140625" style="17" customWidth="1"/>
+    <col min="51" max="51" width="16" style="17" customWidth="1"/>
+    <col min="52" max="52" width="18" style="17" customWidth="1"/>
+    <col min="53" max="53" width="13.42578125" style="17" customWidth="1"/>
+    <col min="54" max="54" width="20.5703125" style="17" customWidth="1"/>
+    <col min="55" max="55" width="24.140625" style="17" customWidth="1"/>
+    <col min="56" max="56" width="9.140625" style="17" customWidth="1"/>
+    <col min="57" max="57" width="16" style="17" customWidth="1"/>
+    <col min="58" max="61" width="18" style="17" customWidth="1"/>
+    <col min="62" max="62" width="9.140625" style="17" customWidth="1"/>
+    <col min="63" max="63" width="11" style="17" customWidth="1"/>
+    <col min="64" max="64" width="12" style="17" customWidth="1"/>
+    <col min="65" max="65" width="12.28515625" style="17" customWidth="1"/>
+    <col min="66" max="66" width="10.42578125" style="17" customWidth="1"/>
+    <col min="67" max="67" width="9.7109375" style="17" customWidth="1"/>
+    <col min="68" max="68" width="16" style="17" customWidth="1"/>
+    <col min="69" max="93" width="9.140625" style="17" customWidth="1"/>
+    <col min="94" max="94" width="32.7109375" style="17" customWidth="1"/>
+    <col min="95" max="95" width="16" style="17" customWidth="1"/>
+    <col min="96" max="96" width="9.7109375" style="17" bestFit="1" customWidth="1"/>
+    <col min="97" max="97" width="13.28515625" style="17" bestFit="1" customWidth="1"/>
+    <col min="98" max="98" width="13.28515625" style="17" customWidth="1"/>
+    <col min="99" max="99" width="10.5703125" style="17" bestFit="1" customWidth="1"/>
+    <col min="100" max="100" width="11" style="17" bestFit="1" customWidth="1"/>
+    <col min="101" max="101" width="11" style="17" customWidth="1"/>
+    <col min="102" max="102" width="8" style="17" bestFit="1" customWidth="1"/>
+    <col min="103" max="103" width="11" style="17" bestFit="1" customWidth="1"/>
+    <col min="104" max="104" width="14.28515625" style="17" bestFit="1" customWidth="1"/>
+    <col min="105" max="105" width="13.140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="106" max="106" width="32.28515625" style="17" bestFit="1" customWidth="1"/>
+    <col min="107" max="107" width="16" style="17" bestFit="1" customWidth="1"/>
+    <col min="108" max="120" width="9.140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="121" max="16384" width="9.140625" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:119" ht="21">
+    <row r="1" spans="1:120" ht="21">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
       <c r="D1" s="4"/>
-      <c r="F1" s="70" t="s">
+      <c r="F1" s="74" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
-      <c r="I1" s="70"/>
-      <c r="J1" s="70"/>
-      <c r="K1" s="70"/>
-      <c r="L1" s="70"/>
-      <c r="M1" s="70"/>
-      <c r="N1" s="70"/>
-      <c r="O1" s="71" t="s">
+      <c r="G1" s="74"/>
+      <c r="H1" s="74"/>
+      <c r="I1" s="74"/>
+      <c r="J1" s="74"/>
+      <c r="K1" s="74"/>
+      <c r="L1" s="74"/>
+      <c r="M1" s="74"/>
+      <c r="N1" s="74"/>
+      <c r="O1" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="72"/>
-      <c r="Q1" s="72"/>
-      <c r="R1" s="72"/>
-      <c r="S1" s="72"/>
-      <c r="T1" s="72"/>
-      <c r="U1" s="72"/>
-      <c r="V1" s="72"/>
-      <c r="W1" s="72"/>
-      <c r="X1" s="72"/>
-      <c r="Y1" s="72"/>
-      <c r="Z1" s="73" t="s">
+      <c r="P1" s="76"/>
+      <c r="Q1" s="76"/>
+      <c r="R1" s="76"/>
+      <c r="S1" s="76"/>
+      <c r="T1" s="76"/>
+      <c r="U1" s="76"/>
+      <c r="V1" s="76"/>
+      <c r="W1" s="76"/>
+      <c r="X1" s="76"/>
+      <c r="Y1" s="76"/>
+      <c r="Z1" s="77" t="s">
         <v>2</v>
       </c>
-      <c r="AA1" s="73"/>
-      <c r="AB1" s="73"/>
-      <c r="AC1" s="73"/>
-      <c r="AD1" s="73"/>
-      <c r="AE1" s="73"/>
-      <c r="AF1" s="73"/>
-      <c r="AG1" s="73"/>
-      <c r="AH1" s="73"/>
-      <c r="AI1" s="73"/>
-      <c r="AJ1" s="79" t="s">
+      <c r="AA1" s="77"/>
+      <c r="AB1" s="77"/>
+      <c r="AC1" s="77"/>
+      <c r="AD1" s="77"/>
+      <c r="AE1" s="77"/>
+      <c r="AF1" s="77"/>
+      <c r="AG1" s="77"/>
+      <c r="AH1" s="77"/>
+      <c r="AI1" s="77"/>
+      <c r="AJ1" s="83" t="s">
         <v>3</v>
       </c>
-      <c r="AK1" s="79"/>
-      <c r="AL1" s="79"/>
-      <c r="AM1" s="79"/>
-      <c r="AN1" s="74" t="s">
+      <c r="AK1" s="83"/>
+      <c r="AL1" s="83"/>
+      <c r="AM1" s="83"/>
+      <c r="AN1" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="AO1" s="74"/>
-      <c r="AP1" s="74"/>
-      <c r="AQ1" s="74"/>
-      <c r="AR1" s="74"/>
-      <c r="AS1" s="75"/>
-      <c r="AT1" s="76" t="s">
+      <c r="AO1" s="78"/>
+      <c r="AP1" s="78"/>
+      <c r="AQ1" s="78"/>
+      <c r="AR1" s="78"/>
+      <c r="AS1" s="79"/>
+      <c r="AT1" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="AU1" s="77"/>
-      <c r="AV1" s="77"/>
-      <c r="AW1" s="77"/>
-      <c r="AX1" s="77"/>
-      <c r="AY1" s="77"/>
-      <c r="AZ1" s="78"/>
-      <c r="BA1" s="59" t="s">
+      <c r="AU1" s="81"/>
+      <c r="AV1" s="81"/>
+      <c r="AW1" s="81"/>
+      <c r="AX1" s="81"/>
+      <c r="AY1" s="81"/>
+      <c r="AZ1" s="82"/>
+      <c r="BA1" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="BB1" s="60"/>
-      <c r="BC1" s="60"/>
-      <c r="BD1" s="60"/>
-      <c r="BE1" s="60"/>
-      <c r="BF1" s="61"/>
-      <c r="BG1" s="67" t="s">
+      <c r="BB1" s="64"/>
+      <c r="BC1" s="64"/>
+      <c r="BD1" s="64"/>
+      <c r="BE1" s="64"/>
+      <c r="BF1" s="65"/>
+      <c r="BG1" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="BH1" s="68"/>
-      <c r="BI1" s="69"/>
-      <c r="BJ1" s="62" t="s">
+      <c r="BH1" s="72"/>
+      <c r="BI1" s="73"/>
+      <c r="BJ1" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="BK1" s="63"/>
-      <c r="BL1" s="64" t="s">
+      <c r="BK1" s="67"/>
+      <c r="BL1" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="BM1" s="64"/>
-      <c r="BN1" s="64"/>
-      <c r="BO1" s="64"/>
-      <c r="BP1" s="64"/>
-      <c r="BQ1" s="65" t="s">
+      <c r="BM1" s="68"/>
+      <c r="BN1" s="68"/>
+      <c r="BO1" s="68"/>
+      <c r="BP1" s="68"/>
+      <c r="BQ1" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="BR1" s="52"/>
-      <c r="BS1" s="52"/>
-      <c r="BT1" s="52"/>
-      <c r="BU1" s="52"/>
-      <c r="BV1" s="66"/>
-      <c r="BW1" s="52" t="s">
+      <c r="BR1" s="56"/>
+      <c r="BS1" s="56"/>
+      <c r="BT1" s="56"/>
+      <c r="BU1" s="56"/>
+      <c r="BV1" s="70"/>
+      <c r="BW1" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="BX1" s="52"/>
-      <c r="BY1" s="52"/>
-      <c r="BZ1" s="52"/>
-      <c r="CA1" s="52"/>
-      <c r="CB1" s="52"/>
-      <c r="CC1" s="52" t="s">
+      <c r="BX1" s="56"/>
+      <c r="BY1" s="56"/>
+      <c r="BZ1" s="56"/>
+      <c r="CA1" s="56"/>
+      <c r="CB1" s="56"/>
+      <c r="CC1" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="CD1" s="52"/>
-      <c r="CE1" s="52"/>
-      <c r="CF1" s="52"/>
-      <c r="CG1" s="52"/>
-      <c r="CH1" s="52"/>
+      <c r="CD1" s="56"/>
+      <c r="CE1" s="56"/>
+      <c r="CF1" s="56"/>
+      <c r="CG1" s="56"/>
+      <c r="CH1" s="56"/>
       <c r="CI1" s="23"/>
-      <c r="CJ1" s="53" t="s">
+      <c r="CJ1" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="CK1" s="53"/>
-      <c r="CL1" s="53"/>
-      <c r="CM1" s="54" t="s">
+      <c r="CK1" s="57"/>
+      <c r="CL1" s="57"/>
+      <c r="CM1" s="58" t="s">
         <v>14</v>
       </c>
-      <c r="CN1" s="54"/>
-      <c r="CO1" s="54"/>
-      <c r="CP1" s="54"/>
-      <c r="CQ1" s="54"/>
-      <c r="CR1" s="55" t="s">
+      <c r="CN1" s="58"/>
+      <c r="CO1" s="58"/>
+      <c r="CP1" s="58"/>
+      <c r="CQ1" s="58"/>
+      <c r="CR1" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="CS1" s="55"/>
-      <c r="CT1" s="55"/>
-      <c r="CU1" s="55"/>
-      <c r="CV1" s="55"/>
-      <c r="CW1" s="55"/>
-      <c r="CX1" s="55"/>
-      <c r="CY1" s="55"/>
-      <c r="CZ1" s="55"/>
-      <c r="DA1" s="55"/>
-      <c r="DB1" s="56"/>
-      <c r="DC1" s="57" t="s">
+      <c r="CS1" s="59"/>
+      <c r="CT1" s="59"/>
+      <c r="CU1" s="59"/>
+      <c r="CV1" s="59"/>
+      <c r="CW1" s="59"/>
+      <c r="CX1" s="59"/>
+      <c r="CY1" s="59"/>
+      <c r="CZ1" s="59"/>
+      <c r="DA1" s="59"/>
+      <c r="DB1" s="59"/>
+      <c r="DC1" s="60"/>
+      <c r="DD1" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="DD1" s="50"/>
-      <c r="DE1" s="58"/>
-      <c r="DF1" s="49" t="s">
+      <c r="DE1" s="54"/>
+      <c r="DF1" s="62"/>
+      <c r="DG1" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="DG1" s="50"/>
-      <c r="DH1" s="50"/>
-      <c r="DI1" s="50" t="s">
+      <c r="DH1" s="54"/>
+      <c r="DI1" s="54"/>
+      <c r="DJ1" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="DJ1" s="50"/>
-      <c r="DK1" s="50"/>
-      <c r="DL1" s="51" t="s">
+      <c r="DK1" s="54"/>
+      <c r="DL1" s="54"/>
+      <c r="DM1" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="DM1" s="51"/>
-      <c r="DN1" s="51"/>
-      <c r="DO1" s="51"/>
-    </row>
-    <row r="2" spans="1:119" ht="21">
+      <c r="DN1" s="55"/>
+      <c r="DO1" s="55"/>
+      <c r="DP1" s="55"/>
+    </row>
+    <row r="2" spans="1:120" ht="21">
       <c r="A2" s="5" t="s">
         <v>20</v>
       </c>
@@ -1934,64 +1976,67 @@
         <v>75</v>
       </c>
       <c r="CW2" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="CX2" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="CX2" s="33" t="s">
+      <c r="CY2" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="CY2" s="33" t="s">
+      <c r="CZ2" s="33" t="s">
         <v>78</v>
       </c>
-      <c r="CZ2" s="33" t="s">
+      <c r="DA2" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="DA2" s="33" t="s">
+      <c r="DB2" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="DB2" s="33" t="s">
+      <c r="DC2" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="DC2" s="24" t="s">
+      <c r="DD2" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="DD2" s="24" t="s">
+      <c r="DE2" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="DE2" s="24" t="s">
+      <c r="DF2" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="DF2" s="25" t="s">
+      <c r="DG2" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="DG2" s="24" t="s">
+      <c r="DH2" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="DH2" s="24" t="s">
+      <c r="DI2" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="DI2" s="25" t="s">
+      <c r="DJ2" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="DJ2" s="24" t="s">
+      <c r="DK2" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="DK2" s="24" t="s">
+      <c r="DL2" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="DL2" s="26" t="s">
+      <c r="DM2" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="DM2" s="26" t="s">
+      <c r="DN2" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="DN2" s="26" t="s">
+      <c r="DO2" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="DO2" s="26" t="s">
+      <c r="DP2" s="26" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:119" ht="21">
+    <row r="3" spans="1:120" ht="21">
       <c r="A3" s="6" t="s">
         <v>86</v>
       </c>
@@ -2035,9 +2080,12 @@
         <v>3.5</v>
       </c>
       <c r="O3" s="17">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P3" s="17">
+        <v>125</v>
+      </c>
+      <c r="R3" s="17">
         <v>100</v>
       </c>
       <c r="S3" s="17" t="s">
@@ -2046,8 +2094,20 @@
       <c r="T3" s="17" t="s">
         <v>90</v>
       </c>
+      <c r="U3" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="V3" s="19">
+        <v>46198</v>
+      </c>
+      <c r="W3" s="19">
+        <v>46198</v>
+      </c>
+      <c r="X3" s="17" t="s">
+        <v>92</v>
+      </c>
       <c r="Y3" s="17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Z3" s="34">
         <v>3</v>
@@ -2067,13 +2127,13 @@
         <v>46158</v>
       </c>
       <c r="AI3" s="34" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AN3" s="34" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AO3" s="34" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AP3" s="34">
         <v>3.6</v>
@@ -2082,26 +2142,51 @@
         <v>46167</v>
       </c>
       <c r="AR3" s="34" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AS3" s="34" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="BL3" s="17">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="BN3" s="17" t="s">
         <v>90</v>
       </c>
       <c r="BP3" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="BS3" s="17">
+        <v>50</v>
+      </c>
+      <c r="BT3" s="17" t="s">
         <v>91</v>
+      </c>
+      <c r="BV3" s="17" t="s">
+        <v>93</v>
       </c>
       <c r="CI3" s="17">
         <f>+CE3+BY3+BS3+BL3</f>
+        <v>125</v>
+      </c>
+      <c r="CM3" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="CN3" s="17">
+        <v>5</v>
+      </c>
+      <c r="CO3" s="17">
+        <f>+C3-63.9-24-40</f>
+        <v>75.59</v>
+      </c>
+      <c r="CP3" s="17" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="4" spans="1:119" ht="21">
+      <c r="CQ3" s="17" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:120" ht="21">
       <c r="A4" s="6" t="s">
         <v>86</v>
       </c>
@@ -2112,17 +2197,17 @@
         <v>215</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AH4" s="18"/>
       <c r="AN4" s="34" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AO4" s="34" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="AP4" s="34">
         <v>40</v>
@@ -2131,17 +2216,26 @@
         <v>46137</v>
       </c>
       <c r="AR4" s="34" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AS4" s="34" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="CI4" s="17">
         <f t="shared" ref="CI4:CI53" si="0">+CE4+BY4+BS4+BL4</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:119" ht="21">
+      <c r="CR4" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="DB4" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="DC4" s="17" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="1:120" ht="21">
       <c r="A5" s="6" t="s">
         <v>86</v>
       </c>
@@ -2152,17 +2246,17 @@
         <v>46.12</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AH5" s="18"/>
       <c r="AN5" s="34" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AO5" s="34" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="AP5" s="34">
         <v>40</v>
@@ -2171,17 +2265,26 @@
         <v>46137</v>
       </c>
       <c r="AR5" s="34" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AS5" s="34" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="CI5" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:119" ht="21">
+      <c r="CR5" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="DB5" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="DC5" s="17" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" spans="1:120" ht="21">
       <c r="A6" s="6" t="s">
         <v>86</v>
       </c>
@@ -2192,17 +2295,17 @@
         <v>24.03</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AH6" s="18"/>
       <c r="AN6" s="34" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AO6" s="34" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="AP6" s="34">
         <v>40</v>
@@ -2211,17 +2314,26 @@
         <v>46137</v>
       </c>
       <c r="AR6" s="34" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AS6" s="34" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="CI6" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:119" ht="21">
+      <c r="CR6" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="DB6" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="DC6" s="17" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" spans="1:120" ht="21">
       <c r="A7" s="6" t="s">
         <v>86</v>
       </c>
@@ -2232,17 +2344,17 @@
         <v>22.55</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AH7" s="18"/>
       <c r="AN7" s="34" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AO7" s="34" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="AP7" s="34">
         <v>40</v>
@@ -2251,17 +2363,26 @@
         <v>46137</v>
       </c>
       <c r="AR7" s="34" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AS7" s="34" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="CI7" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:119" ht="21">
+      <c r="CR7" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="DB7" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="DC7" s="17" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:120" ht="21">
       <c r="A8" s="6" t="s">
         <v>86</v>
       </c>
@@ -2272,17 +2393,17 @@
         <v>62.73</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AH8" s="18"/>
       <c r="AN8" s="34" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AO8" s="34" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="AP8" s="34">
         <v>40</v>
@@ -2291,17 +2412,26 @@
         <v>46137</v>
       </c>
       <c r="AR8" s="34" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AS8" s="34" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="CI8" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:119" ht="21">
+      <c r="CR8" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="DB8" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="DC8" s="17" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" spans="1:120" ht="21">
       <c r="A9" s="6" t="s">
         <v>86</v>
       </c>
@@ -2312,17 +2442,17 @@
         <v>29.7</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AH9" s="18"/>
       <c r="AN9" s="34" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AO9" s="34" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="AP9" s="34">
         <v>40</v>
@@ -2331,17 +2461,26 @@
         <v>46137</v>
       </c>
       <c r="AR9" s="34" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AS9" s="34" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="CI9" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:119" ht="21">
+      <c r="CR9" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="DB9" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="DC9" s="17" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10" spans="1:120" ht="21">
       <c r="A10" s="6" t="s">
         <v>86</v>
       </c>
@@ -2352,17 +2491,17 @@
         <v>270.44</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AH10" s="18"/>
       <c r="AN10" s="34" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AO10" s="34" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="AP10" s="34">
         <v>40</v>
@@ -2371,17 +2510,26 @@
         <v>46137</v>
       </c>
       <c r="AR10" s="34" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AS10" s="34" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="CI10" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:119" ht="21">
+      <c r="CR10" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="DB10" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="DC10" s="17" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="11" spans="1:120" ht="21">
       <c r="A11" s="6" t="s">
         <v>86</v>
       </c>
@@ -2392,17 +2540,17 @@
         <v>64.25</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AH11" s="18"/>
       <c r="AN11" s="34" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AO11" s="34" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="AP11" s="34">
         <v>40</v>
@@ -2411,17 +2559,26 @@
         <v>46137</v>
       </c>
       <c r="AR11" s="34" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AS11" s="34" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="CI11" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:119" ht="21">
+      <c r="CR11" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="DB11" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="DC11" s="17" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="12" spans="1:120" ht="21">
       <c r="A12" s="6" t="s">
         <v>86</v>
       </c>
@@ -2432,17 +2589,17 @@
         <v>29.89</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AH12" s="18"/>
       <c r="AN12" s="34" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AO12" s="34" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="AP12" s="34">
         <v>40</v>
@@ -2451,19 +2608,28 @@
         <v>46137</v>
       </c>
       <c r="AR12" s="34" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AS12" s="34" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="CI12" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:119" ht="21">
+      <c r="CR12" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="DB12" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="DC12" s="17" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="13" spans="1:120" ht="21">
       <c r="A13" s="6" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B13" s="6">
         <v>6</v>
@@ -2472,17 +2638,17 @@
         <v>52.63</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AH13" s="18"/>
       <c r="AN13" s="34" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AO13" s="34" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="AP13" s="34">
         <v>40</v>
@@ -2491,19 +2657,28 @@
         <v>46139</v>
       </c>
       <c r="AR13" s="34" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AS13" s="34" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="CI13" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:119" ht="21">
+      <c r="CR13" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="DB13" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="DC13" s="17" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" spans="1:120" ht="21">
       <c r="A14" s="6" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B14" s="6">
         <v>7</v>
@@ -2512,10 +2687,10 @@
         <v>60.61</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F14" s="19">
         <v>46175</v>
@@ -2557,7 +2732,7 @@
         <v>90</v>
       </c>
       <c r="Y14" s="17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Z14" s="34">
         <v>3</v>
@@ -2575,13 +2750,13 @@
         <v>46174</v>
       </c>
       <c r="AI14" s="34" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AN14" s="34" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="AO14" s="34" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AP14" s="34">
         <v>135</v>
@@ -2590,10 +2765,10 @@
         <v>46176</v>
       </c>
       <c r="AR14" s="34" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AS14" s="34" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="BL14" s="17">
         <v>94</v>
@@ -2602,16 +2777,32 @@
         <v>90</v>
       </c>
       <c r="BP14" s="17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="CI14" s="17">
         <f t="shared" si="0"/>
         <v>94</v>
       </c>
-    </row>
-    <row r="15" spans="1:119" ht="21">
+      <c r="CM14" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="CN14" s="17">
+        <v>5</v>
+      </c>
+      <c r="CO14" s="17">
+        <f>+C14</f>
+        <v>60.61</v>
+      </c>
+      <c r="CP14" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="CQ14" s="17" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="15" spans="1:120" ht="21">
       <c r="A15" s="6" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B15" s="6">
         <v>11</v>
@@ -2620,10 +2811,10 @@
         <v>56.69</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F15" s="19">
         <v>46175</v>
@@ -2665,7 +2856,7 @@
         <v>90</v>
       </c>
       <c r="Y15" s="17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Z15" s="34">
         <v>3</v>
@@ -2683,13 +2874,13 @@
         <v>46174</v>
       </c>
       <c r="AI15" s="34" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AN15" s="34" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="AO15" s="34" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AP15" s="34">
         <v>135</v>
@@ -2698,10 +2889,10 @@
         <v>46172</v>
       </c>
       <c r="AR15" s="34" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AS15" s="34" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="BL15" s="17">
         <v>94</v>
@@ -2710,16 +2901,16 @@
         <v>90</v>
       </c>
       <c r="BP15" s="17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="CI15" s="17">
         <f t="shared" si="0"/>
         <v>94</v>
       </c>
     </row>
-    <row r="16" spans="1:119" ht="21">
+    <row r="16" spans="1:120" ht="21">
       <c r="A16" s="6" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B16" s="6">
         <v>12</v>
@@ -2728,10 +2919,10 @@
         <v>49.78</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F16" s="19">
         <v>46175</v>
@@ -2773,7 +2964,7 @@
         <v>90</v>
       </c>
       <c r="Y16" s="17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Z16" s="34">
         <v>3</v>
@@ -2791,13 +2982,13 @@
         <v>46174</v>
       </c>
       <c r="AI16" s="34" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AN16" s="34" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="AO16" s="34" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AP16" s="34">
         <v>135</v>
@@ -2806,10 +2997,10 @@
         <v>46173</v>
       </c>
       <c r="AR16" s="34" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AS16" s="34" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="BL16" s="17">
         <v>94</v>
@@ -2818,16 +3009,16 @@
         <v>90</v>
       </c>
       <c r="BP16" s="17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="CI16" s="17">
         <f t="shared" si="0"/>
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:87" ht="21">
+    <row r="17" spans="1:107" ht="21">
       <c r="A17" s="6" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B17" s="6">
         <v>13</v>
@@ -2836,10 +3027,10 @@
         <v>26.67</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F17" s="19">
         <v>46175</v>
@@ -2881,7 +3072,7 @@
         <v>90</v>
       </c>
       <c r="Y17" s="17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Z17" s="34">
         <v>3</v>
@@ -2899,13 +3090,13 @@
         <v>46174</v>
       </c>
       <c r="AI17" s="34" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AN17" s="34" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="AO17" s="34" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AP17" s="34">
         <v>135</v>
@@ -2914,10 +3105,10 @@
         <v>46174</v>
       </c>
       <c r="AR17" s="34" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AS17" s="34" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="BL17" s="17">
         <v>94</v>
@@ -2926,16 +3117,16 @@
         <v>90</v>
       </c>
       <c r="BP17" s="17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="CI17" s="17">
         <f t="shared" si="0"/>
         <v>94</v>
       </c>
     </row>
-    <row r="18" spans="1:87" ht="21">
+    <row r="18" spans="1:107" ht="21">
       <c r="A18" s="6" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B18" s="6">
         <v>14</v>
@@ -2944,10 +3135,10 @@
         <v>33.96</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F18" s="19">
         <v>46175</v>
@@ -2989,7 +3180,7 @@
         <v>90</v>
       </c>
       <c r="Y18" s="17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Z18" s="34">
         <v>3</v>
@@ -3007,23 +3198,23 @@
         <v>46174</v>
       </c>
       <c r="AI18" s="34" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AJ18" s="34"/>
       <c r="AK18" s="34" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="AL18" s="35">
         <v>46164</v>
       </c>
       <c r="AM18" s="34" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AN18" s="48" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="AO18" s="48" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AP18" s="34">
         <v>135</v>
@@ -3032,10 +3223,10 @@
         <v>46175</v>
       </c>
       <c r="AR18" s="34" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AS18" s="34" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="BL18" s="17">
         <v>94</v>
@@ -3044,16 +3235,32 @@
         <v>90</v>
       </c>
       <c r="BP18" s="17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="CI18" s="17">
         <f t="shared" si="0"/>
         <v>94</v>
       </c>
-    </row>
-    <row r="19" spans="1:87" ht="21">
+      <c r="CM18" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="CN18" s="17">
+        <v>5</v>
+      </c>
+      <c r="CO18" s="17">
+        <f t="shared" ref="CO15:CO18" si="1">+C18</f>
+        <v>33.96</v>
+      </c>
+      <c r="CP18" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="CQ18" s="17" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="19" spans="1:107" ht="21">
       <c r="A19" s="6" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B19" s="6">
         <v>16</v>
@@ -3062,10 +3269,10 @@
         <v>91.46</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F19" s="19">
         <v>46175</v>
@@ -3107,7 +3314,7 @@
         <v>90</v>
       </c>
       <c r="Y19" s="17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Z19" s="34">
         <v>3</v>
@@ -3125,7 +3332,7 @@
         <v>46174</v>
       </c>
       <c r="AI19" s="34" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AJ19" s="34"/>
       <c r="AK19" s="34">
@@ -3135,13 +3342,13 @@
         <v>46164</v>
       </c>
       <c r="AM19" s="34" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AN19" s="48" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="AO19" s="48" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="AP19" s="34">
         <v>135</v>
@@ -3150,10 +3357,10 @@
         <v>46176</v>
       </c>
       <c r="AR19" s="34" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AS19" s="34" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="BL19" s="17">
         <v>94</v>
@@ -3162,16 +3369,32 @@
         <v>90</v>
       </c>
       <c r="BP19" s="17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="CI19" s="17">
         <f t="shared" si="0"/>
         <v>94</v>
       </c>
-    </row>
-    <row r="20" spans="1:87" ht="21">
+      <c r="CM19" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="CN19" s="17">
+        <v>5</v>
+      </c>
+      <c r="CO19" s="17">
+        <f>91.46-15</f>
+        <v>76.459999999999994</v>
+      </c>
+      <c r="CP19" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="CQ19" s="17" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="20" spans="1:107" ht="21">
       <c r="A20" s="6" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B20" s="6">
         <v>1</v>
@@ -3219,23 +3442,21 @@
         <v>150</v>
       </c>
       <c r="Q20" s="34"/>
-      <c r="R20" s="34"/>
       <c r="S20" s="34" t="s">
         <v>90</v>
       </c>
       <c r="T20" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="U20" s="34"/>
       <c r="V20" s="35">
         <v>46172</v>
       </c>
       <c r="W20" s="35">
         <v>46172</v>
       </c>
-      <c r="X20" s="35"/>
+      <c r="X20" s="19"/>
       <c r="Y20" s="34" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Z20" s="34">
         <v>3</v>
@@ -3255,13 +3476,13 @@
         <v>46159</v>
       </c>
       <c r="AI20" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="AN20" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="AN20" s="34" t="s">
-        <v>92</v>
-      </c>
       <c r="AO20" s="34" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AP20" s="34">
         <v>3.8</v>
@@ -3270,10 +3491,10 @@
         <v>46160</v>
       </c>
       <c r="AR20" s="34" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="AS20" s="34" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="BL20" s="34">
         <v>110</v>
@@ -3286,16 +3507,25 @@
         <v>46172</v>
       </c>
       <c r="BP20" s="34" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="CI20" s="17">
         <f t="shared" si="0"/>
         <v>110</v>
       </c>
-    </row>
-    <row r="21" spans="1:87" ht="21">
+      <c r="CR20" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="CT20" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="DC20" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="21" spans="1:107" ht="21">
       <c r="A21" s="6" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B21" s="6">
         <v>2</v>
@@ -3343,23 +3573,21 @@
         <v>150</v>
       </c>
       <c r="Q21" s="34"/>
-      <c r="R21" s="34"/>
       <c r="S21" s="34" t="s">
         <v>90</v>
       </c>
       <c r="T21" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="U21" s="34"/>
       <c r="V21" s="35">
         <v>46172</v>
       </c>
       <c r="W21" s="35">
         <v>46172</v>
       </c>
-      <c r="X21" s="35"/>
+      <c r="X21" s="19"/>
       <c r="Y21" s="34" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Z21" s="34">
         <v>3</v>
@@ -3379,13 +3607,13 @@
         <v>46159</v>
       </c>
       <c r="AI21" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="AN21" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="AN21" s="34" t="s">
-        <v>92</v>
-      </c>
       <c r="AO21" s="34" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AP21" s="34">
         <v>3.8</v>
@@ -3394,10 +3622,10 @@
         <v>46162</v>
       </c>
       <c r="AR21" s="34" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="AS21" s="34" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="BL21" s="34">
         <v>110</v>
@@ -3410,16 +3638,32 @@
         <v>46172</v>
       </c>
       <c r="BP21" s="34" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="CI21" s="17">
         <f t="shared" si="0"/>
         <v>110</v>
       </c>
-    </row>
-    <row r="22" spans="1:87" ht="21">
+      <c r="CM21" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="CN21" s="17">
+        <v>5</v>
+      </c>
+      <c r="CO21" s="17">
+        <f>+C21</f>
+        <v>40.99</v>
+      </c>
+      <c r="CP21" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="CQ21" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="22" spans="1:107" ht="21">
       <c r="A22" s="6" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B22" s="6">
         <v>3</v>
@@ -3467,23 +3711,21 @@
         <v>150</v>
       </c>
       <c r="Q22" s="34"/>
-      <c r="R22" s="34"/>
       <c r="S22" s="34" t="s">
         <v>90</v>
       </c>
       <c r="T22" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="U22" s="34"/>
       <c r="V22" s="35">
         <v>46172</v>
       </c>
       <c r="W22" s="35">
         <v>46172</v>
       </c>
-      <c r="X22" s="35"/>
+      <c r="X22" s="19"/>
       <c r="Y22" s="34" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Z22" s="34">
         <v>3</v>
@@ -3503,13 +3745,13 @@
         <v>46159</v>
       </c>
       <c r="AI22" s="34" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AN22" s="34" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="AO22" s="34" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AP22" s="34">
         <v>4</v>
@@ -3518,10 +3760,10 @@
         <v>46160</v>
       </c>
       <c r="AR22" s="34" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="AS22" s="34" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="BL22" s="34">
         <v>110</v>
@@ -3534,16 +3776,32 @@
         <v>46172</v>
       </c>
       <c r="BP22" s="34" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="CI22" s="17">
         <f t="shared" si="0"/>
         <v>110</v>
       </c>
-    </row>
-    <row r="23" spans="1:87" ht="21">
+      <c r="CM22" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="CN22" s="17">
+        <v>5</v>
+      </c>
+      <c r="CO22" s="17">
+        <f t="shared" ref="CO22" si="2">+C22</f>
+        <v>63.11</v>
+      </c>
+      <c r="CP22" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="CQ22" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23" spans="1:107" ht="21">
       <c r="A23" s="6" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B23" s="6">
         <v>4</v>
@@ -3591,23 +3849,21 @@
         <v>150</v>
       </c>
       <c r="Q23" s="34"/>
-      <c r="R23" s="34"/>
       <c r="S23" s="34" t="s">
         <v>90</v>
       </c>
       <c r="T23" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="U23" s="34"/>
       <c r="V23" s="35">
         <v>46172</v>
       </c>
       <c r="W23" s="35">
         <v>46172</v>
       </c>
-      <c r="X23" s="35"/>
+      <c r="X23" s="19"/>
       <c r="Y23" s="34" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Z23" s="34">
         <v>3</v>
@@ -3627,14 +3883,14 @@
         <v>46159</v>
       </c>
       <c r="AI23" s="34" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AL23" s="19"/>
       <c r="AN23" s="34" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="AO23" s="34" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AP23" s="34">
         <v>4</v>
@@ -3643,10 +3899,10 @@
         <v>46158</v>
       </c>
       <c r="AR23" s="34" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="AS23" s="34" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="BL23" s="34">
         <v>110</v>
@@ -3659,16 +3915,28 @@
         <v>46172</v>
       </c>
       <c r="BP23" s="34" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="CI23" s="17">
         <f t="shared" si="0"/>
         <v>110</v>
       </c>
-    </row>
-    <row r="24" spans="1:87" ht="21">
+      <c r="CR23" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="CS23" s="17">
+        <v>1</v>
+      </c>
+      <c r="DA23" s="17">
+        <v>0.15</v>
+      </c>
+      <c r="DC23" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="24" spans="1:107" ht="21">
       <c r="A24" s="6" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B24" s="6">
         <v>5</v>
@@ -3677,17 +3945,17 @@
         <v>67.739999999999995</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AH24" s="18"/>
       <c r="AN24" s="34" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AO24" s="34" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="AP24" s="34">
         <v>80</v>
@@ -3696,19 +3964,28 @@
         <v>46135</v>
       </c>
       <c r="AR24" s="34" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AS24" s="34" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="CI24" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:87" ht="21">
+      <c r="CR24" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="DB24" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="DC24" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="25" spans="1:107" ht="21">
       <c r="A25" s="6" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B25" s="6">
         <v>6</v>
@@ -3717,17 +3994,17 @@
         <v>24.52</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AH25" s="18"/>
       <c r="AN25" s="34" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AO25" s="34" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="AP25" s="34">
         <v>80</v>
@@ -3736,19 +4013,28 @@
         <v>46135</v>
       </c>
       <c r="AR25" s="34" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AS25" s="34" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="CI25" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:87" ht="21">
+      <c r="CR25" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="DB25" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="DC25" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="26" spans="1:107" ht="21">
       <c r="A26" s="6" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B26" s="6">
         <v>11</v>
@@ -3796,23 +4082,21 @@
         <v>150</v>
       </c>
       <c r="Q26" s="34"/>
-      <c r="R26" s="34"/>
       <c r="S26" s="34" t="s">
         <v>90</v>
       </c>
       <c r="T26" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="U26" s="34"/>
       <c r="V26" s="35">
         <v>46172</v>
       </c>
       <c r="W26" s="35">
         <v>46172</v>
       </c>
-      <c r="X26" s="35"/>
+      <c r="X26" s="19"/>
       <c r="Y26" s="34" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Z26" s="34">
         <v>3</v>
@@ -3832,13 +4116,13 @@
         <v>46159</v>
       </c>
       <c r="AI26" s="34" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AN26" s="34" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="AO26" s="34" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AP26" s="34">
         <v>4</v>
@@ -3847,10 +4131,10 @@
         <v>46159</v>
       </c>
       <c r="AR26" s="34" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="AS26" s="34" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="BL26" s="34">
         <v>110</v>
@@ -3863,16 +4147,16 @@
         <v>46172</v>
       </c>
       <c r="BP26" s="34" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="CI26" s="17">
         <f t="shared" si="0"/>
         <v>110</v>
       </c>
     </row>
-    <row r="27" spans="1:87" ht="21">
+    <row r="27" spans="1:107" ht="21">
       <c r="A27" s="6" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B27" s="6">
         <v>12</v>
@@ -3881,17 +4165,17 @@
         <v>67</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AH27" s="18"/>
       <c r="AN27" s="34" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AO27" s="34" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="AP27" s="34">
         <v>80</v>
@@ -3900,19 +4184,28 @@
         <v>46135</v>
       </c>
       <c r="AR27" s="34" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AS27" s="34" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="CI27" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:87" ht="21">
+      <c r="CR27" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="DB27" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="DC27" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="28" spans="1:107" ht="21">
       <c r="A28" s="6" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B28" s="6">
         <v>1</v>
@@ -3921,13 +4214,13 @@
         <v>138.88</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>88</v>
       </c>
       <c r="G28" s="17" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="P28" s="17">
         <v>145.9</v>
@@ -3939,13 +4232,13 @@
         <v>100</v>
       </c>
       <c r="S28" s="17" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="T28" s="17" t="s">
         <v>90</v>
       </c>
       <c r="U28" s="17" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="V28" s="19">
         <v>46175</v>
@@ -3957,7 +4250,7 @@
         <v>46175</v>
       </c>
       <c r="Y28" s="17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Z28" s="34">
         <v>3</v>
@@ -3977,7 +4270,7 @@
         <v>46057</v>
       </c>
       <c r="AI28" s="34" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ28" s="34">
         <v>3</v>
@@ -3987,13 +4280,13 @@
         <v>46164</v>
       </c>
       <c r="AM28" s="34" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AN28" s="34" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="AO28" s="34" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AP28" s="34">
         <v>3.5</v>
@@ -4002,16 +4295,16 @@
         <v>46143</v>
       </c>
       <c r="AR28" s="34" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="AS28" s="34" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="AT28" s="34" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AU28" s="34" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AV28" s="34">
         <v>3.6</v>
@@ -4023,10 +4316,10 @@
         <v>138.88</v>
       </c>
       <c r="AY28" s="34" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="AZ28" s="34" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="BL28" s="17">
         <v>100</v>
@@ -4038,16 +4331,32 @@
         <v>46175</v>
       </c>
       <c r="BP28" s="17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="CI28" s="17">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-    </row>
-    <row r="29" spans="1:87" ht="21">
+      <c r="CM28" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="CN28" s="17">
+        <v>5</v>
+      </c>
+      <c r="CO28" s="17">
+        <f>+C28-58.5-15</f>
+        <v>65.38</v>
+      </c>
+      <c r="CP28" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="CQ28" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="29" spans="1:107" ht="21">
       <c r="A29" s="6" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B29" s="6">
         <v>2</v>
@@ -4056,17 +4365,17 @@
         <v>141.69999999999999</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AH29" s="18"/>
       <c r="AN29" s="34" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AO29" s="34" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="AP29" s="34">
         <v>80</v>
@@ -4075,19 +4384,32 @@
         <v>46134</v>
       </c>
       <c r="AR29" s="34" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AS29" s="34" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="CI29" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:87" ht="21">
+      <c r="CR29" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="CV29" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="CW29" s="17">
+        <v>0.8</v>
+      </c>
+      <c r="DB29" s="51"/>
+      <c r="DC29" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="30" spans="1:107" ht="21">
       <c r="A30" s="6" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B30" s="6">
         <v>1</v>
@@ -4096,17 +4418,17 @@
         <v>101.74</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AH30" s="18"/>
       <c r="AN30" s="34" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="AO30" s="34" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="AP30" s="34">
         <v>10</v>
@@ -4115,19 +4437,22 @@
         <v>46170</v>
       </c>
       <c r="AR30" s="34" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="AS30" s="34" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="CI30" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:87" ht="21">
+      <c r="DB30" s="51">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="31" spans="1:107" ht="21">
       <c r="A31" s="6" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B31" s="6">
         <v>2</v>
@@ -4136,13 +4461,13 @@
         <v>34.99</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>88</v>
       </c>
       <c r="G31" s="17" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="P31" s="34">
         <v>120</v>
@@ -4150,19 +4475,29 @@
       <c r="Q31" s="17">
         <v>50</v>
       </c>
+      <c r="R31" s="17">
+        <v>100</v>
+      </c>
       <c r="S31" s="17" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="T31" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="U31" s="34"/>
+      <c r="U31" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="V31" s="19">
+        <v>46189</v>
+      </c>
       <c r="W31" s="35">
         <v>46170</v>
       </c>
-      <c r="X31" s="35"/>
+      <c r="X31" s="19" t="s">
+        <v>92</v>
+      </c>
       <c r="Y31" s="17" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="Z31" s="34">
         <v>3</v>
@@ -4179,10 +4514,10 @@
       <c r="AF31" s="34"/>
       <c r="AG31" s="34"/>
       <c r="AH31" s="47" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="AI31" s="34" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ31" s="34">
         <v>3.5</v>
@@ -4194,13 +4529,13 @@
         <v>46136</v>
       </c>
       <c r="AM31" s="34" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AN31" s="34" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="AO31" s="34" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AP31" s="34">
         <v>3.5</v>
@@ -4209,16 +4544,16 @@
         <v>46139</v>
       </c>
       <c r="AR31" s="34" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AS31" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="AT31" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="AU31" s="34" t="s">
         <v>95</v>
-      </c>
-      <c r="AT31" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="AU31" s="34" t="s">
-        <v>93</v>
       </c>
       <c r="AV31" s="34">
         <v>3.6</v>
@@ -4230,10 +4565,10 @@
         <v>34.99</v>
       </c>
       <c r="AY31" s="34" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="AZ31" s="34" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="BL31" s="34">
         <v>95</v>
@@ -4246,16 +4581,25 @@
         <v>46143</v>
       </c>
       <c r="BP31" s="34" t="s">
-        <v>100</v>
+        <v>103</v>
+      </c>
+      <c r="BS31" s="17">
+        <v>75</v>
+      </c>
+      <c r="BT31" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="BV31" s="17" t="s">
+        <v>93</v>
       </c>
       <c r="CI31" s="17">
         <f t="shared" si="0"/>
-        <v>95</v>
-      </c>
-    </row>
-    <row r="32" spans="1:87" ht="21">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="32" spans="1:107" ht="21">
       <c r="A32" s="6" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B32" s="6">
         <v>3</v>
@@ -4264,13 +4608,13 @@
         <v>301.24</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>88</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="P32" s="34">
         <v>113.3</v>
@@ -4278,19 +4622,29 @@
       <c r="Q32" s="17">
         <v>72.3</v>
       </c>
+      <c r="R32" s="17">
+        <v>100</v>
+      </c>
       <c r="S32" s="17" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="T32" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="U32" s="34"/>
+      <c r="U32" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="V32" s="19">
+        <v>46189</v>
+      </c>
       <c r="W32" s="35">
         <v>46170</v>
       </c>
-      <c r="X32" s="35"/>
+      <c r="X32" s="19" t="s">
+        <v>92</v>
+      </c>
       <c r="Y32" s="17" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="Z32" s="34">
         <v>3</v>
@@ -4307,10 +4661,10 @@
       <c r="AF32" s="34"/>
       <c r="AG32" s="34"/>
       <c r="AH32" s="47" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="AI32" s="34" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ32" s="34">
         <v>3.5</v>
@@ -4322,13 +4676,13 @@
         <v>46136</v>
       </c>
       <c r="AM32" s="34" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AN32" s="34" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="AO32" s="34" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AP32" s="34">
         <v>3.5</v>
@@ -4337,16 +4691,16 @@
         <v>46132</v>
       </c>
       <c r="AR32" s="34" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AS32" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="AT32" s="34" t="s">
+        <v>135</v>
+      </c>
+      <c r="AU32" s="34" t="s">
         <v>95</v>
-      </c>
-      <c r="AT32" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="AU32" s="34" t="s">
-        <v>93</v>
       </c>
       <c r="AV32" s="34">
         <v>3.6</v>
@@ -4358,10 +4712,10 @@
         <v>210</v>
       </c>
       <c r="AY32" s="34" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="AZ32" s="34" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="BL32" s="34">
         <v>95</v>
@@ -4374,16 +4728,25 @@
         <v>46143</v>
       </c>
       <c r="BP32" s="34" t="s">
-        <v>100</v>
+        <v>103</v>
+      </c>
+      <c r="BS32" s="17">
+        <v>75</v>
+      </c>
+      <c r="BT32" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="BV32" s="17" t="s">
+        <v>93</v>
       </c>
       <c r="CI32" s="17">
         <f t="shared" si="0"/>
-        <v>95</v>
-      </c>
-    </row>
-    <row r="33" spans="1:87" ht="21">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="33" spans="1:107" ht="21">
       <c r="A33" s="6" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B33" s="6">
         <v>4</v>
@@ -4392,13 +4755,13 @@
         <v>180.2</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>88</v>
       </c>
       <c r="G33" s="17" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="P33" s="34">
         <v>120.7</v>
@@ -4406,19 +4769,29 @@
       <c r="Q33" s="17">
         <v>92.5</v>
       </c>
+      <c r="R33" s="17">
+        <v>100</v>
+      </c>
       <c r="S33" s="17" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="T33" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="U33" s="34"/>
+      <c r="U33" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="V33" s="19">
+        <v>46189</v>
+      </c>
       <c r="W33" s="35">
         <v>46170</v>
       </c>
-      <c r="X33" s="35"/>
+      <c r="X33" s="19" t="s">
+        <v>92</v>
+      </c>
       <c r="Y33" s="17" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="Z33" s="34">
         <v>3</v>
@@ -4435,10 +4808,10 @@
       <c r="AF33" s="34"/>
       <c r="AG33" s="34"/>
       <c r="AH33" s="47" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="AI33" s="34" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ33" s="34">
         <v>3.5</v>
@@ -4450,13 +4823,13 @@
         <v>46136</v>
       </c>
       <c r="AM33" s="34" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AN33" s="34" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="AO33" s="34" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AP33" s="34">
         <v>3.5</v>
@@ -4465,16 +4838,16 @@
         <v>46141</v>
       </c>
       <c r="AR33" s="34" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AS33" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="AT33" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="AU33" s="34" t="s">
         <v>95</v>
-      </c>
-      <c r="AT33" s="34" t="s">
-        <v>134</v>
-      </c>
-      <c r="AU33" s="34" t="s">
-        <v>93</v>
       </c>
       <c r="AV33" s="34">
         <v>3.6</v>
@@ -4486,10 +4859,10 @@
         <v>131.5</v>
       </c>
       <c r="AY33" s="34" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AZ33" s="34" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="BL33" s="34">
         <v>95</v>
@@ -4502,16 +4875,25 @@
         <v>46143</v>
       </c>
       <c r="BP33" s="34" t="s">
-        <v>100</v>
+        <v>103</v>
+      </c>
+      <c r="BS33" s="17">
+        <v>75</v>
+      </c>
+      <c r="BT33" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="BV33" s="17" t="s">
+        <v>93</v>
       </c>
       <c r="CI33" s="17">
         <f t="shared" si="0"/>
-        <v>95</v>
-      </c>
-    </row>
-    <row r="34" spans="1:87" ht="21">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="34" spans="1:107" ht="21">
       <c r="A34" s="6" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B34" s="6">
         <v>5</v>
@@ -4520,17 +4902,17 @@
         <v>59.08</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AH34" s="18"/>
       <c r="AN34" s="34" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="AO34" s="34" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="AP34" s="34">
         <v>10</v>
@@ -4539,19 +4921,28 @@
         <v>46170</v>
       </c>
       <c r="AR34" s="34" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="AS34" s="34" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="CI34" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:87" ht="21">
+      <c r="CR34" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="DB34" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="DC34" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="35" spans="1:107" ht="21">
       <c r="A35" s="6" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B35" s="6">
         <v>7</v>
@@ -4560,17 +4951,17 @@
         <v>46.79</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AH35" s="18"/>
       <c r="AN35" s="34" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="AO35" s="34" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="AP35" s="34">
         <v>10</v>
@@ -4579,19 +4970,28 @@
         <v>46134</v>
       </c>
       <c r="AR35" s="34" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="AS35" s="34" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="CI35" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:87" ht="21">
+      <c r="CR35" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="DB35" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="DC35" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="36" spans="1:107" ht="21">
       <c r="A36" s="6" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B36" s="6">
         <v>8</v>
@@ -4600,17 +5000,17 @@
         <v>59.05</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AH36" s="18"/>
       <c r="AN36" s="34" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="AO36" s="34" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="AP36" s="34">
         <v>10</v>
@@ -4619,19 +5019,28 @@
         <v>46134</v>
       </c>
       <c r="AR36" s="34" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="AS36" s="34" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="CI36" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:87" ht="21">
+      <c r="CR36" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="DB36" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="DC36" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="37" spans="1:107" ht="21">
       <c r="A37" s="6" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B37" s="6">
         <v>9</v>
@@ -4640,17 +5049,17 @@
         <v>103.45</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AH37" s="18"/>
       <c r="AN37" s="34" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="AO37" s="34" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="AP37" s="34">
         <v>10</v>
@@ -4659,19 +5068,32 @@
         <v>46132</v>
       </c>
       <c r="AR37" s="34" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="AS37" s="34" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="CI37" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:87" ht="21">
+      <c r="CR37" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="CV37" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="CW37" s="17">
+        <v>0.8</v>
+      </c>
+      <c r="DB37" s="51"/>
+      <c r="DC37" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="38" spans="1:107" ht="21">
       <c r="A38" s="6" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B38" s="6">
         <v>10</v>
@@ -4680,13 +5102,13 @@
         <v>101.88</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E38" s="7" t="s">
         <v>88</v>
       </c>
       <c r="G38" s="17" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="P38" s="34">
         <v>97.9</v>
@@ -4695,21 +5117,23 @@
         <v>83.7</v>
       </c>
       <c r="S38" s="17" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="T38" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="U38" s="34"/>
+      <c r="U38" s="17" t="s">
+        <v>91</v>
+      </c>
       <c r="V38" s="19">
         <v>46176</v>
       </c>
       <c r="W38" s="35">
         <v>46170</v>
       </c>
-      <c r="X38" s="35"/>
+      <c r="X38" s="19"/>
       <c r="Y38" s="17" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="Z38" s="34">
         <v>3</v>
@@ -4726,10 +5150,10 @@
       <c r="AF38" s="34"/>
       <c r="AG38" s="34"/>
       <c r="AH38" s="47" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="AI38" s="34" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ38" s="34">
         <v>3.5</v>
@@ -4741,13 +5165,13 @@
         <v>46136</v>
       </c>
       <c r="AM38" s="34" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AN38" s="34" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="AO38" s="34" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AP38" s="34">
         <v>3.5</v>
@@ -4756,16 +5180,16 @@
         <v>46139</v>
       </c>
       <c r="AR38" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="AS38" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="AT38" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="AS38" s="34" t="s">
+      <c r="AU38" s="34" t="s">
         <v>95</v>
-      </c>
-      <c r="AT38" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="AU38" s="34" t="s">
-        <v>93</v>
       </c>
       <c r="AV38" s="34">
         <v>3.6</v>
@@ -4777,10 +5201,10 @@
         <v>101.88</v>
       </c>
       <c r="AY38" s="34" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AZ38" s="34" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="BG38" s="34">
         <v>2</v>
@@ -4789,7 +5213,7 @@
         <v>46174</v>
       </c>
       <c r="BI38" s="34" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="BL38" s="34">
         <v>95</v>
@@ -4802,16 +5226,16 @@
         <v>46143</v>
       </c>
       <c r="BP38" s="34" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="CI38" s="17">
         <f t="shared" si="0"/>
         <v>95</v>
       </c>
     </row>
-    <row r="39" spans="1:87" ht="21">
+    <row r="39" spans="1:107" ht="21">
       <c r="A39" s="6" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B39" s="6">
         <v>11</v>
@@ -4820,17 +5244,17 @@
         <v>53.38</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AH39" s="18"/>
       <c r="AN39" s="34" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="AO39" s="34" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="AP39" s="34">
         <v>10</v>
@@ -4839,19 +5263,28 @@
         <v>46170</v>
       </c>
       <c r="AR39" s="34" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="AS39" s="34" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="CI39" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:87" ht="21">
+      <c r="CR39" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="DB39" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="DC39" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="40" spans="1:107" ht="21">
       <c r="A40" s="6" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B40" s="6">
         <v>12</v>
@@ -4860,17 +5293,17 @@
         <v>102.7</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AH40" s="18"/>
       <c r="AN40" s="34" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="AO40" s="34" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="AP40" s="34">
         <v>10</v>
@@ -4879,19 +5312,32 @@
         <v>46126</v>
       </c>
       <c r="AR40" s="34" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="AS40" s="34" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="CI40" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:87" ht="21">
+      <c r="CR40" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="CV40" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="CW40" s="17">
+        <v>0.8</v>
+      </c>
+      <c r="DB40" s="51"/>
+      <c r="DC40" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="41" spans="1:107" ht="21">
       <c r="A41" s="6" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B41" s="6">
         <v>13</v>
@@ -4900,17 +5346,17 @@
         <v>87.11</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AH41" s="18"/>
       <c r="AN41" s="34" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="AO41" s="34" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="AP41" s="34">
         <v>10</v>
@@ -4919,19 +5365,32 @@
         <v>46135</v>
       </c>
       <c r="AR41" s="34" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="AS41" s="34" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="CI41" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:87" ht="21">
+      <c r="CR41" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="CV41" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="CW41" s="17">
+        <v>0.8</v>
+      </c>
+      <c r="DB41" s="51"/>
+      <c r="DC41" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="42" spans="1:107" ht="21">
       <c r="A42" s="6" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B42" s="6">
         <v>14</v>
@@ -4940,17 +5399,17 @@
         <v>59.42</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AH42" s="18"/>
       <c r="AN42" s="34" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="AO42" s="34" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="AP42" s="34">
         <v>10</v>
@@ -4959,19 +5418,28 @@
         <v>46135</v>
       </c>
       <c r="AR42" s="34" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="AS42" s="34" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="CI42" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:87" ht="21">
+      <c r="CR42" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="DB42" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="DC42" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="43" spans="1:107" ht="21">
       <c r="A43" s="6" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B43" s="6">
         <v>15</v>
@@ -4980,17 +5448,17 @@
         <v>35.96</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AH43" s="18"/>
       <c r="AN43" s="34" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="AO43" s="34" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="AP43" s="34">
         <v>10</v>
@@ -4999,57 +5467,66 @@
         <v>46136</v>
       </c>
       <c r="AR43" s="34" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="AS43" s="34" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="CI43" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:87" ht="21">
+      <c r="CR43" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="DB43" s="51">
+        <v>0.04</v>
+      </c>
+      <c r="DC43" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="44" spans="1:107" ht="21">
       <c r="A44" s="6" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C44" s="6">
         <v>386.2</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="G44" s="17" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="P44" s="34">
         <v>61.5</v>
       </c>
-      <c r="Q44" s="17">
+      <c r="Q44" s="34">
         <v>107.3</v>
       </c>
-      <c r="S44" s="17" t="s">
-        <v>119</v>
+      <c r="S44" s="34" t="s">
+        <v>91</v>
       </c>
       <c r="T44" s="34" t="s">
         <v>90</v>
       </c>
       <c r="U44" s="34"/>
-      <c r="V44" s="19">
+      <c r="V44" s="35">
         <v>46176</v>
       </c>
       <c r="W44" s="35">
         <v>46172</v>
       </c>
       <c r="X44" s="35"/>
-      <c r="Y44" s="17" t="s">
-        <v>100</v>
+      <c r="Y44" s="34" t="s">
+        <v>103</v>
       </c>
       <c r="Z44" s="34">
         <v>3</v>
@@ -5067,13 +5544,13 @@
         <v>46167</v>
       </c>
       <c r="AI44" s="34" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AN44" s="34" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="AO44" s="34" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="AP44" s="34">
         <v>146.93</v>
@@ -5082,10 +5559,13 @@
         <v>46165</v>
       </c>
       <c r="AR44" s="34" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AS44" s="34" t="s">
-        <v>105</v>
+        <v>108</v>
+      </c>
+      <c r="BK44" s="17">
+        <v>9</v>
       </c>
       <c r="BL44" s="17">
         <v>93</v>
@@ -5094,35 +5574,51 @@
         <v>90</v>
       </c>
       <c r="BP44" s="17" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="CI44" s="17">
         <f t="shared" si="0"/>
         <v>93</v>
       </c>
-    </row>
-    <row r="45" spans="1:87" ht="21">
+      <c r="CM44" s="19">
+        <v>46190</v>
+      </c>
+      <c r="CN44" s="17">
+        <v>5</v>
+      </c>
+      <c r="CO44" s="17">
+        <f>+C44-135</f>
+        <v>251.2</v>
+      </c>
+      <c r="CP44" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="CQ44" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="45" spans="1:107" ht="21">
       <c r="A45" s="6" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C45" s="6">
         <v>120</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AH45" s="18"/>
       <c r="AN45" s="34" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="AO45" s="34" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="AP45" s="34">
         <v>10</v>
@@ -5131,57 +5627,60 @@
         <v>46175</v>
       </c>
       <c r="AR45" s="34" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="AS45" s="34" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="CI45" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:87" ht="21">
+      <c r="DB45" s="51">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="46" spans="1:107" ht="21">
       <c r="A46" s="6" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="C46" s="9">
         <v>163</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="G46" s="17" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="P46" s="34">
         <v>93.9</v>
       </c>
-      <c r="Q46" s="17">
+      <c r="Q46" s="34">
         <v>108.1</v>
       </c>
-      <c r="S46" s="17" t="s">
-        <v>119</v>
+      <c r="S46" s="34" t="s">
+        <v>91</v>
       </c>
       <c r="T46" s="34" t="s">
         <v>90</v>
       </c>
       <c r="U46" s="34"/>
-      <c r="V46" s="19">
+      <c r="V46" s="35">
         <v>46176</v>
       </c>
       <c r="W46" s="35">
         <v>46172</v>
       </c>
       <c r="X46" s="35"/>
-      <c r="Y46" s="17" t="s">
-        <v>100</v>
+      <c r="Y46" s="34" t="s">
+        <v>103</v>
       </c>
       <c r="Z46" s="34">
         <v>3</v>
@@ -5199,13 +5698,13 @@
         <v>46167</v>
       </c>
       <c r="AI46" s="34" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AN46" s="34" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="AO46" s="34" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="AP46" s="34">
         <v>146.93</v>
@@ -5214,10 +5713,13 @@
         <v>46169</v>
       </c>
       <c r="AR46" s="34" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="AS46" s="34" t="s">
-        <v>105</v>
+        <v>108</v>
+      </c>
+      <c r="BK46" s="17">
+        <v>9</v>
       </c>
       <c r="BL46" s="17">
         <v>93</v>
@@ -5226,54 +5728,70 @@
         <v>90</v>
       </c>
       <c r="BP46" s="17" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="CI46" s="17">
         <f t="shared" si="0"/>
         <v>93</v>
       </c>
-    </row>
-    <row r="47" spans="1:87" ht="21">
+      <c r="CM46" s="19">
+        <v>46187</v>
+      </c>
+      <c r="CN46" s="17">
+        <v>5</v>
+      </c>
+      <c r="CO46" s="50">
+        <f>+C46-32.4</f>
+        <v>130.6</v>
+      </c>
+      <c r="CP46" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="CQ46" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="47" spans="1:107" ht="21">
       <c r="A47" s="6" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C47" s="6">
         <v>189.75</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="G47" s="17" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="P47" s="34">
         <v>78.8</v>
       </c>
-      <c r="Q47" s="17">
+      <c r="Q47" s="34">
         <v>110.8</v>
       </c>
-      <c r="S47" s="17" t="s">
-        <v>119</v>
+      <c r="S47" s="34" t="s">
+        <v>91</v>
       </c>
       <c r="T47" s="34" t="s">
         <v>90</v>
       </c>
       <c r="U47" s="34"/>
-      <c r="V47" s="19">
+      <c r="V47" s="35">
         <v>46175</v>
       </c>
       <c r="W47" s="35">
         <v>46172</v>
       </c>
       <c r="X47" s="35"/>
-      <c r="Y47" s="17" t="s">
-        <v>100</v>
+      <c r="Y47" s="34" t="s">
+        <v>103</v>
       </c>
       <c r="Z47" s="34">
         <v>3</v>
@@ -5291,13 +5809,13 @@
         <v>46167</v>
       </c>
       <c r="AI47" s="34" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AN47" s="34" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="AO47" s="34" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="AP47" s="34">
         <v>146.93</v>
@@ -5306,10 +5824,13 @@
         <v>46162</v>
       </c>
       <c r="AR47" s="34" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AS47" s="34" t="s">
-        <v>105</v>
+        <v>108</v>
+      </c>
+      <c r="BK47" s="17">
+        <v>9</v>
       </c>
       <c r="BL47" s="17">
         <v>93</v>
@@ -5318,54 +5839,71 @@
         <v>90</v>
       </c>
       <c r="BP47" s="17" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="CI47" s="17">
         <f t="shared" si="0"/>
         <v>93</v>
       </c>
-    </row>
-    <row r="48" spans="1:87" ht="21">
+      <c r="CJ47" s="19"/>
+      <c r="CM47" s="19">
+        <v>46191</v>
+      </c>
+      <c r="CN47" s="17">
+        <v>5</v>
+      </c>
+      <c r="CO47" s="17">
+        <f>+C47-38.3</f>
+        <v>151.44999999999999</v>
+      </c>
+      <c r="CP47" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="CQ47" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="48" spans="1:107" ht="21">
       <c r="A48" s="6" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="C48" s="6">
         <v>169.61</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="G48" s="17" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="P48" s="34">
         <v>91</v>
       </c>
-      <c r="Q48" s="17">
+      <c r="Q48" s="34">
         <v>142.69999999999999</v>
       </c>
-      <c r="S48" s="17" t="s">
-        <v>119</v>
+      <c r="S48" s="34" t="s">
+        <v>91</v>
       </c>
       <c r="T48" s="34" t="s">
         <v>90</v>
       </c>
       <c r="U48" s="34"/>
-      <c r="V48" s="19">
+      <c r="V48" s="35">
         <v>46176</v>
       </c>
       <c r="W48" s="35">
         <v>46172</v>
       </c>
       <c r="X48" s="35"/>
-      <c r="Y48" s="17" t="s">
-        <v>100</v>
+      <c r="Y48" s="34" t="s">
+        <v>103</v>
       </c>
       <c r="Z48" s="34">
         <v>3</v>
@@ -5383,13 +5921,13 @@
         <v>46167</v>
       </c>
       <c r="AI48" s="34" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AN48" s="34" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="AO48" s="34" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="AP48" s="34">
         <v>146.93</v>
@@ -5398,10 +5936,13 @@
         <v>46172</v>
       </c>
       <c r="AR48" s="34" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AS48" s="34" t="s">
-        <v>105</v>
+        <v>108</v>
+      </c>
+      <c r="BK48" s="17">
+        <v>9</v>
       </c>
       <c r="BL48" s="17">
         <v>93</v>
@@ -5410,54 +5951,70 @@
         <v>90</v>
       </c>
       <c r="BP48" s="17" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="CI48" s="17">
         <f t="shared" si="0"/>
         <v>93</v>
       </c>
-    </row>
-    <row r="49" spans="1:87" ht="21">
+      <c r="CM48" s="19">
+        <v>46199</v>
+      </c>
+      <c r="CN48" s="17">
+        <v>5</v>
+      </c>
+      <c r="CO48" s="17">
+        <f>+C48-32.5</f>
+        <v>137.11000000000001</v>
+      </c>
+      <c r="CP48" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="CQ48" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="49" spans="1:107" ht="21">
       <c r="A49" s="6" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="C49" s="6">
         <v>118.35</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="G49" s="17" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="P49" s="34">
         <v>84.8</v>
       </c>
-      <c r="Q49" s="17">
+      <c r="Q49" s="34">
         <v>105.9</v>
       </c>
-      <c r="S49" s="17" t="s">
-        <v>119</v>
+      <c r="S49" s="34" t="s">
+        <v>91</v>
       </c>
       <c r="T49" s="34" t="s">
         <v>90</v>
       </c>
       <c r="U49" s="34"/>
-      <c r="V49" s="19">
+      <c r="V49" s="35">
         <v>46175</v>
       </c>
       <c r="W49" s="35">
         <v>46172</v>
       </c>
       <c r="X49" s="35"/>
-      <c r="Y49" s="17" t="s">
-        <v>100</v>
+      <c r="Y49" s="34" t="s">
+        <v>103</v>
       </c>
       <c r="Z49" s="34">
         <v>3</v>
@@ -5475,13 +6032,13 @@
         <v>46167</v>
       </c>
       <c r="AI49" s="34" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AN49" s="34" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="AO49" s="34" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="AP49" s="34">
         <v>120.28</v>
@@ -5490,10 +6047,13 @@
         <v>46166</v>
       </c>
       <c r="AR49" s="34" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="AS49" s="34" t="s">
-        <v>105</v>
+        <v>108</v>
+      </c>
+      <c r="BK49" s="17">
+        <v>9</v>
       </c>
       <c r="BL49" s="17">
         <v>93</v>
@@ -5502,54 +6062,70 @@
         <v>90</v>
       </c>
       <c r="BP49" s="17" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="CI49" s="17">
         <f t="shared" si="0"/>
         <v>93</v>
       </c>
-    </row>
-    <row r="50" spans="1:87" ht="21">
+      <c r="CM49" s="19">
+        <v>46191</v>
+      </c>
+      <c r="CN49" s="17">
+        <v>5</v>
+      </c>
+      <c r="CO49" s="17">
+        <f>+C49-38.5</f>
+        <v>79.849999999999994</v>
+      </c>
+      <c r="CP49" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="CQ49" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="50" spans="1:107" ht="21">
       <c r="A50" s="6" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="C50" s="6">
         <v>243.29</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="G50" s="17" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="P50" s="34">
         <v>105.1</v>
       </c>
-      <c r="Q50" s="17">
+      <c r="Q50" s="34">
         <v>88.1</v>
       </c>
-      <c r="S50" s="17" t="s">
-        <v>119</v>
+      <c r="S50" s="34" t="s">
+        <v>91</v>
       </c>
       <c r="T50" s="34" t="s">
         <v>90</v>
       </c>
       <c r="U50" s="34"/>
-      <c r="V50" s="19">
+      <c r="V50" s="35">
         <v>46174</v>
       </c>
       <c r="W50" s="35">
         <v>46172</v>
       </c>
       <c r="X50" s="35"/>
-      <c r="Y50" s="17" t="s">
-        <v>100</v>
+      <c r="Y50" s="34" t="s">
+        <v>103</v>
       </c>
       <c r="Z50" s="34">
         <v>3</v>
@@ -5567,13 +6143,13 @@
         <v>46167</v>
       </c>
       <c r="AI50" s="34" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AN50" s="34" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="AO50" s="34" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="AP50" s="34">
         <v>120.28</v>
@@ -5582,10 +6158,13 @@
         <v>46163</v>
       </c>
       <c r="AR50" s="34" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="AS50" s="34" t="s">
-        <v>105</v>
+        <v>108</v>
+      </c>
+      <c r="BK50" s="17">
+        <v>9</v>
       </c>
       <c r="BL50" s="17">
         <v>93</v>
@@ -5594,35 +6173,51 @@
         <v>90</v>
       </c>
       <c r="BP50" s="17" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="CI50" s="17">
         <f t="shared" si="0"/>
         <v>93</v>
       </c>
-    </row>
-    <row r="51" spans="1:87" ht="21">
+      <c r="CM50" s="19">
+        <v>46187</v>
+      </c>
+      <c r="CN50" s="17">
+        <v>5</v>
+      </c>
+      <c r="CO50" s="17">
+        <f>+C50-45.3</f>
+        <v>197.99</v>
+      </c>
+      <c r="CP50" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="CQ50" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="51" spans="1:107" ht="21">
       <c r="A51" s="6" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="C51" s="6">
         <v>201.78</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AH51" s="18"/>
       <c r="AN51" s="34" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="AO51" s="34" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="AP51" s="34">
         <v>10</v>
@@ -5631,38 +6226,51 @@
         <v>46143</v>
       </c>
       <c r="AR51" s="34" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="AS51" s="34" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="CI51" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:87" ht="21">
+      <c r="CR51" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="CV51" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="CW51" s="17">
+        <v>0.8</v>
+      </c>
+      <c r="DB51" s="52"/>
+      <c r="DC51" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="52" spans="1:107" ht="21">
       <c r="A52" s="6" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="C52" s="6">
         <v>150.52000000000001</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AH52" s="18"/>
       <c r="AN52" s="34" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="AO52" s="34" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="AP52" s="34">
         <v>10</v>
@@ -5671,38 +6279,51 @@
         <v>46143</v>
       </c>
       <c r="AR52" s="34" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="AS52" s="34" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="CI52" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:87" ht="21">
+      <c r="CR52" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="CV52" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="CW52" s="17">
+        <v>0.8</v>
+      </c>
+      <c r="DB52" s="52"/>
+      <c r="DC52" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="53" spans="1:107" ht="21">
       <c r="A53" s="6" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="C53" s="6">
         <v>225.15</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AH53" s="18"/>
       <c r="AN53" s="34" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="AO53" s="34" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="AP53" s="34">
         <v>10</v>
@@ -5711,47 +6332,60 @@
         <v>46143</v>
       </c>
       <c r="AR53" s="34" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="AS53" s="34" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="CI53" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:87">
+      <c r="CR53" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="CV53" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="CW53" s="17">
+        <v>0.8</v>
+      </c>
+      <c r="DB53" s="52"/>
+      <c r="DC53" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="54" spans="1:107">
       <c r="AH54" s="18"/>
     </row>
-    <row r="55" spans="1:87">
+    <row r="55" spans="1:107">
       <c r="AH55" s="18"/>
     </row>
-    <row r="56" spans="1:87">
+    <row r="56" spans="1:107">
       <c r="AH56" s="18"/>
     </row>
-    <row r="57" spans="1:87">
+    <row r="57" spans="1:107">
       <c r="AH57" s="18"/>
     </row>
-    <row r="58" spans="1:87">
+    <row r="58" spans="1:107">
       <c r="AH58" s="18"/>
     </row>
-    <row r="59" spans="1:87">
+    <row r="59" spans="1:107">
       <c r="AH59" s="18"/>
     </row>
-    <row r="60" spans="1:87">
+    <row r="60" spans="1:107">
       <c r="AH60" s="18"/>
     </row>
-    <row r="61" spans="1:87">
+    <row r="61" spans="1:107">
       <c r="AH61" s="18"/>
     </row>
-    <row r="62" spans="1:87">
+    <row r="62" spans="1:107">
       <c r="AH62" s="18"/>
     </row>
-    <row r="63" spans="1:87">
+    <row r="63" spans="1:107">
       <c r="AH63" s="18"/>
     </row>
-    <row r="64" spans="1:87">
+    <row r="64" spans="1:107">
       <c r="AH64" s="18"/>
     </row>
     <row r="65" spans="34:34">
@@ -5889,14 +6523,14 @@
     <mergeCell ref="BQ1:BV1"/>
     <mergeCell ref="BW1:CB1"/>
     <mergeCell ref="BG1:BI1"/>
-    <mergeCell ref="DF1:DH1"/>
-    <mergeCell ref="DI1:DK1"/>
-    <mergeCell ref="DL1:DO1"/>
+    <mergeCell ref="DG1:DI1"/>
+    <mergeCell ref="DJ1:DL1"/>
+    <mergeCell ref="DM1:DP1"/>
     <mergeCell ref="CC1:CH1"/>
     <mergeCell ref="CJ1:CL1"/>
     <mergeCell ref="CM1:CQ1"/>
-    <mergeCell ref="CR1:DB1"/>
-    <mergeCell ref="DC1:DE1"/>
+    <mergeCell ref="CR1:DC1"/>
+    <mergeCell ref="DD1:DF1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5904,6 +6538,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB45D919-FE15-4609-BAFC-CE592C260F0A}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:E53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -5932,13 +6567,13 @@
         <v>22</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="21">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="21" hidden="1">
       <c r="A3" s="6" t="s">
         <v>86</v>
       </c>
@@ -5948,11 +6583,11 @@
       <c r="C3" s="6">
         <v>203.49</v>
       </c>
-      <c r="D3" s="84" t="s">
+      <c r="D3" s="49" t="s">
         <v>88</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="21">
@@ -5965,8 +6600,8 @@
       <c r="C4" s="6">
         <v>215</v>
       </c>
-      <c r="D4" s="84" t="s">
-        <v>97</v>
+      <c r="D4" s="49" t="s">
+        <v>100</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>87</v>
@@ -5982,8 +6617,8 @@
       <c r="C5" s="6">
         <v>46.12</v>
       </c>
-      <c r="D5" s="84" t="s">
-        <v>97</v>
+      <c r="D5" s="49" t="s">
+        <v>100</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>87</v>
@@ -5999,8 +6634,8 @@
       <c r="C6" s="6">
         <v>24.03</v>
       </c>
-      <c r="D6" s="84" t="s">
-        <v>97</v>
+      <c r="D6" s="49" t="s">
+        <v>100</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>87</v>
@@ -6016,8 +6651,8 @@
       <c r="C7" s="6">
         <v>22.55</v>
       </c>
-      <c r="D7" s="84" t="s">
-        <v>97</v>
+      <c r="D7" s="49" t="s">
+        <v>100</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>87</v>
@@ -6033,8 +6668,8 @@
       <c r="C8" s="6">
         <v>62.73</v>
       </c>
-      <c r="D8" s="84" t="s">
-        <v>97</v>
+      <c r="D8" s="49" t="s">
+        <v>100</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>87</v>
@@ -6050,8 +6685,8 @@
       <c r="C9" s="6">
         <v>29.7</v>
       </c>
-      <c r="D9" s="84" t="s">
-        <v>97</v>
+      <c r="D9" s="49" t="s">
+        <v>100</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>87</v>
@@ -6067,8 +6702,8 @@
       <c r="C10" s="6">
         <v>270.44</v>
       </c>
-      <c r="D10" s="84" t="s">
-        <v>97</v>
+      <c r="D10" s="49" t="s">
+        <v>100</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>87</v>
@@ -6084,8 +6719,8 @@
       <c r="C11" s="6">
         <v>64.25</v>
       </c>
-      <c r="D11" s="84" t="s">
-        <v>97</v>
+      <c r="D11" s="49" t="s">
+        <v>100</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>87</v>
@@ -6101,8 +6736,8 @@
       <c r="C12" s="6">
         <v>29.89</v>
       </c>
-      <c r="D12" s="84" t="s">
-        <v>97</v>
+      <c r="D12" s="49" t="s">
+        <v>100</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>87</v>
@@ -6110,7 +6745,7 @@
     </row>
     <row r="13" spans="1:5" ht="21">
       <c r="A13" s="6" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B13" s="6">
         <v>6</v>
@@ -6118,16 +6753,16 @@
       <c r="C13" s="6">
         <v>52.63</v>
       </c>
-      <c r="D13" s="84" t="s">
-        <v>97</v>
+      <c r="D13" s="49" t="s">
+        <v>100</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="21">
+    <row r="14" spans="1:5" ht="21" hidden="1">
       <c r="A14" s="6" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B14" s="6">
         <v>7</v>
@@ -6135,16 +6770,16 @@
       <c r="C14" s="6">
         <v>60.61</v>
       </c>
-      <c r="D14" s="84" t="s">
-        <v>103</v>
+      <c r="D14" s="49" t="s">
+        <v>106</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="21">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="21" hidden="1">
       <c r="A15" s="6" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B15" s="6">
         <v>11</v>
@@ -6152,16 +6787,16 @@
       <c r="C15" s="6">
         <v>56.69</v>
       </c>
-      <c r="D15" s="84" t="s">
-        <v>103</v>
+      <c r="D15" s="49" t="s">
+        <v>106</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="21">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="21" hidden="1">
       <c r="A16" s="6" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B16" s="6">
         <v>12</v>
@@ -6169,16 +6804,16 @@
       <c r="C16" s="6">
         <v>49.78</v>
       </c>
-      <c r="D16" s="84" t="s">
-        <v>103</v>
+      <c r="D16" s="49" t="s">
+        <v>106</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="21">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="21" hidden="1">
       <c r="A17" s="6" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B17" s="6">
         <v>13</v>
@@ -6186,16 +6821,16 @@
       <c r="C17" s="6">
         <v>26.67</v>
       </c>
-      <c r="D17" s="84" t="s">
-        <v>103</v>
+      <c r="D17" s="49" t="s">
+        <v>106</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="21">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="21" hidden="1">
       <c r="A18" s="6" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B18" s="6">
         <v>14</v>
@@ -6203,16 +6838,16 @@
       <c r="C18" s="6">
         <v>33.96</v>
       </c>
-      <c r="D18" s="84" t="s">
-        <v>103</v>
+      <c r="D18" s="49" t="s">
+        <v>106</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="21">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="21" hidden="1">
       <c r="A19" s="6" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B19" s="6">
         <v>16</v>
@@ -6220,16 +6855,16 @@
       <c r="C19" s="6">
         <v>91.46</v>
       </c>
-      <c r="D19" s="84" t="s">
-        <v>103</v>
+      <c r="D19" s="49" t="s">
+        <v>106</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="21">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="21" hidden="1">
       <c r="A20" s="6" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B20" s="6">
         <v>1</v>
@@ -6237,16 +6872,16 @@
       <c r="C20" s="6">
         <v>58.59</v>
       </c>
-      <c r="D20" s="84" t="s">
+      <c r="D20" s="49" t="s">
         <v>88</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="21">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="21" hidden="1">
       <c r="A21" s="6" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B21" s="6">
         <v>2</v>
@@ -6254,16 +6889,16 @@
       <c r="C21" s="6">
         <v>40.99</v>
       </c>
-      <c r="D21" s="84" t="s">
+      <c r="D21" s="49" t="s">
         <v>88</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="21">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="21" hidden="1">
       <c r="A22" s="6" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B22" s="6">
         <v>3</v>
@@ -6271,16 +6906,16 @@
       <c r="C22" s="6">
         <v>63.11</v>
       </c>
-      <c r="D22" s="84" t="s">
+      <c r="D22" s="49" t="s">
         <v>88</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="21">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="21" hidden="1">
       <c r="A23" s="6" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B23" s="6">
         <v>4</v>
@@ -6288,16 +6923,16 @@
       <c r="C23" s="6">
         <v>71.48</v>
       </c>
-      <c r="D23" s="84" t="s">
+      <c r="D23" s="49" t="s">
         <v>88</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="21">
       <c r="A24" s="6" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B24" s="6">
         <v>5</v>
@@ -6305,8 +6940,8 @@
       <c r="C24" s="6">
         <v>67.739999999999995</v>
       </c>
-      <c r="D24" s="84" t="s">
-        <v>97</v>
+      <c r="D24" s="49" t="s">
+        <v>100</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>87</v>
@@ -6314,7 +6949,7 @@
     </row>
     <row r="25" spans="1:5" ht="21">
       <c r="A25" s="6" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B25" s="6">
         <v>6</v>
@@ -6322,16 +6957,16 @@
       <c r="C25" s="6">
         <v>24.52</v>
       </c>
-      <c r="D25" s="84" t="s">
-        <v>97</v>
+      <c r="D25" s="49" t="s">
+        <v>100</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="21">
+    <row r="26" spans="1:5" ht="21" hidden="1">
       <c r="A26" s="6" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B26" s="6">
         <v>11</v>
@@ -6339,16 +6974,16 @@
       <c r="C26" s="6">
         <v>31</v>
       </c>
-      <c r="D26" s="84" t="s">
+      <c r="D26" s="49" t="s">
         <v>88</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="21">
       <c r="A27" s="6" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B27" s="6">
         <v>12</v>
@@ -6356,16 +6991,16 @@
       <c r="C27" s="6">
         <v>67</v>
       </c>
-      <c r="D27" s="84" t="s">
-        <v>97</v>
+      <c r="D27" s="49" t="s">
+        <v>100</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="21">
+    <row r="28" spans="1:5" ht="21" hidden="1">
       <c r="A28" s="6" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B28" s="6">
         <v>1</v>
@@ -6373,16 +7008,16 @@
       <c r="C28" s="6">
         <v>138.88</v>
       </c>
-      <c r="D28" s="84" t="s">
+      <c r="D28" s="49" t="s">
         <v>88</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="21">
       <c r="A29" s="6" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B29" s="6">
         <v>2</v>
@@ -6390,16 +7025,16 @@
       <c r="C29" s="6">
         <v>141.69999999999999</v>
       </c>
-      <c r="D29" s="84" t="s">
-        <v>97</v>
+      <c r="D29" s="49" t="s">
+        <v>100</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="21">
       <c r="A30" s="6" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B30" s="6">
         <v>1</v>
@@ -6407,16 +7042,16 @@
       <c r="C30" s="6">
         <v>101.74</v>
       </c>
-      <c r="D30" s="84" t="s">
-        <v>97</v>
+      <c r="D30" s="49" t="s">
+        <v>100</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="21">
+    <row r="31" spans="1:5" ht="21" hidden="1">
       <c r="A31" s="6" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B31" s="6">
         <v>2</v>
@@ -6424,16 +7059,16 @@
       <c r="C31" s="6">
         <v>34.99</v>
       </c>
-      <c r="D31" s="84" t="s">
+      <c r="D31" s="49" t="s">
         <v>88</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="21">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="21" hidden="1">
       <c r="A32" s="6" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B32" s="6">
         <v>3</v>
@@ -6441,16 +7076,16 @@
       <c r="C32" s="6">
         <v>301.24</v>
       </c>
-      <c r="D32" s="84" t="s">
+      <c r="D32" s="49" t="s">
         <v>88</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="21">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="21" hidden="1">
       <c r="A33" s="6" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B33" s="6">
         <v>4</v>
@@ -6458,16 +7093,16 @@
       <c r="C33" s="6">
         <v>180.2</v>
       </c>
-      <c r="D33" s="84" t="s">
+      <c r="D33" s="49" t="s">
         <v>88</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="21">
       <c r="A34" s="6" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B34" s="6">
         <v>5</v>
@@ -6475,8 +7110,8 @@
       <c r="C34" s="6">
         <v>59.08</v>
       </c>
-      <c r="D34" s="84" t="s">
-        <v>97</v>
+      <c r="D34" s="49" t="s">
+        <v>100</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>87</v>
@@ -6484,7 +7119,7 @@
     </row>
     <row r="35" spans="1:5" ht="21">
       <c r="A35" s="6" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B35" s="6">
         <v>7</v>
@@ -6492,8 +7127,8 @@
       <c r="C35" s="6">
         <v>46.79</v>
       </c>
-      <c r="D35" s="84" t="s">
-        <v>97</v>
+      <c r="D35" s="49" t="s">
+        <v>100</v>
       </c>
       <c r="E35" s="6" t="s">
         <v>87</v>
@@ -6501,7 +7136,7 @@
     </row>
     <row r="36" spans="1:5" ht="21">
       <c r="A36" s="6" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B36" s="6">
         <v>8</v>
@@ -6509,8 +7144,8 @@
       <c r="C36" s="6">
         <v>59.05</v>
       </c>
-      <c r="D36" s="84" t="s">
-        <v>97</v>
+      <c r="D36" s="49" t="s">
+        <v>100</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>87</v>
@@ -6518,7 +7153,7 @@
     </row>
     <row r="37" spans="1:5" ht="21">
       <c r="A37" s="6" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B37" s="6">
         <v>9</v>
@@ -6526,16 +7161,16 @@
       <c r="C37" s="6">
         <v>103.45</v>
       </c>
-      <c r="D37" s="84" t="s">
-        <v>97</v>
+      <c r="D37" s="49" t="s">
+        <v>100</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="21">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="21" hidden="1">
       <c r="A38" s="6" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B38" s="6">
         <v>10</v>
@@ -6543,16 +7178,16 @@
       <c r="C38" s="6">
         <v>101.88</v>
       </c>
-      <c r="D38" s="84" t="s">
+      <c r="D38" s="49" t="s">
         <v>88</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="21">
       <c r="A39" s="6" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B39" s="6">
         <v>11</v>
@@ -6560,8 +7195,8 @@
       <c r="C39" s="6">
         <v>53.38</v>
       </c>
-      <c r="D39" s="84" t="s">
-        <v>97</v>
+      <c r="D39" s="49" t="s">
+        <v>100</v>
       </c>
       <c r="E39" s="6" t="s">
         <v>87</v>
@@ -6569,7 +7204,7 @@
     </row>
     <row r="40" spans="1:5" ht="21">
       <c r="A40" s="6" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B40" s="6">
         <v>12</v>
@@ -6577,16 +7212,16 @@
       <c r="C40" s="6">
         <v>102.7</v>
       </c>
-      <c r="D40" s="84" t="s">
-        <v>97</v>
+      <c r="D40" s="49" t="s">
+        <v>100</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="21">
       <c r="A41" s="6" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B41" s="6">
         <v>13</v>
@@ -6594,16 +7229,16 @@
       <c r="C41" s="6">
         <v>87.11</v>
       </c>
-      <c r="D41" s="84" t="s">
-        <v>97</v>
+      <c r="D41" s="49" t="s">
+        <v>100</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="21">
       <c r="A42" s="6" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B42" s="6">
         <v>14</v>
@@ -6611,8 +7246,8 @@
       <c r="C42" s="6">
         <v>59.42</v>
       </c>
-      <c r="D42" s="84" t="s">
-        <v>97</v>
+      <c r="D42" s="49" t="s">
+        <v>100</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>87</v>
@@ -6620,7 +7255,7 @@
     </row>
     <row r="43" spans="1:5" ht="21">
       <c r="A43" s="6" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B43" s="6">
         <v>15</v>
@@ -6628,184 +7263,191 @@
       <c r="C43" s="6">
         <v>35.96</v>
       </c>
-      <c r="D43" s="84" t="s">
-        <v>97</v>
+      <c r="D43" s="49" t="s">
+        <v>100</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="21">
+    <row r="44" spans="1:5" ht="21" hidden="1">
       <c r="A44" s="6" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C44" s="6">
         <v>386.2</v>
       </c>
-      <c r="D44" s="84" t="s">
-        <v>139</v>
+      <c r="D44" s="49" t="s">
+        <v>144</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="21">
       <c r="A45" s="6" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C45" s="6">
         <v>120</v>
       </c>
-      <c r="D45" s="84" t="s">
-        <v>97</v>
+      <c r="D45" s="49" t="s">
+        <v>100</v>
       </c>
       <c r="E45" s="6" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="21">
+    <row r="46" spans="1:5" ht="21" hidden="1">
       <c r="A46" s="6" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="C46" s="9">
         <v>163</v>
       </c>
-      <c r="D46" s="84" t="s">
-        <v>139</v>
+      <c r="D46" s="49" t="s">
+        <v>144</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" ht="21">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="21" hidden="1">
       <c r="A47" s="6" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C47" s="6">
         <v>189.75</v>
       </c>
-      <c r="D47" s="84" t="s">
-        <v>139</v>
+      <c r="D47" s="49" t="s">
+        <v>144</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" ht="21">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="21" hidden="1">
       <c r="A48" s="6" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="C48" s="6">
         <v>169.61</v>
       </c>
-      <c r="D48" s="84" t="s">
-        <v>139</v>
+      <c r="D48" s="49" t="s">
+        <v>144</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" ht="21">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="21" hidden="1">
       <c r="A49" s="6" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="C49" s="6">
         <v>118.35</v>
       </c>
-      <c r="D49" s="84" t="s">
-        <v>139</v>
+      <c r="D49" s="49" t="s">
+        <v>144</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" ht="21">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="21" hidden="1">
       <c r="A50" s="6" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="C50" s="6">
         <v>243.29</v>
       </c>
-      <c r="D50" s="84" t="s">
-        <v>139</v>
+      <c r="D50" s="49" t="s">
+        <v>144</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="21">
       <c r="A51" s="6" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="C51" s="6">
         <v>201.78</v>
       </c>
-      <c r="D51" s="84" t="s">
-        <v>97</v>
+      <c r="D51" s="49" t="s">
+        <v>100</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="21">
       <c r="A52" s="6" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="C52" s="6">
         <v>150.52000000000001</v>
       </c>
-      <c r="D52" s="84" t="s">
-        <v>97</v>
+      <c r="D52" s="49" t="s">
+        <v>100</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="21">
       <c r="A53" s="6" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="C53" s="6">
         <v>225.15</v>
       </c>
-      <c r="D53" s="84" t="s">
-        <v>97</v>
+      <c r="D53" s="49" t="s">
+        <v>100</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A2:E53" xr:uid="{BB45D919-FE15-4609-BAFC-CE592C260F0A}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="Cobertura"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6824,218 +7466,218 @@
       <c r="B1" s="37">
         <v>2022</v>
       </c>
-      <c r="C1" s="80">
+      <c r="C1" s="84">
         <v>2023</v>
       </c>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="81"/>
-      <c r="K1" s="81"/>
-      <c r="L1" s="81"/>
-      <c r="M1" s="81"/>
-      <c r="N1" s="81"/>
-      <c r="O1" s="80">
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="85"/>
+      <c r="I1" s="85"/>
+      <c r="J1" s="85"/>
+      <c r="K1" s="85"/>
+      <c r="L1" s="85"/>
+      <c r="M1" s="85"/>
+      <c r="N1" s="85"/>
+      <c r="O1" s="84">
         <v>2024</v>
       </c>
-      <c r="P1" s="81"/>
-      <c r="Q1" s="81"/>
-      <c r="R1" s="81"/>
-      <c r="S1" s="81"/>
-      <c r="T1" s="81"/>
-      <c r="U1" s="81"/>
-      <c r="V1" s="81"/>
-      <c r="W1" s="81"/>
-      <c r="X1" s="81"/>
-      <c r="Y1" s="81"/>
-      <c r="Z1" s="82"/>
-      <c r="AA1" s="81">
+      <c r="P1" s="85"/>
+      <c r="Q1" s="85"/>
+      <c r="R1" s="85"/>
+      <c r="S1" s="85"/>
+      <c r="T1" s="85"/>
+      <c r="U1" s="85"/>
+      <c r="V1" s="85"/>
+      <c r="W1" s="85"/>
+      <c r="X1" s="85"/>
+      <c r="Y1" s="85"/>
+      <c r="Z1" s="86"/>
+      <c r="AA1" s="85">
         <v>2025</v>
       </c>
-      <c r="AB1" s="81"/>
-      <c r="AC1" s="81"/>
-      <c r="AD1" s="81"/>
-      <c r="AE1" s="81"/>
-      <c r="AF1" s="81"/>
-      <c r="AG1" s="81"/>
-      <c r="AH1" s="81"/>
-      <c r="AI1" s="81"/>
-      <c r="AJ1" s="81"/>
-      <c r="AK1" s="81"/>
-      <c r="AL1" s="81"/>
-      <c r="AM1" s="83">
+      <c r="AB1" s="85"/>
+      <c r="AC1" s="85"/>
+      <c r="AD1" s="85"/>
+      <c r="AE1" s="85"/>
+      <c r="AF1" s="85"/>
+      <c r="AG1" s="85"/>
+      <c r="AH1" s="85"/>
+      <c r="AI1" s="85"/>
+      <c r="AJ1" s="85"/>
+      <c r="AK1" s="85"/>
+      <c r="AL1" s="85"/>
+      <c r="AM1" s="87">
         <v>2026</v>
       </c>
-      <c r="AN1" s="83"/>
-      <c r="AO1" s="83"/>
-      <c r="AP1" s="83"/>
-      <c r="AQ1" s="83"/>
-      <c r="AR1" s="83"/>
-      <c r="AS1" s="83"/>
-      <c r="AT1" s="83"/>
-      <c r="AU1" s="83"/>
-      <c r="AV1" s="83"/>
-      <c r="AW1" s="83"/>
-      <c r="AX1" s="83"/>
+      <c r="AN1" s="87"/>
+      <c r="AO1" s="87"/>
+      <c r="AP1" s="87"/>
+      <c r="AQ1" s="87"/>
+      <c r="AR1" s="87"/>
+      <c r="AS1" s="87"/>
+      <c r="AT1" s="87"/>
+      <c r="AU1" s="87"/>
+      <c r="AV1" s="87"/>
+      <c r="AW1" s="87"/>
+      <c r="AX1" s="87"/>
     </row>
     <row r="2" spans="1:50">
       <c r="A2" s="37" t="s">
         <v>20</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="C2" s="38" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="D2" s="37" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="E2" s="37" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="F2" s="37" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="G2" s="37" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="H2" s="37" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="I2" s="37" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="J2" s="37" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="K2" s="37" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="L2" s="37" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="M2" s="37" t="s">
+        <v>177</v>
+      </c>
+      <c r="N2" s="37" t="s">
         <v>166</v>
       </c>
-      <c r="N2" s="37" t="s">
-        <v>155</v>
-      </c>
       <c r="O2" s="38" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="P2" s="37" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="Q2" s="37" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="R2" s="37" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="S2" s="37" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="T2" s="37" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="U2" s="37" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="V2" s="37" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="W2" s="37" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="X2" s="37" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="Y2" s="37" t="s">
+        <v>177</v>
+      </c>
+      <c r="Z2" s="39" t="s">
         <v>166</v>
       </c>
-      <c r="Z2" s="39" t="s">
-        <v>155</v>
-      </c>
       <c r="AA2" s="37" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="AB2" s="37" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="AC2" s="37" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="AD2" s="37" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="AE2" s="37" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="AF2" s="37" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="AG2" s="37" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="AH2" s="37" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="AI2" s="37" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="AJ2" s="37" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="AK2" s="37" t="s">
+        <v>177</v>
+      </c>
+      <c r="AL2" s="37" t="s">
         <v>166</v>
       </c>
-      <c r="AL2" s="37" t="s">
-        <v>155</v>
-      </c>
       <c r="AM2" s="17" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="AN2" s="17" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="AO2" s="17" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="AP2" s="17" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="AQ2" s="17" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="AR2" s="17" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="AS2" s="17" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="AT2" s="17" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="AU2" s="17" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="AV2" s="17" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="AW2" s="17" t="s">
+        <v>177</v>
+      </c>
+      <c r="AX2" s="17" t="s">
         <v>166</v>
-      </c>
-      <c r="AX2" s="17" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="3" spans="1:50">
       <c r="A3" s="37" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="B3" s="37">
         <v>45</v>
@@ -7331,7 +7973,7 @@
     </row>
     <row r="5" spans="1:50">
       <c r="A5" s="37" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="B5" s="37">
         <v>35</v>
@@ -7479,7 +8121,7 @@
     </row>
     <row r="6" spans="1:50">
       <c r="A6" s="37" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B6" s="37">
         <v>47</v>
@@ -7627,7 +8269,7 @@
     </row>
     <row r="7" spans="1:50">
       <c r="A7" s="37" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B7" s="37">
         <v>35</v>

--- a/Planilla labores 26-27.xlsx
+++ b/Planilla labores 26-27.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30224"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30305"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://provinvestsa.sharepoint.com/sites/CeibosAgro-Uy-Produccin/Documentos compartidos/Litoral Norte/26-27/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{56483CA4-5D97-4F20-B6B3-02E35CAA0A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{039113A9-2A97-4A9A-BCAD-2B7018DDD57A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3781" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3770" uniqueCount="184">
   <si>
     <t>Análisis suelo</t>
   </si>
@@ -335,9 +335,6 @@
     <t>Plantadora</t>
   </si>
   <si>
-    <t>Programado</t>
-  </si>
-  <si>
     <t>todo menos fondo y frente de 24ha</t>
   </si>
   <si>
@@ -357,6 +354,9 @@
   </si>
   <si>
     <t>Altina</t>
+  </si>
+  <si>
+    <t>Programado</t>
   </si>
   <si>
     <t>Montecristo</t>
@@ -1155,6 +1155,9 @@
     <xf numFmtId="166" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1255,9 +1258,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1644,161 +1644,161 @@
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
       <c r="D1" s="4"/>
-      <c r="F1" s="68" t="s">
+      <c r="F1" s="69" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="68"/>
-      <c r="K1" s="68"/>
-      <c r="L1" s="68"/>
-      <c r="M1" s="68"/>
-      <c r="N1" s="68"/>
-      <c r="O1" s="69" t="s">
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
+      <c r="N1" s="69"/>
+      <c r="O1" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="70"/>
-      <c r="Q1" s="70"/>
-      <c r="R1" s="70"/>
-      <c r="S1" s="70"/>
-      <c r="T1" s="70"/>
-      <c r="U1" s="70"/>
-      <c r="V1" s="70"/>
-      <c r="W1" s="70"/>
-      <c r="X1" s="70"/>
-      <c r="Y1" s="70"/>
-      <c r="Z1" s="71" t="s">
+      <c r="P1" s="71"/>
+      <c r="Q1" s="71"/>
+      <c r="R1" s="71"/>
+      <c r="S1" s="71"/>
+      <c r="T1" s="71"/>
+      <c r="U1" s="71"/>
+      <c r="V1" s="71"/>
+      <c r="W1" s="71"/>
+      <c r="X1" s="71"/>
+      <c r="Y1" s="71"/>
+      <c r="Z1" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="AA1" s="71"/>
-      <c r="AB1" s="71"/>
-      <c r="AC1" s="71"/>
-      <c r="AD1" s="71"/>
-      <c r="AE1" s="71"/>
-      <c r="AF1" s="71"/>
-      <c r="AG1" s="71"/>
-      <c r="AH1" s="71"/>
-      <c r="AI1" s="71"/>
-      <c r="AJ1" s="77" t="s">
+      <c r="AA1" s="72"/>
+      <c r="AB1" s="72"/>
+      <c r="AC1" s="72"/>
+      <c r="AD1" s="72"/>
+      <c r="AE1" s="72"/>
+      <c r="AF1" s="72"/>
+      <c r="AG1" s="72"/>
+      <c r="AH1" s="72"/>
+      <c r="AI1" s="72"/>
+      <c r="AJ1" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="AK1" s="77"/>
-      <c r="AL1" s="77"/>
-      <c r="AM1" s="77"/>
-      <c r="AN1" s="72" t="s">
+      <c r="AK1" s="78"/>
+      <c r="AL1" s="78"/>
+      <c r="AM1" s="78"/>
+      <c r="AN1" s="73" t="s">
         <v>4</v>
       </c>
-      <c r="AO1" s="72"/>
-      <c r="AP1" s="72"/>
-      <c r="AQ1" s="72"/>
-      <c r="AR1" s="72"/>
-      <c r="AS1" s="73"/>
-      <c r="AT1" s="74" t="s">
+      <c r="AO1" s="73"/>
+      <c r="AP1" s="73"/>
+      <c r="AQ1" s="73"/>
+      <c r="AR1" s="73"/>
+      <c r="AS1" s="74"/>
+      <c r="AT1" s="75" t="s">
         <v>5</v>
       </c>
-      <c r="AU1" s="75"/>
-      <c r="AV1" s="75"/>
-      <c r="AW1" s="75"/>
-      <c r="AX1" s="75"/>
-      <c r="AY1" s="75"/>
-      <c r="AZ1" s="76"/>
-      <c r="BA1" s="78" t="s">
+      <c r="AU1" s="76"/>
+      <c r="AV1" s="76"/>
+      <c r="AW1" s="76"/>
+      <c r="AX1" s="76"/>
+      <c r="AY1" s="76"/>
+      <c r="AZ1" s="77"/>
+      <c r="BA1" s="79" t="s">
         <v>6</v>
       </c>
-      <c r="BB1" s="79"/>
-      <c r="BC1" s="79"/>
-      <c r="BD1" s="79"/>
-      <c r="BE1" s="79"/>
-      <c r="BF1" s="80"/>
-      <c r="BG1" s="87" t="s">
+      <c r="BB1" s="80"/>
+      <c r="BC1" s="80"/>
+      <c r="BD1" s="80"/>
+      <c r="BE1" s="80"/>
+      <c r="BF1" s="81"/>
+      <c r="BG1" s="88" t="s">
         <v>7</v>
       </c>
-      <c r="BH1" s="88"/>
-      <c r="BI1" s="89"/>
-      <c r="BJ1" s="81" t="s">
+      <c r="BH1" s="89"/>
+      <c r="BI1" s="90"/>
+      <c r="BJ1" s="82" t="s">
         <v>8</v>
       </c>
-      <c r="BK1" s="82"/>
-      <c r="BL1" s="83" t="s">
+      <c r="BK1" s="83"/>
+      <c r="BL1" s="84" t="s">
         <v>9</v>
       </c>
-      <c r="BM1" s="83"/>
-      <c r="BN1" s="83"/>
-      <c r="BO1" s="83"/>
-      <c r="BP1" s="83"/>
-      <c r="BQ1" s="84" t="s">
+      <c r="BM1" s="84"/>
+      <c r="BN1" s="84"/>
+      <c r="BO1" s="84"/>
+      <c r="BP1" s="84"/>
+      <c r="BQ1" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="BR1" s="85"/>
-      <c r="BS1" s="85"/>
-      <c r="BT1" s="85"/>
-      <c r="BU1" s="85"/>
-      <c r="BV1" s="86"/>
-      <c r="BW1" s="85" t="s">
+      <c r="BR1" s="86"/>
+      <c r="BS1" s="86"/>
+      <c r="BT1" s="86"/>
+      <c r="BU1" s="86"/>
+      <c r="BV1" s="87"/>
+      <c r="BW1" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="BX1" s="85"/>
-      <c r="BY1" s="85"/>
-      <c r="BZ1" s="85"/>
-      <c r="CA1" s="85"/>
-      <c r="CB1" s="85"/>
-      <c r="CC1" s="85" t="s">
+      <c r="BX1" s="86"/>
+      <c r="BY1" s="86"/>
+      <c r="BZ1" s="86"/>
+      <c r="CA1" s="86"/>
+      <c r="CB1" s="86"/>
+      <c r="CC1" s="86" t="s">
         <v>12</v>
       </c>
-      <c r="CD1" s="85"/>
-      <c r="CE1" s="85"/>
-      <c r="CF1" s="85"/>
-      <c r="CG1" s="85"/>
-      <c r="CH1" s="85"/>
+      <c r="CD1" s="86"/>
+      <c r="CE1" s="86"/>
+      <c r="CF1" s="86"/>
+      <c r="CG1" s="86"/>
+      <c r="CH1" s="86"/>
       <c r="CI1" s="23"/>
-      <c r="CJ1" s="93" t="s">
+      <c r="CJ1" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="CK1" s="93"/>
-      <c r="CL1" s="93"/>
-      <c r="CM1" s="94" t="s">
+      <c r="CK1" s="94"/>
+      <c r="CL1" s="94"/>
+      <c r="CM1" s="95" t="s">
         <v>14</v>
       </c>
-      <c r="CN1" s="94"/>
-      <c r="CO1" s="94"/>
-      <c r="CP1" s="94"/>
-      <c r="CQ1" s="94"/>
-      <c r="CR1" s="95" t="s">
+      <c r="CN1" s="95"/>
+      <c r="CO1" s="95"/>
+      <c r="CP1" s="95"/>
+      <c r="CQ1" s="95"/>
+      <c r="CR1" s="96" t="s">
         <v>15</v>
       </c>
-      <c r="CS1" s="95"/>
-      <c r="CT1" s="95"/>
-      <c r="CU1" s="95"/>
-      <c r="CV1" s="95"/>
-      <c r="CW1" s="95"/>
-      <c r="CX1" s="95"/>
-      <c r="CY1" s="95"/>
-      <c r="CZ1" s="95"/>
-      <c r="DA1" s="95"/>
-      <c r="DB1" s="95"/>
-      <c r="DC1" s="96"/>
-      <c r="DD1" s="97" t="s">
+      <c r="CS1" s="96"/>
+      <c r="CT1" s="96"/>
+      <c r="CU1" s="96"/>
+      <c r="CV1" s="96"/>
+      <c r="CW1" s="96"/>
+      <c r="CX1" s="96"/>
+      <c r="CY1" s="96"/>
+      <c r="CZ1" s="96"/>
+      <c r="DA1" s="96"/>
+      <c r="DB1" s="96"/>
+      <c r="DC1" s="97"/>
+      <c r="DD1" s="98" t="s">
         <v>16</v>
       </c>
-      <c r="DE1" s="91"/>
-      <c r="DF1" s="98"/>
-      <c r="DG1" s="90" t="s">
+      <c r="DE1" s="92"/>
+      <c r="DF1" s="99"/>
+      <c r="DG1" s="91" t="s">
         <v>17</v>
       </c>
-      <c r="DH1" s="91"/>
-      <c r="DI1" s="91"/>
-      <c r="DJ1" s="91" t="s">
+      <c r="DH1" s="92"/>
+      <c r="DI1" s="92"/>
+      <c r="DJ1" s="92" t="s">
         <v>18</v>
       </c>
-      <c r="DK1" s="91"/>
-      <c r="DL1" s="91"/>
-      <c r="DM1" s="92" t="s">
+      <c r="DK1" s="92"/>
+      <c r="DL1" s="92"/>
+      <c r="DM1" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="DN1" s="92"/>
-      <c r="DO1" s="92"/>
-      <c r="DP1" s="92"/>
+      <c r="DN1" s="93"/>
+      <c r="DO1" s="93"/>
+      <c r="DP1" s="93"/>
     </row>
     <row r="2" spans="1:120" ht="21">
       <c r="A2" s="5" t="s">
@@ -2212,7 +2212,7 @@
         <v>131</v>
       </c>
       <c r="Q3" s="34"/>
-      <c r="R3" s="17">
+      <c r="R3" s="34">
         <v>100</v>
       </c>
       <c r="S3" s="34" t="s">
@@ -2221,7 +2221,7 @@
       <c r="T3" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="U3" s="17" t="s">
+      <c r="U3" s="34" t="s">
         <v>91</v>
       </c>
       <c r="V3" s="35">
@@ -2230,10 +2230,10 @@
       <c r="W3" s="35">
         <v>46198</v>
       </c>
-      <c r="X3" s="19">
+      <c r="X3" s="35">
         <v>46200</v>
       </c>
-      <c r="Y3" s="17" t="s">
+      <c r="Y3" s="34" t="s">
         <v>92</v>
       </c>
       <c r="Z3" s="34">
@@ -2274,6 +2274,12 @@
       <c r="AS3" s="34" t="s">
         <v>96</v>
       </c>
+      <c r="BJ3" s="17">
+        <v>12.6</v>
+      </c>
+      <c r="BK3" s="17">
+        <v>6</v>
+      </c>
       <c r="BL3" s="34">
         <v>75</v>
       </c>
@@ -2287,24 +2293,26 @@
       <c r="BP3" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="BR3" s="19">
-        <v>46199</v>
-      </c>
-      <c r="BS3" s="17">
+      <c r="BQ3" s="34"/>
+      <c r="BR3" s="35">
+        <v>46200</v>
+      </c>
+      <c r="BS3" s="34">
         <v>50</v>
       </c>
-      <c r="BT3" s="17" t="s">
+      <c r="BT3" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="BV3" s="17" t="s">
+      <c r="BU3" s="34"/>
+      <c r="BV3" s="34" t="s">
         <v>92</v>
       </c>
       <c r="CI3" s="17">
         <f>+CE3+BY3+BS3+BL3</f>
         <v>125</v>
       </c>
-      <c r="CM3" s="17" t="s">
-        <v>97</v>
+      <c r="CM3" s="19">
+        <v>46205</v>
       </c>
       <c r="CN3" s="17">
         <v>5</v>
@@ -2314,7 +2322,7 @@
         <v>75.59</v>
       </c>
       <c r="CP3" s="17" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="CQ3" s="17" t="s">
         <v>92</v>
@@ -2343,17 +2351,17 @@
         <v>215</v>
       </c>
       <c r="D4" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>99</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>100</v>
       </c>
       <c r="AH4" s="18"/>
       <c r="AN4" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="AO4" s="34" t="s">
         <v>101</v>
-      </c>
-      <c r="AO4" s="34" t="s">
-        <v>102</v>
       </c>
       <c r="AP4" s="34">
         <v>40</v>
@@ -2362,17 +2370,17 @@
         <v>46137</v>
       </c>
       <c r="AR4" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="AS4" s="34" t="s">
         <v>103</v>
-      </c>
-      <c r="AS4" s="34" t="s">
-        <v>104</v>
       </c>
       <c r="CI4" s="17">
         <f t="shared" ref="CI4:CI53" si="0">+CE4+BY4+BS4+BL4</f>
         <v>0</v>
       </c>
       <c r="CR4" s="17" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="DB4" s="43">
         <v>0.04</v>
@@ -2392,17 +2400,17 @@
         <v>46.12</v>
       </c>
       <c r="D5" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>99</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>100</v>
       </c>
       <c r="AH5" s="18"/>
       <c r="AN5" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="AO5" s="34" t="s">
         <v>101</v>
-      </c>
-      <c r="AO5" s="34" t="s">
-        <v>102</v>
       </c>
       <c r="AP5" s="34">
         <v>40</v>
@@ -2411,17 +2419,17 @@
         <v>46137</v>
       </c>
       <c r="AR5" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="AS5" s="34" t="s">
         <v>103</v>
-      </c>
-      <c r="AS5" s="34" t="s">
-        <v>104</v>
       </c>
       <c r="CI5" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="CR5" s="17" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="DB5" s="43">
         <v>0.04</v>
@@ -2441,17 +2449,17 @@
         <v>24.03</v>
       </c>
       <c r="D6" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>99</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>100</v>
       </c>
       <c r="AH6" s="18"/>
       <c r="AN6" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="AO6" s="34" t="s">
         <v>101</v>
-      </c>
-      <c r="AO6" s="34" t="s">
-        <v>102</v>
       </c>
       <c r="AP6" s="34">
         <v>40</v>
@@ -2460,17 +2468,17 @@
         <v>46137</v>
       </c>
       <c r="AR6" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="AS6" s="34" t="s">
         <v>103</v>
-      </c>
-      <c r="AS6" s="34" t="s">
-        <v>104</v>
       </c>
       <c r="CI6" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="CR6" s="17" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="DB6" s="43">
         <v>0.04</v>
@@ -2490,17 +2498,17 @@
         <v>22.55</v>
       </c>
       <c r="D7" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>99</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>100</v>
       </c>
       <c r="AH7" s="18"/>
       <c r="AN7" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="AO7" s="34" t="s">
         <v>101</v>
-      </c>
-      <c r="AO7" s="34" t="s">
-        <v>102</v>
       </c>
       <c r="AP7" s="34">
         <v>40</v>
@@ -2509,17 +2517,17 @@
         <v>46137</v>
       </c>
       <c r="AR7" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="AS7" s="34" t="s">
         <v>103</v>
-      </c>
-      <c r="AS7" s="34" t="s">
-        <v>104</v>
       </c>
       <c r="CI7" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="CR7" s="17" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="DB7" s="43">
         <v>0.04</v>
@@ -2539,17 +2547,17 @@
         <v>62.73</v>
       </c>
       <c r="D8" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>99</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>100</v>
       </c>
       <c r="AH8" s="18"/>
       <c r="AN8" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="AO8" s="34" t="s">
         <v>101</v>
-      </c>
-      <c r="AO8" s="34" t="s">
-        <v>102</v>
       </c>
       <c r="AP8" s="34">
         <v>40</v>
@@ -2558,17 +2566,17 @@
         <v>46137</v>
       </c>
       <c r="AR8" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="AS8" s="34" t="s">
         <v>103</v>
-      </c>
-      <c r="AS8" s="34" t="s">
-        <v>104</v>
       </c>
       <c r="CI8" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="CR8" s="17" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="DB8" s="43">
         <v>0.04</v>
@@ -2588,17 +2596,17 @@
         <v>29.7</v>
       </c>
       <c r="D9" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>99</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>100</v>
       </c>
       <c r="AH9" s="18"/>
       <c r="AN9" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="AO9" s="34" t="s">
         <v>101</v>
-      </c>
-      <c r="AO9" s="34" t="s">
-        <v>102</v>
       </c>
       <c r="AP9" s="34">
         <v>40</v>
@@ -2607,17 +2615,17 @@
         <v>46137</v>
       </c>
       <c r="AR9" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="AS9" s="34" t="s">
         <v>103</v>
-      </c>
-      <c r="AS9" s="34" t="s">
-        <v>104</v>
       </c>
       <c r="CI9" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="CR9" s="17" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="DB9" s="43">
         <v>0.04</v>
@@ -2637,17 +2645,17 @@
         <v>270.44</v>
       </c>
       <c r="D10" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E10" s="7" t="s">
         <v>99</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>100</v>
       </c>
       <c r="AH10" s="18"/>
       <c r="AN10" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="AO10" s="34" t="s">
         <v>101</v>
-      </c>
-      <c r="AO10" s="34" t="s">
-        <v>102</v>
       </c>
       <c r="AP10" s="34">
         <v>40</v>
@@ -2656,17 +2664,17 @@
         <v>46137</v>
       </c>
       <c r="AR10" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="AS10" s="34" t="s">
         <v>103</v>
-      </c>
-      <c r="AS10" s="34" t="s">
-        <v>104</v>
       </c>
       <c r="CI10" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="CR10" s="17" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="DB10" s="43">
         <v>0.04</v>
@@ -2686,17 +2694,17 @@
         <v>64.25</v>
       </c>
       <c r="D11" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>99</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>100</v>
       </c>
       <c r="AH11" s="18"/>
       <c r="AN11" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="AO11" s="34" t="s">
         <v>101</v>
-      </c>
-      <c r="AO11" s="34" t="s">
-        <v>102</v>
       </c>
       <c r="AP11" s="34">
         <v>40</v>
@@ -2705,17 +2713,17 @@
         <v>46137</v>
       </c>
       <c r="AR11" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="AS11" s="34" t="s">
         <v>103</v>
-      </c>
-      <c r="AS11" s="34" t="s">
-        <v>104</v>
       </c>
       <c r="CI11" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="CR11" s="17" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="DB11" s="43">
         <v>0.04</v>
@@ -2735,17 +2743,17 @@
         <v>29.89</v>
       </c>
       <c r="D12" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E12" s="7" t="s">
         <v>99</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>100</v>
       </c>
       <c r="AH12" s="18"/>
       <c r="AN12" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="AO12" s="34" t="s">
         <v>101</v>
-      </c>
-      <c r="AO12" s="34" t="s">
-        <v>102</v>
       </c>
       <c r="AP12" s="34">
         <v>40</v>
@@ -2754,17 +2762,17 @@
         <v>46137</v>
       </c>
       <c r="AR12" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="AS12" s="34" t="s">
         <v>103</v>
-      </c>
-      <c r="AS12" s="34" t="s">
-        <v>104</v>
       </c>
       <c r="CI12" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="CR12" s="17" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="DB12" s="43">
         <v>0.04</v>
@@ -2784,17 +2792,17 @@
         <v>52.63</v>
       </c>
       <c r="D13" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>99</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>100</v>
       </c>
       <c r="AH13" s="18"/>
       <c r="AN13" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="AO13" s="34" t="s">
         <v>101</v>
-      </c>
-      <c r="AO13" s="34" t="s">
-        <v>102</v>
       </c>
       <c r="AP13" s="34">
         <v>40</v>
@@ -2803,17 +2811,17 @@
         <v>46139</v>
       </c>
       <c r="AR13" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="AS13" s="34" t="s">
         <v>103</v>
-      </c>
-      <c r="AS13" s="34" t="s">
-        <v>104</v>
       </c>
       <c r="CI13" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="CR13" s="17" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="DB13" s="43">
         <v>0.04</v>
@@ -2833,7 +2841,7 @@
         <v>60.61</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>106</v>
@@ -2926,6 +2934,12 @@
       <c r="AS14" s="34" t="s">
         <v>108</v>
       </c>
+      <c r="BJ14" s="17">
+        <v>42</v>
+      </c>
+      <c r="BK14" s="17">
+        <v>9</v>
+      </c>
       <c r="BL14" s="34">
         <v>95</v>
       </c>
@@ -2943,8 +2957,8 @@
         <f t="shared" si="0"/>
         <v>95</v>
       </c>
-      <c r="CM14" s="17" t="s">
-        <v>97</v>
+      <c r="CM14" s="19">
+        <v>46210</v>
       </c>
       <c r="CN14" s="17">
         <v>5</v>
@@ -2959,8 +2973,8 @@
       <c r="CQ14" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="CR14" s="17" t="s">
-        <v>97</v>
+      <c r="CR14" s="19">
+        <v>46210</v>
       </c>
       <c r="CY14" s="17">
         <v>0.24</v>
@@ -2983,7 +2997,7 @@
         <v>56.69</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>106</v>
@@ -3076,6 +3090,12 @@
       <c r="AS15" s="34" t="s">
         <v>108</v>
       </c>
+      <c r="BJ15" s="17">
+        <v>44</v>
+      </c>
+      <c r="BK15" s="17">
+        <v>9</v>
+      </c>
       <c r="BL15" s="34">
         <v>95</v>
       </c>
@@ -3093,8 +3113,8 @@
         <f t="shared" si="0"/>
         <v>95</v>
       </c>
-      <c r="CR15" s="17" t="s">
-        <v>97</v>
+      <c r="CR15" s="19">
+        <v>46210</v>
       </c>
       <c r="CY15" s="17">
         <v>0.24</v>
@@ -3117,7 +3137,7 @@
         <v>49.78</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>106</v>
@@ -3210,6 +3230,12 @@
       <c r="AS16" s="34" t="s">
         <v>108</v>
       </c>
+      <c r="BJ16" s="17">
+        <v>45</v>
+      </c>
+      <c r="BK16" s="17">
+        <v>9</v>
+      </c>
       <c r="BL16" s="34">
         <v>95</v>
       </c>
@@ -3227,8 +3253,8 @@
         <f t="shared" si="0"/>
         <v>95</v>
       </c>
-      <c r="CR16" s="17" t="s">
-        <v>97</v>
+      <c r="CR16" s="19">
+        <v>46210</v>
       </c>
       <c r="CY16" s="17">
         <v>0.24</v>
@@ -3251,7 +3277,7 @@
         <v>26.67</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>106</v>
@@ -3344,6 +3370,12 @@
       <c r="AS17" s="34" t="s">
         <v>108</v>
       </c>
+      <c r="BJ17" s="17">
+        <v>43</v>
+      </c>
+      <c r="BK17" s="17">
+        <v>9</v>
+      </c>
       <c r="BL17" s="34">
         <v>95</v>
       </c>
@@ -3361,8 +3393,8 @@
         <f t="shared" si="0"/>
         <v>95</v>
       </c>
-      <c r="CR17" s="17" t="s">
-        <v>97</v>
+      <c r="CR17" s="19">
+        <v>46210</v>
       </c>
       <c r="CY17" s="17">
         <v>0.24</v>
@@ -3385,7 +3417,7 @@
         <v>33.96</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>106</v>
@@ -3473,7 +3505,7 @@
       <c r="AN18" s="41" t="s">
         <v>111</v>
       </c>
-      <c r="AO18" s="102" t="s">
+      <c r="AO18" s="68" t="s">
         <v>112</v>
       </c>
       <c r="AP18" s="34">
@@ -3487,6 +3519,12 @@
       </c>
       <c r="AS18" s="34" t="s">
         <v>108</v>
+      </c>
+      <c r="BJ18" s="17">
+        <v>43</v>
+      </c>
+      <c r="BK18" s="17">
+        <v>9</v>
       </c>
       <c r="BL18" s="34">
         <v>95</v>
@@ -3505,8 +3543,8 @@
         <f t="shared" si="0"/>
         <v>95</v>
       </c>
-      <c r="CM18" s="17" t="s">
-        <v>97</v>
+      <c r="CM18" s="19">
+        <v>46210</v>
       </c>
       <c r="CN18" s="17">
         <v>5</v>
@@ -3521,8 +3559,8 @@
       <c r="CQ18" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="CR18" s="17" t="s">
-        <v>97</v>
+      <c r="CR18" s="19">
+        <v>46210</v>
       </c>
       <c r="CY18" s="17">
         <v>0.24</v>
@@ -3545,7 +3583,7 @@
         <v>91.46</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>106</v>
@@ -3633,7 +3671,7 @@
       <c r="AN19" s="41" t="s">
         <v>113</v>
       </c>
-      <c r="AO19" s="102" t="s">
+      <c r="AO19" s="68" t="s">
         <v>114</v>
       </c>
       <c r="AP19" s="34">
@@ -3647,6 +3685,12 @@
       </c>
       <c r="AS19" s="34" t="s">
         <v>108</v>
+      </c>
+      <c r="BJ19" s="17">
+        <v>42</v>
+      </c>
+      <c r="BK19" s="17">
+        <v>9</v>
       </c>
       <c r="BL19" s="34">
         <v>95</v>
@@ -3665,8 +3709,8 @@
         <f t="shared" si="0"/>
         <v>95</v>
       </c>
-      <c r="CM19" s="17" t="s">
-        <v>97</v>
+      <c r="CM19" s="19">
+        <v>46210</v>
       </c>
       <c r="CN19" s="17">
         <v>5</v>
@@ -3681,8 +3725,8 @@
       <c r="CQ19" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="CR19" s="17" t="s">
-        <v>97</v>
+      <c r="CR19" s="19">
+        <v>46210</v>
       </c>
       <c r="CY19" s="17">
         <v>0.24</v>
@@ -3744,7 +3788,7 @@
         <v>150</v>
       </c>
       <c r="Q20" s="34"/>
-      <c r="R20" s="17">
+      <c r="R20" s="34">
         <v>110</v>
       </c>
       <c r="S20" s="34" t="s">
@@ -3753,7 +3797,7 @@
       <c r="T20" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="U20" s="17" t="s">
+      <c r="U20" s="34" t="s">
         <v>91</v>
       </c>
       <c r="V20" s="35">
@@ -3762,7 +3806,7 @@
       <c r="W20" s="35">
         <v>46172</v>
       </c>
-      <c r="X20" s="19">
+      <c r="X20" s="35">
         <v>46205</v>
       </c>
       <c r="Y20" s="34" t="s">
@@ -3806,6 +3850,12 @@
       <c r="AS20" s="34" t="s">
         <v>119</v>
       </c>
+      <c r="BJ20" s="17">
+        <v>19</v>
+      </c>
+      <c r="BK20" s="17">
+        <v>9</v>
+      </c>
       <c r="BL20" s="34">
         <v>110</v>
       </c>
@@ -3819,17 +3869,18 @@
       <c r="BP20" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="BR20" s="19">
+      <c r="BR20" s="35">
         <v>46205</v>
       </c>
-      <c r="BS20" s="17">
+      <c r="BS20" s="34">
         <v>110</v>
       </c>
-      <c r="BT20" s="17" t="s">
+      <c r="BT20" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="BV20" s="17" t="s">
-        <v>103</v>
+      <c r="BU20" s="34"/>
+      <c r="BV20" s="34" t="s">
+        <v>102</v>
       </c>
       <c r="CI20" s="17">
         <f t="shared" si="0"/>
@@ -3904,7 +3955,7 @@
         <v>150</v>
       </c>
       <c r="Q21" s="34"/>
-      <c r="R21" s="17">
+      <c r="R21" s="34">
         <v>110</v>
       </c>
       <c r="S21" s="34" t="s">
@@ -3913,7 +3964,7 @@
       <c r="T21" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="U21" s="17" t="s">
+      <c r="U21" s="34" t="s">
         <v>91</v>
       </c>
       <c r="V21" s="35">
@@ -3922,7 +3973,7 @@
       <c r="W21" s="35">
         <v>46172</v>
       </c>
-      <c r="X21" s="19">
+      <c r="X21" s="35">
         <v>46205</v>
       </c>
       <c r="Y21" s="34" t="s">
@@ -3966,6 +4017,12 @@
       <c r="AS21" s="34" t="s">
         <v>119</v>
       </c>
+      <c r="BJ21" s="17">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="BK21" s="17">
+        <v>9</v>
+      </c>
       <c r="BL21" s="34">
         <v>110</v>
       </c>
@@ -3979,17 +4036,18 @@
       <c r="BP21" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="BR21" s="19">
+      <c r="BR21" s="35">
         <v>46205</v>
       </c>
-      <c r="BS21" s="17">
+      <c r="BS21" s="34">
         <v>110</v>
       </c>
-      <c r="BT21" s="17" t="s">
+      <c r="BT21" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="BV21" s="17" t="s">
-        <v>103</v>
+      <c r="BU21" s="34"/>
+      <c r="BV21" s="34" t="s">
+        <v>102</v>
       </c>
       <c r="CI21" s="17">
         <f t="shared" si="0"/>
@@ -4062,7 +4120,7 @@
         <v>150</v>
       </c>
       <c r="Q22" s="34"/>
-      <c r="R22" s="17">
+      <c r="R22" s="34">
         <v>110</v>
       </c>
       <c r="S22" s="34" t="s">
@@ -4071,7 +4129,7 @@
       <c r="T22" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="U22" s="17" t="s">
+      <c r="U22" s="34" t="s">
         <v>91</v>
       </c>
       <c r="V22" s="35">
@@ -4080,7 +4138,7 @@
       <c r="W22" s="35">
         <v>46172</v>
       </c>
-      <c r="X22" s="19">
+      <c r="X22" s="35">
         <v>46205</v>
       </c>
       <c r="Y22" s="34" t="s">
@@ -4124,6 +4182,12 @@
       <c r="AS22" s="34" t="s">
         <v>119</v>
       </c>
+      <c r="BJ22" s="17">
+        <v>19.329999999999998</v>
+      </c>
+      <c r="BK22" s="17">
+        <v>9</v>
+      </c>
       <c r="BL22" s="34">
         <v>110</v>
       </c>
@@ -4137,17 +4201,18 @@
       <c r="BP22" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="BR22" s="19">
+      <c r="BR22" s="35">
         <v>46205</v>
       </c>
-      <c r="BS22" s="17">
+      <c r="BS22" s="34">
         <v>110</v>
       </c>
-      <c r="BT22" s="17" t="s">
+      <c r="BT22" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="BV22" s="17" t="s">
-        <v>103</v>
+      <c r="BU22" s="34"/>
+      <c r="BV22" s="34" t="s">
+        <v>102</v>
       </c>
       <c r="CI22" s="17">
         <f t="shared" si="0"/>
@@ -4240,7 +4305,7 @@
         <v>150</v>
       </c>
       <c r="Q23" s="34"/>
-      <c r="R23" s="17">
+      <c r="R23" s="34">
         <v>110</v>
       </c>
       <c r="S23" s="34" t="s">
@@ -4249,7 +4314,7 @@
       <c r="T23" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="U23" s="17" t="s">
+      <c r="U23" s="34" t="s">
         <v>91</v>
       </c>
       <c r="V23" s="35">
@@ -4258,7 +4323,7 @@
       <c r="W23" s="35">
         <v>46172</v>
       </c>
-      <c r="X23" s="19">
+      <c r="X23" s="35">
         <v>46205</v>
       </c>
       <c r="Y23" s="34" t="s">
@@ -4303,6 +4368,12 @@
       <c r="AS23" s="34" t="s">
         <v>119</v>
       </c>
+      <c r="BJ23" s="17">
+        <v>19.25</v>
+      </c>
+      <c r="BK23" s="17">
+        <v>9</v>
+      </c>
       <c r="BL23" s="34">
         <v>110</v>
       </c>
@@ -4316,17 +4387,18 @@
       <c r="BP23" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="BR23" s="19">
+      <c r="BR23" s="35">
         <v>46205</v>
       </c>
-      <c r="BS23" s="17">
+      <c r="BS23" s="34">
         <v>110</v>
       </c>
-      <c r="BT23" s="17" t="s">
+      <c r="BT23" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="BV23" s="17" t="s">
-        <v>103</v>
+      <c r="BU23" s="34"/>
+      <c r="BV23" s="34" t="s">
+        <v>102</v>
       </c>
       <c r="CI23" s="17">
         <f t="shared" si="0"/>
@@ -4364,17 +4436,17 @@
         <v>67.739999999999995</v>
       </c>
       <c r="D24" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E24" s="7" t="s">
         <v>99</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>100</v>
       </c>
       <c r="AH24" s="18"/>
       <c r="AN24" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="AO24" s="34" t="s">
         <v>101</v>
-      </c>
-      <c r="AO24" s="34" t="s">
-        <v>102</v>
       </c>
       <c r="AP24" s="34">
         <v>80</v>
@@ -4383,10 +4455,10 @@
         <v>46135</v>
       </c>
       <c r="AR24" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="AS24" s="34" t="s">
         <v>103</v>
-      </c>
-      <c r="AS24" s="34" t="s">
-        <v>104</v>
       </c>
       <c r="CI24" s="17">
         <f t="shared" si="0"/>
@@ -4422,17 +4494,17 @@
         <v>24.52</v>
       </c>
       <c r="D25" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E25" s="7" t="s">
         <v>99</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>100</v>
       </c>
       <c r="AH25" s="18"/>
       <c r="AN25" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="AO25" s="34" t="s">
         <v>101</v>
-      </c>
-      <c r="AO25" s="34" t="s">
-        <v>102</v>
       </c>
       <c r="AP25" s="34">
         <v>80</v>
@@ -4441,10 +4513,10 @@
         <v>46135</v>
       </c>
       <c r="AR25" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="AS25" s="34" t="s">
         <v>103</v>
-      </c>
-      <c r="AS25" s="34" t="s">
-        <v>104</v>
       </c>
       <c r="CI25" s="17">
         <f t="shared" si="0"/>
@@ -4519,7 +4591,7 @@
         <v>150</v>
       </c>
       <c r="Q26" s="34"/>
-      <c r="R26" s="17">
+      <c r="R26" s="34">
         <v>110</v>
       </c>
       <c r="S26" s="34" t="s">
@@ -4528,7 +4600,7 @@
       <c r="T26" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="U26" s="17" t="s">
+      <c r="U26" s="34" t="s">
         <v>91</v>
       </c>
       <c r="V26" s="35">
@@ -4537,7 +4609,7 @@
       <c r="W26" s="35">
         <v>46172</v>
       </c>
-      <c r="X26" s="19">
+      <c r="X26" s="35">
         <v>46205</v>
       </c>
       <c r="Y26" s="34" t="s">
@@ -4581,6 +4653,12 @@
       <c r="AS26" s="34" t="s">
         <v>119</v>
       </c>
+      <c r="BJ26" s="17">
+        <v>18.5</v>
+      </c>
+      <c r="BK26" s="17">
+        <v>9</v>
+      </c>
       <c r="BL26" s="34">
         <v>110</v>
       </c>
@@ -4594,17 +4672,18 @@
       <c r="BP26" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="BR26" s="19">
+      <c r="BR26" s="35">
         <v>46205</v>
       </c>
-      <c r="BS26" s="17">
+      <c r="BS26" s="34">
         <v>110</v>
       </c>
-      <c r="BT26" s="17" t="s">
+      <c r="BT26" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="BV26" s="17" t="s">
-        <v>103</v>
+      <c r="BU26" s="34"/>
+      <c r="BV26" s="34" t="s">
+        <v>102</v>
       </c>
       <c r="CI26" s="17">
         <f t="shared" si="0"/>
@@ -4622,17 +4701,17 @@
         <v>67</v>
       </c>
       <c r="D27" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E27" s="7" t="s">
         <v>99</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>100</v>
       </c>
       <c r="AH27" s="18"/>
       <c r="AN27" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="AO27" s="34" t="s">
         <v>101</v>
-      </c>
-      <c r="AO27" s="34" t="s">
-        <v>102</v>
       </c>
       <c r="AP27" s="34">
         <v>80</v>
@@ -4641,10 +4720,10 @@
         <v>46135</v>
       </c>
       <c r="AR27" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="AS27" s="34" t="s">
         <v>103</v>
-      </c>
-      <c r="AS27" s="34" t="s">
-        <v>104</v>
       </c>
       <c r="CI27" s="17">
         <f t="shared" si="0"/>
@@ -4788,6 +4867,12 @@
       <c r="AZ28" s="34" t="s">
         <v>119</v>
       </c>
+      <c r="BJ28" s="17">
+        <v>18</v>
+      </c>
+      <c r="BK28" s="17">
+        <v>8</v>
+      </c>
       <c r="BL28" s="34">
         <v>75</v>
       </c>
@@ -4801,12 +4886,18 @@
       <c r="BP28" s="34" t="s">
         <v>92</v>
       </c>
+      <c r="BR28" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="BS28" s="17">
+        <v>100</v>
+      </c>
       <c r="CI28" s="17">
         <f t="shared" si="0"/>
-        <v>75</v>
+        <v>175</v>
       </c>
       <c r="CM28" s="17" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="CN28" s="17">
         <v>5</v>
@@ -4833,17 +4924,17 @@
         <v>141.69999999999999</v>
       </c>
       <c r="D29" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E29" s="7" t="s">
         <v>99</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>100</v>
       </c>
       <c r="AH29" s="18"/>
       <c r="AN29" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="AO29" s="34" t="s">
         <v>101</v>
-      </c>
-      <c r="AO29" s="34" t="s">
-        <v>102</v>
       </c>
       <c r="AP29" s="34">
         <v>80</v>
@@ -4852,17 +4943,17 @@
         <v>46134</v>
       </c>
       <c r="AR29" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="AS29" s="34" t="s">
         <v>103</v>
-      </c>
-      <c r="AS29" s="34" t="s">
-        <v>104</v>
       </c>
       <c r="CI29" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="CR29" s="17" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="CV29" s="17">
         <v>0.1</v>
@@ -4889,7 +4980,7 @@
         <v>128</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AH30" s="18"/>
       <c r="AN30" s="34" t="s">
@@ -4943,7 +5034,7 @@
       <c r="Q31" s="34">
         <v>50</v>
       </c>
-      <c r="R31" s="17">
+      <c r="R31" s="34">
         <v>100</v>
       </c>
       <c r="S31" s="34" t="s">
@@ -4952,7 +5043,7 @@
       <c r="T31" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="U31" s="17" t="s">
+      <c r="U31" s="34" t="s">
         <v>91</v>
       </c>
       <c r="V31" s="35">
@@ -4961,11 +5052,11 @@
       <c r="W31" s="35">
         <v>46170</v>
       </c>
-      <c r="X31" s="19">
+      <c r="X31" s="35">
         <v>46199</v>
       </c>
-      <c r="Y31" s="17" t="s">
-        <v>103</v>
+      <c r="Y31" s="34" t="s">
+        <v>102</v>
       </c>
       <c r="Z31" s="34">
         <v>3</v>
@@ -5038,6 +5129,12 @@
       <c r="AZ31" s="34" t="s">
         <v>119</v>
       </c>
+      <c r="BJ31" s="17">
+        <v>19.329999999999998</v>
+      </c>
+      <c r="BK31" s="17">
+        <v>7</v>
+      </c>
       <c r="BL31" s="34">
         <v>95</v>
       </c>
@@ -5049,23 +5146,27 @@
         <v>46143</v>
       </c>
       <c r="BP31" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="BS31" s="17">
+        <v>102</v>
+      </c>
+      <c r="BR31" s="35">
+        <v>46199</v>
+      </c>
+      <c r="BS31" s="34">
         <v>75</v>
       </c>
-      <c r="BT31" s="17" t="s">
+      <c r="BT31" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="BV31" s="17" t="s">
-        <v>92</v>
+      <c r="BU31" s="34"/>
+      <c r="BV31" s="34" t="s">
+        <v>102</v>
       </c>
       <c r="CI31" s="17">
         <f t="shared" si="0"/>
         <v>170</v>
       </c>
       <c r="CR31" s="17" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="CS31" s="17">
         <v>1</v>
@@ -5102,7 +5203,7 @@
       <c r="Q32" s="34">
         <v>72.3</v>
       </c>
-      <c r="R32" s="17">
+      <c r="R32" s="34">
         <v>100</v>
       </c>
       <c r="S32" s="34" t="s">
@@ -5111,7 +5212,7 @@
       <c r="T32" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="U32" s="17" t="s">
+      <c r="U32" s="34" t="s">
         <v>91</v>
       </c>
       <c r="V32" s="35">
@@ -5120,11 +5221,11 @@
       <c r="W32" s="35">
         <v>46170</v>
       </c>
-      <c r="X32" s="19">
+      <c r="X32" s="35">
         <v>46199</v>
       </c>
-      <c r="Y32" s="17" t="s">
-        <v>103</v>
+      <c r="Y32" s="34" t="s">
+        <v>102</v>
       </c>
       <c r="Z32" s="34">
         <v>3</v>
@@ -5197,6 +5298,12 @@
       <c r="AZ32" s="34" t="s">
         <v>139</v>
       </c>
+      <c r="BJ32" s="17">
+        <v>15.71</v>
+      </c>
+      <c r="BK32" s="17">
+        <v>7</v>
+      </c>
       <c r="BL32" s="34">
         <v>95</v>
       </c>
@@ -5208,23 +5315,27 @@
         <v>46143</v>
       </c>
       <c r="BP32" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="BS32" s="17">
+        <v>102</v>
+      </c>
+      <c r="BR32" s="35">
+        <v>46199</v>
+      </c>
+      <c r="BS32" s="34">
         <v>75</v>
       </c>
-      <c r="BT32" s="17" t="s">
+      <c r="BT32" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="BV32" s="17" t="s">
-        <v>92</v>
+      <c r="BU32" s="34"/>
+      <c r="BV32" s="34" t="s">
+        <v>102</v>
       </c>
       <c r="CI32" s="17">
         <f t="shared" si="0"/>
         <v>170</v>
       </c>
       <c r="CR32" s="17" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="CS32" s="17">
         <v>1</v>
@@ -5261,7 +5372,7 @@
       <c r="Q33" s="34">
         <v>92.5</v>
       </c>
-      <c r="R33" s="17">
+      <c r="R33" s="34">
         <v>100</v>
       </c>
       <c r="S33" s="34" t="s">
@@ -5270,7 +5381,7 @@
       <c r="T33" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="U33" s="17" t="s">
+      <c r="U33" s="34" t="s">
         <v>91</v>
       </c>
       <c r="V33" s="35">
@@ -5279,11 +5390,11 @@
       <c r="W33" s="35">
         <v>46170</v>
       </c>
-      <c r="X33" s="19">
+      <c r="X33" s="35">
         <v>46199</v>
       </c>
-      <c r="Y33" s="17" t="s">
-        <v>103</v>
+      <c r="Y33" s="34" t="s">
+        <v>102</v>
       </c>
       <c r="Z33" s="34">
         <v>3</v>
@@ -5356,6 +5467,12 @@
       <c r="AZ33" s="34" t="s">
         <v>119</v>
       </c>
+      <c r="BJ33" s="17">
+        <v>19</v>
+      </c>
+      <c r="BK33" s="17">
+        <v>8</v>
+      </c>
       <c r="BL33" s="34">
         <v>95</v>
       </c>
@@ -5367,23 +5484,27 @@
         <v>46143</v>
       </c>
       <c r="BP33" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="BS33" s="17">
+        <v>102</v>
+      </c>
+      <c r="BR33" s="35">
+        <v>46199</v>
+      </c>
+      <c r="BS33" s="34">
         <v>75</v>
       </c>
-      <c r="BT33" s="17" t="s">
+      <c r="BT33" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="BV33" s="17" t="s">
-        <v>92</v>
+      <c r="BU33" s="34"/>
+      <c r="BV33" s="34" t="s">
+        <v>102</v>
       </c>
       <c r="CI33" s="17">
         <f t="shared" si="0"/>
         <v>170</v>
       </c>
       <c r="CR33" s="17" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="CS33" s="17">
         <v>1</v>
@@ -5409,7 +5530,7 @@
         <v>128</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AH34" s="18"/>
       <c r="AN34" s="34" t="s">
@@ -5435,7 +5556,7 @@
         <v>0</v>
       </c>
       <c r="CR34" s="17" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="DB34" s="43">
         <v>0.04</v>
@@ -5455,10 +5576,10 @@
         <v>46.79</v>
       </c>
       <c r="D35" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E35" s="7" t="s">
         <v>99</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>100</v>
       </c>
       <c r="AH35" s="18"/>
       <c r="AN35" s="34" t="s">
@@ -5513,10 +5634,10 @@
         <v>59.05</v>
       </c>
       <c r="D36" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E36" s="7" t="s">
         <v>99</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>100</v>
       </c>
       <c r="AH36" s="18"/>
       <c r="AN36" s="34" t="s">
@@ -5571,10 +5692,10 @@
         <v>103.45</v>
       </c>
       <c r="D37" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E37" s="7" t="s">
         <v>99</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>100</v>
       </c>
       <c r="AH37" s="18"/>
       <c r="AN37" s="34" t="s">
@@ -5651,9 +5772,6 @@
       <c r="T38" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="U38" s="17" t="s">
-        <v>91</v>
-      </c>
       <c r="V38" s="35">
         <v>46176</v>
       </c>
@@ -5661,9 +5779,6 @@
         <v>46170</v>
       </c>
       <c r="X38" s="19"/>
-      <c r="Y38" s="17" t="s">
-        <v>103</v>
-      </c>
       <c r="Z38" s="34">
         <v>3</v>
       </c>
@@ -5744,6 +5859,12 @@
       <c r="BI38" s="34" t="s">
         <v>131</v>
       </c>
+      <c r="BJ38" s="17">
+        <v>12.5</v>
+      </c>
+      <c r="BK38" s="17">
+        <v>6</v>
+      </c>
       <c r="BL38" s="34">
         <v>95</v>
       </c>
@@ -5755,14 +5876,14 @@
         <v>46143</v>
       </c>
       <c r="BP38" s="34" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="CI38" s="17">
         <f t="shared" si="0"/>
         <v>95</v>
       </c>
       <c r="CR38" s="17" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="CS38" s="17">
         <v>1</v>
@@ -5788,7 +5909,7 @@
         <v>128</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AH39" s="18"/>
       <c r="AN39" s="34" t="s">
@@ -5814,7 +5935,7 @@
         <v>0</v>
       </c>
       <c r="CR39" s="17" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="DB39" s="43">
         <v>0.04</v>
@@ -5834,10 +5955,10 @@
         <v>102.7</v>
       </c>
       <c r="D40" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E40" s="7" t="s">
         <v>99</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>100</v>
       </c>
       <c r="AH40" s="18"/>
       <c r="AN40" s="34" t="s">
@@ -5894,10 +6015,10 @@
         <v>87.11</v>
       </c>
       <c r="D41" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E41" s="7" t="s">
         <v>99</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>100</v>
       </c>
       <c r="AH41" s="18"/>
       <c r="AN41" s="34" t="s">
@@ -5954,10 +6075,10 @@
         <v>59.42</v>
       </c>
       <c r="D42" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E42" s="7" t="s">
         <v>99</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>100</v>
       </c>
       <c r="AH42" s="18"/>
       <c r="AN42" s="34" t="s">
@@ -6012,10 +6133,10 @@
         <v>35.96</v>
       </c>
       <c r="D43" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E43" s="7" t="s">
         <v>99</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>100</v>
       </c>
       <c r="AH43" s="18"/>
       <c r="AN43" s="34" t="s">
@@ -6070,7 +6191,7 @@
         <v>386.2</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E44" s="7" t="s">
         <v>146</v>
@@ -6099,7 +6220,7 @@
       </c>
       <c r="X44" s="35"/>
       <c r="Y44" s="34" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Z44" s="34">
         <v>3</v>
@@ -6137,6 +6258,9 @@
       <c r="AS44" s="34" t="s">
         <v>108</v>
       </c>
+      <c r="BJ44" s="17">
+        <v>42</v>
+      </c>
       <c r="BK44" s="17">
         <v>9</v>
       </c>
@@ -6151,7 +6275,7 @@
         <v>46176</v>
       </c>
       <c r="BP44" s="34" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="CI44" s="17">
         <f t="shared" si="0"/>
@@ -6200,7 +6324,7 @@
         <v>128</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AH45" s="18"/>
       <c r="AN45" s="34" t="s">
@@ -6240,7 +6364,7 @@
         <v>163</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E46" s="7" t="s">
         <v>146</v>
@@ -6269,7 +6393,7 @@
       </c>
       <c r="X46" s="35"/>
       <c r="Y46" s="34" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Z46" s="34">
         <v>3</v>
@@ -6307,6 +6431,9 @@
       <c r="AS46" s="34" t="s">
         <v>108</v>
       </c>
+      <c r="BJ46" s="17">
+        <v>41</v>
+      </c>
       <c r="BK46" s="17">
         <v>9</v>
       </c>
@@ -6321,7 +6448,7 @@
         <v>46176</v>
       </c>
       <c r="BP46" s="34" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="CI46" s="17">
         <f t="shared" si="0"/>
@@ -6367,7 +6494,7 @@
         <v>189.75</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E47" s="7" t="s">
         <v>146</v>
@@ -6396,7 +6523,7 @@
       </c>
       <c r="X47" s="35"/>
       <c r="Y47" s="34" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Z47" s="34">
         <v>3</v>
@@ -6434,6 +6561,9 @@
       <c r="AS47" s="34" t="s">
         <v>108</v>
       </c>
+      <c r="BJ47" s="17">
+        <v>43</v>
+      </c>
       <c r="BK47" s="17">
         <v>9</v>
       </c>
@@ -6448,7 +6578,7 @@
         <v>46176</v>
       </c>
       <c r="BP47" s="34" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="CI47" s="17">
         <f t="shared" si="0"/>
@@ -6495,7 +6625,7 @@
         <v>169.61</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E48" s="7" t="s">
         <v>146</v>
@@ -6524,7 +6654,7 @@
       </c>
       <c r="X48" s="35"/>
       <c r="Y48" s="34" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Z48" s="34">
         <v>3</v>
@@ -6562,6 +6692,9 @@
       <c r="AS48" s="34" t="s">
         <v>108</v>
       </c>
+      <c r="BJ48" s="17">
+        <v>42</v>
+      </c>
       <c r="BK48" s="17">
         <v>9</v>
       </c>
@@ -6576,7 +6709,7 @@
         <v>46176</v>
       </c>
       <c r="BP48" s="34" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="CI48" s="17">
         <f t="shared" si="0"/>
@@ -6622,7 +6755,7 @@
         <v>118.35</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E49" s="7" t="s">
         <v>146</v>
@@ -6651,7 +6784,7 @@
       </c>
       <c r="X49" s="35"/>
       <c r="Y49" s="34" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Z49" s="34">
         <v>3</v>
@@ -6689,6 +6822,9 @@
       <c r="AS49" s="34" t="s">
         <v>108</v>
       </c>
+      <c r="BJ49" s="17">
+        <v>41</v>
+      </c>
       <c r="BK49" s="17">
         <v>9</v>
       </c>
@@ -6703,7 +6839,7 @@
         <v>46176</v>
       </c>
       <c r="BP49" s="34" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="CI49" s="17">
         <f t="shared" si="0"/>
@@ -6749,7 +6885,7 @@
         <v>243.29</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E50" s="7" t="s">
         <v>146</v>
@@ -6778,7 +6914,7 @@
       </c>
       <c r="X50" s="35"/>
       <c r="Y50" s="34" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Z50" s="34">
         <v>3</v>
@@ -6816,6 +6952,9 @@
       <c r="AS50" s="34" t="s">
         <v>108</v>
       </c>
+      <c r="BJ50" s="17">
+        <v>41</v>
+      </c>
       <c r="BK50" s="17">
         <v>9</v>
       </c>
@@ -6830,7 +6969,7 @@
         <v>46176</v>
       </c>
       <c r="BP50" s="34" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="CI50" s="17">
         <f t="shared" si="0"/>
@@ -6876,10 +7015,10 @@
         <v>201.78</v>
       </c>
       <c r="D51" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E51" s="7" t="s">
         <v>99</v>
-      </c>
-      <c r="E51" s="7" t="s">
-        <v>100</v>
       </c>
       <c r="AH51" s="18"/>
       <c r="AN51" s="34" t="s">
@@ -6936,10 +7075,10 @@
         <v>150.52000000000001</v>
       </c>
       <c r="D52" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E52" s="7" t="s">
         <v>99</v>
-      </c>
-      <c r="E52" s="7" t="s">
-        <v>100</v>
       </c>
       <c r="AH52" s="18"/>
       <c r="AN52" s="34" t="s">
@@ -6996,10 +7135,10 @@
         <v>225.15</v>
       </c>
       <c r="D53" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E53" s="7" t="s">
         <v>99</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>100</v>
       </c>
       <c r="AH53" s="18"/>
       <c r="AN53" s="34" t="s">
@@ -7285,7 +7424,7 @@
         <v>88</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="21">
@@ -7299,7 +7438,7 @@
         <v>215</v>
       </c>
       <c r="D4" s="42" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>87</v>
@@ -7316,7 +7455,7 @@
         <v>46.12</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>87</v>
@@ -7333,7 +7472,7 @@
         <v>24.03</v>
       </c>
       <c r="D6" s="42" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>87</v>
@@ -7350,7 +7489,7 @@
         <v>22.55</v>
       </c>
       <c r="D7" s="42" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>87</v>
@@ -7367,7 +7506,7 @@
         <v>62.73</v>
       </c>
       <c r="D8" s="42" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>87</v>
@@ -7384,7 +7523,7 @@
         <v>29.7</v>
       </c>
       <c r="D9" s="42" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>87</v>
@@ -7401,7 +7540,7 @@
         <v>270.44</v>
       </c>
       <c r="D10" s="42" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>87</v>
@@ -7418,7 +7557,7 @@
         <v>64.25</v>
       </c>
       <c r="D11" s="42" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>87</v>
@@ -7435,7 +7574,7 @@
         <v>29.89</v>
       </c>
       <c r="D12" s="42" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>87</v>
@@ -7452,7 +7591,7 @@
         <v>52.63</v>
       </c>
       <c r="D13" s="42" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>87</v>
@@ -7472,7 +7611,7 @@
         <v>106</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="21" hidden="1">
@@ -7489,7 +7628,7 @@
         <v>106</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="21" hidden="1">
@@ -7506,7 +7645,7 @@
         <v>106</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="21" hidden="1">
@@ -7523,7 +7662,7 @@
         <v>106</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="21" hidden="1">
@@ -7540,7 +7679,7 @@
         <v>106</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="21" hidden="1">
@@ -7557,7 +7696,7 @@
         <v>106</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="21" hidden="1">
@@ -7574,7 +7713,7 @@
         <v>88</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="21" hidden="1">
@@ -7591,7 +7730,7 @@
         <v>88</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="21" hidden="1">
@@ -7608,7 +7747,7 @@
         <v>88</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="21" hidden="1">
@@ -7625,7 +7764,7 @@
         <v>88</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="21">
@@ -7639,7 +7778,7 @@
         <v>67.739999999999995</v>
       </c>
       <c r="D24" s="42" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>87</v>
@@ -7656,7 +7795,7 @@
         <v>24.52</v>
       </c>
       <c r="D25" s="42" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>87</v>
@@ -7676,7 +7815,7 @@
         <v>88</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="21">
@@ -7690,7 +7829,7 @@
         <v>67</v>
       </c>
       <c r="D27" s="42" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>87</v>
@@ -7710,7 +7849,7 @@
         <v>88</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="21">
@@ -7724,7 +7863,7 @@
         <v>141.69999999999999</v>
       </c>
       <c r="D29" s="42" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>124</v>
@@ -7741,7 +7880,7 @@
         <v>101.74</v>
       </c>
       <c r="D30" s="42" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>87</v>
@@ -7761,7 +7900,7 @@
         <v>88</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="21" hidden="1">
@@ -7778,7 +7917,7 @@
         <v>88</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="21" hidden="1">
@@ -7795,7 +7934,7 @@
         <v>88</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="21">
@@ -7809,7 +7948,7 @@
         <v>59.08</v>
       </c>
       <c r="D34" s="42" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>87</v>
@@ -7826,7 +7965,7 @@
         <v>46.79</v>
       </c>
       <c r="D35" s="42" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E35" s="6" t="s">
         <v>87</v>
@@ -7843,7 +7982,7 @@
         <v>59.05</v>
       </c>
       <c r="D36" s="42" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>87</v>
@@ -7860,7 +7999,7 @@
         <v>103.45</v>
       </c>
       <c r="D37" s="42" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E37" s="6" t="s">
         <v>124</v>
@@ -7880,7 +8019,7 @@
         <v>88</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="21">
@@ -7894,7 +8033,7 @@
         <v>53.38</v>
       </c>
       <c r="D39" s="42" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E39" s="6" t="s">
         <v>87</v>
@@ -7911,7 +8050,7 @@
         <v>102.7</v>
       </c>
       <c r="D40" s="42" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>124</v>
@@ -7928,7 +8067,7 @@
         <v>87.11</v>
       </c>
       <c r="D41" s="42" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E41" s="6" t="s">
         <v>124</v>
@@ -7945,7 +8084,7 @@
         <v>59.42</v>
       </c>
       <c r="D42" s="42" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>87</v>
@@ -7962,7 +8101,7 @@
         <v>35.96</v>
       </c>
       <c r="D43" s="42" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>87</v>
@@ -7996,7 +8135,7 @@
         <v>120</v>
       </c>
       <c r="D45" s="42" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E45" s="6" t="s">
         <v>87</v>
@@ -8016,7 +8155,7 @@
         <v>146</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="21" hidden="1">
@@ -8033,7 +8172,7 @@
         <v>146</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="21" hidden="1">
@@ -8050,7 +8189,7 @@
         <v>146</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="21" hidden="1">
@@ -8084,7 +8223,7 @@
         <v>146</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="21">
@@ -8098,7 +8237,7 @@
         <v>201.78</v>
       </c>
       <c r="D51" s="42" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E51" s="6" t="s">
         <v>124</v>
@@ -8115,7 +8254,7 @@
         <v>150.52000000000001</v>
       </c>
       <c r="D52" s="42" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>124</v>
@@ -8132,7 +8271,7 @@
         <v>225.15</v>
       </c>
       <c r="D53" s="42" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E53" s="6" t="s">
         <v>124</v>
@@ -8168,62 +8307,62 @@
       <c r="B1" s="49">
         <v>2022</v>
       </c>
-      <c r="C1" s="99">
+      <c r="C1" s="100">
         <v>2023</v>
       </c>
-      <c r="D1" s="100"/>
-      <c r="E1" s="100"/>
-      <c r="F1" s="100"/>
-      <c r="G1" s="100"/>
-      <c r="H1" s="100"/>
-      <c r="I1" s="100"/>
-      <c r="J1" s="100"/>
-      <c r="K1" s="100"/>
-      <c r="L1" s="100"/>
-      <c r="M1" s="100"/>
-      <c r="N1" s="100"/>
-      <c r="O1" s="99">
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="100">
         <v>2024</v>
       </c>
-      <c r="P1" s="100"/>
-      <c r="Q1" s="100"/>
-      <c r="R1" s="100"/>
-      <c r="S1" s="100"/>
-      <c r="T1" s="100"/>
-      <c r="U1" s="100"/>
-      <c r="V1" s="100"/>
-      <c r="W1" s="100"/>
-      <c r="X1" s="100"/>
-      <c r="Y1" s="100"/>
-      <c r="Z1" s="101"/>
-      <c r="AA1" s="100">
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="101"/>
+      <c r="T1" s="101"/>
+      <c r="U1" s="101"/>
+      <c r="V1" s="101"/>
+      <c r="W1" s="101"/>
+      <c r="X1" s="101"/>
+      <c r="Y1" s="101"/>
+      <c r="Z1" s="102"/>
+      <c r="AA1" s="101">
         <v>2025</v>
       </c>
-      <c r="AB1" s="100"/>
-      <c r="AC1" s="100"/>
-      <c r="AD1" s="100"/>
-      <c r="AE1" s="100"/>
-      <c r="AF1" s="100"/>
-      <c r="AG1" s="100"/>
-      <c r="AH1" s="100"/>
-      <c r="AI1" s="100"/>
-      <c r="AJ1" s="100"/>
-      <c r="AK1" s="100"/>
-      <c r="AL1" s="100"/>
-      <c r="AM1" s="100">
+      <c r="AB1" s="101"/>
+      <c r="AC1" s="101"/>
+      <c r="AD1" s="101"/>
+      <c r="AE1" s="101"/>
+      <c r="AF1" s="101"/>
+      <c r="AG1" s="101"/>
+      <c r="AH1" s="101"/>
+      <c r="AI1" s="101"/>
+      <c r="AJ1" s="101"/>
+      <c r="AK1" s="101"/>
+      <c r="AL1" s="101"/>
+      <c r="AM1" s="101">
         <v>2026</v>
       </c>
-      <c r="AN1" s="100"/>
-      <c r="AO1" s="100"/>
-      <c r="AP1" s="100"/>
-      <c r="AQ1" s="100"/>
-      <c r="AR1" s="100"/>
-      <c r="AS1" s="100"/>
-      <c r="AT1" s="100"/>
-      <c r="AU1" s="100"/>
-      <c r="AV1" s="100"/>
-      <c r="AW1" s="100"/>
-      <c r="AX1" s="100"/>
+      <c r="AN1" s="101"/>
+      <c r="AO1" s="101"/>
+      <c r="AP1" s="101"/>
+      <c r="AQ1" s="101"/>
+      <c r="AR1" s="101"/>
+      <c r="AS1" s="101"/>
+      <c r="AT1" s="101"/>
+      <c r="AU1" s="101"/>
+      <c r="AV1" s="101"/>
+      <c r="AW1" s="101"/>
+      <c r="AX1" s="101"/>
       <c r="AY1" s="44"/>
       <c r="AZ1" s="51" t="s">
         <v>168</v>
@@ -26064,26 +26203,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="28867580-4592-47a8-a490-5f1990c83971" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6f4b1271-3e48-4fa4-9395-5da21e2ace23">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100711D466C73CDF643807BA842554885B1" ma:contentTypeVersion="16" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="8e1c5aa86496f51e6901b2b089969625">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6f4b1271-3e48-4fa4-9395-5da21e2ace23" xmlns:ns3="28867580-4592-47a8-a490-5f1990c83971" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8574df20a81ac730ef1e2c2435c9ef30" ns2:_="" ns3:_="">
     <xsd:import namespace="6f4b1271-3e48-4fa4-9395-5da21e2ace23"/>
@@ -26324,14 +26443,34 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="28867580-4592-47a8-a490-5f1990c83971" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6f4b1271-3e48-4fa4-9395-5da21e2ace23">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE668D04-A599-40BD-83B4-4E55F7C43B16}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14CBE609-95E4-45D1-B334-D32AADDB8A39}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ABBBF542-46E2-4D90-B593-1F03D9E2A95E}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE668D04-A599-40BD-83B4-4E55F7C43B16}"/>
 </file>
--- a/Planilla labores 26-27.xlsx
+++ b/Planilla labores 26-27.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://provinvestsa.sharepoint.com/sites/CeibosAgro-Uy-Produccin/Documentos compartidos/Litoral Norte/26-27/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{039113A9-2A97-4A9A-BCAD-2B7018DDD57A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{283F4F93-3192-4BF3-8112-8D330942A38E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3770" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3767" uniqueCount="184">
   <si>
     <t>Análisis suelo</t>
   </si>
@@ -4912,6 +4912,21 @@
       <c r="CQ28" s="17" t="s">
         <v>95</v>
       </c>
+      <c r="CR28" s="19">
+        <v>46209</v>
+      </c>
+      <c r="CS28" s="17">
+        <v>0.8</v>
+      </c>
+      <c r="CT28" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="DA28" s="17">
+        <v>0.15</v>
+      </c>
+      <c r="DC28" s="17" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="29" spans="1:107" ht="21" hidden="1">
       <c r="A29" s="6" t="s">
@@ -5165,11 +5180,11 @@
         <f t="shared" si="0"/>
         <v>170</v>
       </c>
-      <c r="CR31" s="17" t="s">
-        <v>104</v>
+      <c r="CR31" s="19">
+        <v>46208</v>
       </c>
       <c r="CS31" s="17">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="DA31" s="17">
         <v>0.15</v>
@@ -5334,11 +5349,14 @@
         <f t="shared" si="0"/>
         <v>170</v>
       </c>
-      <c r="CR32" s="17" t="s">
-        <v>104</v>
+      <c r="CR32" s="19">
+        <v>46208</v>
       </c>
       <c r="CS32" s="17">
-        <v>1</v>
+        <v>0.8</v>
+      </c>
+      <c r="CT32" s="17">
+        <v>0.5</v>
       </c>
       <c r="DA32" s="17">
         <v>0.15</v>
@@ -5503,11 +5521,11 @@
         <f t="shared" si="0"/>
         <v>170</v>
       </c>
-      <c r="CR33" s="17" t="s">
-        <v>104</v>
+      <c r="CR33" s="19">
+        <v>46208</v>
       </c>
       <c r="CS33" s="17">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="DA33" s="17">
         <v>0.15</v>
@@ -5882,11 +5900,14 @@
         <f t="shared" si="0"/>
         <v>95</v>
       </c>
-      <c r="CR38" s="17" t="s">
-        <v>104</v>
+      <c r="CR38" s="19">
+        <v>46208</v>
       </c>
       <c r="CS38" s="17">
-        <v>1</v>
+        <v>0.8</v>
+      </c>
+      <c r="CT38" s="17">
+        <v>0.5</v>
       </c>
       <c r="DA38" s="17">
         <v>0.15</v>

--- a/Planilla labores 26-27.xlsx
+++ b/Planilla labores 26-27.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30305"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30306"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://provinvestsa.sharepoint.com/sites/CeibosAgro-Uy-Produccin/Documentos compartidos/Litoral Norte/26-27/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DDA45656-640D-4EE1-A652-B284DE021F03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4285E0D0-57BB-4070-B9B0-192952D30F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,8 +18,8 @@
     <sheet name="Lluvias" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Verano!$A$2:$E$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Invierno!$A$2:$AI$53</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Verano!$A$2:$E$2</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -425,9 +425,6 @@
     <t>Programado</t>
   </si>
   <si>
-    <t>de la entrada hasta la mitad</t>
-  </si>
-  <si>
     <t>La Blanqueada</t>
   </si>
   <si>
@@ -456,6 +453,9 @@
   </si>
   <si>
     <t>F. Ibarra</t>
+  </si>
+  <si>
+    <t>0.5</t>
   </si>
   <si>
     <t>45Y95 (Bajo derecha camino) y Floriana</t>
@@ -1161,6 +1161,69 @@
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1189,69 +1252,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1622,19 +1622,18 @@
     <col min="67" max="67" width="9.7109375" style="17" hidden="1" customWidth="1"/>
     <col min="68" max="68" width="16" style="17" hidden="1" customWidth="1"/>
     <col min="69" max="90" width="9.140625" style="17" customWidth="1"/>
-    <col min="91" max="91" width="11.85546875" style="17" bestFit="1" customWidth="1"/>
-    <col min="92" max="93" width="9.140625" style="17" customWidth="1"/>
-    <col min="94" max="94" width="32.7109375" style="17" customWidth="1"/>
-    <col min="95" max="95" width="16" style="17" customWidth="1"/>
+    <col min="91" max="93" width="9.140625" style="17" hidden="1" customWidth="1"/>
+    <col min="94" max="94" width="32.7109375" style="17" hidden="1" customWidth="1"/>
+    <col min="95" max="95" width="16" style="17" hidden="1" customWidth="1"/>
     <col min="96" max="96" width="11.42578125" style="17" bestFit="1" customWidth="1"/>
     <col min="97" max="97" width="13.28515625" style="17" bestFit="1" customWidth="1"/>
     <col min="98" max="98" width="13.28515625" style="17" customWidth="1"/>
-    <col min="99" max="99" width="10.5703125" style="17" bestFit="1" customWidth="1"/>
+    <col min="99" max="99" width="10.5703125" style="17" hidden="1" customWidth="1"/>
     <col min="100" max="100" width="11" style="17" bestFit="1" customWidth="1"/>
     <col min="101" max="101" width="11" style="17" customWidth="1"/>
     <col min="102" max="102" width="8" style="17" bestFit="1" customWidth="1"/>
     <col min="103" max="103" width="11" style="17" bestFit="1" customWidth="1"/>
-    <col min="104" max="104" width="14.28515625" style="17" bestFit="1" customWidth="1"/>
+    <col min="104" max="104" width="14.28515625" style="17" hidden="1" customWidth="1"/>
     <col min="105" max="105" width="14.28515625" style="17" customWidth="1"/>
     <col min="106" max="106" width="13.140625" style="17" bestFit="1" customWidth="1"/>
     <col min="107" max="107" width="32.28515625" style="17" bestFit="1" customWidth="1"/>
@@ -1648,65 +1647,65 @@
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
       <c r="D1" s="4"/>
-      <c r="F1" s="69" t="s">
+      <c r="F1" s="90" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="69"/>
-      <c r="H1" s="69"/>
-      <c r="I1" s="69"/>
-      <c r="J1" s="69"/>
-      <c r="K1" s="69"/>
-      <c r="L1" s="69"/>
-      <c r="M1" s="69"/>
-      <c r="N1" s="69"/>
-      <c r="O1" s="70" t="s">
+      <c r="G1" s="90"/>
+      <c r="H1" s="90"/>
+      <c r="I1" s="90"/>
+      <c r="J1" s="90"/>
+      <c r="K1" s="90"/>
+      <c r="L1" s="90"/>
+      <c r="M1" s="90"/>
+      <c r="N1" s="90"/>
+      <c r="O1" s="91" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="71"/>
-      <c r="Q1" s="71"/>
-      <c r="R1" s="71"/>
-      <c r="S1" s="71"/>
-      <c r="T1" s="71"/>
-      <c r="U1" s="71"/>
-      <c r="V1" s="71"/>
-      <c r="W1" s="71"/>
-      <c r="X1" s="71"/>
-      <c r="Y1" s="71"/>
-      <c r="Z1" s="72" t="s">
+      <c r="P1" s="92"/>
+      <c r="Q1" s="92"/>
+      <c r="R1" s="92"/>
+      <c r="S1" s="92"/>
+      <c r="T1" s="92"/>
+      <c r="U1" s="92"/>
+      <c r="V1" s="92"/>
+      <c r="W1" s="92"/>
+      <c r="X1" s="92"/>
+      <c r="Y1" s="92"/>
+      <c r="Z1" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="AA1" s="72"/>
-      <c r="AB1" s="72"/>
-      <c r="AC1" s="72"/>
-      <c r="AD1" s="72"/>
-      <c r="AE1" s="72"/>
-      <c r="AF1" s="72"/>
-      <c r="AG1" s="72"/>
-      <c r="AH1" s="72"/>
-      <c r="AI1" s="72"/>
-      <c r="AJ1" s="78" t="s">
+      <c r="AA1" s="93"/>
+      <c r="AB1" s="93"/>
+      <c r="AC1" s="93"/>
+      <c r="AD1" s="93"/>
+      <c r="AE1" s="93"/>
+      <c r="AF1" s="93"/>
+      <c r="AG1" s="93"/>
+      <c r="AH1" s="93"/>
+      <c r="AI1" s="93"/>
+      <c r="AJ1" s="99" t="s">
         <v>3</v>
       </c>
-      <c r="AK1" s="78"/>
-      <c r="AL1" s="78"/>
-      <c r="AM1" s="78"/>
-      <c r="AN1" s="73" t="s">
+      <c r="AK1" s="99"/>
+      <c r="AL1" s="99"/>
+      <c r="AM1" s="99"/>
+      <c r="AN1" s="94" t="s">
         <v>4</v>
       </c>
-      <c r="AO1" s="73"/>
-      <c r="AP1" s="73"/>
-      <c r="AQ1" s="73"/>
-      <c r="AR1" s="73"/>
-      <c r="AS1" s="74"/>
-      <c r="AT1" s="75" t="s">
+      <c r="AO1" s="94"/>
+      <c r="AP1" s="94"/>
+      <c r="AQ1" s="94"/>
+      <c r="AR1" s="94"/>
+      <c r="AS1" s="95"/>
+      <c r="AT1" s="96" t="s">
         <v>5</v>
       </c>
-      <c r="AU1" s="76"/>
-      <c r="AV1" s="76"/>
-      <c r="AW1" s="76"/>
-      <c r="AX1" s="76"/>
-      <c r="AY1" s="76"/>
-      <c r="AZ1" s="77"/>
+      <c r="AU1" s="97"/>
+      <c r="AV1" s="97"/>
+      <c r="AW1" s="97"/>
+      <c r="AX1" s="97"/>
+      <c r="AY1" s="97"/>
+      <c r="AZ1" s="98"/>
       <c r="BA1" s="79" t="s">
         <v>6</v>
       </c>
@@ -1715,11 +1714,11 @@
       <c r="BD1" s="80"/>
       <c r="BE1" s="80"/>
       <c r="BF1" s="81"/>
-      <c r="BG1" s="88" t="s">
+      <c r="BG1" s="87" t="s">
         <v>7</v>
       </c>
-      <c r="BH1" s="89"/>
-      <c r="BI1" s="90"/>
+      <c r="BH1" s="88"/>
+      <c r="BI1" s="89"/>
       <c r="BJ1" s="82" t="s">
         <v>8</v>
       </c>
@@ -1734,76 +1733,76 @@
       <c r="BQ1" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="BR1" s="86"/>
-      <c r="BS1" s="86"/>
-      <c r="BT1" s="86"/>
-      <c r="BU1" s="86"/>
-      <c r="BV1" s="87"/>
-      <c r="BW1" s="86" t="s">
+      <c r="BR1" s="72"/>
+      <c r="BS1" s="72"/>
+      <c r="BT1" s="72"/>
+      <c r="BU1" s="72"/>
+      <c r="BV1" s="86"/>
+      <c r="BW1" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="BX1" s="86"/>
-      <c r="BY1" s="86"/>
-      <c r="BZ1" s="86"/>
-      <c r="CA1" s="86"/>
-      <c r="CB1" s="86"/>
-      <c r="CC1" s="86" t="s">
+      <c r="BX1" s="72"/>
+      <c r="BY1" s="72"/>
+      <c r="BZ1" s="72"/>
+      <c r="CA1" s="72"/>
+      <c r="CB1" s="72"/>
+      <c r="CC1" s="72" t="s">
         <v>12</v>
       </c>
-      <c r="CD1" s="86"/>
-      <c r="CE1" s="86"/>
-      <c r="CF1" s="86"/>
-      <c r="CG1" s="86"/>
-      <c r="CH1" s="86"/>
+      <c r="CD1" s="72"/>
+      <c r="CE1" s="72"/>
+      <c r="CF1" s="72"/>
+      <c r="CG1" s="72"/>
+      <c r="CH1" s="72"/>
       <c r="CI1" s="23"/>
-      <c r="CJ1" s="94" t="s">
+      <c r="CJ1" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="CK1" s="94"/>
-      <c r="CL1" s="94"/>
-      <c r="CM1" s="95" t="s">
+      <c r="CK1" s="73"/>
+      <c r="CL1" s="73"/>
+      <c r="CM1" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="CN1" s="95"/>
-      <c r="CO1" s="95"/>
-      <c r="CP1" s="95"/>
-      <c r="CQ1" s="95"/>
-      <c r="CR1" s="96" t="s">
+      <c r="CN1" s="74"/>
+      <c r="CO1" s="74"/>
+      <c r="CP1" s="74"/>
+      <c r="CQ1" s="74"/>
+      <c r="CR1" s="75" t="s">
         <v>15</v>
       </c>
-      <c r="CS1" s="96"/>
-      <c r="CT1" s="96"/>
-      <c r="CU1" s="96"/>
-      <c r="CV1" s="96"/>
-      <c r="CW1" s="96"/>
-      <c r="CX1" s="96"/>
-      <c r="CY1" s="96"/>
-      <c r="CZ1" s="96"/>
-      <c r="DA1" s="96"/>
-      <c r="DB1" s="96"/>
-      <c r="DC1" s="96"/>
-      <c r="DD1" s="97"/>
-      <c r="DE1" s="98" t="s">
+      <c r="CS1" s="75"/>
+      <c r="CT1" s="75"/>
+      <c r="CU1" s="75"/>
+      <c r="CV1" s="75"/>
+      <c r="CW1" s="75"/>
+      <c r="CX1" s="75"/>
+      <c r="CY1" s="75"/>
+      <c r="CZ1" s="75"/>
+      <c r="DA1" s="75"/>
+      <c r="DB1" s="75"/>
+      <c r="DC1" s="75"/>
+      <c r="DD1" s="76"/>
+      <c r="DE1" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="DF1" s="92"/>
-      <c r="DG1" s="99"/>
-      <c r="DH1" s="91" t="s">
+      <c r="DF1" s="70"/>
+      <c r="DG1" s="78"/>
+      <c r="DH1" s="69" t="s">
         <v>17</v>
       </c>
-      <c r="DI1" s="92"/>
-      <c r="DJ1" s="92"/>
-      <c r="DK1" s="92" t="s">
+      <c r="DI1" s="70"/>
+      <c r="DJ1" s="70"/>
+      <c r="DK1" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="DL1" s="92"/>
-      <c r="DM1" s="92"/>
-      <c r="DN1" s="93" t="s">
+      <c r="DL1" s="70"/>
+      <c r="DM1" s="70"/>
+      <c r="DN1" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="DO1" s="93"/>
-      <c r="DP1" s="93"/>
-      <c r="DQ1" s="93"/>
+      <c r="DO1" s="71"/>
+      <c r="DP1" s="71"/>
+      <c r="DQ1" s="71"/>
     </row>
     <row r="2" spans="1:121" ht="21">
       <c r="A2" s="5" t="s">
@@ -2341,9 +2340,18 @@
       <c r="CS3" s="34">
         <v>1</v>
       </c>
+      <c r="CT3" s="34"/>
+      <c r="CU3" s="34"/>
+      <c r="CV3" s="34"/>
+      <c r="CW3" s="34"/>
+      <c r="CX3" s="34"/>
+      <c r="CY3" s="34"/>
+      <c r="CZ3" s="34"/>
+      <c r="DA3" s="34"/>
       <c r="DB3" s="34">
         <v>0.15</v>
       </c>
+      <c r="DC3" s="34"/>
       <c r="DD3" s="34" t="s">
         <v>93</v>
       </c>
@@ -2390,6 +2398,16 @@
       <c r="CR4" s="40">
         <v>46199</v>
       </c>
+      <c r="CS4" s="34"/>
+      <c r="CT4" s="34"/>
+      <c r="CU4" s="34"/>
+      <c r="CV4" s="34"/>
+      <c r="CW4" s="34"/>
+      <c r="CX4" s="34"/>
+      <c r="CY4" s="34"/>
+      <c r="CZ4" s="34"/>
+      <c r="DA4" s="34"/>
+      <c r="DB4" s="34"/>
       <c r="DC4" s="65">
         <v>0.04</v>
       </c>
@@ -2439,6 +2457,16 @@
       <c r="CR5" s="40">
         <v>46199</v>
       </c>
+      <c r="CS5" s="34"/>
+      <c r="CT5" s="34"/>
+      <c r="CU5" s="34"/>
+      <c r="CV5" s="34"/>
+      <c r="CW5" s="34"/>
+      <c r="CX5" s="34"/>
+      <c r="CY5" s="34"/>
+      <c r="CZ5" s="34"/>
+      <c r="DA5" s="34"/>
+      <c r="DB5" s="34"/>
       <c r="DC5" s="65">
         <v>0.04</v>
       </c>
@@ -2488,6 +2516,16 @@
       <c r="CR6" s="40">
         <v>46199</v>
       </c>
+      <c r="CS6" s="34"/>
+      <c r="CT6" s="34"/>
+      <c r="CU6" s="34"/>
+      <c r="CV6" s="34"/>
+      <c r="CW6" s="34"/>
+      <c r="CX6" s="34"/>
+      <c r="CY6" s="34"/>
+      <c r="CZ6" s="34"/>
+      <c r="DA6" s="34"/>
+      <c r="DB6" s="34"/>
       <c r="DC6" s="65">
         <v>0.04</v>
       </c>
@@ -2537,6 +2575,16 @@
       <c r="CR7" s="40">
         <v>46199</v>
       </c>
+      <c r="CS7" s="34"/>
+      <c r="CT7" s="34"/>
+      <c r="CU7" s="34"/>
+      <c r="CV7" s="34"/>
+      <c r="CW7" s="34"/>
+      <c r="CX7" s="34"/>
+      <c r="CY7" s="34"/>
+      <c r="CZ7" s="34"/>
+      <c r="DA7" s="34"/>
+      <c r="DB7" s="34"/>
       <c r="DC7" s="65">
         <v>0.04</v>
       </c>
@@ -2586,6 +2634,16 @@
       <c r="CR8" s="40">
         <v>46199</v>
       </c>
+      <c r="CS8" s="34"/>
+      <c r="CT8" s="34"/>
+      <c r="CU8" s="34"/>
+      <c r="CV8" s="34"/>
+      <c r="CW8" s="34"/>
+      <c r="CX8" s="34"/>
+      <c r="CY8" s="34"/>
+      <c r="CZ8" s="34"/>
+      <c r="DA8" s="34"/>
+      <c r="DB8" s="34"/>
       <c r="DC8" s="65">
         <v>0.04</v>
       </c>
@@ -2635,6 +2693,16 @@
       <c r="CR9" s="40">
         <v>46199</v>
       </c>
+      <c r="CS9" s="34"/>
+      <c r="CT9" s="34"/>
+      <c r="CU9" s="34"/>
+      <c r="CV9" s="34"/>
+      <c r="CW9" s="34"/>
+      <c r="CX9" s="34"/>
+      <c r="CY9" s="34"/>
+      <c r="CZ9" s="34"/>
+      <c r="DA9" s="34"/>
+      <c r="DB9" s="34"/>
       <c r="DC9" s="65">
         <v>0.04</v>
       </c>
@@ -2684,6 +2752,16 @@
       <c r="CR10" s="40">
         <v>46199</v>
       </c>
+      <c r="CS10" s="34"/>
+      <c r="CT10" s="34"/>
+      <c r="CU10" s="34"/>
+      <c r="CV10" s="34"/>
+      <c r="CW10" s="34"/>
+      <c r="CX10" s="34"/>
+      <c r="CY10" s="34"/>
+      <c r="CZ10" s="34"/>
+      <c r="DA10" s="34"/>
+      <c r="DB10" s="34"/>
       <c r="DC10" s="65">
         <v>0.04</v>
       </c>
@@ -2733,6 +2811,16 @@
       <c r="CR11" s="40">
         <v>46199</v>
       </c>
+      <c r="CS11" s="34"/>
+      <c r="CT11" s="34"/>
+      <c r="CU11" s="34"/>
+      <c r="CV11" s="34"/>
+      <c r="CW11" s="34"/>
+      <c r="CX11" s="34"/>
+      <c r="CY11" s="34"/>
+      <c r="CZ11" s="34"/>
+      <c r="DA11" s="34"/>
+      <c r="DB11" s="34"/>
       <c r="DC11" s="65">
         <v>0.04</v>
       </c>
@@ -2782,6 +2870,16 @@
       <c r="CR12" s="40">
         <v>46199</v>
       </c>
+      <c r="CS12" s="34"/>
+      <c r="CT12" s="34"/>
+      <c r="CU12" s="34"/>
+      <c r="CV12" s="34"/>
+      <c r="CW12" s="34"/>
+      <c r="CX12" s="34"/>
+      <c r="CY12" s="34"/>
+      <c r="CZ12" s="34"/>
+      <c r="DA12" s="34"/>
+      <c r="DB12" s="34"/>
       <c r="DC12" s="65">
         <v>0.04</v>
       </c>
@@ -2831,6 +2929,16 @@
       <c r="CR13" s="40">
         <v>46210</v>
       </c>
+      <c r="CS13" s="34"/>
+      <c r="CT13" s="34"/>
+      <c r="CU13" s="34"/>
+      <c r="CV13" s="34"/>
+      <c r="CW13" s="34"/>
+      <c r="CX13" s="34"/>
+      <c r="CY13" s="34"/>
+      <c r="CZ13" s="34"/>
+      <c r="DA13" s="34"/>
+      <c r="DB13" s="34"/>
       <c r="DC13" s="65">
         <v>0.04</v>
       </c>
@@ -2984,9 +3092,18 @@
       <c r="CR14" s="35">
         <v>46210</v>
       </c>
+      <c r="CS14" s="34"/>
+      <c r="CT14" s="34"/>
+      <c r="CU14" s="34"/>
+      <c r="CV14" s="34"/>
+      <c r="CW14" s="34"/>
+      <c r="CX14" s="34"/>
       <c r="CY14" s="34">
         <v>0.24</v>
       </c>
+      <c r="CZ14" s="34"/>
+      <c r="DA14" s="34"/>
+      <c r="DB14" s="34"/>
       <c r="DC14" s="34">
         <v>0.04</v>
       </c>
@@ -3124,9 +3241,18 @@
       <c r="CR15" s="35">
         <v>46210</v>
       </c>
+      <c r="CS15" s="34"/>
+      <c r="CT15" s="34"/>
+      <c r="CU15" s="34"/>
+      <c r="CV15" s="34"/>
+      <c r="CW15" s="34"/>
+      <c r="CX15" s="34"/>
       <c r="CY15" s="34">
         <v>0.24</v>
       </c>
+      <c r="CZ15" s="34"/>
+      <c r="DA15" s="34"/>
+      <c r="DB15" s="34"/>
       <c r="DC15" s="34">
         <v>0.04</v>
       </c>
@@ -3264,9 +3390,18 @@
       <c r="CR16" s="35">
         <v>46210</v>
       </c>
+      <c r="CS16" s="34"/>
+      <c r="CT16" s="34"/>
+      <c r="CU16" s="34"/>
+      <c r="CV16" s="34"/>
+      <c r="CW16" s="34"/>
+      <c r="CX16" s="34"/>
       <c r="CY16" s="34">
         <v>0.24</v>
       </c>
+      <c r="CZ16" s="34"/>
+      <c r="DA16" s="34"/>
+      <c r="DB16" s="34"/>
       <c r="DC16" s="34">
         <v>0.04</v>
       </c>
@@ -3404,9 +3539,18 @@
       <c r="CR17" s="35">
         <v>46210</v>
       </c>
+      <c r="CS17" s="34"/>
+      <c r="CT17" s="34"/>
+      <c r="CU17" s="34"/>
+      <c r="CV17" s="34"/>
+      <c r="CW17" s="34"/>
+      <c r="CX17" s="34"/>
       <c r="CY17" s="34">
         <v>0.24</v>
       </c>
+      <c r="CZ17" s="34"/>
+      <c r="DA17" s="34"/>
+      <c r="DB17" s="34"/>
       <c r="DC17" s="34">
         <v>0.04</v>
       </c>
@@ -3570,9 +3714,18 @@
       <c r="CR18" s="35">
         <v>46210</v>
       </c>
+      <c r="CS18" s="34"/>
+      <c r="CT18" s="34"/>
+      <c r="CU18" s="34"/>
+      <c r="CV18" s="34"/>
+      <c r="CW18" s="34"/>
+      <c r="CX18" s="34"/>
       <c r="CY18" s="34">
         <v>0.24</v>
       </c>
+      <c r="CZ18" s="34"/>
+      <c r="DA18" s="34"/>
+      <c r="DB18" s="34"/>
       <c r="DC18" s="34">
         <v>0.04</v>
       </c>
@@ -3736,9 +3889,18 @@
       <c r="CR19" s="35">
         <v>46210</v>
       </c>
+      <c r="CS19" s="34"/>
+      <c r="CT19" s="34"/>
+      <c r="CU19" s="34"/>
+      <c r="CV19" s="34"/>
+      <c r="CW19" s="34"/>
+      <c r="CX19" s="34"/>
       <c r="CY19" s="34">
         <v>0.24</v>
       </c>
+      <c r="CZ19" s="34"/>
+      <c r="DA19" s="34"/>
+      <c r="DB19" s="34"/>
       <c r="DC19" s="34">
         <v>0.04</v>
       </c>
@@ -3877,6 +4039,7 @@
       <c r="BP20" s="34" t="s">
         <v>93</v>
       </c>
+      <c r="BQ20" s="34"/>
       <c r="BR20" s="35">
         <v>46205</v>
       </c>
@@ -4045,6 +4208,7 @@
       <c r="BP21" s="34" t="s">
         <v>93</v>
       </c>
+      <c r="BQ21" s="34"/>
       <c r="BR21" s="35">
         <v>46205</v>
       </c>
@@ -4210,6 +4374,7 @@
       <c r="BP22" s="34" t="s">
         <v>93</v>
       </c>
+      <c r="BQ22" s="34"/>
       <c r="BR22" s="35">
         <v>46205</v>
       </c>
@@ -4397,6 +4562,7 @@
       <c r="BP23" s="34" t="s">
         <v>93</v>
       </c>
+      <c r="BQ23" s="34"/>
       <c r="BR23" s="35">
         <v>46205</v>
       </c>
@@ -4685,6 +4851,7 @@
       <c r="BP26" s="34" t="s">
         <v>93</v>
       </c>
+      <c r="BQ26" s="34"/>
       <c r="BR26" s="35">
         <v>46205</v>
       </c>
@@ -4910,35 +5077,27 @@
         <f t="shared" si="0"/>
         <v>175</v>
       </c>
-      <c r="CM28" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="CN28" s="17">
-        <v>5</v>
-      </c>
-      <c r="CO28" s="17">
-        <f>+C28-58.5-15</f>
-        <v>65.38</v>
-      </c>
-      <c r="CP28" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="CQ28" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="CR28" s="19">
+      <c r="CR28" s="35">
         <v>46209</v>
       </c>
-      <c r="CS28" s="17">
+      <c r="CS28" s="34">
         <v>0.8</v>
       </c>
-      <c r="CT28" s="17">
+      <c r="CT28" s="34">
         <v>0.5</v>
       </c>
-      <c r="DA28" s="17">
-        <v>0.6</v>
-      </c>
-      <c r="DD28" s="17" t="s">
+      <c r="CU28" s="34"/>
+      <c r="CV28" s="34"/>
+      <c r="CW28" s="34"/>
+      <c r="CX28" s="34"/>
+      <c r="CY28" s="34"/>
+      <c r="CZ28" s="34"/>
+      <c r="DA28" s="34">
+        <v>0.5</v>
+      </c>
+      <c r="DB28" s="34"/>
+      <c r="DC28" s="34"/>
+      <c r="DD28" s="34" t="s">
         <v>96</v>
       </c>
     </row>
@@ -4981,23 +5140,31 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="CR29" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="CV29" s="17">
+      <c r="CR29" s="35">
+        <v>46210</v>
+      </c>
+      <c r="CS29" s="34"/>
+      <c r="CT29" s="34"/>
+      <c r="CU29" s="34"/>
+      <c r="CV29" s="34">
         <v>0.1</v>
       </c>
-      <c r="CW29" s="17">
+      <c r="CW29" s="34">
         <v>0.8</v>
       </c>
-      <c r="DC29" s="43"/>
-      <c r="DD29" s="17" t="s">
+      <c r="CX29" s="34"/>
+      <c r="CY29" s="34"/>
+      <c r="CZ29" s="34"/>
+      <c r="DA29" s="34"/>
+      <c r="DB29" s="34"/>
+      <c r="DC29" s="65"/>
+      <c r="DD29" s="34" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="30" spans="1:108" ht="21" hidden="1">
       <c r="A30" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B30" s="6">
         <v>1</v>
@@ -5006,17 +5173,17 @@
         <v>101.74</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>100</v>
       </c>
       <c r="AH30" s="18"/>
       <c r="AN30" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="AO30" s="34" t="s">
         <v>130</v>
-      </c>
-      <c r="AO30" s="34" t="s">
-        <v>131</v>
       </c>
       <c r="AP30" s="34">
         <v>10</v>
@@ -5025,10 +5192,10 @@
         <v>46170</v>
       </c>
       <c r="AR30" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="AS30" s="34" t="s">
         <v>132</v>
-      </c>
-      <c r="AS30" s="34" t="s">
-        <v>133</v>
       </c>
       <c r="CI30" s="17">
         <f t="shared" si="0"/>
@@ -5040,7 +5207,7 @@
     </row>
     <row r="31" spans="1:108" ht="21">
       <c r="A31" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B31" s="6">
         <v>2</v>
@@ -5102,7 +5269,7 @@
       <c r="AF31" s="34"/>
       <c r="AG31" s="34"/>
       <c r="AH31" s="40" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AI31" s="34" t="s">
         <v>96</v>
@@ -5120,7 +5287,7 @@
         <v>96</v>
       </c>
       <c r="AN31" s="34" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AO31" s="34" t="s">
         <v>95</v>
@@ -5138,7 +5305,7 @@
         <v>97</v>
       </c>
       <c r="AT31" s="34" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AU31" s="34" t="s">
         <v>95</v>
@@ -5153,7 +5320,7 @@
         <v>34.99</v>
       </c>
       <c r="AY31" s="34" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AZ31" s="34" t="s">
         <v>119</v>
@@ -5177,6 +5344,7 @@
       <c r="BP31" s="34" t="s">
         <v>103</v>
       </c>
+      <c r="BQ31" s="34"/>
       <c r="BR31" s="35">
         <v>46199</v>
       </c>
@@ -5194,22 +5362,31 @@
         <f t="shared" si="0"/>
         <v>170</v>
       </c>
-      <c r="CR31" s="19">
+      <c r="CR31" s="35">
         <v>46208</v>
       </c>
-      <c r="CS31" s="17">
+      <c r="CS31" s="34">
         <v>0.8</v>
       </c>
-      <c r="DB31" s="17">
-        <v>0.15</v>
-      </c>
-      <c r="DD31" s="17" t="s">
+      <c r="CT31" s="34"/>
+      <c r="CU31" s="34"/>
+      <c r="CV31" s="34"/>
+      <c r="CW31" s="34"/>
+      <c r="CX31" s="34"/>
+      <c r="CY31" s="34"/>
+      <c r="CZ31" s="34"/>
+      <c r="DA31" s="34" t="s">
+        <v>137</v>
+      </c>
+      <c r="DB31" s="34"/>
+      <c r="DC31" s="34"/>
+      <c r="DD31" s="34" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="32" spans="1:108" ht="21">
       <c r="A32" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B32" s="6">
         <v>3</v>
@@ -5271,7 +5448,7 @@
       <c r="AF32" s="34"/>
       <c r="AG32" s="34"/>
       <c r="AH32" s="40" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AI32" s="34" t="s">
         <v>96</v>
@@ -5289,7 +5466,7 @@
         <v>96</v>
       </c>
       <c r="AN32" s="34" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AO32" s="34" t="s">
         <v>95</v>
@@ -5346,6 +5523,7 @@
       <c r="BP32" s="34" t="s">
         <v>103</v>
       </c>
+      <c r="BQ32" s="34"/>
       <c r="BR32" s="35">
         <v>46199</v>
       </c>
@@ -5363,25 +5541,33 @@
         <f t="shared" si="0"/>
         <v>170</v>
       </c>
-      <c r="CR32" s="19">
+      <c r="CR32" s="35">
         <v>46208</v>
       </c>
-      <c r="CS32" s="17">
+      <c r="CS32" s="34">
         <v>0.8</v>
       </c>
-      <c r="CT32" s="17">
+      <c r="CT32" s="34">
         <v>0.5</v>
       </c>
-      <c r="DB32" s="17">
-        <v>0.15</v>
-      </c>
-      <c r="DD32" s="17" t="s">
+      <c r="CU32" s="34"/>
+      <c r="CV32" s="34"/>
+      <c r="CW32" s="34"/>
+      <c r="CX32" s="34"/>
+      <c r="CY32" s="34"/>
+      <c r="CZ32" s="34"/>
+      <c r="DA32" s="34" t="s">
+        <v>137</v>
+      </c>
+      <c r="DB32" s="34"/>
+      <c r="DC32" s="34"/>
+      <c r="DD32" s="34" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="33" spans="1:108" ht="21">
       <c r="A33" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B33" s="6">
         <v>4</v>
@@ -5443,7 +5629,7 @@
       <c r="AF33" s="34"/>
       <c r="AG33" s="34"/>
       <c r="AH33" s="40" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AI33" s="34" t="s">
         <v>96</v>
@@ -5518,6 +5704,7 @@
       <c r="BP33" s="34" t="s">
         <v>103</v>
       </c>
+      <c r="BQ33" s="34"/>
       <c r="BR33" s="35">
         <v>46199</v>
       </c>
@@ -5535,22 +5722,31 @@
         <f t="shared" si="0"/>
         <v>170</v>
       </c>
-      <c r="CR33" s="19">
+      <c r="CR33" s="35">
         <v>46208</v>
       </c>
-      <c r="CS33" s="17">
+      <c r="CS33" s="34">
         <v>0.8</v>
       </c>
-      <c r="DB33" s="17">
-        <v>0.15</v>
-      </c>
-      <c r="DD33" s="17" t="s">
+      <c r="CT33" s="34"/>
+      <c r="CU33" s="34"/>
+      <c r="CV33" s="34"/>
+      <c r="CW33" s="34"/>
+      <c r="CX33" s="34"/>
+      <c r="CY33" s="34"/>
+      <c r="CZ33" s="34"/>
+      <c r="DA33" s="34" t="s">
+        <v>137</v>
+      </c>
+      <c r="DB33" s="34"/>
+      <c r="DC33" s="34"/>
+      <c r="DD33" s="34" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="34" spans="1:108" ht="21" hidden="1">
       <c r="A34" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B34" s="6">
         <v>5</v>
@@ -5559,17 +5755,17 @@
         <v>59.08</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>100</v>
       </c>
       <c r="AH34" s="18"/>
       <c r="AN34" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="AO34" s="34" t="s">
         <v>130</v>
-      </c>
-      <c r="AO34" s="34" t="s">
-        <v>131</v>
       </c>
       <c r="AP34" s="34">
         <v>10</v>
@@ -5578,10 +5774,10 @@
         <v>46170</v>
       </c>
       <c r="AR34" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="AS34" s="34" t="s">
         <v>132</v>
-      </c>
-      <c r="AS34" s="34" t="s">
-        <v>133</v>
       </c>
       <c r="CI34" s="17">
         <f t="shared" si="0"/>
@@ -5599,7 +5795,7 @@
     </row>
     <row r="35" spans="1:108" ht="21" hidden="1">
       <c r="A35" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B35" s="6">
         <v>7</v>
@@ -5615,10 +5811,10 @@
       </c>
       <c r="AH35" s="18"/>
       <c r="AN35" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="AO35" s="34" t="s">
         <v>130</v>
-      </c>
-      <c r="AO35" s="34" t="s">
-        <v>131</v>
       </c>
       <c r="AP35" s="34">
         <v>10</v>
@@ -5627,7 +5823,7 @@
         <v>46134</v>
       </c>
       <c r="AR35" s="34" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AS35" s="34" t="s">
         <v>144</v>
@@ -5658,7 +5854,7 @@
     </row>
     <row r="36" spans="1:108" ht="21" hidden="1">
       <c r="A36" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B36" s="6">
         <v>8</v>
@@ -5674,10 +5870,10 @@
       </c>
       <c r="AH36" s="18"/>
       <c r="AN36" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="AO36" s="34" t="s">
         <v>130</v>
-      </c>
-      <c r="AO36" s="34" t="s">
-        <v>131</v>
       </c>
       <c r="AP36" s="34">
         <v>10</v>
@@ -5686,7 +5882,7 @@
         <v>46134</v>
       </c>
       <c r="AR36" s="34" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AS36" s="34" t="s">
         <v>144</v>
@@ -5717,7 +5913,7 @@
     </row>
     <row r="37" spans="1:108" ht="21" hidden="1">
       <c r="A37" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B37" s="6">
         <v>9</v>
@@ -5733,10 +5929,10 @@
       </c>
       <c r="AH37" s="18"/>
       <c r="AN37" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="AO37" s="34" t="s">
         <v>130</v>
-      </c>
-      <c r="AO37" s="34" t="s">
-        <v>131</v>
       </c>
       <c r="AP37" s="34">
         <v>10</v>
@@ -5745,7 +5941,7 @@
         <v>46132</v>
       </c>
       <c r="AR37" s="34" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AS37" s="34" t="s">
         <v>144</v>
@@ -5778,7 +5974,7 @@
     </row>
     <row r="38" spans="1:108" ht="21">
       <c r="A38" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B38" s="6">
         <v>10</v>
@@ -5829,7 +6025,7 @@
       <c r="AF38" s="34"/>
       <c r="AG38" s="34"/>
       <c r="AH38" s="40" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AI38" s="34" t="s">
         <v>96</v>
@@ -5847,7 +6043,7 @@
         <v>96</v>
       </c>
       <c r="AN38" s="34" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AO38" s="34" t="s">
         <v>95</v>
@@ -5892,7 +6088,7 @@
         <v>46174</v>
       </c>
       <c r="BI38" s="34" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BJ38" s="17">
         <v>12.5</v>
@@ -5917,25 +6113,33 @@
         <f t="shared" si="0"/>
         <v>95</v>
       </c>
-      <c r="CR38" s="19">
+      <c r="CR38" s="35">
         <v>46208</v>
       </c>
-      <c r="CS38" s="17">
+      <c r="CS38" s="34">
         <v>0.8</v>
       </c>
-      <c r="CT38" s="17">
+      <c r="CT38" s="34">
         <v>0.5</v>
       </c>
-      <c r="DB38" s="17">
-        <v>0.15</v>
-      </c>
-      <c r="DD38" s="17" t="s">
+      <c r="CU38" s="34"/>
+      <c r="CV38" s="34"/>
+      <c r="CW38" s="34"/>
+      <c r="CX38" s="34"/>
+      <c r="CY38" s="34"/>
+      <c r="CZ38" s="34"/>
+      <c r="DA38" s="34" t="s">
+        <v>137</v>
+      </c>
+      <c r="DB38" s="34"/>
+      <c r="DC38" s="34"/>
+      <c r="DD38" s="34" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="39" spans="1:108" ht="21" hidden="1">
       <c r="A39" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B39" s="6">
         <v>11</v>
@@ -5944,17 +6148,17 @@
         <v>53.38</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E39" s="7" t="s">
         <v>100</v>
       </c>
       <c r="AH39" s="18"/>
       <c r="AN39" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="AO39" s="34" t="s">
         <v>130</v>
-      </c>
-      <c r="AO39" s="34" t="s">
-        <v>131</v>
       </c>
       <c r="AP39" s="34">
         <v>10</v>
@@ -5963,10 +6167,10 @@
         <v>46170</v>
       </c>
       <c r="AR39" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="AS39" s="34" t="s">
         <v>132</v>
-      </c>
-      <c r="AS39" s="34" t="s">
-        <v>133</v>
       </c>
       <c r="CI39" s="17">
         <f t="shared" si="0"/>
@@ -5984,7 +6188,7 @@
     </row>
     <row r="40" spans="1:108" ht="21" hidden="1">
       <c r="A40" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B40" s="6">
         <v>12</v>
@@ -6000,10 +6204,10 @@
       </c>
       <c r="AH40" s="18"/>
       <c r="AN40" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="AO40" s="34" t="s">
         <v>130</v>
-      </c>
-      <c r="AO40" s="34" t="s">
-        <v>131</v>
       </c>
       <c r="AP40" s="34">
         <v>10</v>
@@ -6012,7 +6216,7 @@
         <v>46126</v>
       </c>
       <c r="AR40" s="34" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AS40" s="34" t="s">
         <v>144</v>
@@ -6045,7 +6249,7 @@
     </row>
     <row r="41" spans="1:108" ht="21" hidden="1">
       <c r="A41" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B41" s="6">
         <v>13</v>
@@ -6061,10 +6265,10 @@
       </c>
       <c r="AH41" s="18"/>
       <c r="AN41" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="AO41" s="34" t="s">
         <v>130</v>
-      </c>
-      <c r="AO41" s="34" t="s">
-        <v>131</v>
       </c>
       <c r="AP41" s="34">
         <v>10</v>
@@ -6073,7 +6277,7 @@
         <v>46135</v>
       </c>
       <c r="AR41" s="34" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AS41" s="34" t="s">
         <v>144</v>
@@ -6106,7 +6310,7 @@
     </row>
     <row r="42" spans="1:108" ht="21" hidden="1">
       <c r="A42" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B42" s="6">
         <v>14</v>
@@ -6122,10 +6326,10 @@
       </c>
       <c r="AH42" s="18"/>
       <c r="AN42" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="AO42" s="34" t="s">
         <v>130</v>
-      </c>
-      <c r="AO42" s="34" t="s">
-        <v>131</v>
       </c>
       <c r="AP42" s="34">
         <v>10</v>
@@ -6134,7 +6338,7 @@
         <v>46135</v>
       </c>
       <c r="AR42" s="34" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AS42" s="34" t="s">
         <v>144</v>
@@ -6165,7 +6369,7 @@
     </row>
     <row r="43" spans="1:108" ht="21" hidden="1">
       <c r="A43" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B43" s="6">
         <v>15</v>
@@ -6181,10 +6385,10 @@
       </c>
       <c r="AH43" s="18"/>
       <c r="AN43" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="AO43" s="34" t="s">
         <v>130</v>
-      </c>
-      <c r="AO43" s="34" t="s">
-        <v>131</v>
       </c>
       <c r="AP43" s="34">
         <v>10</v>
@@ -6193,7 +6397,7 @@
         <v>46136</v>
       </c>
       <c r="AR43" s="34" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AS43" s="34" t="s">
         <v>144</v>
@@ -6286,7 +6490,7 @@
         <v>148</v>
       </c>
       <c r="AO44" s="34" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AP44" s="34">
         <v>146.93</v>
@@ -6339,16 +6543,25 @@
       <c r="CQ44" s="34" t="s">
         <v>96</v>
       </c>
-      <c r="CR44" s="19">
+      <c r="CR44" s="35">
         <v>46204</v>
       </c>
-      <c r="CX44" s="17">
+      <c r="CS44" s="34"/>
+      <c r="CT44" s="34"/>
+      <c r="CU44" s="34"/>
+      <c r="CV44" s="34"/>
+      <c r="CW44" s="34"/>
+      <c r="CX44" s="34">
         <v>0.6</v>
       </c>
-      <c r="DC44" s="17">
+      <c r="CY44" s="34"/>
+      <c r="CZ44" s="34"/>
+      <c r="DA44" s="34"/>
+      <c r="DB44" s="34"/>
+      <c r="DC44" s="34">
         <v>0.04</v>
       </c>
-      <c r="DD44" s="17" t="s">
+      <c r="DD44" s="34" t="s">
         <v>96</v>
       </c>
     </row>
@@ -6363,17 +6576,17 @@
         <v>120</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E45" s="7" t="s">
         <v>100</v>
       </c>
       <c r="AH45" s="18"/>
       <c r="AN45" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="AO45" s="34" t="s">
         <v>130</v>
-      </c>
-      <c r="AO45" s="34" t="s">
-        <v>131</v>
       </c>
       <c r="AP45" s="34">
         <v>10</v>
@@ -6382,7 +6595,7 @@
         <v>46175</v>
       </c>
       <c r="AR45" s="34" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AS45" s="34" t="s">
         <v>144</v>
@@ -6391,9 +6604,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="DC45" s="43">
-        <v>0.04</v>
-      </c>
+      <c r="DC45" s="43"/>
     </row>
     <row r="46" spans="1:108" ht="21">
       <c r="A46" s="6" t="s">
@@ -6512,16 +6723,25 @@
       <c r="CQ46" s="34" t="s">
         <v>96</v>
       </c>
-      <c r="CR46" s="19">
+      <c r="CR46" s="35">
         <v>46204</v>
       </c>
-      <c r="CX46" s="17">
+      <c r="CS46" s="34"/>
+      <c r="CT46" s="34"/>
+      <c r="CU46" s="34"/>
+      <c r="CV46" s="34"/>
+      <c r="CW46" s="34"/>
+      <c r="CX46" s="34">
         <v>0.6</v>
       </c>
-      <c r="DC46" s="17">
+      <c r="CY46" s="34"/>
+      <c r="CZ46" s="34"/>
+      <c r="DA46" s="34"/>
+      <c r="DB46" s="34"/>
+      <c r="DC46" s="34">
         <v>0.04</v>
       </c>
-      <c r="DD46" s="17" t="s">
+      <c r="DD46" s="34" t="s">
         <v>96</v>
       </c>
     </row>
@@ -6589,7 +6809,7 @@
         <v>148</v>
       </c>
       <c r="AO47" s="34" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AP47" s="34">
         <v>146.93</v>
@@ -6643,16 +6863,25 @@
       <c r="CQ47" s="34" t="s">
         <v>96</v>
       </c>
-      <c r="CR47" s="19">
+      <c r="CR47" s="35">
         <v>46204</v>
       </c>
-      <c r="CX47" s="17">
+      <c r="CS47" s="34"/>
+      <c r="CT47" s="34"/>
+      <c r="CU47" s="34"/>
+      <c r="CV47" s="34"/>
+      <c r="CW47" s="34"/>
+      <c r="CX47" s="34">
         <v>0.6</v>
       </c>
-      <c r="DC47" s="17">
+      <c r="CY47" s="34"/>
+      <c r="CZ47" s="34"/>
+      <c r="DA47" s="34"/>
+      <c r="DB47" s="34"/>
+      <c r="DC47" s="34">
         <v>0.04</v>
       </c>
-      <c r="DD47" s="17" t="s">
+      <c r="DD47" s="34" t="s">
         <v>96</v>
       </c>
     </row>
@@ -6773,16 +7002,25 @@
       <c r="CQ48" s="34" t="s">
         <v>96</v>
       </c>
-      <c r="CR48" s="19">
+      <c r="CR48" s="35">
         <v>46204</v>
       </c>
-      <c r="CX48" s="17">
+      <c r="CS48" s="34"/>
+      <c r="CT48" s="34"/>
+      <c r="CU48" s="34"/>
+      <c r="CV48" s="34"/>
+      <c r="CW48" s="34"/>
+      <c r="CX48" s="34">
         <v>0.6</v>
       </c>
-      <c r="DC48" s="17">
+      <c r="CY48" s="34"/>
+      <c r="CZ48" s="34"/>
+      <c r="DA48" s="34"/>
+      <c r="DB48" s="34"/>
+      <c r="DC48" s="34">
         <v>0.04</v>
       </c>
-      <c r="DD48" s="17" t="s">
+      <c r="DD48" s="34" t="s">
         <v>96</v>
       </c>
     </row>
@@ -6850,7 +7088,7 @@
         <v>160</v>
       </c>
       <c r="AO49" s="34" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AP49" s="34">
         <v>120.28</v>
@@ -6903,16 +7141,25 @@
       <c r="CQ49" s="34" t="s">
         <v>96</v>
       </c>
-      <c r="CR49" s="19">
+      <c r="CR49" s="35">
         <v>46204</v>
       </c>
-      <c r="CX49" s="17">
+      <c r="CS49" s="34"/>
+      <c r="CT49" s="34"/>
+      <c r="CU49" s="34"/>
+      <c r="CV49" s="34"/>
+      <c r="CW49" s="34"/>
+      <c r="CX49" s="34">
         <v>0.6</v>
       </c>
-      <c r="DC49" s="17">
+      <c r="CY49" s="34"/>
+      <c r="CZ49" s="34"/>
+      <c r="DA49" s="34"/>
+      <c r="DB49" s="34"/>
+      <c r="DC49" s="34">
         <v>0.04</v>
       </c>
-      <c r="DD49" s="17" t="s">
+      <c r="DD49" s="34" t="s">
         <v>96</v>
       </c>
     </row>
@@ -6980,7 +7227,7 @@
         <v>160</v>
       </c>
       <c r="AO50" s="34" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AP50" s="34">
         <v>120.28</v>
@@ -7033,16 +7280,25 @@
       <c r="CQ50" s="34" t="s">
         <v>96</v>
       </c>
-      <c r="CR50" s="19">
+      <c r="CR50" s="35">
         <v>46204</v>
       </c>
-      <c r="CX50" s="17">
+      <c r="CS50" s="34"/>
+      <c r="CT50" s="34"/>
+      <c r="CU50" s="34"/>
+      <c r="CV50" s="34"/>
+      <c r="CW50" s="34"/>
+      <c r="CX50" s="34">
         <v>0.6</v>
       </c>
-      <c r="DC50" s="17">
+      <c r="CY50" s="34"/>
+      <c r="CZ50" s="34"/>
+      <c r="DA50" s="34"/>
+      <c r="DB50" s="34"/>
+      <c r="DC50" s="34">
         <v>0.04</v>
       </c>
-      <c r="DD50" s="17" t="s">
+      <c r="DD50" s="34" t="s">
         <v>96</v>
       </c>
     </row>
@@ -7064,10 +7320,10 @@
       </c>
       <c r="AH51" s="18"/>
       <c r="AN51" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="AO51" s="34" t="s">
         <v>130</v>
-      </c>
-      <c r="AO51" s="34" t="s">
-        <v>131</v>
       </c>
       <c r="AP51" s="34">
         <v>10</v>
@@ -7076,7 +7332,7 @@
         <v>46143</v>
       </c>
       <c r="AR51" s="34" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AS51" s="34" t="s">
         <v>144</v>
@@ -7125,10 +7381,10 @@
       </c>
       <c r="AH52" s="18"/>
       <c r="AN52" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="AO52" s="34" t="s">
         <v>130</v>
-      </c>
-      <c r="AO52" s="34" t="s">
-        <v>131</v>
       </c>
       <c r="AP52" s="34">
         <v>10</v>
@@ -7137,7 +7393,7 @@
         <v>46143</v>
       </c>
       <c r="AR52" s="34" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AS52" s="34" t="s">
         <v>144</v>
@@ -7186,10 +7442,10 @@
       </c>
       <c r="AH53" s="18"/>
       <c r="AN53" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="AO53" s="34" t="s">
         <v>130</v>
-      </c>
-      <c r="AO53" s="34" t="s">
-        <v>131</v>
       </c>
       <c r="AP53" s="34">
         <v>10</v>
@@ -7198,7 +7454,7 @@
         <v>46143</v>
       </c>
       <c r="AR53" s="34" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AS53" s="34" t="s">
         <v>144</v>
@@ -7393,6 +7649,18 @@
     </filterColumn>
   </autoFilter>
   <mergeCells count="20">
+    <mergeCell ref="F1:N1"/>
+    <mergeCell ref="O1:Y1"/>
+    <mergeCell ref="Z1:AI1"/>
+    <mergeCell ref="AN1:AS1"/>
+    <mergeCell ref="AT1:AZ1"/>
+    <mergeCell ref="AJ1:AM1"/>
+    <mergeCell ref="BA1:BF1"/>
+    <mergeCell ref="BJ1:BK1"/>
+    <mergeCell ref="BL1:BP1"/>
+    <mergeCell ref="BQ1:BV1"/>
+    <mergeCell ref="BW1:CB1"/>
+    <mergeCell ref="BG1:BI1"/>
     <mergeCell ref="DH1:DJ1"/>
     <mergeCell ref="DK1:DM1"/>
     <mergeCell ref="DN1:DQ1"/>
@@ -7401,18 +7669,6 @@
     <mergeCell ref="CM1:CQ1"/>
     <mergeCell ref="CR1:DD1"/>
     <mergeCell ref="DE1:DG1"/>
-    <mergeCell ref="BA1:BF1"/>
-    <mergeCell ref="BJ1:BK1"/>
-    <mergeCell ref="BL1:BP1"/>
-    <mergeCell ref="BQ1:BV1"/>
-    <mergeCell ref="BW1:CB1"/>
-    <mergeCell ref="BG1:BI1"/>
-    <mergeCell ref="F1:N1"/>
-    <mergeCell ref="O1:Y1"/>
-    <mergeCell ref="Z1:AI1"/>
-    <mergeCell ref="AN1:AS1"/>
-    <mergeCell ref="AT1:AZ1"/>
-    <mergeCell ref="AJ1:AM1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7916,7 +8172,7 @@
     </row>
     <row r="30" spans="1:5" ht="21">
       <c r="A30" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B30" s="6">
         <v>1</v>
@@ -7933,7 +8189,7 @@
     </row>
     <row r="31" spans="1:5" ht="21" hidden="1">
       <c r="A31" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B31" s="6">
         <v>2</v>
@@ -7950,7 +8206,7 @@
     </row>
     <row r="32" spans="1:5" ht="21" hidden="1">
       <c r="A32" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B32" s="6">
         <v>3</v>
@@ -7967,7 +8223,7 @@
     </row>
     <row r="33" spans="1:5" ht="21" hidden="1">
       <c r="A33" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B33" s="6">
         <v>4</v>
@@ -7984,7 +8240,7 @@
     </row>
     <row r="34" spans="1:5" ht="21">
       <c r="A34" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B34" s="6">
         <v>5</v>
@@ -8001,7 +8257,7 @@
     </row>
     <row r="35" spans="1:5" ht="21">
       <c r="A35" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B35" s="6">
         <v>7</v>
@@ -8018,7 +8274,7 @@
     </row>
     <row r="36" spans="1:5" ht="21">
       <c r="A36" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B36" s="6">
         <v>8</v>
@@ -8035,7 +8291,7 @@
     </row>
     <row r="37" spans="1:5" ht="21">
       <c r="A37" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B37" s="6">
         <v>9</v>
@@ -8052,7 +8308,7 @@
     </row>
     <row r="38" spans="1:5" ht="21" hidden="1">
       <c r="A38" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B38" s="6">
         <v>10</v>
@@ -8069,7 +8325,7 @@
     </row>
     <row r="39" spans="1:5" ht="21">
       <c r="A39" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B39" s="6">
         <v>11</v>
@@ -8086,7 +8342,7 @@
     </row>
     <row r="40" spans="1:5" ht="21">
       <c r="A40" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B40" s="6">
         <v>12</v>
@@ -8103,7 +8359,7 @@
     </row>
     <row r="41" spans="1:5" ht="21">
       <c r="A41" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B41" s="6">
         <v>13</v>
@@ -8120,7 +8376,7 @@
     </row>
     <row r="42" spans="1:5" ht="21">
       <c r="A42" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B42" s="6">
         <v>14</v>
@@ -8137,7 +8393,7 @@
     </row>
     <row r="43" spans="1:5" ht="21">
       <c r="A43" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B43" s="6">
         <v>15</v>
@@ -8166,7 +8422,7 @@
         <v>147</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="21">
@@ -8251,7 +8507,7 @@
         <v>147</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="21" hidden="1">
@@ -8590,7 +8846,7 @@
         <v>123</v>
       </c>
       <c r="BF2" s="52" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:58">
@@ -26489,15 +26745,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="28867580-4592-47a8-a490-5f1990c83971" xsi:nil="true"/>
@@ -26508,14 +26755,23 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE668D04-A599-40BD-83B4-4E55F7C43B16}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14CBE609-95E4-45D1-B334-D32AADDB8A39}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ABBBF542-46E2-4D90-B593-1F03D9E2A95E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ABBBF542-46E2-4D90-B593-1F03D9E2A95E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14CBE609-95E4-45D1-B334-D32AADDB8A39}"/>
 </file>
--- a/Planilla labores 26-27.xlsx
+++ b/Planilla labores 26-27.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30306"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30305"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://provinvestsa.sharepoint.com/sites/CeibosAgro-Uy-Produccin/Documentos compartidos/Litoral Norte/26-27/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4108657B-5F0C-4CCA-8040-EE19CA57672E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{66929808-80A2-4D56-9A2D-18B110CD733F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3886" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3898" uniqueCount="203">
   <si>
     <t>Análisis suelo</t>
   </si>
@@ -371,6 +371,9 @@
     <t>Araña</t>
   </si>
   <si>
+    <t>Programado</t>
+  </si>
+  <si>
     <t>todo</t>
   </si>
   <si>
@@ -420,9 +423,6 @@
   </si>
   <si>
     <t>EasyAgro</t>
-  </si>
-  <si>
-    <t>Programado</t>
   </si>
   <si>
     <t>La Blanqueada</t>
@@ -1669,6 +1669,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:DQ104"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -1677,41 +1678,41 @@
     <col min="3" max="3" width="10.85546875" style="17" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.140625" style="17" customWidth="1"/>
     <col min="5" max="5" width="18.28515625" style="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" style="17" customWidth="1"/>
-    <col min="7" max="7" width="16.5703125" style="17" customWidth="1"/>
-    <col min="8" max="16" width="9.140625" style="17" customWidth="1"/>
-    <col min="17" max="18" width="11.7109375" style="17" customWidth="1"/>
-    <col min="19" max="21" width="15.5703125" style="17" customWidth="1"/>
-    <col min="22" max="22" width="16.85546875" style="17" customWidth="1"/>
-    <col min="23" max="23" width="16.42578125" style="17" customWidth="1"/>
-    <col min="24" max="24" width="14.7109375" style="17" customWidth="1"/>
-    <col min="25" max="33" width="9.140625" style="17" customWidth="1"/>
-    <col min="34" max="34" width="11.42578125" style="17" customWidth="1"/>
-    <col min="35" max="38" width="9.140625" style="17" customWidth="1"/>
-    <col min="39" max="39" width="10.85546875" style="17" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="17" customWidth="1"/>
-    <col min="41" max="42" width="20.5703125" style="17" customWidth="1"/>
-    <col min="43" max="44" width="16" style="17" customWidth="1"/>
-    <col min="45" max="45" width="18" style="17" customWidth="1"/>
-    <col min="46" max="46" width="13.42578125" style="17" customWidth="1"/>
-    <col min="47" max="48" width="20.5703125" style="17" customWidth="1"/>
-    <col min="49" max="49" width="24.140625" style="17" customWidth="1"/>
-    <col min="50" max="50" width="9.140625" style="17" customWidth="1"/>
-    <col min="51" max="51" width="16" style="17" customWidth="1"/>
-    <col min="52" max="52" width="18" style="17" customWidth="1"/>
-    <col min="53" max="53" width="13.42578125" style="17" customWidth="1"/>
-    <col min="54" max="54" width="20.5703125" style="17" customWidth="1"/>
-    <col min="55" max="55" width="24.140625" style="17" customWidth="1"/>
-    <col min="56" max="56" width="9.140625" style="17" customWidth="1"/>
-    <col min="57" max="57" width="16" style="17" customWidth="1"/>
-    <col min="58" max="61" width="18" style="17" customWidth="1"/>
-    <col min="62" max="62" width="9.140625" style="17" customWidth="1"/>
-    <col min="63" max="63" width="11" style="17" customWidth="1"/>
-    <col min="64" max="64" width="12" style="17" customWidth="1"/>
-    <col min="65" max="65" width="12.28515625" style="17" customWidth="1"/>
-    <col min="66" max="66" width="10.42578125" style="17" customWidth="1"/>
-    <col min="67" max="67" width="9.7109375" style="17" customWidth="1"/>
-    <col min="68" max="68" width="16" style="17" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" style="17" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="16.5703125" style="17" hidden="1" customWidth="1"/>
+    <col min="8" max="16" width="9.140625" style="17" hidden="1" customWidth="1"/>
+    <col min="17" max="18" width="11.7109375" style="17" hidden="1" customWidth="1"/>
+    <col min="19" max="21" width="15.5703125" style="17" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="16.85546875" style="17" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="16.42578125" style="17" hidden="1" customWidth="1"/>
+    <col min="24" max="24" width="14.7109375" style="17" hidden="1" customWidth="1"/>
+    <col min="25" max="33" width="9.140625" style="17" hidden="1" customWidth="1"/>
+    <col min="34" max="34" width="11.42578125" style="17" hidden="1" customWidth="1"/>
+    <col min="35" max="38" width="9.140625" style="17" hidden="1" customWidth="1"/>
+    <col min="39" max="39" width="10.85546875" style="17" hidden="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="17" hidden="1" customWidth="1"/>
+    <col min="41" max="42" width="20.5703125" style="17" hidden="1" customWidth="1"/>
+    <col min="43" max="44" width="16" style="17" hidden="1" customWidth="1"/>
+    <col min="45" max="45" width="18" style="17" hidden="1" customWidth="1"/>
+    <col min="46" max="46" width="13.42578125" style="17" hidden="1" customWidth="1"/>
+    <col min="47" max="48" width="20.5703125" style="17" hidden="1" customWidth="1"/>
+    <col min="49" max="49" width="24.140625" style="17" hidden="1" customWidth="1"/>
+    <col min="50" max="50" width="9.140625" style="17" hidden="1" customWidth="1"/>
+    <col min="51" max="51" width="16" style="17" hidden="1" customWidth="1"/>
+    <col min="52" max="52" width="18" style="17" hidden="1" customWidth="1"/>
+    <col min="53" max="53" width="13.42578125" style="17" hidden="1" customWidth="1"/>
+    <col min="54" max="54" width="20.5703125" style="17" hidden="1" customWidth="1"/>
+    <col min="55" max="55" width="24.140625" style="17" hidden="1" customWidth="1"/>
+    <col min="56" max="56" width="9.140625" style="17" hidden="1" customWidth="1"/>
+    <col min="57" max="57" width="16" style="17" hidden="1" customWidth="1"/>
+    <col min="58" max="61" width="18" style="17" hidden="1" customWidth="1"/>
+    <col min="62" max="62" width="9.140625" style="17" hidden="1" customWidth="1"/>
+    <col min="63" max="63" width="11" style="17" hidden="1" customWidth="1"/>
+    <col min="64" max="64" width="12" style="17" hidden="1" customWidth="1"/>
+    <col min="65" max="65" width="12.28515625" style="17" hidden="1" customWidth="1"/>
+    <col min="66" max="66" width="10.42578125" style="17" hidden="1" customWidth="1"/>
+    <col min="67" max="67" width="9.7109375" style="17" hidden="1" customWidth="1"/>
+    <col min="68" max="68" width="16" style="17" hidden="1" customWidth="1"/>
     <col min="69" max="90" width="9.140625" style="17" customWidth="1"/>
     <col min="91" max="93" width="9.140625" style="17" hidden="1" customWidth="1"/>
     <col min="94" max="94" width="32.7109375" style="17" hidden="1" customWidth="1"/>
@@ -2447,7 +2448,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="4" spans="1:121" ht="21">
+    <row r="4" spans="1:121" ht="21" hidden="1">
       <c r="A4" s="6" t="s">
         <v>87</v>
       </c>
@@ -2483,7 +2484,7 @@
         <v>104</v>
       </c>
       <c r="CI4" s="17">
-        <f t="shared" ref="CI4:CI53" si="0">+CE4+BY4+BS4+BL4</f>
+        <f t="shared" ref="CI4:CI61" si="0">+CE4+BY4+BS4+BL4</f>
         <v>0</v>
       </c>
       <c r="CR4" s="40">
@@ -2506,7 +2507,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="5" spans="1:121" ht="21">
+    <row r="5" spans="1:121" ht="21" hidden="1">
       <c r="A5" s="6" t="s">
         <v>87</v>
       </c>
@@ -2565,7 +2566,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="6" spans="1:121" ht="21">
+    <row r="6" spans="1:121" ht="21" hidden="1">
       <c r="A6" s="6" t="s">
         <v>87</v>
       </c>
@@ -2624,7 +2625,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="7" spans="1:121" ht="21">
+    <row r="7" spans="1:121" ht="21" hidden="1">
       <c r="A7" s="6" t="s">
         <v>87</v>
       </c>
@@ -2683,7 +2684,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="8" spans="1:121" ht="21">
+    <row r="8" spans="1:121" ht="21" hidden="1">
       <c r="A8" s="6" t="s">
         <v>87</v>
       </c>
@@ -2742,7 +2743,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="9" spans="1:121" ht="21">
+    <row r="9" spans="1:121" ht="21" hidden="1">
       <c r="A9" s="6" t="s">
         <v>87</v>
       </c>
@@ -2801,7 +2802,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="10" spans="1:121" ht="21">
+    <row r="10" spans="1:121" ht="21" hidden="1">
       <c r="A10" s="6" t="s">
         <v>87</v>
       </c>
@@ -2860,7 +2861,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="11" spans="1:121" ht="21">
+    <row r="11" spans="1:121" ht="21" hidden="1">
       <c r="A11" s="6" t="s">
         <v>87</v>
       </c>
@@ -2919,7 +2920,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="12" spans="1:121" ht="21">
+    <row r="12" spans="1:121" ht="21" hidden="1">
       <c r="A12" s="6" t="s">
         <v>87</v>
       </c>
@@ -2978,7 +2979,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="13" spans="1:121" ht="21">
+    <row r="13" spans="1:121" ht="21" hidden="1">
       <c r="A13" s="6" t="s">
         <v>105</v>
       </c>
@@ -3160,9 +3161,18 @@
       <c r="BP14" s="34" t="s">
         <v>93</v>
       </c>
+      <c r="BQ14" s="17">
+        <v>11</v>
+      </c>
+      <c r="BR14" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="BS14" s="17">
+        <v>100</v>
+      </c>
       <c r="CI14" s="17">
         <f t="shared" si="0"/>
-        <v>95</v>
+        <v>195</v>
       </c>
       <c r="CM14" s="35">
         <v>46210</v>
@@ -3175,7 +3185,7 @@
         <v>60.61</v>
       </c>
       <c r="CP14" s="34" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="CQ14" s="34" t="s">
         <v>93</v>
@@ -3325,9 +3335,18 @@
       <c r="BP15" s="34" t="s">
         <v>93</v>
       </c>
+      <c r="BQ15" s="17">
+        <v>4</v>
+      </c>
+      <c r="BR15" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="BS15" s="17">
+        <v>100</v>
+      </c>
       <c r="CI15" s="17">
         <f t="shared" si="0"/>
-        <v>95</v>
+        <v>195</v>
       </c>
       <c r="CR15" s="35">
         <v>46210</v>
@@ -3474,9 +3493,18 @@
       <c r="BP16" s="34" t="s">
         <v>93</v>
       </c>
+      <c r="BQ16" s="17">
+        <v>7</v>
+      </c>
+      <c r="BR16" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="BS16" s="17">
+        <v>100</v>
+      </c>
       <c r="CI16" s="17">
         <f t="shared" si="0"/>
-        <v>95</v>
+        <v>195</v>
       </c>
       <c r="CR16" s="35">
         <v>46210</v>
@@ -3623,9 +3651,18 @@
       <c r="BP17" s="34" t="s">
         <v>93</v>
       </c>
+      <c r="BQ17" s="17">
+        <v>8</v>
+      </c>
+      <c r="BR17" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="BS17" s="17">
+        <v>100</v>
+      </c>
       <c r="CI17" s="17">
         <f t="shared" si="0"/>
-        <v>95</v>
+        <v>195</v>
       </c>
       <c r="CR17" s="35">
         <v>46210</v>
@@ -3737,7 +3774,7 @@
       </c>
       <c r="AJ18" s="34"/>
       <c r="AK18" s="34" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AL18" s="35">
         <v>46164</v>
@@ -3746,10 +3783,10 @@
         <v>93</v>
       </c>
       <c r="AN18" s="41" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AO18" s="68" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AP18" s="34">
         <v>135</v>
@@ -3782,9 +3819,18 @@
       <c r="BP18" s="34" t="s">
         <v>93</v>
       </c>
+      <c r="BQ18" s="17">
+        <v>8</v>
+      </c>
+      <c r="BR18" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="BS18" s="17">
+        <v>100</v>
+      </c>
       <c r="CI18" s="17">
         <f t="shared" si="0"/>
-        <v>95</v>
+        <v>195</v>
       </c>
       <c r="CM18" s="35">
         <v>46210</v>
@@ -3797,7 +3843,7 @@
         <v>33.96</v>
       </c>
       <c r="CP18" s="34" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="CQ18" s="34" t="s">
         <v>93</v>
@@ -3921,10 +3967,10 @@
         <v>93</v>
       </c>
       <c r="AN19" s="41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AO19" s="68" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AP19" s="34">
         <v>135</v>
@@ -3957,9 +4003,18 @@
       <c r="BP19" s="34" t="s">
         <v>93</v>
       </c>
+      <c r="BQ19" s="17">
+        <v>7</v>
+      </c>
+      <c r="BR19" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="BS19" s="17">
+        <v>100</v>
+      </c>
       <c r="CI19" s="17">
         <f t="shared" si="0"/>
-        <v>95</v>
+        <v>195</v>
       </c>
       <c r="CM19" s="35">
         <v>46210</v>
@@ -3972,7 +4027,7 @@
         <v>76.459999999999994</v>
       </c>
       <c r="CP19" s="34" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="CQ19" s="34" t="s">
         <v>93</v>
@@ -4001,7 +4056,7 @@
     </row>
     <row r="20" spans="1:108" ht="21">
       <c r="A20" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B20" s="6">
         <v>1</v>
@@ -4071,7 +4126,7 @@
         <v>46205</v>
       </c>
       <c r="Y20" s="34" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Z20" s="34">
         <v>3</v>
@@ -4106,10 +4161,10 @@
         <v>46160</v>
       </c>
       <c r="AR20" s="34" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AS20" s="34" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BJ20" s="17">
         <v>19</v>
@@ -4170,7 +4225,7 @@
     </row>
     <row r="21" spans="1:108" ht="21">
       <c r="A21" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B21" s="6">
         <v>2</v>
@@ -4240,7 +4295,7 @@
         <v>46205</v>
       </c>
       <c r="Y21" s="34" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Z21" s="34">
         <v>3</v>
@@ -4275,10 +4330,10 @@
         <v>46162</v>
       </c>
       <c r="AR21" s="34" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AS21" s="34" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BJ21" s="17">
         <v>19.600000000000001</v>
@@ -4328,7 +4383,7 @@
         <v>40.99</v>
       </c>
       <c r="CP21" s="34" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="CQ21" s="34" t="s">
         <v>96</v>
@@ -4336,7 +4391,7 @@
     </row>
     <row r="22" spans="1:108" ht="21">
       <c r="A22" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B22" s="6">
         <v>3</v>
@@ -4406,7 +4461,7 @@
         <v>46205</v>
       </c>
       <c r="Y22" s="34" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Z22" s="34">
         <v>3</v>
@@ -4429,7 +4484,7 @@
         <v>96</v>
       </c>
       <c r="AN22" s="34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AO22" s="34" t="s">
         <v>95</v>
@@ -4441,10 +4496,10 @@
         <v>46160</v>
       </c>
       <c r="AR22" s="34" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AS22" s="34" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BJ22" s="17">
         <v>19.329999999999998</v>
@@ -4494,7 +4549,7 @@
         <v>63.11</v>
       </c>
       <c r="CP22" s="34" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="CQ22" s="34" t="s">
         <v>96</v>
@@ -4503,7 +4558,7 @@
         <v>46199</v>
       </c>
       <c r="CS22" s="34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="CT22" s="34"/>
       <c r="CU22" s="34"/>
@@ -4523,7 +4578,7 @@
     </row>
     <row r="23" spans="1:108" ht="21">
       <c r="A23" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B23" s="6">
         <v>4</v>
@@ -4593,7 +4648,7 @@
         <v>46205</v>
       </c>
       <c r="Y23" s="34" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Z23" s="34">
         <v>3</v>
@@ -4617,7 +4672,7 @@
       </c>
       <c r="AL23" s="19"/>
       <c r="AN23" s="34" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AO23" s="34" t="s">
         <v>95</v>
@@ -4629,10 +4684,10 @@
         <v>46158</v>
       </c>
       <c r="AR23" s="34" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AS23" s="34" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BJ23" s="17">
         <v>19.25</v>
@@ -4693,9 +4748,9 @@
         <v>96</v>
       </c>
     </row>
-    <row r="24" spans="1:108" ht="21">
+    <row r="24" spans="1:108" ht="21" hidden="1">
       <c r="A24" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B24" s="6">
         <v>5</v>
@@ -4752,9 +4807,9 @@
         <v>96</v>
       </c>
     </row>
-    <row r="25" spans="1:108" ht="21">
+    <row r="25" spans="1:108" ht="21" hidden="1">
       <c r="A25" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B25" s="6">
         <v>6</v>
@@ -4813,7 +4868,7 @@
     </row>
     <row r="26" spans="1:108" ht="21">
       <c r="A26" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B26" s="6">
         <v>11</v>
@@ -4883,7 +4938,7 @@
         <v>46205</v>
       </c>
       <c r="Y26" s="34" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Z26" s="34">
         <v>3</v>
@@ -4906,7 +4961,7 @@
         <v>96</v>
       </c>
       <c r="AN26" s="34" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AO26" s="34" t="s">
         <v>95</v>
@@ -4918,10 +4973,10 @@
         <v>46159</v>
       </c>
       <c r="AR26" s="34" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AS26" s="34" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BJ26" s="17">
         <v>18.5</v>
@@ -4961,9 +5016,9 @@
         <v>220</v>
       </c>
     </row>
-    <row r="27" spans="1:108" ht="21">
+    <row r="27" spans="1:108" ht="21" hidden="1">
       <c r="A27" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B27" s="6">
         <v>12</v>
@@ -5022,7 +5077,7 @@
     </row>
     <row r="28" spans="1:108" ht="21">
       <c r="A28" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B28" s="6">
         <v>1</v>
@@ -5031,13 +5086,13 @@
         <v>138.88</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>89</v>
       </c>
       <c r="G28" s="17" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O28" s="34"/>
       <c r="P28" s="34">
@@ -5101,7 +5156,7 @@
         <v>96</v>
       </c>
       <c r="AN28" s="34" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AO28" s="34" t="s">
         <v>95</v>
@@ -5113,10 +5168,10 @@
         <v>46143</v>
       </c>
       <c r="AR28" s="34" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AS28" s="34" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AT28" s="34" t="s">
         <v>94</v>
@@ -5134,10 +5189,10 @@
         <v>138.88</v>
       </c>
       <c r="AY28" s="34" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AZ28" s="34" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BJ28" s="17">
         <v>18</v>
@@ -5159,7 +5214,7 @@
         <v>93</v>
       </c>
       <c r="BR28" s="17" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="BS28" s="17">
         <v>100</v>
@@ -5192,9 +5247,9 @@
         <v>96</v>
       </c>
     </row>
-    <row r="29" spans="1:108" ht="21">
+    <row r="29" spans="1:108" ht="21" hidden="1">
       <c r="A29" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B29" s="6">
         <v>2</v>
@@ -5253,7 +5308,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="30" spans="1:108" ht="21">
+    <row r="30" spans="1:108" ht="21" hidden="1">
       <c r="A30" s="6" t="s">
         <v>127</v>
       </c>
@@ -5307,13 +5362,13 @@
         <v>34.99</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>89</v>
       </c>
       <c r="G31" s="17" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P31" s="34">
         <v>120</v>
@@ -5414,7 +5469,7 @@
         <v>136</v>
       </c>
       <c r="AZ31" s="34" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BJ31" s="17">
         <v>19.329999999999998</v>
@@ -5486,13 +5541,13 @@
         <v>301.24</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>89</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P32" s="34">
         <v>113.3</v>
@@ -5667,13 +5722,13 @@
         <v>180.2</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>89</v>
       </c>
       <c r="G33" s="17" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P33" s="34">
         <v>120.7</v>
@@ -5774,7 +5829,7 @@
         <v>143</v>
       </c>
       <c r="AZ33" s="34" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BJ33" s="17">
         <v>19</v>
@@ -5835,7 +5890,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="34" spans="1:108" ht="21">
+    <row r="34" spans="1:108" ht="21" hidden="1">
       <c r="A34" s="6" t="s">
         <v>127</v>
       </c>
@@ -5875,7 +5930,7 @@
         <v>0</v>
       </c>
       <c r="CR34" s="17" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="DC34" s="43">
         <v>0.04</v>
@@ -5884,7 +5939,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="35" spans="1:108" ht="21">
+    <row r="35" spans="1:108" ht="21" hidden="1">
       <c r="A35" s="6" t="s">
         <v>127</v>
       </c>
@@ -5943,7 +5998,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="36" spans="1:108" ht="21">
+    <row r="36" spans="1:108" ht="21" hidden="1">
       <c r="A36" s="6" t="s">
         <v>127</v>
       </c>
@@ -6002,7 +6057,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="37" spans="1:108" ht="21">
+    <row r="37" spans="1:108" ht="21" hidden="1">
       <c r="A37" s="6" t="s">
         <v>127</v>
       </c>
@@ -6074,13 +6129,13 @@
         <v>101.88</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E38" s="7" t="s">
         <v>89</v>
       </c>
       <c r="G38" s="17" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P38" s="34">
         <v>97.9</v>
@@ -6228,7 +6283,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="39" spans="1:108" ht="21">
+    <row r="39" spans="1:108" ht="21" hidden="1">
       <c r="A39" s="6" t="s">
         <v>127</v>
       </c>
@@ -6268,7 +6323,7 @@
         <v>0</v>
       </c>
       <c r="CR39" s="17" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="DC39" s="43">
         <v>0.04</v>
@@ -6277,7 +6332,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="40" spans="1:108" ht="21">
+    <row r="40" spans="1:108" ht="21" hidden="1">
       <c r="A40" s="6" t="s">
         <v>127</v>
       </c>
@@ -6338,7 +6393,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="41" spans="1:108" ht="21">
+    <row r="41" spans="1:108" ht="21" hidden="1">
       <c r="A41" s="6" t="s">
         <v>127</v>
       </c>
@@ -6399,7 +6454,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="42" spans="1:108" ht="21">
+    <row r="42" spans="1:108" ht="21" hidden="1">
       <c r="A42" s="6" t="s">
         <v>127</v>
       </c>
@@ -6458,7 +6513,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="43" spans="1:108" ht="21">
+    <row r="43" spans="1:108" ht="21" hidden="1">
       <c r="A43" s="6" t="s">
         <v>127</v>
       </c>
@@ -6534,7 +6589,7 @@
         <v>147</v>
       </c>
       <c r="G44" s="17" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P44" s="34">
         <v>61.5</v>
@@ -6614,9 +6669,18 @@
       <c r="BP44" s="34" t="s">
         <v>103</v>
       </c>
+      <c r="BQ44" s="17">
+        <v>7</v>
+      </c>
+      <c r="BR44" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="BS44" s="17">
+        <v>100</v>
+      </c>
       <c r="CI44" s="17">
         <f t="shared" si="0"/>
-        <v>93</v>
+        <v>193</v>
       </c>
       <c r="CM44" s="35">
         <v>46190</v>
@@ -6656,7 +6720,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="45" spans="1:108" ht="21">
+    <row r="45" spans="1:108" ht="21" hidden="1">
       <c r="A45" s="6" t="s">
         <v>145</v>
       </c>
@@ -6714,7 +6778,7 @@
         <v>147</v>
       </c>
       <c r="G46" s="17" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P46" s="34">
         <v>93.9</v>
@@ -6794,9 +6858,18 @@
       <c r="BP46" s="34" t="s">
         <v>103</v>
       </c>
+      <c r="BQ46" s="17">
+        <v>6</v>
+      </c>
+      <c r="BR46" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="BS46" s="17">
+        <v>100</v>
+      </c>
       <c r="CI46" s="17">
         <f t="shared" si="0"/>
-        <v>93</v>
+        <v>193</v>
       </c>
       <c r="CM46" s="35">
         <v>46187</v>
@@ -6853,7 +6926,7 @@
         <v>147</v>
       </c>
       <c r="G47" s="17" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P47" s="34">
         <v>78.8</v>
@@ -6933,9 +7006,18 @@
       <c r="BP47" s="34" t="s">
         <v>103</v>
       </c>
+      <c r="BQ47" s="17">
+        <v>6</v>
+      </c>
+      <c r="BR47" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="BS47" s="17">
+        <v>100</v>
+      </c>
       <c r="CI47" s="17">
         <f t="shared" si="0"/>
-        <v>93</v>
+        <v>193</v>
       </c>
       <c r="CJ47" s="19"/>
       <c r="CM47" s="35">
@@ -6993,7 +7075,7 @@
         <v>147</v>
       </c>
       <c r="G48" s="17" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P48" s="34">
         <v>91</v>
@@ -7073,9 +7155,18 @@
       <c r="BP48" s="34" t="s">
         <v>103</v>
       </c>
+      <c r="BQ48" s="17">
+        <v>8</v>
+      </c>
+      <c r="BR48" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="BS48" s="17">
+        <v>100</v>
+      </c>
       <c r="CI48" s="17">
         <f t="shared" si="0"/>
-        <v>93</v>
+        <v>193</v>
       </c>
       <c r="CM48" s="35">
         <v>46199</v>
@@ -7132,7 +7223,7 @@
         <v>147</v>
       </c>
       <c r="G49" s="17" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P49" s="34">
         <v>84.8</v>
@@ -7212,9 +7303,18 @@
       <c r="BP49" s="34" t="s">
         <v>103</v>
       </c>
+      <c r="BQ49" s="17">
+        <v>9</v>
+      </c>
+      <c r="BR49" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="BS49" s="17">
+        <v>100</v>
+      </c>
       <c r="CI49" s="17">
         <f t="shared" si="0"/>
-        <v>93</v>
+        <v>193</v>
       </c>
       <c r="CM49" s="35">
         <v>46191</v>
@@ -7271,7 +7371,7 @@
         <v>147</v>
       </c>
       <c r="G50" s="17" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P50" s="34">
         <v>105.1</v>
@@ -7351,9 +7451,18 @@
       <c r="BP50" s="34" t="s">
         <v>103</v>
       </c>
+      <c r="BQ50" s="17">
+        <v>11</v>
+      </c>
+      <c r="BR50" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="BS50" s="17">
+        <v>100</v>
+      </c>
       <c r="CI50" s="17">
         <f t="shared" si="0"/>
-        <v>93</v>
+        <v>193</v>
       </c>
       <c r="CM50" s="35">
         <v>46187</v>
@@ -7393,7 +7502,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="51" spans="1:108" ht="21">
+    <row r="51" spans="1:108" ht="21" hidden="1">
       <c r="A51" s="6" t="s">
         <v>145</v>
       </c>
@@ -7454,7 +7563,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="52" spans="1:108" ht="21">
+    <row r="52" spans="1:108" ht="21" hidden="1">
       <c r="A52" s="6" t="s">
         <v>145</v>
       </c>
@@ -7515,7 +7624,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="53" spans="1:108" ht="21">
+    <row r="53" spans="1:108" ht="21" hidden="1">
       <c r="A53" s="6" t="s">
         <v>145</v>
       </c>
@@ -7576,20 +7685,20 @@
         <v>96</v>
       </c>
     </row>
-    <row r="54" spans="1:108" ht="15.75">
-      <c r="A54" s="17" t="s">
+    <row r="54" spans="1:108" ht="21">
+      <c r="A54" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="B54" s="17" t="s">
+      <c r="B54" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="C54" s="17">
+      <c r="C54" s="6">
         <v>116.8</v>
       </c>
-      <c r="D54" s="17" t="s">
+      <c r="D54" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="E54" s="17" t="s">
+      <c r="E54" s="7" t="s">
         <v>89</v>
       </c>
       <c r="G54" s="17" t="s">
@@ -7714,20 +7823,20 @@
         <v>170</v>
       </c>
     </row>
-    <row r="55" spans="1:108" ht="15.75">
-      <c r="A55" s="17" t="s">
+    <row r="55" spans="1:108" ht="21">
+      <c r="A55" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="B55" s="17" t="s">
+      <c r="B55" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="C55" s="17">
+      <c r="C55" s="6">
         <v>69</v>
       </c>
-      <c r="D55" s="17" t="s">
+      <c r="D55" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="E55" s="17" t="s">
+      <c r="E55" s="7" t="s">
         <v>89</v>
       </c>
       <c r="G55" s="17" t="s">
@@ -7848,24 +7957,24 @@
         <v>171</v>
       </c>
       <c r="CI55" s="17">
-        <f>+CE55+BY55+BS55+BL55</f>
+        <f t="shared" si="0"/>
         <v>170</v>
       </c>
     </row>
-    <row r="56" spans="1:108" ht="15.75">
-      <c r="A56" s="17" t="s">
+    <row r="56" spans="1:108" ht="21">
+      <c r="A56" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="B56" s="17" t="s">
+      <c r="B56" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="C56" s="17">
+      <c r="C56" s="6">
         <v>62</v>
       </c>
-      <c r="D56" s="17" t="s">
+      <c r="D56" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="E56" s="17" t="s">
+      <c r="E56" s="7" t="s">
         <v>106</v>
       </c>
       <c r="G56" s="17" t="s">
@@ -7974,25 +8083,25 @@
         <v>171</v>
       </c>
       <c r="CI56" s="17">
-        <f>+CE56+BY56+BS56+BL56</f>
+        <f t="shared" si="0"/>
         <v>170</v>
       </c>
     </row>
-    <row r="57" spans="1:108" ht="15.75">
-      <c r="A57" s="17" t="s">
+    <row r="57" spans="1:108" ht="21">
+      <c r="A57" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="B57" s="17" t="s">
+      <c r="B57" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="C57" s="17">
+      <c r="C57" s="6">
         <f>98-C56</f>
         <v>36</v>
       </c>
-      <c r="D57" s="17" t="s">
+      <c r="D57" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="E57" s="17" t="s">
+      <c r="E57" s="7" t="s">
         <v>106</v>
       </c>
       <c r="G57" s="17" t="s">
@@ -8101,24 +8210,24 @@
         <v>171</v>
       </c>
       <c r="CI57" s="17">
-        <f>+CE57+BY57+BS57+BL57</f>
+        <f t="shared" si="0"/>
         <v>170</v>
       </c>
     </row>
-    <row r="58" spans="1:108" ht="15.75">
-      <c r="A58" s="17" t="s">
+    <row r="58" spans="1:108" ht="21">
+      <c r="A58" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="B58" s="17" t="s">
+      <c r="B58" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="C58" s="17">
+      <c r="C58" s="6">
         <v>18.7</v>
       </c>
-      <c r="D58" s="17" t="s">
+      <c r="D58" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="E58" s="17" t="s">
+      <c r="E58" s="7" t="s">
         <v>106</v>
       </c>
       <c r="G58" s="17" t="s">
@@ -8227,24 +8336,24 @@
         <v>171</v>
       </c>
       <c r="CI58" s="17">
-        <f>+CE58+BY58+BS58+BL58</f>
+        <f t="shared" si="0"/>
         <v>170</v>
       </c>
     </row>
-    <row r="59" spans="1:108" ht="15.75">
-      <c r="A59" s="17" t="s">
+    <row r="59" spans="1:108" ht="21">
+      <c r="A59" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="B59" s="17" t="s">
+      <c r="B59" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="C59" s="17">
+      <c r="C59" s="6">
         <v>37.1</v>
       </c>
-      <c r="D59" s="17" t="s">
+      <c r="D59" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="E59" s="17" t="s">
+      <c r="E59" s="7" t="s">
         <v>106</v>
       </c>
       <c r="G59" s="17" t="s">
@@ -8353,24 +8462,24 @@
         <v>171</v>
       </c>
       <c r="CI59" s="17">
-        <f>+CE59+BY59+BS59+BL59</f>
+        <f t="shared" si="0"/>
         <v>170</v>
       </c>
     </row>
-    <row r="60" spans="1:108" ht="15.75">
-      <c r="A60" s="17" t="s">
+    <row r="60" spans="1:108" ht="21">
+      <c r="A60" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="B60" s="17" t="s">
+      <c r="B60" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="C60" s="17">
+      <c r="C60" s="6">
         <v>86</v>
       </c>
-      <c r="D60" s="17" t="s">
+      <c r="D60" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="E60" s="17" t="s">
+      <c r="E60" s="7" t="s">
         <v>106</v>
       </c>
       <c r="G60" s="17" t="s">
@@ -8479,7 +8588,7 @@
         <v>171</v>
       </c>
       <c r="CI60" s="17">
-        <f>+CE60+BY60+BS60+BL60</f>
+        <f t="shared" si="0"/>
         <v>170</v>
       </c>
     </row>
@@ -8616,7 +8725,15 @@
       <c r="AH104" s="18"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AI53" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:AI60" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="Ceb"/>
+        <filter val="Cz"/>
+        <filter val="Tr"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="20">
     <mergeCell ref="DH1:DJ1"/>
     <mergeCell ref="DK1:DM1"/>
@@ -8971,7 +9088,7 @@
     </row>
     <row r="20" spans="1:5" ht="21" hidden="1">
       <c r="A20" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B20" s="6">
         <v>1</v>
@@ -8988,7 +9105,7 @@
     </row>
     <row r="21" spans="1:5" ht="21" hidden="1">
       <c r="A21" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B21" s="6">
         <v>2</v>
@@ -9005,7 +9122,7 @@
     </row>
     <row r="22" spans="1:5" ht="21" hidden="1">
       <c r="A22" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B22" s="6">
         <v>3</v>
@@ -9022,7 +9139,7 @@
     </row>
     <row r="23" spans="1:5" ht="21" hidden="1">
       <c r="A23" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B23" s="6">
         <v>4</v>
@@ -9039,7 +9156,7 @@
     </row>
     <row r="24" spans="1:5" ht="21">
       <c r="A24" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B24" s="6">
         <v>5</v>
@@ -9056,7 +9173,7 @@
     </row>
     <row r="25" spans="1:5" ht="21">
       <c r="A25" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B25" s="6">
         <v>6</v>
@@ -9073,7 +9190,7 @@
     </row>
     <row r="26" spans="1:5" ht="21" hidden="1">
       <c r="A26" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B26" s="6">
         <v>11</v>
@@ -9090,7 +9207,7 @@
     </row>
     <row r="27" spans="1:5" ht="21">
       <c r="A27" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B27" s="6">
         <v>12</v>
@@ -9107,7 +9224,7 @@
     </row>
     <row r="28" spans="1:5" ht="21" hidden="1">
       <c r="A28" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B28" s="6">
         <v>1</v>
@@ -9124,7 +9241,7 @@
     </row>
     <row r="29" spans="1:5" ht="21">
       <c r="A29" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B29" s="6">
         <v>2</v>
@@ -9136,7 +9253,7 @@
         <v>100</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="21">
@@ -9272,7 +9389,7 @@
         <v>100</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="21" hidden="1">
@@ -9323,7 +9440,7 @@
         <v>100</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="21">
@@ -9340,7 +9457,7 @@
         <v>100</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="21">
@@ -9510,7 +9627,7 @@
         <v>100</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="21">
@@ -9527,7 +9644,7 @@
         <v>100</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="21">
@@ -9544,7 +9661,7 @@
         <v>100</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -9806,13 +9923,13 @@
         <v>87</v>
       </c>
       <c r="BC2" s="52" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="BD2" s="52" t="s">
         <v>105</v>
       </c>
       <c r="BE2" s="52" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="BF2" s="52" t="s">
         <v>127</v>
@@ -10514,7 +10631,7 @@
     </row>
     <row r="7" spans="1:58">
       <c r="A7" s="49" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B7" s="49">
         <v>35</v>
@@ -27473,6 +27590,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="28867580-4592-47a8-a490-5f1990c83971" xsi:nil="true"/>
@@ -27483,7 +27609,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100711D466C73CDF643807BA842554885B1" ma:contentTypeVersion="16" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="8e1c5aa86496f51e6901b2b089969625">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6f4b1271-3e48-4fa4-9395-5da21e2ace23" xmlns:ns3="28867580-4592-47a8-a490-5f1990c83971" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8574df20a81ac730ef1e2c2435c9ef30" ns2:_="" ns3:_="">
     <xsd:import namespace="6f4b1271-3e48-4fa4-9395-5da21e2ace23"/>
@@ -27724,23 +27850,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14CBE609-95E4-45D1-B334-D32AADDB8A39}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ABBBF542-46E2-4D90-B593-1F03D9E2A95E}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE668D04-A599-40BD-83B4-4E55F7C43B16}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14CBE609-95E4-45D1-B334-D32AADDB8A39}"/>
 </file>